--- a/Customer Rate Tariff Template_Week 29_2026.xlsx
+++ b/Customer Rate Tariff Template_Week 29_2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\stephanie.galera.RAMPSLOGISTICS\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F218645C-F42F-4940-838E-A7B2A42EA509}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{59108480-641A-42DC-AA8C-47A54E412526}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{493693A0-0616-4273-B364-7C8DEB21885C}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{493693A0-0616-4273-B364-7C8DEB21885C}"/>
   </bookViews>
   <sheets>
     <sheet name="TT" sheetId="28" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4478" uniqueCount="242">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4480" uniqueCount="245">
   <si>
     <t>USA / TRINIDAD SHIPPING TARIFF</t>
   </si>
@@ -772,6 +772,15 @@
   </si>
   <si>
     <t>Foshan/Gaoming</t>
+  </si>
+  <si>
+    <t>7-9 days</t>
+  </si>
+  <si>
+    <t>17/07/2026</t>
+  </si>
+  <si>
+    <t>ZIM</t>
   </si>
 </sst>
 </file>
@@ -1810,7 +1819,7 @@
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="375">
+  <cellXfs count="376">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -2333,10 +2342,295 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="70" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="36" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="46" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="47" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="61" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="60" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="60" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="59" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="45" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="66" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="63" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="31" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="32" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="33" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="34" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="35" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="36" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="60" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="36" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2360,9 +2654,6 @@
     <xf numFmtId="0" fontId="0" fillId="5" borderId="54" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="55" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
@@ -2375,296 +2666,48 @@
     <xf numFmtId="0" fontId="0" fillId="5" borderId="58" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="36" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="45" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="60" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="36" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="31" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="32" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="33" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="34" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="35" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="59" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="60" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="60" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="66" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="63" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="61" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="46" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="47" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="38" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="61" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="65" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="61" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="62" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="62" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="64" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="3" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -2679,71 +2722,25 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="61" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="62" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="61" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="62" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="64" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="65" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="38" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="70" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="26" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="27" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="29" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -2769,8 +2766,23 @@
     <xf numFmtId="0" fontId="0" fillId="5" borderId="35" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="26" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="29" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="5" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="27" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -4232,32 +4244,32 @@
       <c r="P7" s="18"/>
     </row>
     <row r="8" spans="2:20" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B8" s="244" t="s">
+      <c r="B8" s="229" t="s">
         <v>0</v>
       </c>
-      <c r="C8" s="244"/>
-      <c r="D8" s="244"/>
-      <c r="E8" s="244"/>
-      <c r="F8" s="244"/>
-      <c r="G8" s="244"/>
-      <c r="H8" s="244"/>
-      <c r="I8" s="244"/>
-      <c r="J8" s="244"/>
-      <c r="K8" s="244"/>
-      <c r="L8" s="244"/>
-      <c r="M8" s="244"/>
-      <c r="N8" s="244"/>
-      <c r="O8" s="244"/>
-      <c r="P8" s="244"/>
+      <c r="C8" s="229"/>
+      <c r="D8" s="229"/>
+      <c r="E8" s="229"/>
+      <c r="F8" s="229"/>
+      <c r="G8" s="229"/>
+      <c r="H8" s="229"/>
+      <c r="I8" s="229"/>
+      <c r="J8" s="229"/>
+      <c r="K8" s="229"/>
+      <c r="L8" s="229"/>
+      <c r="M8" s="229"/>
+      <c r="N8" s="229"/>
+      <c r="O8" s="229"/>
+      <c r="P8" s="229"/>
     </row>
     <row r="9" spans="2:20" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B9" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C9" s="243" t="s">
+      <c r="C9" s="230" t="s">
         <v>2</v>
       </c>
-      <c r="D9" s="243"/>
+      <c r="D9" s="230"/>
       <c r="E9" s="120" t="s">
         <v>3</v>
       </c>
@@ -4299,10 +4311,10 @@
       </c>
     </row>
     <row r="10" spans="2:20" x14ac:dyDescent="0.3">
-      <c r="B10" s="321" t="s">
+      <c r="B10" s="248" t="s">
         <v>16</v>
       </c>
-      <c r="C10" s="321" t="s">
+      <c r="C10" s="248" t="s">
         <v>17</v>
       </c>
       <c r="D10" s="20" t="s">
@@ -4351,8 +4363,8 @@
       </c>
     </row>
     <row r="11" spans="2:20" x14ac:dyDescent="0.3">
-      <c r="B11" s="322"/>
-      <c r="C11" s="322"/>
+      <c r="B11" s="249"/>
+      <c r="C11" s="249"/>
       <c r="D11" s="20" t="s">
         <v>24</v>
       </c>
@@ -4399,8 +4411,8 @@
       </c>
     </row>
     <row r="12" spans="2:20" x14ac:dyDescent="0.3">
-      <c r="B12" s="322"/>
-      <c r="C12" s="321" t="s">
+      <c r="B12" s="249"/>
+      <c r="C12" s="248" t="s">
         <v>17</v>
       </c>
       <c r="D12" s="111" t="s">
@@ -4450,8 +4462,8 @@
       </c>
     </row>
     <row r="13" spans="2:20" x14ac:dyDescent="0.3">
-      <c r="B13" s="322"/>
-      <c r="C13" s="322"/>
+      <c r="B13" s="249"/>
+      <c r="C13" s="249"/>
       <c r="D13" s="111" t="s">
         <v>24</v>
       </c>
@@ -4500,10 +4512,10 @@
       </c>
     </row>
     <row r="14" spans="2:20" x14ac:dyDescent="0.3">
-      <c r="B14" s="264" t="s">
+      <c r="B14" s="250" t="s">
         <v>26</v>
       </c>
-      <c r="C14" s="225" t="s">
+      <c r="C14" s="252" t="s">
         <v>17</v>
       </c>
       <c r="D14" s="20" t="s">
@@ -4553,8 +4565,8 @@
       </c>
     </row>
     <row r="15" spans="2:20" x14ac:dyDescent="0.3">
-      <c r="B15" s="323"/>
-      <c r="C15" s="225"/>
+      <c r="B15" s="251"/>
+      <c r="C15" s="252"/>
       <c r="D15" s="20" t="s">
         <v>24</v>
       </c>
@@ -4602,10 +4614,10 @@
       </c>
     </row>
     <row r="16" spans="2:20" x14ac:dyDescent="0.3">
-      <c r="B16" s="264" t="s">
+      <c r="B16" s="250" t="s">
         <v>28</v>
       </c>
-      <c r="C16" s="264" t="s">
+      <c r="C16" s="250" t="s">
         <v>17</v>
       </c>
       <c r="D16" s="20" t="s">
@@ -4655,8 +4667,8 @@
       </c>
     </row>
     <row r="17" spans="2:20" x14ac:dyDescent="0.3">
-      <c r="B17" s="323"/>
-      <c r="C17" s="323"/>
+      <c r="B17" s="251"/>
+      <c r="C17" s="251"/>
       <c r="D17" s="20" t="s">
         <v>24</v>
       </c>
@@ -4704,10 +4716,10 @@
       </c>
     </row>
     <row r="18" spans="2:20" x14ac:dyDescent="0.3">
-      <c r="B18" s="264" t="s">
+      <c r="B18" s="250" t="s">
         <v>30</v>
       </c>
-      <c r="C18" s="225" t="s">
+      <c r="C18" s="252" t="s">
         <v>31</v>
       </c>
       <c r="D18" s="20" t="s">
@@ -4758,8 +4770,8 @@
       </c>
     </row>
     <row r="19" spans="2:20" x14ac:dyDescent="0.3">
-      <c r="B19" s="324"/>
-      <c r="C19" s="225"/>
+      <c r="B19" s="260"/>
+      <c r="C19" s="252"/>
       <c r="D19" s="20" t="s">
         <v>24</v>
       </c>
@@ -4808,8 +4820,8 @@
       </c>
     </row>
     <row r="20" spans="2:20" x14ac:dyDescent="0.3">
-      <c r="B20" s="324"/>
-      <c r="C20" s="225" t="s">
+      <c r="B20" s="260"/>
+      <c r="C20" s="252" t="s">
         <v>17</v>
       </c>
       <c r="D20" s="20" t="s">
@@ -4859,8 +4871,8 @@
       </c>
     </row>
     <row r="21" spans="2:20" x14ac:dyDescent="0.3">
-      <c r="B21" s="323"/>
-      <c r="C21" s="225"/>
+      <c r="B21" s="251"/>
+      <c r="C21" s="252"/>
       <c r="D21" s="20" t="s">
         <v>24</v>
       </c>
@@ -4945,74 +4957,74 @@
       <c r="P23" s="192"/>
     </row>
     <row r="24" spans="2:20" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B24" s="241" t="s">
+      <c r="B24" s="263" t="s">
         <v>35</v>
       </c>
-      <c r="C24" s="241"/>
-      <c r="D24" s="241"/>
-      <c r="E24" s="241"/>
-      <c r="F24" s="241"/>
-      <c r="G24" s="241"/>
-      <c r="H24" s="241"/>
-      <c r="I24" s="241"/>
-      <c r="J24" s="241"/>
-      <c r="K24" s="241"/>
-      <c r="L24" s="241"/>
-      <c r="M24" s="241"/>
-      <c r="N24" s="241"/>
-      <c r="O24" s="241"/>
-      <c r="P24" s="241"/>
+      <c r="C24" s="263"/>
+      <c r="D24" s="263"/>
+      <c r="E24" s="263"/>
+      <c r="F24" s="263"/>
+      <c r="G24" s="263"/>
+      <c r="H24" s="263"/>
+      <c r="I24" s="263"/>
+      <c r="J24" s="263"/>
+      <c r="K24" s="263"/>
+      <c r="L24" s="263"/>
+      <c r="M24" s="263"/>
+      <c r="N24" s="263"/>
+      <c r="O24" s="263"/>
+      <c r="P24" s="263"/>
     </row>
     <row r="25" spans="2:20" x14ac:dyDescent="0.3">
-      <c r="B25" s="241"/>
-      <c r="C25" s="241"/>
-      <c r="D25" s="241"/>
-      <c r="E25" s="241"/>
-      <c r="F25" s="241"/>
-      <c r="G25" s="241"/>
-      <c r="H25" s="241"/>
-      <c r="I25" s="241"/>
-      <c r="J25" s="241"/>
-      <c r="K25" s="241"/>
-      <c r="L25" s="241"/>
-      <c r="M25" s="241"/>
-      <c r="N25" s="241"/>
-      <c r="O25" s="241"/>
-      <c r="P25" s="241"/>
+      <c r="B25" s="263"/>
+      <c r="C25" s="263"/>
+      <c r="D25" s="263"/>
+      <c r="E25" s="263"/>
+      <c r="F25" s="263"/>
+      <c r="G25" s="263"/>
+      <c r="H25" s="263"/>
+      <c r="I25" s="263"/>
+      <c r="J25" s="263"/>
+      <c r="K25" s="263"/>
+      <c r="L25" s="263"/>
+      <c r="M25" s="263"/>
+      <c r="N25" s="263"/>
+      <c r="O25" s="263"/>
+      <c r="P25" s="263"/>
     </row>
     <row r="26" spans="2:20" x14ac:dyDescent="0.3">
-      <c r="B26" s="241"/>
-      <c r="C26" s="241"/>
-      <c r="D26" s="241"/>
-      <c r="E26" s="241"/>
-      <c r="F26" s="241"/>
-      <c r="G26" s="241"/>
-      <c r="H26" s="241"/>
-      <c r="I26" s="241"/>
-      <c r="J26" s="241"/>
-      <c r="K26" s="241"/>
-      <c r="L26" s="241"/>
-      <c r="M26" s="241"/>
-      <c r="N26" s="241"/>
-      <c r="O26" s="241"/>
-      <c r="P26" s="241"/>
+      <c r="B26" s="263"/>
+      <c r="C26" s="263"/>
+      <c r="D26" s="263"/>
+      <c r="E26" s="263"/>
+      <c r="F26" s="263"/>
+      <c r="G26" s="263"/>
+      <c r="H26" s="263"/>
+      <c r="I26" s="263"/>
+      <c r="J26" s="263"/>
+      <c r="K26" s="263"/>
+      <c r="L26" s="263"/>
+      <c r="M26" s="263"/>
+      <c r="N26" s="263"/>
+      <c r="O26" s="263"/>
+      <c r="P26" s="263"/>
     </row>
     <row r="27" spans="2:20" x14ac:dyDescent="0.3">
-      <c r="B27" s="241"/>
-      <c r="C27" s="241"/>
-      <c r="D27" s="241"/>
-      <c r="E27" s="241"/>
-      <c r="F27" s="241"/>
-      <c r="G27" s="241"/>
-      <c r="H27" s="241"/>
-      <c r="I27" s="241"/>
-      <c r="J27" s="241"/>
-      <c r="K27" s="241"/>
-      <c r="L27" s="241"/>
-      <c r="M27" s="241"/>
-      <c r="N27" s="241"/>
-      <c r="O27" s="241"/>
-      <c r="P27" s="241"/>
+      <c r="B27" s="263"/>
+      <c r="C27" s="263"/>
+      <c r="D27" s="263"/>
+      <c r="E27" s="263"/>
+      <c r="F27" s="263"/>
+      <c r="G27" s="263"/>
+      <c r="H27" s="263"/>
+      <c r="I27" s="263"/>
+      <c r="J27" s="263"/>
+      <c r="K27" s="263"/>
+      <c r="L27" s="263"/>
+      <c r="M27" s="263"/>
+      <c r="N27" s="263"/>
+      <c r="O27" s="263"/>
+      <c r="P27" s="263"/>
     </row>
     <row r="28" spans="2:20" x14ac:dyDescent="0.3">
       <c r="B28" s="35"/>
@@ -5141,32 +5153,32 @@
       <c r="Q34" s="28"/>
     </row>
     <row r="35" spans="2:20" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B35" s="256" t="s">
+      <c r="B35" s="253" t="s">
         <v>36</v>
       </c>
-      <c r="C35" s="297"/>
-      <c r="D35" s="297"/>
-      <c r="E35" s="297"/>
-      <c r="F35" s="297"/>
-      <c r="G35" s="297"/>
-      <c r="H35" s="297"/>
-      <c r="I35" s="297"/>
-      <c r="J35" s="297"/>
-      <c r="K35" s="297"/>
-      <c r="L35" s="297"/>
-      <c r="M35" s="297"/>
-      <c r="N35" s="297"/>
-      <c r="O35" s="297"/>
-      <c r="P35" s="297"/>
+      <c r="C35" s="226"/>
+      <c r="D35" s="226"/>
+      <c r="E35" s="226"/>
+      <c r="F35" s="226"/>
+      <c r="G35" s="226"/>
+      <c r="H35" s="226"/>
+      <c r="I35" s="226"/>
+      <c r="J35" s="226"/>
+      <c r="K35" s="226"/>
+      <c r="L35" s="226"/>
+      <c r="M35" s="226"/>
+      <c r="N35" s="226"/>
+      <c r="O35" s="226"/>
+      <c r="P35" s="226"/>
     </row>
     <row r="36" spans="2:20" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B36" s="120" t="s">
         <v>1</v>
       </c>
-      <c r="C36" s="243" t="s">
+      <c r="C36" s="230" t="s">
         <v>2</v>
       </c>
-      <c r="D36" s="243"/>
+      <c r="D36" s="230"/>
       <c r="E36" s="120" t="s">
         <v>3</v>
       </c>
@@ -5197,16 +5209,16 @@
       <c r="N36" s="120" t="s">
         <v>14</v>
       </c>
-      <c r="O36" s="243" t="s">
+      <c r="O36" s="230" t="s">
         <v>38</v>
       </c>
-      <c r="P36" s="243"/>
+      <c r="P36" s="230"/>
       <c r="T36" s="193" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="37" spans="2:20" x14ac:dyDescent="0.3">
-      <c r="B37" s="265" t="s">
+      <c r="B37" s="254" t="s">
         <v>39</v>
       </c>
       <c r="C37" s="138" t="s">
@@ -5248,16 +5260,16 @@
       <c r="N37" s="94" t="s">
         <v>41</v>
       </c>
-      <c r="O37" s="266" t="s">
+      <c r="O37" s="255" t="s">
         <v>42</v>
       </c>
-      <c r="P37" s="268"/>
+      <c r="P37" s="256"/>
       <c r="T37" s="53" t="s">
         <v>43</v>
       </c>
     </row>
     <row r="38" spans="2:20" x14ac:dyDescent="0.3">
-      <c r="B38" s="265"/>
+      <c r="B38" s="254"/>
       <c r="C38" s="138" t="s">
         <v>17</v>
       </c>
@@ -5297,8 +5309,8 @@
       <c r="N38" s="94" t="s">
         <v>41</v>
       </c>
-      <c r="O38" s="309"/>
-      <c r="P38" s="310"/>
+      <c r="O38" s="257"/>
+      <c r="P38" s="258"/>
       <c r="T38" s="53" t="s">
         <v>43</v>
       </c>
@@ -5345,10 +5357,10 @@
       <c r="N39" s="94" t="s">
         <v>46</v>
       </c>
-      <c r="O39" s="240" t="s">
+      <c r="O39" s="259" t="s">
         <v>47</v>
       </c>
-      <c r="P39" s="240"/>
+      <c r="P39" s="259"/>
       <c r="T39" s="53" t="s">
         <v>48</v>
       </c>
@@ -5396,10 +5408,10 @@
       <c r="N40" s="94" t="s">
         <v>41</v>
       </c>
-      <c r="O40" s="240" t="s">
+      <c r="O40" s="259" t="s">
         <v>47</v>
       </c>
-      <c r="P40" s="240"/>
+      <c r="P40" s="259"/>
       <c r="T40" s="53" t="s">
         <v>43</v>
       </c>
@@ -5443,78 +5455,78 @@
       <c r="Q42" s="7"/>
     </row>
     <row r="43" spans="2:20" x14ac:dyDescent="0.3">
-      <c r="B43" s="254" t="s">
+      <c r="B43" s="237" t="s">
         <v>35</v>
       </c>
-      <c r="C43" s="274"/>
-      <c r="D43" s="274"/>
-      <c r="E43" s="274"/>
-      <c r="F43" s="274"/>
-      <c r="G43" s="274"/>
-      <c r="H43" s="274"/>
-      <c r="I43" s="274"/>
-      <c r="J43" s="274"/>
-      <c r="K43" s="274"/>
-      <c r="L43" s="274"/>
-      <c r="M43" s="274"/>
-      <c r="N43" s="274"/>
-      <c r="O43" s="274"/>
-      <c r="P43" s="274"/>
-      <c r="Q43" s="275"/>
+      <c r="C43" s="238"/>
+      <c r="D43" s="238"/>
+      <c r="E43" s="238"/>
+      <c r="F43" s="238"/>
+      <c r="G43" s="238"/>
+      <c r="H43" s="238"/>
+      <c r="I43" s="238"/>
+      <c r="J43" s="238"/>
+      <c r="K43" s="238"/>
+      <c r="L43" s="238"/>
+      <c r="M43" s="238"/>
+      <c r="N43" s="238"/>
+      <c r="O43" s="238"/>
+      <c r="P43" s="238"/>
+      <c r="Q43" s="239"/>
     </row>
     <row r="44" spans="2:20" x14ac:dyDescent="0.3">
-      <c r="B44" s="254"/>
-      <c r="C44" s="274"/>
-      <c r="D44" s="274"/>
-      <c r="E44" s="274"/>
-      <c r="F44" s="274"/>
-      <c r="G44" s="274"/>
-      <c r="H44" s="274"/>
-      <c r="I44" s="274"/>
-      <c r="J44" s="274"/>
-      <c r="K44" s="274"/>
-      <c r="L44" s="274"/>
-      <c r="M44" s="274"/>
-      <c r="N44" s="274"/>
-      <c r="O44" s="274"/>
-      <c r="P44" s="274"/>
-      <c r="Q44" s="275"/>
+      <c r="B44" s="237"/>
+      <c r="C44" s="238"/>
+      <c r="D44" s="238"/>
+      <c r="E44" s="238"/>
+      <c r="F44" s="238"/>
+      <c r="G44" s="238"/>
+      <c r="H44" s="238"/>
+      <c r="I44" s="238"/>
+      <c r="J44" s="238"/>
+      <c r="K44" s="238"/>
+      <c r="L44" s="238"/>
+      <c r="M44" s="238"/>
+      <c r="N44" s="238"/>
+      <c r="O44" s="238"/>
+      <c r="P44" s="238"/>
+      <c r="Q44" s="239"/>
     </row>
     <row r="45" spans="2:20" x14ac:dyDescent="0.3">
-      <c r="B45" s="254"/>
-      <c r="C45" s="274"/>
-      <c r="D45" s="274"/>
-      <c r="E45" s="274"/>
-      <c r="F45" s="274"/>
-      <c r="G45" s="274"/>
-      <c r="H45" s="274"/>
-      <c r="I45" s="274"/>
-      <c r="J45" s="274"/>
-      <c r="K45" s="274"/>
-      <c r="L45" s="274"/>
-      <c r="M45" s="274"/>
-      <c r="N45" s="274"/>
-      <c r="O45" s="274"/>
-      <c r="P45" s="274"/>
-      <c r="Q45" s="275"/>
+      <c r="B45" s="237"/>
+      <c r="C45" s="238"/>
+      <c r="D45" s="238"/>
+      <c r="E45" s="238"/>
+      <c r="F45" s="238"/>
+      <c r="G45" s="238"/>
+      <c r="H45" s="238"/>
+      <c r="I45" s="238"/>
+      <c r="J45" s="238"/>
+      <c r="K45" s="238"/>
+      <c r="L45" s="238"/>
+      <c r="M45" s="238"/>
+      <c r="N45" s="238"/>
+      <c r="O45" s="238"/>
+      <c r="P45" s="238"/>
+      <c r="Q45" s="239"/>
     </row>
     <row r="46" spans="2:20" x14ac:dyDescent="0.3">
-      <c r="B46" s="255"/>
-      <c r="C46" s="276"/>
-      <c r="D46" s="276"/>
-      <c r="E46" s="276"/>
-      <c r="F46" s="276"/>
-      <c r="G46" s="276"/>
-      <c r="H46" s="276"/>
-      <c r="I46" s="276"/>
-      <c r="J46" s="276"/>
-      <c r="K46" s="276"/>
-      <c r="L46" s="276"/>
-      <c r="M46" s="276"/>
-      <c r="N46" s="276"/>
-      <c r="O46" s="276"/>
-      <c r="P46" s="276"/>
-      <c r="Q46" s="277"/>
+      <c r="B46" s="240"/>
+      <c r="C46" s="241"/>
+      <c r="D46" s="241"/>
+      <c r="E46" s="241"/>
+      <c r="F46" s="241"/>
+      <c r="G46" s="241"/>
+      <c r="H46" s="241"/>
+      <c r="I46" s="241"/>
+      <c r="J46" s="241"/>
+      <c r="K46" s="241"/>
+      <c r="L46" s="241"/>
+      <c r="M46" s="241"/>
+      <c r="N46" s="241"/>
+      <c r="O46" s="241"/>
+      <c r="P46" s="241"/>
+      <c r="Q46" s="242"/>
     </row>
     <row r="47" spans="2:20" x14ac:dyDescent="0.3">
       <c r="B47" s="35"/>
@@ -5680,35 +5692,35 @@
       <c r="R55" s="28"/>
     </row>
     <row r="56" spans="2:20" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B56" s="242" t="s">
+      <c r="B56" s="245" t="s">
         <v>50</v>
       </c>
-      <c r="C56" s="272"/>
-      <c r="D56" s="272"/>
-      <c r="E56" s="272"/>
-      <c r="F56" s="272"/>
-      <c r="G56" s="272"/>
-      <c r="H56" s="272"/>
-      <c r="I56" s="272"/>
-      <c r="J56" s="272"/>
-      <c r="K56" s="272"/>
-      <c r="L56" s="272"/>
-      <c r="M56" s="272"/>
-      <c r="N56" s="272"/>
-      <c r="O56" s="272"/>
-      <c r="P56" s="272"/>
-      <c r="Q56" s="272"/>
-      <c r="R56" s="272"/>
-      <c r="S56" s="287"/>
+      <c r="C56" s="246"/>
+      <c r="D56" s="246"/>
+      <c r="E56" s="246"/>
+      <c r="F56" s="246"/>
+      <c r="G56" s="246"/>
+      <c r="H56" s="246"/>
+      <c r="I56" s="246"/>
+      <c r="J56" s="246"/>
+      <c r="K56" s="246"/>
+      <c r="L56" s="246"/>
+      <c r="M56" s="246"/>
+      <c r="N56" s="246"/>
+      <c r="O56" s="246"/>
+      <c r="P56" s="246"/>
+      <c r="Q56" s="246"/>
+      <c r="R56" s="246"/>
+      <c r="S56" s="264"/>
     </row>
     <row r="57" spans="2:20" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B57" s="97" t="s">
         <v>1</v>
       </c>
-      <c r="C57" s="243" t="s">
+      <c r="C57" s="230" t="s">
         <v>2</v>
       </c>
-      <c r="D57" s="243"/>
+      <c r="D57" s="230"/>
       <c r="E57" s="120" t="s">
         <v>3</v>
       </c>
@@ -5748,19 +5760,19 @@
       <c r="Q57" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="R57" s="319" t="s">
+      <c r="R57" s="265" t="s">
         <v>38</v>
       </c>
-      <c r="S57" s="320"/>
+      <c r="S57" s="266"/>
       <c r="T57" s="129" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="58" spans="2:20" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B58" s="291" t="s">
+      <c r="B58" s="261" t="s">
         <v>55</v>
       </c>
-      <c r="C58" s="292" t="s">
+      <c r="C58" s="262" t="s">
         <v>56</v>
       </c>
       <c r="D58" s="139" t="s">
@@ -5808,17 +5820,17 @@
       <c r="Q58" s="142" t="s">
         <v>60</v>
       </c>
-      <c r="R58" s="293" t="s">
+      <c r="R58" s="267" t="s">
         <v>61</v>
       </c>
-      <c r="S58" s="294"/>
+      <c r="S58" s="268"/>
       <c r="T58" s="130" t="s">
         <v>62</v>
       </c>
     </row>
     <row r="59" spans="2:20" x14ac:dyDescent="0.3">
-      <c r="B59" s="291"/>
-      <c r="C59" s="292"/>
+      <c r="B59" s="261"/>
+      <c r="C59" s="262"/>
       <c r="D59" s="139" t="s">
         <v>24</v>
       </c>
@@ -5864,17 +5876,17 @@
       <c r="Q59" s="142" t="s">
         <v>60</v>
       </c>
-      <c r="R59" s="295"/>
-      <c r="S59" s="296"/>
+      <c r="R59" s="269"/>
+      <c r="S59" s="270"/>
       <c r="T59" s="130" t="s">
         <v>62</v>
       </c>
     </row>
     <row r="60" spans="2:20" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B60" s="291" t="s">
+      <c r="B60" s="261" t="s">
         <v>241</v>
       </c>
-      <c r="C60" s="292" t="s">
+      <c r="C60" s="262" t="s">
         <v>56</v>
       </c>
       <c r="D60" s="139" t="s">
@@ -5922,15 +5934,15 @@
       <c r="Q60" s="142" t="s">
         <v>60</v>
       </c>
-      <c r="R60" s="295"/>
-      <c r="S60" s="296"/>
+      <c r="R60" s="269"/>
+      <c r="S60" s="270"/>
       <c r="T60" s="130" t="s">
         <v>62</v>
       </c>
     </row>
     <row r="61" spans="2:20" x14ac:dyDescent="0.3">
-      <c r="B61" s="291"/>
-      <c r="C61" s="292"/>
+      <c r="B61" s="261"/>
+      <c r="C61" s="262"/>
       <c r="D61" s="139" t="s">
         <v>24</v>
       </c>
@@ -5976,17 +5988,17 @@
       <c r="Q61" s="142" t="s">
         <v>60</v>
       </c>
-      <c r="R61" s="304"/>
-      <c r="S61" s="305"/>
+      <c r="R61" s="271"/>
+      <c r="S61" s="272"/>
       <c r="T61" s="130" t="s">
         <v>62</v>
       </c>
     </row>
     <row r="62" spans="2:20" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B62" s="306" t="s">
+      <c r="B62" s="278" t="s">
         <v>63</v>
       </c>
-      <c r="C62" s="238" t="s">
+      <c r="C62" s="231" t="s">
         <v>31</v>
       </c>
       <c r="D62" s="117" t="s">
@@ -6034,17 +6046,17 @@
       <c r="Q62" s="94" t="s">
         <v>64</v>
       </c>
-      <c r="R62" s="266" t="s">
+      <c r="R62" s="255" t="s">
         <v>65</v>
       </c>
-      <c r="S62" s="268"/>
+      <c r="S62" s="256"/>
       <c r="T62" s="130" t="s">
         <v>66</v>
       </c>
     </row>
     <row r="63" spans="2:20" x14ac:dyDescent="0.3">
-      <c r="B63" s="307"/>
-      <c r="C63" s="308"/>
+      <c r="B63" s="279"/>
+      <c r="C63" s="232"/>
       <c r="D63" s="117" t="s">
         <v>24</v>
       </c>
@@ -6090,17 +6102,17 @@
       <c r="Q63" s="94" t="s">
         <v>64</v>
       </c>
-      <c r="R63" s="309"/>
-      <c r="S63" s="310"/>
+      <c r="R63" s="257"/>
+      <c r="S63" s="258"/>
       <c r="T63" s="130" t="s">
         <v>66</v>
       </c>
     </row>
     <row r="64" spans="2:20" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B64" s="291" t="s">
+      <c r="B64" s="261" t="s">
         <v>67</v>
       </c>
-      <c r="C64" s="292" t="s">
+      <c r="C64" s="262" t="s">
         <v>56</v>
       </c>
       <c r="D64" s="139" t="s">
@@ -6148,17 +6160,17 @@
       <c r="Q64" s="142" t="s">
         <v>60</v>
       </c>
-      <c r="R64" s="293" t="s">
+      <c r="R64" s="267" t="s">
         <v>61</v>
       </c>
-      <c r="S64" s="294"/>
+      <c r="S64" s="268"/>
       <c r="T64" s="130" t="s">
         <v>62</v>
       </c>
     </row>
     <row r="65" spans="2:20" x14ac:dyDescent="0.3">
-      <c r="B65" s="291"/>
-      <c r="C65" s="292"/>
+      <c r="B65" s="261"/>
+      <c r="C65" s="262"/>
       <c r="D65" s="139" t="s">
         <v>24</v>
       </c>
@@ -6204,17 +6216,17 @@
       <c r="Q65" s="142" t="s">
         <v>60</v>
       </c>
-      <c r="R65" s="295"/>
-      <c r="S65" s="296"/>
+      <c r="R65" s="269"/>
+      <c r="S65" s="270"/>
       <c r="T65" s="130" t="s">
         <v>62</v>
       </c>
     </row>
     <row r="66" spans="2:20" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B66" s="306" t="s">
+      <c r="B66" s="278" t="s">
         <v>68</v>
       </c>
-      <c r="C66" s="238" t="s">
+      <c r="C66" s="231" t="s">
         <v>31</v>
       </c>
       <c r="D66" s="117" t="s">
@@ -6262,17 +6274,17 @@
       <c r="Q66" s="94" t="s">
         <v>64</v>
       </c>
-      <c r="R66" s="266" t="s">
+      <c r="R66" s="255" t="s">
         <v>65</v>
       </c>
-      <c r="S66" s="268"/>
+      <c r="S66" s="256"/>
       <c r="T66" s="130" t="s">
         <v>66</v>
       </c>
     </row>
     <row r="67" spans="2:20" x14ac:dyDescent="0.3">
-      <c r="B67" s="307"/>
-      <c r="C67" s="308"/>
+      <c r="B67" s="279"/>
+      <c r="C67" s="232"/>
       <c r="D67" s="117" t="s">
         <v>24</v>
       </c>
@@ -6318,17 +6330,17 @@
       <c r="Q67" s="94" t="s">
         <v>64</v>
       </c>
-      <c r="R67" s="309"/>
-      <c r="S67" s="310"/>
+      <c r="R67" s="257"/>
+      <c r="S67" s="258"/>
       <c r="T67" s="130" t="s">
         <v>66</v>
       </c>
     </row>
     <row r="68" spans="2:20" x14ac:dyDescent="0.3">
-      <c r="B68" s="314" t="s">
+      <c r="B68" s="283" t="s">
         <v>69</v>
       </c>
-      <c r="C68" s="292" t="s">
+      <c r="C68" s="262" t="s">
         <v>56</v>
       </c>
       <c r="D68" s="139" t="s">
@@ -6376,17 +6388,17 @@
       <c r="Q68" s="142" t="s">
         <v>60</v>
       </c>
-      <c r="R68" s="293" t="s">
+      <c r="R68" s="267" t="s">
         <v>61</v>
       </c>
-      <c r="S68" s="294"/>
+      <c r="S68" s="268"/>
       <c r="T68" s="130" t="s">
         <v>62</v>
       </c>
     </row>
     <row r="69" spans="2:20" x14ac:dyDescent="0.3">
-      <c r="B69" s="315"/>
-      <c r="C69" s="292"/>
+      <c r="B69" s="284"/>
+      <c r="C69" s="262"/>
       <c r="D69" s="139" t="s">
         <v>24</v>
       </c>
@@ -6432,17 +6444,17 @@
       <c r="Q69" s="142" t="s">
         <v>60</v>
       </c>
-      <c r="R69" s="295"/>
-      <c r="S69" s="296"/>
+      <c r="R69" s="269"/>
+      <c r="S69" s="270"/>
       <c r="T69" s="130" t="s">
         <v>62</v>
       </c>
     </row>
     <row r="70" spans="2:20" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B70" s="291" t="s">
+      <c r="B70" s="261" t="s">
         <v>70</v>
       </c>
-      <c r="C70" s="292" t="s">
+      <c r="C70" s="262" t="s">
         <v>56</v>
       </c>
       <c r="D70" s="139" t="s">
@@ -6490,15 +6502,15 @@
       <c r="Q70" s="142" t="s">
         <v>60</v>
       </c>
-      <c r="R70" s="295"/>
-      <c r="S70" s="296"/>
+      <c r="R70" s="269"/>
+      <c r="S70" s="270"/>
       <c r="T70" s="130" t="s">
         <v>62</v>
       </c>
     </row>
     <row r="71" spans="2:20" x14ac:dyDescent="0.3">
-      <c r="B71" s="291"/>
-      <c r="C71" s="292"/>
+      <c r="B71" s="261"/>
+      <c r="C71" s="262"/>
       <c r="D71" s="139" t="s">
         <v>24</v>
       </c>
@@ -6544,17 +6556,17 @@
       <c r="Q71" s="142" t="s">
         <v>60</v>
       </c>
-      <c r="R71" s="304"/>
-      <c r="S71" s="305"/>
+      <c r="R71" s="271"/>
+      <c r="S71" s="272"/>
       <c r="T71" s="130" t="s">
         <v>62</v>
       </c>
     </row>
     <row r="72" spans="2:20" x14ac:dyDescent="0.3">
-      <c r="B72" s="311" t="s">
+      <c r="B72" s="280" t="s">
         <v>71</v>
       </c>
-      <c r="C72" s="312" t="s">
+      <c r="C72" s="281" t="s">
         <v>31</v>
       </c>
       <c r="D72" s="185" t="s">
@@ -6602,17 +6614,17 @@
       <c r="Q72" s="187" t="s">
         <v>72</v>
       </c>
-      <c r="R72" s="299" t="s">
+      <c r="R72" s="274" t="s">
         <v>73</v>
       </c>
-      <c r="S72" s="300"/>
+      <c r="S72" s="275"/>
       <c r="T72" s="130" t="s">
         <v>74</v>
       </c>
     </row>
     <row r="73" spans="2:20" x14ac:dyDescent="0.3">
-      <c r="B73" s="311"/>
-      <c r="C73" s="313"/>
+      <c r="B73" s="280"/>
+      <c r="C73" s="282"/>
       <c r="D73" s="185" t="s">
         <v>24</v>
       </c>
@@ -6658,17 +6670,17 @@
       <c r="Q73" s="187" t="s">
         <v>72</v>
       </c>
-      <c r="R73" s="301"/>
-      <c r="S73" s="302"/>
+      <c r="R73" s="276"/>
+      <c r="S73" s="277"/>
       <c r="T73" s="130" t="s">
         <v>74</v>
       </c>
     </row>
     <row r="74" spans="2:20" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B74" s="291" t="s">
-        <v>75</v>
-      </c>
-      <c r="C74" s="292" t="s">
+      <c r="B74" s="261" t="s">
+        <v>75</v>
+      </c>
+      <c r="C74" s="262" t="s">
         <v>56</v>
       </c>
       <c r="D74" s="139" t="s">
@@ -6716,17 +6728,17 @@
       <c r="Q74" s="142" t="s">
         <v>60</v>
       </c>
-      <c r="R74" s="293" t="s">
+      <c r="R74" s="267" t="s">
         <v>61</v>
       </c>
-      <c r="S74" s="294"/>
+      <c r="S74" s="268"/>
       <c r="T74" s="130" t="s">
         <v>62</v>
       </c>
     </row>
     <row r="75" spans="2:20" x14ac:dyDescent="0.3">
-      <c r="B75" s="291"/>
-      <c r="C75" s="292"/>
+      <c r="B75" s="261"/>
+      <c r="C75" s="262"/>
       <c r="D75" s="139" t="s">
         <v>24</v>
       </c>
@@ -6772,17 +6784,17 @@
       <c r="Q75" s="142" t="s">
         <v>60</v>
       </c>
-      <c r="R75" s="295"/>
-      <c r="S75" s="296"/>
+      <c r="R75" s="269"/>
+      <c r="S75" s="270"/>
       <c r="T75" s="130" t="s">
         <v>62</v>
       </c>
     </row>
     <row r="76" spans="2:20" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B76" s="291" t="s">
+      <c r="B76" s="261" t="s">
         <v>76</v>
       </c>
-      <c r="C76" s="292" t="s">
+      <c r="C76" s="262" t="s">
         <v>56</v>
       </c>
       <c r="D76" s="139" t="s">
@@ -6830,15 +6842,15 @@
       <c r="Q76" s="142" t="s">
         <v>60</v>
       </c>
-      <c r="R76" s="295"/>
-      <c r="S76" s="296"/>
+      <c r="R76" s="269"/>
+      <c r="S76" s="270"/>
       <c r="T76" s="130" t="s">
         <v>62</v>
       </c>
     </row>
     <row r="77" spans="2:20" x14ac:dyDescent="0.3">
-      <c r="B77" s="291"/>
-      <c r="C77" s="292"/>
+      <c r="B77" s="261"/>
+      <c r="C77" s="262"/>
       <c r="D77" s="139" t="s">
         <v>24</v>
       </c>
@@ -6884,17 +6896,17 @@
       <c r="Q77" s="142" t="s">
         <v>60</v>
       </c>
-      <c r="R77" s="295"/>
-      <c r="S77" s="296"/>
+      <c r="R77" s="269"/>
+      <c r="S77" s="270"/>
       <c r="T77" s="130" t="s">
         <v>62</v>
       </c>
     </row>
     <row r="78" spans="2:20" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B78" s="291" t="s">
+      <c r="B78" s="261" t="s">
         <v>77</v>
       </c>
-      <c r="C78" s="292" t="s">
+      <c r="C78" s="262" t="s">
         <v>56</v>
       </c>
       <c r="D78" s="139" t="s">
@@ -6942,15 +6954,15 @@
       <c r="Q78" s="142" t="s">
         <v>60</v>
       </c>
-      <c r="R78" s="295"/>
-      <c r="S78" s="296"/>
+      <c r="R78" s="269"/>
+      <c r="S78" s="270"/>
       <c r="T78" s="130" t="s">
         <v>62</v>
       </c>
     </row>
     <row r="79" spans="2:20" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B79" s="291"/>
-      <c r="C79" s="292"/>
+      <c r="B79" s="261"/>
+      <c r="C79" s="262"/>
       <c r="D79" s="139" t="s">
         <v>24</v>
       </c>
@@ -6996,43 +7008,43 @@
       <c r="Q79" s="142" t="s">
         <v>60</v>
       </c>
-      <c r="R79" s="304"/>
-      <c r="S79" s="305"/>
+      <c r="R79" s="271"/>
+      <c r="S79" s="272"/>
       <c r="T79" s="130" t="s">
         <v>62</v>
       </c>
     </row>
     <row r="80" spans="2:20" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B80" s="242" t="s">
+      <c r="B80" s="245" t="s">
         <v>78</v>
       </c>
-      <c r="C80" s="272"/>
-      <c r="D80" s="272"/>
-      <c r="E80" s="272"/>
-      <c r="F80" s="272"/>
-      <c r="G80" s="272"/>
-      <c r="H80" s="272"/>
-      <c r="I80" s="272"/>
-      <c r="J80" s="272"/>
-      <c r="K80" s="272"/>
-      <c r="L80" s="272"/>
-      <c r="M80" s="272"/>
-      <c r="N80" s="272"/>
-      <c r="O80" s="272"/>
-      <c r="P80" s="272"/>
-      <c r="Q80" s="272"/>
-      <c r="R80" s="244"/>
-      <c r="S80" s="303"/>
+      <c r="C80" s="246"/>
+      <c r="D80" s="246"/>
+      <c r="E80" s="246"/>
+      <c r="F80" s="246"/>
+      <c r="G80" s="246"/>
+      <c r="H80" s="246"/>
+      <c r="I80" s="246"/>
+      <c r="J80" s="246"/>
+      <c r="K80" s="246"/>
+      <c r="L80" s="246"/>
+      <c r="M80" s="246"/>
+      <c r="N80" s="246"/>
+      <c r="O80" s="246"/>
+      <c r="P80" s="246"/>
+      <c r="Q80" s="246"/>
+      <c r="R80" s="229"/>
+      <c r="S80" s="288"/>
       <c r="T80" s="130"/>
     </row>
     <row r="81" spans="2:20" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B81" s="97" t="s">
         <v>1</v>
       </c>
-      <c r="C81" s="288" t="s">
+      <c r="C81" s="285" t="s">
         <v>2</v>
       </c>
-      <c r="D81" s="289"/>
+      <c r="D81" s="286"/>
       <c r="E81" s="120" t="s">
         <v>3</v>
       </c>
@@ -7072,17 +7084,17 @@
       <c r="Q81" s="120" t="s">
         <v>14</v>
       </c>
-      <c r="R81" s="288" t="s">
+      <c r="R81" s="285" t="s">
         <v>38</v>
       </c>
-      <c r="S81" s="290"/>
+      <c r="S81" s="287"/>
       <c r="T81" s="130"/>
     </row>
     <row r="82" spans="2:20" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B82" s="250" t="s">
+      <c r="B82" s="289" t="s">
         <v>79</v>
       </c>
-      <c r="C82" s="317" t="s">
+      <c r="C82" s="291" t="s">
         <v>80</v>
       </c>
       <c r="D82" s="139" t="s">
@@ -7130,17 +7142,17 @@
       <c r="Q82" s="142" t="s">
         <v>60</v>
       </c>
-      <c r="R82" s="299" t="s">
+      <c r="R82" s="274" t="s">
         <v>81</v>
       </c>
-      <c r="S82" s="300"/>
+      <c r="S82" s="275"/>
       <c r="T82" s="130" t="s">
         <v>74</v>
       </c>
     </row>
     <row r="83" spans="2:20" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B83" s="316"/>
-      <c r="C83" s="318"/>
+      <c r="B83" s="290"/>
+      <c r="C83" s="292"/>
       <c r="D83" s="139" t="s">
         <v>24</v>
       </c>
@@ -7186,43 +7198,43 @@
       <c r="Q83" s="142" t="s">
         <v>60</v>
       </c>
-      <c r="R83" s="301"/>
-      <c r="S83" s="302"/>
+      <c r="R83" s="276"/>
+      <c r="S83" s="277"/>
       <c r="T83" s="130" t="s">
         <v>74</v>
       </c>
     </row>
     <row r="84" spans="2:20" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B84" s="242" t="s">
+      <c r="B84" s="245" t="s">
         <v>82</v>
       </c>
-      <c r="C84" s="272"/>
-      <c r="D84" s="272"/>
-      <c r="E84" s="272"/>
-      <c r="F84" s="272"/>
-      <c r="G84" s="272"/>
-      <c r="H84" s="272"/>
-      <c r="I84" s="272"/>
-      <c r="J84" s="272"/>
-      <c r="K84" s="272"/>
-      <c r="L84" s="272"/>
-      <c r="M84" s="272"/>
-      <c r="N84" s="272"/>
-      <c r="O84" s="272"/>
-      <c r="P84" s="272"/>
-      <c r="Q84" s="272"/>
-      <c r="R84" s="272"/>
-      <c r="S84" s="287"/>
+      <c r="C84" s="246"/>
+      <c r="D84" s="246"/>
+      <c r="E84" s="246"/>
+      <c r="F84" s="246"/>
+      <c r="G84" s="246"/>
+      <c r="H84" s="246"/>
+      <c r="I84" s="246"/>
+      <c r="J84" s="246"/>
+      <c r="K84" s="246"/>
+      <c r="L84" s="246"/>
+      <c r="M84" s="246"/>
+      <c r="N84" s="246"/>
+      <c r="O84" s="246"/>
+      <c r="P84" s="246"/>
+      <c r="Q84" s="246"/>
+      <c r="R84" s="246"/>
+      <c r="S84" s="264"/>
       <c r="T84" s="130"/>
     </row>
     <row r="85" spans="2:20" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B85" s="97" t="s">
         <v>1</v>
       </c>
-      <c r="C85" s="288" t="s">
+      <c r="C85" s="285" t="s">
         <v>2</v>
       </c>
-      <c r="D85" s="289"/>
+      <c r="D85" s="286"/>
       <c r="E85" s="120" t="s">
         <v>3</v>
       </c>
@@ -7262,17 +7274,17 @@
       <c r="Q85" s="120" t="s">
         <v>14</v>
       </c>
-      <c r="R85" s="288" t="s">
+      <c r="R85" s="285" t="s">
         <v>38</v>
       </c>
-      <c r="S85" s="290"/>
+      <c r="S85" s="287"/>
       <c r="T85" s="130"/>
     </row>
     <row r="86" spans="2:20" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B86" s="291" t="s">
+      <c r="B86" s="261" t="s">
         <v>83</v>
       </c>
-      <c r="C86" s="292" t="s">
+      <c r="C86" s="262" t="s">
         <v>80</v>
       </c>
       <c r="D86" s="139" t="s">
@@ -7320,17 +7332,17 @@
       <c r="Q86" s="142" t="s">
         <v>60</v>
       </c>
-      <c r="R86" s="299" t="s">
+      <c r="R86" s="274" t="s">
         <v>81</v>
       </c>
-      <c r="S86" s="300"/>
+      <c r="S86" s="275"/>
       <c r="T86" s="130" t="s">
         <v>62</v>
       </c>
     </row>
     <row r="87" spans="2:20" x14ac:dyDescent="0.3">
-      <c r="B87" s="291"/>
-      <c r="C87" s="292"/>
+      <c r="B87" s="261"/>
+      <c r="C87" s="262"/>
       <c r="D87" s="139" t="s">
         <v>24</v>
       </c>
@@ -7376,43 +7388,43 @@
       <c r="Q87" s="142" t="s">
         <v>60</v>
       </c>
-      <c r="R87" s="301"/>
-      <c r="S87" s="302"/>
+      <c r="R87" s="276"/>
+      <c r="S87" s="277"/>
       <c r="T87" s="130" t="s">
         <v>62</v>
       </c>
     </row>
     <row r="88" spans="2:20" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B88" s="248" t="s">
-        <v>85</v>
-      </c>
-      <c r="C88" s="297"/>
-      <c r="D88" s="297"/>
-      <c r="E88" s="297"/>
-      <c r="F88" s="297"/>
-      <c r="G88" s="297"/>
-      <c r="H88" s="297"/>
-      <c r="I88" s="297"/>
-      <c r="J88" s="297"/>
-      <c r="K88" s="297"/>
-      <c r="L88" s="297"/>
-      <c r="M88" s="297"/>
-      <c r="N88" s="297"/>
-      <c r="O88" s="297"/>
-      <c r="P88" s="297"/>
-      <c r="Q88" s="297"/>
-      <c r="R88" s="297"/>
-      <c r="S88" s="298"/>
+      <c r="B88" s="225" t="s">
+        <v>85</v>
+      </c>
+      <c r="C88" s="226"/>
+      <c r="D88" s="226"/>
+      <c r="E88" s="226"/>
+      <c r="F88" s="226"/>
+      <c r="G88" s="226"/>
+      <c r="H88" s="226"/>
+      <c r="I88" s="226"/>
+      <c r="J88" s="226"/>
+      <c r="K88" s="226"/>
+      <c r="L88" s="226"/>
+      <c r="M88" s="226"/>
+      <c r="N88" s="226"/>
+      <c r="O88" s="226"/>
+      <c r="P88" s="226"/>
+      <c r="Q88" s="226"/>
+      <c r="R88" s="226"/>
+      <c r="S88" s="273"/>
       <c r="T88" s="130"/>
     </row>
     <row r="89" spans="2:20" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B89" s="97" t="s">
         <v>1</v>
       </c>
-      <c r="C89" s="288" t="s">
+      <c r="C89" s="285" t="s">
         <v>2</v>
       </c>
-      <c r="D89" s="289"/>
+      <c r="D89" s="286"/>
       <c r="E89" s="120" t="s">
         <v>3</v>
       </c>
@@ -7452,17 +7464,17 @@
       <c r="Q89" s="120" t="s">
         <v>14</v>
       </c>
-      <c r="R89" s="288" t="s">
+      <c r="R89" s="285" t="s">
         <v>38</v>
       </c>
-      <c r="S89" s="290"/>
+      <c r="S89" s="287"/>
       <c r="T89" s="130"/>
     </row>
     <row r="90" spans="2:20" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B90" s="291" t="s">
+      <c r="B90" s="261" t="s">
         <v>86</v>
       </c>
-      <c r="C90" s="292" t="s">
+      <c r="C90" s="262" t="s">
         <v>80</v>
       </c>
       <c r="D90" s="139" t="s">
@@ -7510,17 +7522,17 @@
       <c r="Q90" s="142" t="s">
         <v>60</v>
       </c>
-      <c r="R90" s="299" t="s">
+      <c r="R90" s="274" t="s">
         <v>81</v>
       </c>
-      <c r="S90" s="300"/>
+      <c r="S90" s="275"/>
       <c r="T90" s="130" t="s">
         <v>62</v>
       </c>
     </row>
     <row r="91" spans="2:20" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B91" s="291"/>
-      <c r="C91" s="292"/>
+      <c r="B91" s="261"/>
+      <c r="C91" s="262"/>
       <c r="D91" s="139" t="s">
         <v>24</v>
       </c>
@@ -7566,43 +7578,43 @@
       <c r="Q91" s="142" t="s">
         <v>60</v>
       </c>
-      <c r="R91" s="301"/>
-      <c r="S91" s="302"/>
+      <c r="R91" s="276"/>
+      <c r="S91" s="277"/>
       <c r="T91" s="130" t="s">
         <v>62</v>
       </c>
     </row>
     <row r="92" spans="2:20" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B92" s="248" t="s">
+      <c r="B92" s="225" t="s">
         <v>87</v>
       </c>
-      <c r="C92" s="297"/>
-      <c r="D92" s="297"/>
-      <c r="E92" s="297"/>
-      <c r="F92" s="297"/>
-      <c r="G92" s="297"/>
-      <c r="H92" s="297"/>
-      <c r="I92" s="297"/>
-      <c r="J92" s="297"/>
-      <c r="K92" s="297"/>
-      <c r="L92" s="297"/>
-      <c r="M92" s="297"/>
-      <c r="N92" s="297"/>
-      <c r="O92" s="297"/>
-      <c r="P92" s="297"/>
-      <c r="Q92" s="297"/>
-      <c r="R92" s="297"/>
-      <c r="S92" s="298"/>
+      <c r="C92" s="226"/>
+      <c r="D92" s="226"/>
+      <c r="E92" s="226"/>
+      <c r="F92" s="226"/>
+      <c r="G92" s="226"/>
+      <c r="H92" s="226"/>
+      <c r="I92" s="226"/>
+      <c r="J92" s="226"/>
+      <c r="K92" s="226"/>
+      <c r="L92" s="226"/>
+      <c r="M92" s="226"/>
+      <c r="N92" s="226"/>
+      <c r="O92" s="226"/>
+      <c r="P92" s="226"/>
+      <c r="Q92" s="226"/>
+      <c r="R92" s="226"/>
+      <c r="S92" s="273"/>
       <c r="T92" s="130"/>
     </row>
     <row r="93" spans="2:20" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B93" s="97" t="s">
         <v>1</v>
       </c>
-      <c r="C93" s="288" t="s">
+      <c r="C93" s="285" t="s">
         <v>2</v>
       </c>
-      <c r="D93" s="289"/>
+      <c r="D93" s="286"/>
       <c r="E93" s="120" t="s">
         <v>3</v>
       </c>
@@ -7642,17 +7654,17 @@
       <c r="Q93" s="120" t="s">
         <v>14</v>
       </c>
-      <c r="R93" s="288" t="s">
+      <c r="R93" s="285" t="s">
         <v>38</v>
       </c>
-      <c r="S93" s="290"/>
+      <c r="S93" s="287"/>
       <c r="T93" s="130"/>
     </row>
     <row r="94" spans="2:20" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B94" s="291" t="s">
+      <c r="B94" s="261" t="s">
         <v>88</v>
       </c>
-      <c r="C94" s="292" t="s">
+      <c r="C94" s="262" t="s">
         <v>80</v>
       </c>
       <c r="D94" s="139" t="s">
@@ -7700,17 +7712,17 @@
       <c r="Q94" s="142" t="s">
         <v>60</v>
       </c>
-      <c r="R94" s="299" t="s">
+      <c r="R94" s="274" t="s">
         <v>81</v>
       </c>
-      <c r="S94" s="300"/>
+      <c r="S94" s="275"/>
       <c r="T94" s="130" t="s">
         <v>62</v>
       </c>
     </row>
     <row r="95" spans="2:20" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B95" s="291"/>
-      <c r="C95" s="292"/>
+      <c r="B95" s="261"/>
+      <c r="C95" s="262"/>
       <c r="D95" s="139" t="s">
         <v>24</v>
       </c>
@@ -7756,42 +7768,42 @@
       <c r="Q95" s="142" t="s">
         <v>60</v>
       </c>
-      <c r="R95" s="301"/>
-      <c r="S95" s="302"/>
+      <c r="R95" s="276"/>
+      <c r="S95" s="277"/>
       <c r="T95" s="130" t="s">
         <v>62</v>
       </c>
     </row>
     <row r="96" spans="2:20" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B96" s="242" t="s">
+      <c r="B96" s="245" t="s">
         <v>91</v>
       </c>
-      <c r="C96" s="272"/>
-      <c r="D96" s="272"/>
-      <c r="E96" s="272"/>
-      <c r="F96" s="272"/>
-      <c r="G96" s="272"/>
-      <c r="H96" s="272"/>
-      <c r="I96" s="272"/>
-      <c r="J96" s="272"/>
-      <c r="K96" s="272"/>
-      <c r="L96" s="272"/>
-      <c r="M96" s="272"/>
-      <c r="N96" s="272"/>
-      <c r="O96" s="272"/>
-      <c r="P96" s="272"/>
-      <c r="Q96" s="272"/>
-      <c r="R96" s="244"/>
-      <c r="S96" s="244"/>
+      <c r="C96" s="246"/>
+      <c r="D96" s="246"/>
+      <c r="E96" s="246"/>
+      <c r="F96" s="246"/>
+      <c r="G96" s="246"/>
+      <c r="H96" s="246"/>
+      <c r="I96" s="246"/>
+      <c r="J96" s="246"/>
+      <c r="K96" s="246"/>
+      <c r="L96" s="246"/>
+      <c r="M96" s="246"/>
+      <c r="N96" s="246"/>
+      <c r="O96" s="246"/>
+      <c r="P96" s="246"/>
+      <c r="Q96" s="246"/>
+      <c r="R96" s="229"/>
+      <c r="S96" s="229"/>
     </row>
     <row r="97" spans="2:21" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B97" s="97" t="s">
         <v>1</v>
       </c>
-      <c r="C97" s="288" t="s">
+      <c r="C97" s="285" t="s">
         <v>2</v>
       </c>
-      <c r="D97" s="289"/>
+      <c r="D97" s="286"/>
       <c r="E97" s="120" t="s">
         <v>3</v>
       </c>
@@ -7831,16 +7843,16 @@
       <c r="Q97" s="120" t="s">
         <v>14</v>
       </c>
-      <c r="R97" s="288" t="s">
+      <c r="R97" s="285" t="s">
         <v>38</v>
       </c>
-      <c r="S97" s="290"/>
+      <c r="S97" s="287"/>
     </row>
     <row r="98" spans="2:21" x14ac:dyDescent="0.3">
-      <c r="B98" s="291" t="s">
+      <c r="B98" s="261" t="s">
         <v>92</v>
       </c>
-      <c r="C98" s="292" t="s">
+      <c r="C98" s="262" t="s">
         <v>80</v>
       </c>
       <c r="D98" s="139" t="s">
@@ -7888,18 +7900,18 @@
       <c r="Q98" s="142" t="s">
         <v>60</v>
       </c>
-      <c r="R98" s="293" t="s">
+      <c r="R98" s="267" t="s">
         <v>93</v>
       </c>
-      <c r="S98" s="294"/>
+      <c r="S98" s="268"/>
       <c r="T98" s="130" t="s">
         <v>62</v>
       </c>
       <c r="U98"/>
     </row>
     <row r="99" spans="2:21" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B99" s="291"/>
-      <c r="C99" s="292"/>
+      <c r="B99" s="261"/>
+      <c r="C99" s="262"/>
       <c r="D99" s="139" t="s">
         <v>24</v>
       </c>
@@ -7945,43 +7957,43 @@
       <c r="Q99" s="142" t="s">
         <v>60</v>
       </c>
-      <c r="R99" s="295"/>
-      <c r="S99" s="296"/>
+      <c r="R99" s="269"/>
+      <c r="S99" s="270"/>
       <c r="T99" s="130" t="s">
         <v>62</v>
       </c>
       <c r="U99"/>
     </row>
     <row r="100" spans="2:21" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B100" s="242" t="s">
+      <c r="B100" s="245" t="s">
         <v>94</v>
       </c>
-      <c r="C100" s="272"/>
-      <c r="D100" s="272"/>
-      <c r="E100" s="272"/>
-      <c r="F100" s="272"/>
-      <c r="G100" s="272"/>
-      <c r="H100" s="272"/>
-      <c r="I100" s="272"/>
-      <c r="J100" s="272"/>
-      <c r="K100" s="272"/>
-      <c r="L100" s="272"/>
-      <c r="M100" s="272"/>
-      <c r="N100" s="272"/>
-      <c r="O100" s="272"/>
-      <c r="P100" s="272"/>
-      <c r="Q100" s="272"/>
-      <c r="R100" s="272"/>
-      <c r="S100" s="287"/>
+      <c r="C100" s="246"/>
+      <c r="D100" s="246"/>
+      <c r="E100" s="246"/>
+      <c r="F100" s="246"/>
+      <c r="G100" s="246"/>
+      <c r="H100" s="246"/>
+      <c r="I100" s="246"/>
+      <c r="J100" s="246"/>
+      <c r="K100" s="246"/>
+      <c r="L100" s="246"/>
+      <c r="M100" s="246"/>
+      <c r="N100" s="246"/>
+      <c r="O100" s="246"/>
+      <c r="P100" s="246"/>
+      <c r="Q100" s="246"/>
+      <c r="R100" s="246"/>
+      <c r="S100" s="264"/>
     </row>
     <row r="101" spans="2:21" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B101" s="97" t="s">
         <v>1</v>
       </c>
-      <c r="C101" s="288" t="s">
+      <c r="C101" s="285" t="s">
         <v>2</v>
       </c>
-      <c r="D101" s="289"/>
+      <c r="D101" s="286"/>
       <c r="E101" s="120" t="s">
         <v>3</v>
       </c>
@@ -8021,16 +8033,16 @@
       <c r="Q101" s="120" t="s">
         <v>14</v>
       </c>
-      <c r="R101" s="288" t="s">
+      <c r="R101" s="285" t="s">
         <v>38</v>
       </c>
-      <c r="S101" s="290"/>
+      <c r="S101" s="287"/>
     </row>
     <row r="102" spans="2:21" x14ac:dyDescent="0.3">
-      <c r="B102" s="291" t="s">
+      <c r="B102" s="261" t="s">
         <v>95</v>
       </c>
-      <c r="C102" s="292" t="s">
+      <c r="C102" s="262" t="s">
         <v>31</v>
       </c>
       <c r="D102" s="139" t="s">
@@ -8078,18 +8090,18 @@
       <c r="Q102" s="142" t="s">
         <v>60</v>
       </c>
-      <c r="R102" s="293" t="s">
+      <c r="R102" s="267" t="s">
         <v>93</v>
       </c>
-      <c r="S102" s="294"/>
+      <c r="S102" s="268"/>
       <c r="T102" s="184" t="s">
         <v>96</v>
       </c>
       <c r="U102"/>
     </row>
     <row r="103" spans="2:21" x14ac:dyDescent="0.3">
-      <c r="B103" s="291"/>
-      <c r="C103" s="292"/>
+      <c r="B103" s="261"/>
+      <c r="C103" s="262"/>
       <c r="D103" s="139" t="s">
         <v>24</v>
       </c>
@@ -8135,8 +8147,8 @@
       <c r="Q103" s="142" t="s">
         <v>60</v>
       </c>
-      <c r="R103" s="295"/>
-      <c r="S103" s="296"/>
+      <c r="R103" s="269"/>
+      <c r="S103" s="270"/>
       <c r="T103" s="184" t="s">
         <v>96</v>
       </c>
@@ -8163,137 +8175,137 @@
       <c r="S104" s="136"/>
     </row>
     <row r="105" spans="2:21" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B105" s="278" t="s">
+      <c r="B105" s="293" t="s">
         <v>34</v>
       </c>
-      <c r="C105" s="279"/>
-      <c r="D105" s="279"/>
-      <c r="E105" s="279"/>
-      <c r="F105" s="279"/>
-      <c r="G105" s="279"/>
-      <c r="H105" s="279"/>
-      <c r="I105" s="279"/>
-      <c r="J105" s="279"/>
-      <c r="K105" s="279"/>
-      <c r="L105" s="279"/>
-      <c r="M105" s="279"/>
-      <c r="N105" s="279"/>
-      <c r="O105" s="279"/>
-      <c r="P105" s="279"/>
-      <c r="Q105" s="279"/>
-      <c r="R105" s="279"/>
-      <c r="S105" s="280"/>
+      <c r="C105" s="294"/>
+      <c r="D105" s="294"/>
+      <c r="E105" s="294"/>
+      <c r="F105" s="294"/>
+      <c r="G105" s="294"/>
+      <c r="H105" s="294"/>
+      <c r="I105" s="294"/>
+      <c r="J105" s="294"/>
+      <c r="K105" s="294"/>
+      <c r="L105" s="294"/>
+      <c r="M105" s="294"/>
+      <c r="N105" s="294"/>
+      <c r="O105" s="294"/>
+      <c r="P105" s="294"/>
+      <c r="Q105" s="294"/>
+      <c r="R105" s="294"/>
+      <c r="S105" s="295"/>
     </row>
     <row r="106" spans="2:21" x14ac:dyDescent="0.3">
-      <c r="B106" s="281" t="s">
+      <c r="B106" s="296" t="s">
         <v>35</v>
       </c>
-      <c r="C106" s="233"/>
-      <c r="D106" s="233"/>
-      <c r="E106" s="233"/>
-      <c r="F106" s="233"/>
-      <c r="G106" s="233"/>
-      <c r="H106" s="233"/>
-      <c r="I106" s="233"/>
-      <c r="J106" s="233"/>
-      <c r="K106" s="233"/>
-      <c r="L106" s="233"/>
-      <c r="M106" s="233"/>
-      <c r="N106" s="233"/>
-      <c r="O106" s="233"/>
-      <c r="P106" s="233"/>
-      <c r="Q106" s="233"/>
-      <c r="R106" s="233"/>
-      <c r="S106" s="282"/>
+      <c r="C106" s="297"/>
+      <c r="D106" s="297"/>
+      <c r="E106" s="297"/>
+      <c r="F106" s="297"/>
+      <c r="G106" s="297"/>
+      <c r="H106" s="297"/>
+      <c r="I106" s="297"/>
+      <c r="J106" s="297"/>
+      <c r="K106" s="297"/>
+      <c r="L106" s="297"/>
+      <c r="M106" s="297"/>
+      <c r="N106" s="297"/>
+      <c r="O106" s="297"/>
+      <c r="P106" s="297"/>
+      <c r="Q106" s="297"/>
+      <c r="R106" s="297"/>
+      <c r="S106" s="298"/>
     </row>
     <row r="107" spans="2:21" x14ac:dyDescent="0.3">
-      <c r="B107" s="281"/>
-      <c r="C107" s="233"/>
-      <c r="D107" s="233"/>
-      <c r="E107" s="233"/>
-      <c r="F107" s="233"/>
-      <c r="G107" s="233"/>
-      <c r="H107" s="233"/>
-      <c r="I107" s="233"/>
-      <c r="J107" s="233"/>
-      <c r="K107" s="233"/>
-      <c r="L107" s="233"/>
-      <c r="M107" s="233"/>
-      <c r="N107" s="233"/>
-      <c r="O107" s="233"/>
-      <c r="P107" s="233"/>
-      <c r="Q107" s="233"/>
-      <c r="R107" s="233"/>
-      <c r="S107" s="282"/>
+      <c r="B107" s="296"/>
+      <c r="C107" s="297"/>
+      <c r="D107" s="297"/>
+      <c r="E107" s="297"/>
+      <c r="F107" s="297"/>
+      <c r="G107" s="297"/>
+      <c r="H107" s="297"/>
+      <c r="I107" s="297"/>
+      <c r="J107" s="297"/>
+      <c r="K107" s="297"/>
+      <c r="L107" s="297"/>
+      <c r="M107" s="297"/>
+      <c r="N107" s="297"/>
+      <c r="O107" s="297"/>
+      <c r="P107" s="297"/>
+      <c r="Q107" s="297"/>
+      <c r="R107" s="297"/>
+      <c r="S107" s="298"/>
     </row>
     <row r="108" spans="2:21" x14ac:dyDescent="0.3">
-      <c r="B108" s="281"/>
-      <c r="C108" s="233"/>
-      <c r="D108" s="233"/>
-      <c r="E108" s="233"/>
-      <c r="F108" s="233"/>
-      <c r="G108" s="233"/>
-      <c r="H108" s="233"/>
-      <c r="I108" s="233"/>
-      <c r="J108" s="233"/>
-      <c r="K108" s="233"/>
-      <c r="L108" s="233"/>
-      <c r="M108" s="233"/>
-      <c r="N108" s="233"/>
-      <c r="O108" s="233"/>
-      <c r="P108" s="233"/>
-      <c r="Q108" s="233"/>
-      <c r="R108" s="233"/>
-      <c r="S108" s="282"/>
+      <c r="B108" s="296"/>
+      <c r="C108" s="297"/>
+      <c r="D108" s="297"/>
+      <c r="E108" s="297"/>
+      <c r="F108" s="297"/>
+      <c r="G108" s="297"/>
+      <c r="H108" s="297"/>
+      <c r="I108" s="297"/>
+      <c r="J108" s="297"/>
+      <c r="K108" s="297"/>
+      <c r="L108" s="297"/>
+      <c r="M108" s="297"/>
+      <c r="N108" s="297"/>
+      <c r="O108" s="297"/>
+      <c r="P108" s="297"/>
+      <c r="Q108" s="297"/>
+      <c r="R108" s="297"/>
+      <c r="S108" s="298"/>
     </row>
     <row r="109" spans="2:21" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B109" s="283"/>
-      <c r="C109" s="284"/>
-      <c r="D109" s="284"/>
-      <c r="E109" s="284"/>
-      <c r="F109" s="284"/>
-      <c r="G109" s="284"/>
-      <c r="H109" s="284"/>
-      <c r="I109" s="284"/>
-      <c r="J109" s="284"/>
-      <c r="K109" s="284"/>
-      <c r="L109" s="284"/>
-      <c r="M109" s="284"/>
-      <c r="N109" s="284"/>
-      <c r="O109" s="284"/>
-      <c r="P109" s="284"/>
-      <c r="Q109" s="284"/>
-      <c r="R109" s="284"/>
-      <c r="S109" s="285"/>
+      <c r="B109" s="299"/>
+      <c r="C109" s="300"/>
+      <c r="D109" s="300"/>
+      <c r="E109" s="300"/>
+      <c r="F109" s="300"/>
+      <c r="G109" s="300"/>
+      <c r="H109" s="300"/>
+      <c r="I109" s="300"/>
+      <c r="J109" s="300"/>
+      <c r="K109" s="300"/>
+      <c r="L109" s="300"/>
+      <c r="M109" s="300"/>
+      <c r="N109" s="300"/>
+      <c r="O109" s="300"/>
+      <c r="P109" s="300"/>
+      <c r="Q109" s="300"/>
+      <c r="R109" s="300"/>
+      <c r="S109" s="301"/>
     </row>
     <row r="118" spans="2:20" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B118" s="286" t="s">
+      <c r="B118" s="302" t="s">
         <v>97</v>
       </c>
-      <c r="C118" s="286"/>
-      <c r="D118" s="286"/>
-      <c r="E118" s="286"/>
-      <c r="F118" s="286"/>
-      <c r="G118" s="286"/>
-      <c r="H118" s="286"/>
-      <c r="I118" s="286"/>
-      <c r="J118" s="286"/>
-      <c r="K118" s="286"/>
-      <c r="L118" s="286"/>
-      <c r="M118" s="286"/>
-      <c r="N118" s="286"/>
-      <c r="O118" s="286"/>
-      <c r="P118" s="286"/>
+      <c r="C118" s="302"/>
+      <c r="D118" s="302"/>
+      <c r="E118" s="302"/>
+      <c r="F118" s="302"/>
+      <c r="G118" s="302"/>
+      <c r="H118" s="302"/>
+      <c r="I118" s="302"/>
+      <c r="J118" s="302"/>
+      <c r="K118" s="302"/>
+      <c r="L118" s="302"/>
+      <c r="M118" s="302"/>
+      <c r="N118" s="302"/>
+      <c r="O118" s="302"/>
+      <c r="P118" s="302"/>
       <c r="Q118" s="131"/>
     </row>
     <row r="119" spans="2:20" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B119" s="120" t="s">
         <v>1</v>
       </c>
-      <c r="C119" s="243" t="s">
+      <c r="C119" s="230" t="s">
         <v>2</v>
       </c>
-      <c r="D119" s="243"/>
+      <c r="D119" s="230"/>
       <c r="E119" s="120" t="s">
         <v>3</v>
       </c>
@@ -8324,20 +8336,20 @@
       <c r="N119" s="120" t="s">
         <v>14</v>
       </c>
-      <c r="O119" s="243" t="s">
+      <c r="O119" s="230" t="s">
         <v>38</v>
       </c>
-      <c r="P119" s="243"/>
-      <c r="Q119" s="243"/>
+      <c r="P119" s="230"/>
+      <c r="Q119" s="230"/>
       <c r="T119" s="129" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="120" spans="2:20" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B120" s="239" t="s">
+      <c r="B120" s="227" t="s">
         <v>99</v>
       </c>
-      <c r="C120" s="225" t="s">
+      <c r="C120" s="252" t="s">
         <v>17</v>
       </c>
       <c r="D120" s="20" t="s">
@@ -8375,18 +8387,18 @@
       <c r="N120" s="20" t="s">
         <v>41</v>
       </c>
-      <c r="O120" s="240" t="s">
+      <c r="O120" s="259" t="s">
         <v>47</v>
       </c>
-      <c r="P120" s="240"/>
-      <c r="Q120" s="240"/>
+      <c r="P120" s="259"/>
+      <c r="Q120" s="259"/>
       <c r="T120" s="130" t="s">
         <v>100</v>
       </c>
     </row>
     <row r="121" spans="2:20" x14ac:dyDescent="0.3">
-      <c r="B121" s="239"/>
-      <c r="C121" s="225"/>
+      <c r="B121" s="227"/>
+      <c r="C121" s="252"/>
       <c r="D121" s="20" t="s">
         <v>24</v>
       </c>
@@ -8422,9 +8434,9 @@
       <c r="N121" s="20" t="s">
         <v>41</v>
       </c>
-      <c r="O121" s="240"/>
-      <c r="P121" s="240"/>
-      <c r="Q121" s="240"/>
+      <c r="O121" s="259"/>
+      <c r="P121" s="259"/>
+      <c r="Q121" s="259"/>
       <c r="T121" s="130" t="s">
         <v>100</v>
       </c>
@@ -8468,78 +8480,78 @@
       <c r="Q123" s="7"/>
     </row>
     <row r="124" spans="2:20" x14ac:dyDescent="0.3">
-      <c r="B124" s="254" t="s">
+      <c r="B124" s="237" t="s">
         <v>35</v>
       </c>
-      <c r="C124" s="274"/>
-      <c r="D124" s="274"/>
-      <c r="E124" s="274"/>
-      <c r="F124" s="274"/>
-      <c r="G124" s="274"/>
-      <c r="H124" s="274"/>
-      <c r="I124" s="274"/>
-      <c r="J124" s="274"/>
-      <c r="K124" s="274"/>
-      <c r="L124" s="274"/>
-      <c r="M124" s="274"/>
-      <c r="N124" s="274"/>
-      <c r="O124" s="274"/>
-      <c r="P124" s="274"/>
-      <c r="Q124" s="275"/>
+      <c r="C124" s="238"/>
+      <c r="D124" s="238"/>
+      <c r="E124" s="238"/>
+      <c r="F124" s="238"/>
+      <c r="G124" s="238"/>
+      <c r="H124" s="238"/>
+      <c r="I124" s="238"/>
+      <c r="J124" s="238"/>
+      <c r="K124" s="238"/>
+      <c r="L124" s="238"/>
+      <c r="M124" s="238"/>
+      <c r="N124" s="238"/>
+      <c r="O124" s="238"/>
+      <c r="P124" s="238"/>
+      <c r="Q124" s="239"/>
     </row>
     <row r="125" spans="2:20" x14ac:dyDescent="0.3">
-      <c r="B125" s="254"/>
-      <c r="C125" s="274"/>
-      <c r="D125" s="274"/>
-      <c r="E125" s="274"/>
-      <c r="F125" s="274"/>
-      <c r="G125" s="274"/>
-      <c r="H125" s="274"/>
-      <c r="I125" s="274"/>
-      <c r="J125" s="274"/>
-      <c r="K125" s="274"/>
-      <c r="L125" s="274"/>
-      <c r="M125" s="274"/>
-      <c r="N125" s="274"/>
-      <c r="O125" s="274"/>
-      <c r="P125" s="274"/>
-      <c r="Q125" s="275"/>
+      <c r="B125" s="237"/>
+      <c r="C125" s="238"/>
+      <c r="D125" s="238"/>
+      <c r="E125" s="238"/>
+      <c r="F125" s="238"/>
+      <c r="G125" s="238"/>
+      <c r="H125" s="238"/>
+      <c r="I125" s="238"/>
+      <c r="J125" s="238"/>
+      <c r="K125" s="238"/>
+      <c r="L125" s="238"/>
+      <c r="M125" s="238"/>
+      <c r="N125" s="238"/>
+      <c r="O125" s="238"/>
+      <c r="P125" s="238"/>
+      <c r="Q125" s="239"/>
     </row>
     <row r="126" spans="2:20" x14ac:dyDescent="0.3">
-      <c r="B126" s="254"/>
-      <c r="C126" s="274"/>
-      <c r="D126" s="274"/>
-      <c r="E126" s="274"/>
-      <c r="F126" s="274"/>
-      <c r="G126" s="274"/>
-      <c r="H126" s="274"/>
-      <c r="I126" s="274"/>
-      <c r="J126" s="274"/>
-      <c r="K126" s="274"/>
-      <c r="L126" s="274"/>
-      <c r="M126" s="274"/>
-      <c r="N126" s="274"/>
-      <c r="O126" s="274"/>
-      <c r="P126" s="274"/>
-      <c r="Q126" s="275"/>
+      <c r="B126" s="237"/>
+      <c r="C126" s="238"/>
+      <c r="D126" s="238"/>
+      <c r="E126" s="238"/>
+      <c r="F126" s="238"/>
+      <c r="G126" s="238"/>
+      <c r="H126" s="238"/>
+      <c r="I126" s="238"/>
+      <c r="J126" s="238"/>
+      <c r="K126" s="238"/>
+      <c r="L126" s="238"/>
+      <c r="M126" s="238"/>
+      <c r="N126" s="238"/>
+      <c r="O126" s="238"/>
+      <c r="P126" s="238"/>
+      <c r="Q126" s="239"/>
     </row>
     <row r="127" spans="2:20" x14ac:dyDescent="0.3">
-      <c r="B127" s="255"/>
-      <c r="C127" s="276"/>
-      <c r="D127" s="276"/>
-      <c r="E127" s="276"/>
-      <c r="F127" s="276"/>
-      <c r="G127" s="276"/>
-      <c r="H127" s="276"/>
-      <c r="I127" s="276"/>
-      <c r="J127" s="276"/>
-      <c r="K127" s="276"/>
-      <c r="L127" s="276"/>
-      <c r="M127" s="276"/>
-      <c r="N127" s="276"/>
-      <c r="O127" s="276"/>
-      <c r="P127" s="276"/>
-      <c r="Q127" s="277"/>
+      <c r="B127" s="240"/>
+      <c r="C127" s="241"/>
+      <c r="D127" s="241"/>
+      <c r="E127" s="241"/>
+      <c r="F127" s="241"/>
+      <c r="G127" s="241"/>
+      <c r="H127" s="241"/>
+      <c r="I127" s="241"/>
+      <c r="J127" s="241"/>
+      <c r="K127" s="241"/>
+      <c r="L127" s="241"/>
+      <c r="M127" s="241"/>
+      <c r="N127" s="241"/>
+      <c r="O127" s="241"/>
+      <c r="P127" s="241"/>
+      <c r="Q127" s="242"/>
     </row>
     <row r="128" spans="2:20" x14ac:dyDescent="0.3">
       <c r="B128" s="35"/>
@@ -8562,32 +8574,32 @@
     <row r="129" spans="2:20" ht="13.8" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="133" spans="2:20" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="134" spans="2:20" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B134" s="242" t="s">
+      <c r="B134" s="245" t="s">
         <v>101</v>
       </c>
-      <c r="C134" s="272"/>
-      <c r="D134" s="272"/>
-      <c r="E134" s="272"/>
-      <c r="F134" s="272"/>
-      <c r="G134" s="272"/>
-      <c r="H134" s="272"/>
-      <c r="I134" s="272"/>
-      <c r="J134" s="272"/>
-      <c r="K134" s="272"/>
-      <c r="L134" s="272"/>
-      <c r="M134" s="272"/>
-      <c r="N134" s="272"/>
-      <c r="O134" s="272"/>
-      <c r="P134" s="272"/>
+      <c r="C134" s="246"/>
+      <c r="D134" s="246"/>
+      <c r="E134" s="246"/>
+      <c r="F134" s="246"/>
+      <c r="G134" s="246"/>
+      <c r="H134" s="246"/>
+      <c r="I134" s="246"/>
+      <c r="J134" s="246"/>
+      <c r="K134" s="246"/>
+      <c r="L134" s="246"/>
+      <c r="M134" s="246"/>
+      <c r="N134" s="246"/>
+      <c r="O134" s="246"/>
+      <c r="P134" s="246"/>
     </row>
     <row r="135" spans="2:20" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B135" s="97" t="s">
         <v>1</v>
       </c>
-      <c r="C135" s="243" t="s">
+      <c r="C135" s="230" t="s">
         <v>2</v>
       </c>
-      <c r="D135" s="243"/>
+      <c r="D135" s="230"/>
       <c r="E135" s="120" t="s">
         <v>3</v>
       </c>
@@ -8681,10 +8693,10 @@
       </c>
     </row>
     <row r="137" spans="2:20" x14ac:dyDescent="0.3">
-      <c r="B137" s="273" t="s">
+      <c r="B137" s="247" t="s">
         <v>106</v>
       </c>
-      <c r="C137" s="239" t="s">
+      <c r="C137" s="227" t="s">
         <v>31</v>
       </c>
       <c r="D137" s="117" t="s">
@@ -8734,8 +8746,8 @@
       </c>
     </row>
     <row r="138" spans="2:20" x14ac:dyDescent="0.3">
-      <c r="B138" s="273"/>
-      <c r="C138" s="239"/>
+      <c r="B138" s="247"/>
+      <c r="C138" s="227"/>
       <c r="D138" s="117" t="s">
         <v>24</v>
       </c>
@@ -8784,32 +8796,32 @@
     </row>
     <row r="140" spans="2:20" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="141" spans="2:20" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B141" s="242" t="s">
+      <c r="B141" s="245" t="s">
         <v>107</v>
       </c>
-      <c r="C141" s="272"/>
-      <c r="D141" s="272"/>
-      <c r="E141" s="272"/>
-      <c r="F141" s="272"/>
-      <c r="G141" s="272"/>
-      <c r="H141" s="272"/>
-      <c r="I141" s="272"/>
-      <c r="J141" s="272"/>
-      <c r="K141" s="272"/>
-      <c r="L141" s="272"/>
-      <c r="M141" s="272"/>
-      <c r="N141" s="272"/>
-      <c r="O141" s="272"/>
-      <c r="P141" s="272"/>
+      <c r="C141" s="246"/>
+      <c r="D141" s="246"/>
+      <c r="E141" s="246"/>
+      <c r="F141" s="246"/>
+      <c r="G141" s="246"/>
+      <c r="H141" s="246"/>
+      <c r="I141" s="246"/>
+      <c r="J141" s="246"/>
+      <c r="K141" s="246"/>
+      <c r="L141" s="246"/>
+      <c r="M141" s="246"/>
+      <c r="N141" s="246"/>
+      <c r="O141" s="246"/>
+      <c r="P141" s="246"/>
     </row>
     <row r="142" spans="2:20" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B142" s="97" t="s">
         <v>1</v>
       </c>
-      <c r="C142" s="243" t="s">
+      <c r="C142" s="230" t="s">
         <v>2</v>
       </c>
-      <c r="D142" s="243"/>
+      <c r="D142" s="230"/>
       <c r="E142" s="120" t="s">
         <v>3</v>
       </c>
@@ -8848,10 +8860,10 @@
       </c>
     </row>
     <row r="143" spans="2:20" x14ac:dyDescent="0.3">
-      <c r="B143" s="239" t="s">
+      <c r="B143" s="227" t="s">
         <v>108</v>
       </c>
-      <c r="C143" s="239" t="s">
+      <c r="C143" s="227" t="s">
         <v>17</v>
       </c>
       <c r="D143" s="117" t="s">
@@ -8897,8 +8909,8 @@
       </c>
     </row>
     <row r="144" spans="2:20" x14ac:dyDescent="0.3">
-      <c r="B144" s="239"/>
-      <c r="C144" s="239"/>
+      <c r="B144" s="227"/>
+      <c r="C144" s="227"/>
       <c r="D144" s="117" t="s">
         <v>24</v>
       </c>
@@ -8942,10 +8954,10 @@
       </c>
     </row>
     <row r="145" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B145" s="239" t="s">
+      <c r="B145" s="227" t="s">
         <v>110</v>
       </c>
-      <c r="C145" s="239" t="s">
+      <c r="C145" s="227" t="s">
         <v>31</v>
       </c>
       <c r="D145" s="117" t="s">
@@ -8991,8 +9003,8 @@
       </c>
     </row>
     <row r="146" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B146" s="239"/>
-      <c r="C146" s="239"/>
+      <c r="B146" s="227"/>
+      <c r="C146" s="227"/>
       <c r="D146" s="117" t="s">
         <v>24</v>
       </c>
@@ -9062,78 +9074,78 @@
       <c r="Q148" s="7"/>
     </row>
     <row r="149" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B149" s="254" t="s">
+      <c r="B149" s="237" t="s">
         <v>35</v>
       </c>
-      <c r="C149" s="274"/>
-      <c r="D149" s="274"/>
-      <c r="E149" s="274"/>
-      <c r="F149" s="274"/>
-      <c r="G149" s="274"/>
-      <c r="H149" s="274"/>
-      <c r="I149" s="274"/>
-      <c r="J149" s="274"/>
-      <c r="K149" s="274"/>
-      <c r="L149" s="274"/>
-      <c r="M149" s="274"/>
-      <c r="N149" s="274"/>
-      <c r="O149" s="274"/>
-      <c r="P149" s="274"/>
-      <c r="Q149" s="275"/>
+      <c r="C149" s="238"/>
+      <c r="D149" s="238"/>
+      <c r="E149" s="238"/>
+      <c r="F149" s="238"/>
+      <c r="G149" s="238"/>
+      <c r="H149" s="238"/>
+      <c r="I149" s="238"/>
+      <c r="J149" s="238"/>
+      <c r="K149" s="238"/>
+      <c r="L149" s="238"/>
+      <c r="M149" s="238"/>
+      <c r="N149" s="238"/>
+      <c r="O149" s="238"/>
+      <c r="P149" s="238"/>
+      <c r="Q149" s="239"/>
     </row>
     <row r="150" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B150" s="254"/>
-      <c r="C150" s="274"/>
-      <c r="D150" s="274"/>
-      <c r="E150" s="274"/>
-      <c r="F150" s="274"/>
-      <c r="G150" s="274"/>
-      <c r="H150" s="274"/>
-      <c r="I150" s="274"/>
-      <c r="J150" s="274"/>
-      <c r="K150" s="274"/>
-      <c r="L150" s="274"/>
-      <c r="M150" s="274"/>
-      <c r="N150" s="274"/>
-      <c r="O150" s="274"/>
-      <c r="P150" s="274"/>
-      <c r="Q150" s="275"/>
+      <c r="B150" s="237"/>
+      <c r="C150" s="238"/>
+      <c r="D150" s="238"/>
+      <c r="E150" s="238"/>
+      <c r="F150" s="238"/>
+      <c r="G150" s="238"/>
+      <c r="H150" s="238"/>
+      <c r="I150" s="238"/>
+      <c r="J150" s="238"/>
+      <c r="K150" s="238"/>
+      <c r="L150" s="238"/>
+      <c r="M150" s="238"/>
+      <c r="N150" s="238"/>
+      <c r="O150" s="238"/>
+      <c r="P150" s="238"/>
+      <c r="Q150" s="239"/>
     </row>
     <row r="151" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B151" s="254"/>
-      <c r="C151" s="274"/>
-      <c r="D151" s="274"/>
-      <c r="E151" s="274"/>
-      <c r="F151" s="274"/>
-      <c r="G151" s="274"/>
-      <c r="H151" s="274"/>
-      <c r="I151" s="274"/>
-      <c r="J151" s="274"/>
-      <c r="K151" s="274"/>
-      <c r="L151" s="274"/>
-      <c r="M151" s="274"/>
-      <c r="N151" s="274"/>
-      <c r="O151" s="274"/>
-      <c r="P151" s="274"/>
-      <c r="Q151" s="275"/>
+      <c r="B151" s="237"/>
+      <c r="C151" s="238"/>
+      <c r="D151" s="238"/>
+      <c r="E151" s="238"/>
+      <c r="F151" s="238"/>
+      <c r="G151" s="238"/>
+      <c r="H151" s="238"/>
+      <c r="I151" s="238"/>
+      <c r="J151" s="238"/>
+      <c r="K151" s="238"/>
+      <c r="L151" s="238"/>
+      <c r="M151" s="238"/>
+      <c r="N151" s="238"/>
+      <c r="O151" s="238"/>
+      <c r="P151" s="238"/>
+      <c r="Q151" s="239"/>
     </row>
     <row r="152" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B152" s="255"/>
-      <c r="C152" s="276"/>
-      <c r="D152" s="276"/>
-      <c r="E152" s="276"/>
-      <c r="F152" s="276"/>
-      <c r="G152" s="276"/>
-      <c r="H152" s="276"/>
-      <c r="I152" s="276"/>
-      <c r="J152" s="276"/>
-      <c r="K152" s="276"/>
-      <c r="L152" s="276"/>
-      <c r="M152" s="276"/>
-      <c r="N152" s="276"/>
-      <c r="O152" s="276"/>
-      <c r="P152" s="276"/>
-      <c r="Q152" s="277"/>
+      <c r="B152" s="240"/>
+      <c r="C152" s="241"/>
+      <c r="D152" s="241"/>
+      <c r="E152" s="241"/>
+      <c r="F152" s="241"/>
+      <c r="G152" s="241"/>
+      <c r="H152" s="241"/>
+      <c r="I152" s="241"/>
+      <c r="J152" s="241"/>
+      <c r="K152" s="241"/>
+      <c r="L152" s="241"/>
+      <c r="M152" s="241"/>
+      <c r="N152" s="241"/>
+      <c r="O152" s="241"/>
+      <c r="P152" s="241"/>
+      <c r="Q152" s="242"/>
     </row>
     <row r="154" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B154" s="35"/>
@@ -9154,32 +9166,32 @@
     </row>
     <row r="159" spans="2:17" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="160" spans="2:17" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B160" s="242" t="s">
+      <c r="B160" s="245" t="s">
         <v>111</v>
       </c>
-      <c r="C160" s="272"/>
-      <c r="D160" s="272"/>
-      <c r="E160" s="272"/>
-      <c r="F160" s="272"/>
-      <c r="G160" s="272"/>
-      <c r="H160" s="272"/>
-      <c r="I160" s="272"/>
-      <c r="J160" s="272"/>
-      <c r="K160" s="272"/>
-      <c r="L160" s="272"/>
-      <c r="M160" s="272"/>
-      <c r="N160" s="272"/>
-      <c r="O160" s="272"/>
-      <c r="P160" s="272"/>
+      <c r="C160" s="246"/>
+      <c r="D160" s="246"/>
+      <c r="E160" s="246"/>
+      <c r="F160" s="246"/>
+      <c r="G160" s="246"/>
+      <c r="H160" s="246"/>
+      <c r="I160" s="246"/>
+      <c r="J160" s="246"/>
+      <c r="K160" s="246"/>
+      <c r="L160" s="246"/>
+      <c r="M160" s="246"/>
+      <c r="N160" s="246"/>
+      <c r="O160" s="246"/>
+      <c r="P160" s="246"/>
     </row>
     <row r="161" spans="2:17" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B161" s="97" t="s">
         <v>1</v>
       </c>
-      <c r="C161" s="243" t="s">
+      <c r="C161" s="230" t="s">
         <v>2</v>
       </c>
-      <c r="D161" s="243"/>
+      <c r="D161" s="230"/>
       <c r="E161" s="120" t="s">
         <v>3</v>
       </c>
@@ -9218,10 +9230,10 @@
       </c>
     </row>
     <row r="162" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B162" s="273" t="s">
+      <c r="B162" s="247" t="s">
         <v>112</v>
       </c>
-      <c r="C162" s="239" t="s">
+      <c r="C162" s="227" t="s">
         <v>113</v>
       </c>
       <c r="D162" s="117" t="s">
@@ -9267,8 +9279,8 @@
       </c>
     </row>
     <row r="163" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B163" s="273"/>
-      <c r="C163" s="239"/>
+      <c r="B163" s="247"/>
+      <c r="C163" s="227"/>
       <c r="D163" s="117" t="s">
         <v>24</v>
       </c>
@@ -9332,78 +9344,78 @@
       <c r="Q165" s="7"/>
     </row>
     <row r="166" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B166" s="254" t="s">
+      <c r="B166" s="237" t="s">
         <v>35</v>
       </c>
-      <c r="C166" s="274"/>
-      <c r="D166" s="274"/>
-      <c r="E166" s="274"/>
-      <c r="F166" s="274"/>
-      <c r="G166" s="274"/>
-      <c r="H166" s="274"/>
-      <c r="I166" s="274"/>
-      <c r="J166" s="274"/>
-      <c r="K166" s="274"/>
-      <c r="L166" s="274"/>
-      <c r="M166" s="274"/>
-      <c r="N166" s="274"/>
-      <c r="O166" s="274"/>
-      <c r="P166" s="274"/>
-      <c r="Q166" s="275"/>
+      <c r="C166" s="238"/>
+      <c r="D166" s="238"/>
+      <c r="E166" s="238"/>
+      <c r="F166" s="238"/>
+      <c r="G166" s="238"/>
+      <c r="H166" s="238"/>
+      <c r="I166" s="238"/>
+      <c r="J166" s="238"/>
+      <c r="K166" s="238"/>
+      <c r="L166" s="238"/>
+      <c r="M166" s="238"/>
+      <c r="N166" s="238"/>
+      <c r="O166" s="238"/>
+      <c r="P166" s="238"/>
+      <c r="Q166" s="239"/>
     </row>
     <row r="167" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B167" s="254"/>
-      <c r="C167" s="274"/>
-      <c r="D167" s="274"/>
-      <c r="E167" s="274"/>
-      <c r="F167" s="274"/>
-      <c r="G167" s="274"/>
-      <c r="H167" s="274"/>
-      <c r="I167" s="274"/>
-      <c r="J167" s="274"/>
-      <c r="K167" s="274"/>
-      <c r="L167" s="274"/>
-      <c r="M167" s="274"/>
-      <c r="N167" s="274"/>
-      <c r="O167" s="274"/>
-      <c r="P167" s="274"/>
-      <c r="Q167" s="275"/>
+      <c r="B167" s="237"/>
+      <c r="C167" s="238"/>
+      <c r="D167" s="238"/>
+      <c r="E167" s="238"/>
+      <c r="F167" s="238"/>
+      <c r="G167" s="238"/>
+      <c r="H167" s="238"/>
+      <c r="I167" s="238"/>
+      <c r="J167" s="238"/>
+      <c r="K167" s="238"/>
+      <c r="L167" s="238"/>
+      <c r="M167" s="238"/>
+      <c r="N167" s="238"/>
+      <c r="O167" s="238"/>
+      <c r="P167" s="238"/>
+      <c r="Q167" s="239"/>
     </row>
     <row r="168" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B168" s="254"/>
-      <c r="C168" s="274"/>
-      <c r="D168" s="274"/>
-      <c r="E168" s="274"/>
-      <c r="F168" s="274"/>
-      <c r="G168" s="274"/>
-      <c r="H168" s="274"/>
-      <c r="I168" s="274"/>
-      <c r="J168" s="274"/>
-      <c r="K168" s="274"/>
-      <c r="L168" s="274"/>
-      <c r="M168" s="274"/>
-      <c r="N168" s="274"/>
-      <c r="O168" s="274"/>
-      <c r="P168" s="274"/>
-      <c r="Q168" s="275"/>
+      <c r="B168" s="237"/>
+      <c r="C168" s="238"/>
+      <c r="D168" s="238"/>
+      <c r="E168" s="238"/>
+      <c r="F168" s="238"/>
+      <c r="G168" s="238"/>
+      <c r="H168" s="238"/>
+      <c r="I168" s="238"/>
+      <c r="J168" s="238"/>
+      <c r="K168" s="238"/>
+      <c r="L168" s="238"/>
+      <c r="M168" s="238"/>
+      <c r="N168" s="238"/>
+      <c r="O168" s="238"/>
+      <c r="P168" s="238"/>
+      <c r="Q168" s="239"/>
     </row>
     <row r="169" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B169" s="255"/>
-      <c r="C169" s="276"/>
-      <c r="D169" s="276"/>
-      <c r="E169" s="276"/>
-      <c r="F169" s="276"/>
-      <c r="G169" s="276"/>
-      <c r="H169" s="276"/>
-      <c r="I169" s="276"/>
-      <c r="J169" s="276"/>
-      <c r="K169" s="276"/>
-      <c r="L169" s="276"/>
-      <c r="M169" s="276"/>
-      <c r="N169" s="276"/>
-      <c r="O169" s="276"/>
-      <c r="P169" s="276"/>
-      <c r="Q169" s="277"/>
+      <c r="B169" s="240"/>
+      <c r="C169" s="241"/>
+      <c r="D169" s="241"/>
+      <c r="E169" s="241"/>
+      <c r="F169" s="241"/>
+      <c r="G169" s="241"/>
+      <c r="H169" s="241"/>
+      <c r="I169" s="241"/>
+      <c r="J169" s="241"/>
+      <c r="K169" s="241"/>
+      <c r="L169" s="241"/>
+      <c r="M169" s="241"/>
+      <c r="N169" s="241"/>
+      <c r="O169" s="241"/>
+      <c r="P169" s="241"/>
+      <c r="Q169" s="242"/>
     </row>
     <row r="170" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B170" s="35"/>
@@ -9442,33 +9454,33 @@
       <c r="Q171" s="35"/>
     </row>
     <row r="173" spans="2:17" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B173" s="249" t="s">
+      <c r="B173" s="228" t="s">
         <v>114</v>
       </c>
-      <c r="C173" s="244"/>
-      <c r="D173" s="244"/>
-      <c r="E173" s="244"/>
-      <c r="F173" s="244"/>
-      <c r="G173" s="244"/>
-      <c r="H173" s="244"/>
-      <c r="I173" s="244"/>
-      <c r="J173" s="244"/>
-      <c r="K173" s="244"/>
-      <c r="L173" s="244"/>
-      <c r="M173" s="244"/>
-      <c r="N173" s="244"/>
-      <c r="O173" s="244"/>
-      <c r="P173" s="244"/>
-      <c r="Q173" s="244"/>
+      <c r="C173" s="229"/>
+      <c r="D173" s="229"/>
+      <c r="E173" s="229"/>
+      <c r="F173" s="229"/>
+      <c r="G173" s="229"/>
+      <c r="H173" s="229"/>
+      <c r="I173" s="229"/>
+      <c r="J173" s="229"/>
+      <c r="K173" s="229"/>
+      <c r="L173" s="229"/>
+      <c r="M173" s="229"/>
+      <c r="N173" s="229"/>
+      <c r="O173" s="229"/>
+      <c r="P173" s="229"/>
+      <c r="Q173" s="229"/>
     </row>
     <row r="174" spans="2:17" ht="43.2" x14ac:dyDescent="0.3">
       <c r="B174" s="97" t="s">
         <v>1</v>
       </c>
-      <c r="C174" s="243" t="s">
+      <c r="C174" s="230" t="s">
         <v>2</v>
       </c>
-      <c r="D174" s="243"/>
+      <c r="D174" s="230"/>
       <c r="E174" s="120" t="s">
         <v>3</v>
       </c>
@@ -9510,10 +9522,10 @@
       </c>
     </row>
     <row r="175" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B175" s="238" t="s">
+      <c r="B175" s="231" t="s">
         <v>120</v>
       </c>
-      <c r="C175" s="239" t="s">
+      <c r="C175" s="227" t="s">
         <v>31</v>
       </c>
       <c r="D175" s="117" t="s">
@@ -9562,8 +9574,8 @@
       </c>
     </row>
     <row r="176" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B176" s="308"/>
-      <c r="C176" s="239"/>
+      <c r="B176" s="232"/>
+      <c r="C176" s="227"/>
       <c r="D176" s="117" t="s">
         <v>24</v>
       </c>
@@ -9628,32 +9640,32 @@
     </row>
     <row r="185" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="186" spans="2:16" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B186" s="242" t="s">
+      <c r="B186" s="245" t="s">
         <v>122</v>
       </c>
-      <c r="C186" s="272"/>
-      <c r="D186" s="272"/>
-      <c r="E186" s="272"/>
-      <c r="F186" s="272"/>
-      <c r="G186" s="272"/>
-      <c r="H186" s="272"/>
-      <c r="I186" s="272"/>
-      <c r="J186" s="272"/>
-      <c r="K186" s="272"/>
-      <c r="L186" s="272"/>
-      <c r="M186" s="272"/>
-      <c r="N186" s="272"/>
-      <c r="O186" s="272"/>
-      <c r="P186" s="272"/>
+      <c r="C186" s="246"/>
+      <c r="D186" s="246"/>
+      <c r="E186" s="246"/>
+      <c r="F186" s="246"/>
+      <c r="G186" s="246"/>
+      <c r="H186" s="246"/>
+      <c r="I186" s="246"/>
+      <c r="J186" s="246"/>
+      <c r="K186" s="246"/>
+      <c r="L186" s="246"/>
+      <c r="M186" s="246"/>
+      <c r="N186" s="246"/>
+      <c r="O186" s="246"/>
+      <c r="P186" s="246"/>
     </row>
     <row r="187" spans="2:16" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B187" s="97" t="s">
         <v>1</v>
       </c>
-      <c r="C187" s="243" t="s">
+      <c r="C187" s="230" t="s">
         <v>2</v>
       </c>
-      <c r="D187" s="243"/>
+      <c r="D187" s="230"/>
       <c r="E187" s="120" t="s">
         <v>3</v>
       </c>
@@ -9692,10 +9704,10 @@
       </c>
     </row>
     <row r="188" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="B188" s="273" t="s">
+      <c r="B188" s="247" t="s">
         <v>124</v>
       </c>
-      <c r="C188" s="239" t="s">
+      <c r="C188" s="227" t="s">
         <v>89</v>
       </c>
       <c r="D188" s="117" t="s">
@@ -9741,8 +9753,8 @@
       </c>
     </row>
     <row r="189" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="B189" s="273"/>
-      <c r="C189" s="239"/>
+      <c r="B189" s="247"/>
+      <c r="C189" s="227"/>
       <c r="D189" s="117" t="s">
         <v>24</v>
       </c>
@@ -9790,6 +9802,104 @@
     </row>
   </sheetData>
   <mergeCells count="122">
+    <mergeCell ref="B160:P160"/>
+    <mergeCell ref="C161:D161"/>
+    <mergeCell ref="B162:B163"/>
+    <mergeCell ref="C162:C163"/>
+    <mergeCell ref="B166:Q169"/>
+    <mergeCell ref="C142:D142"/>
+    <mergeCell ref="B145:B146"/>
+    <mergeCell ref="C145:C146"/>
+    <mergeCell ref="B149:Q152"/>
+    <mergeCell ref="B124:Q127"/>
+    <mergeCell ref="B134:P134"/>
+    <mergeCell ref="C135:D135"/>
+    <mergeCell ref="B137:B138"/>
+    <mergeCell ref="C137:C138"/>
+    <mergeCell ref="B141:P141"/>
+    <mergeCell ref="B143:B144"/>
+    <mergeCell ref="C143:C144"/>
+    <mergeCell ref="B105:S105"/>
+    <mergeCell ref="B106:S109"/>
+    <mergeCell ref="B118:P118"/>
+    <mergeCell ref="C119:D119"/>
+    <mergeCell ref="O119:Q119"/>
+    <mergeCell ref="B120:B121"/>
+    <mergeCell ref="C120:C121"/>
+    <mergeCell ref="O120:Q121"/>
+    <mergeCell ref="C101:D101"/>
+    <mergeCell ref="R101:S101"/>
+    <mergeCell ref="B102:B103"/>
+    <mergeCell ref="C102:C103"/>
+    <mergeCell ref="R102:S103"/>
+    <mergeCell ref="B96:S96"/>
+    <mergeCell ref="C97:D97"/>
+    <mergeCell ref="R97:S97"/>
+    <mergeCell ref="B98:B99"/>
+    <mergeCell ref="C98:C99"/>
+    <mergeCell ref="R98:S99"/>
+    <mergeCell ref="B94:B95"/>
+    <mergeCell ref="C94:C95"/>
+    <mergeCell ref="R94:S95"/>
+    <mergeCell ref="C89:D89"/>
+    <mergeCell ref="R89:S89"/>
+    <mergeCell ref="B90:B91"/>
+    <mergeCell ref="C90:C91"/>
+    <mergeCell ref="R90:S91"/>
+    <mergeCell ref="B100:S100"/>
+    <mergeCell ref="R86:S87"/>
+    <mergeCell ref="B80:S80"/>
+    <mergeCell ref="C81:D81"/>
+    <mergeCell ref="R81:S81"/>
+    <mergeCell ref="B82:B83"/>
+    <mergeCell ref="C82:C83"/>
+    <mergeCell ref="R82:S83"/>
+    <mergeCell ref="B92:S92"/>
+    <mergeCell ref="C93:D93"/>
+    <mergeCell ref="R93:S93"/>
+    <mergeCell ref="B88:S88"/>
+    <mergeCell ref="B173:Q173"/>
+    <mergeCell ref="R72:S73"/>
+    <mergeCell ref="B62:B63"/>
+    <mergeCell ref="C62:C63"/>
+    <mergeCell ref="B64:B65"/>
+    <mergeCell ref="C64:C65"/>
+    <mergeCell ref="R64:S65"/>
+    <mergeCell ref="R62:S63"/>
+    <mergeCell ref="R66:S67"/>
+    <mergeCell ref="B70:B71"/>
+    <mergeCell ref="C70:C71"/>
+    <mergeCell ref="B72:B73"/>
+    <mergeCell ref="C72:C73"/>
+    <mergeCell ref="R68:S71"/>
+    <mergeCell ref="B66:B67"/>
+    <mergeCell ref="C66:C67"/>
+    <mergeCell ref="B68:B69"/>
+    <mergeCell ref="C68:C69"/>
+    <mergeCell ref="B84:S84"/>
+    <mergeCell ref="C85:D85"/>
+    <mergeCell ref="R85:S85"/>
+    <mergeCell ref="B86:B87"/>
+    <mergeCell ref="C86:C87"/>
+    <mergeCell ref="B78:B79"/>
+    <mergeCell ref="C78:C79"/>
+    <mergeCell ref="C20:C21"/>
+    <mergeCell ref="B24:P27"/>
+    <mergeCell ref="O40:P40"/>
+    <mergeCell ref="B43:Q46"/>
+    <mergeCell ref="B56:S56"/>
+    <mergeCell ref="C57:D57"/>
+    <mergeCell ref="R57:S57"/>
+    <mergeCell ref="B58:B59"/>
+    <mergeCell ref="C58:C59"/>
+    <mergeCell ref="R58:S61"/>
+    <mergeCell ref="B60:B61"/>
+    <mergeCell ref="C60:C61"/>
+    <mergeCell ref="R74:S79"/>
+    <mergeCell ref="B74:B75"/>
+    <mergeCell ref="C74:C75"/>
+    <mergeCell ref="B76:B77"/>
+    <mergeCell ref="C76:C77"/>
     <mergeCell ref="B186:P186"/>
     <mergeCell ref="C187:D187"/>
     <mergeCell ref="B188:B189"/>
@@ -9814,104 +9924,6 @@
     <mergeCell ref="C16:C17"/>
     <mergeCell ref="B18:B21"/>
     <mergeCell ref="C18:C19"/>
-    <mergeCell ref="B78:B79"/>
-    <mergeCell ref="C78:C79"/>
-    <mergeCell ref="C20:C21"/>
-    <mergeCell ref="B24:P27"/>
-    <mergeCell ref="O40:P40"/>
-    <mergeCell ref="B43:Q46"/>
-    <mergeCell ref="B56:S56"/>
-    <mergeCell ref="C57:D57"/>
-    <mergeCell ref="R57:S57"/>
-    <mergeCell ref="B58:B59"/>
-    <mergeCell ref="C58:C59"/>
-    <mergeCell ref="R58:S61"/>
-    <mergeCell ref="B60:B61"/>
-    <mergeCell ref="C60:C61"/>
-    <mergeCell ref="R74:S79"/>
-    <mergeCell ref="B74:B75"/>
-    <mergeCell ref="C74:C75"/>
-    <mergeCell ref="B76:B77"/>
-    <mergeCell ref="C76:C77"/>
-    <mergeCell ref="B88:S88"/>
-    <mergeCell ref="B173:Q173"/>
-    <mergeCell ref="R72:S73"/>
-    <mergeCell ref="B62:B63"/>
-    <mergeCell ref="C62:C63"/>
-    <mergeCell ref="B64:B65"/>
-    <mergeCell ref="C64:C65"/>
-    <mergeCell ref="R64:S65"/>
-    <mergeCell ref="R62:S63"/>
-    <mergeCell ref="R66:S67"/>
-    <mergeCell ref="B70:B71"/>
-    <mergeCell ref="C70:C71"/>
-    <mergeCell ref="B72:B73"/>
-    <mergeCell ref="C72:C73"/>
-    <mergeCell ref="R68:S71"/>
-    <mergeCell ref="B66:B67"/>
-    <mergeCell ref="C66:C67"/>
-    <mergeCell ref="B68:B69"/>
-    <mergeCell ref="C68:C69"/>
-    <mergeCell ref="B84:S84"/>
-    <mergeCell ref="C85:D85"/>
-    <mergeCell ref="R85:S85"/>
-    <mergeCell ref="B86:B87"/>
-    <mergeCell ref="C86:C87"/>
-    <mergeCell ref="R86:S87"/>
-    <mergeCell ref="B80:S80"/>
-    <mergeCell ref="C81:D81"/>
-    <mergeCell ref="R81:S81"/>
-    <mergeCell ref="B82:B83"/>
-    <mergeCell ref="C82:C83"/>
-    <mergeCell ref="R82:S83"/>
-    <mergeCell ref="B92:S92"/>
-    <mergeCell ref="C93:D93"/>
-    <mergeCell ref="R93:S93"/>
-    <mergeCell ref="B94:B95"/>
-    <mergeCell ref="C94:C95"/>
-    <mergeCell ref="R94:S95"/>
-    <mergeCell ref="C89:D89"/>
-    <mergeCell ref="R89:S89"/>
-    <mergeCell ref="B90:B91"/>
-    <mergeCell ref="C90:C91"/>
-    <mergeCell ref="R90:S91"/>
-    <mergeCell ref="B100:S100"/>
-    <mergeCell ref="C101:D101"/>
-    <mergeCell ref="R101:S101"/>
-    <mergeCell ref="B102:B103"/>
-    <mergeCell ref="C102:C103"/>
-    <mergeCell ref="R102:S103"/>
-    <mergeCell ref="B96:S96"/>
-    <mergeCell ref="C97:D97"/>
-    <mergeCell ref="R97:S97"/>
-    <mergeCell ref="B98:B99"/>
-    <mergeCell ref="C98:C99"/>
-    <mergeCell ref="R98:S99"/>
-    <mergeCell ref="B124:Q127"/>
-    <mergeCell ref="B134:P134"/>
-    <mergeCell ref="C135:D135"/>
-    <mergeCell ref="B137:B138"/>
-    <mergeCell ref="C137:C138"/>
-    <mergeCell ref="B141:P141"/>
-    <mergeCell ref="B143:B144"/>
-    <mergeCell ref="C143:C144"/>
-    <mergeCell ref="B105:S105"/>
-    <mergeCell ref="B106:S109"/>
-    <mergeCell ref="B118:P118"/>
-    <mergeCell ref="C119:D119"/>
-    <mergeCell ref="O119:Q119"/>
-    <mergeCell ref="B120:B121"/>
-    <mergeCell ref="C120:C121"/>
-    <mergeCell ref="O120:Q121"/>
-    <mergeCell ref="B160:P160"/>
-    <mergeCell ref="C161:D161"/>
-    <mergeCell ref="B162:B163"/>
-    <mergeCell ref="C162:C163"/>
-    <mergeCell ref="B166:Q169"/>
-    <mergeCell ref="C142:D142"/>
-    <mergeCell ref="B145:B146"/>
-    <mergeCell ref="C145:C146"/>
-    <mergeCell ref="B149:Q152"/>
   </mergeCells>
   <phoneticPr fontId="14" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -9950,33 +9962,33 @@
   <sheetData>
     <row r="6" spans="2:17" ht="12" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="9" spans="2:17" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B9" s="244" t="s">
+      <c r="B9" s="229" t="s">
         <v>126</v>
       </c>
-      <c r="C9" s="244"/>
-      <c r="D9" s="244"/>
-      <c r="E9" s="244"/>
-      <c r="F9" s="244"/>
-      <c r="G9" s="244"/>
-      <c r="H9" s="244"/>
-      <c r="I9" s="244"/>
-      <c r="J9" s="244"/>
-      <c r="K9" s="244"/>
-      <c r="L9" s="244"/>
-      <c r="M9" s="244"/>
-      <c r="N9" s="244"/>
-      <c r="O9" s="244"/>
-      <c r="P9" s="244"/>
-      <c r="Q9" s="244"/>
+      <c r="C9" s="229"/>
+      <c r="D9" s="229"/>
+      <c r="E9" s="229"/>
+      <c r="F9" s="229"/>
+      <c r="G9" s="229"/>
+      <c r="H9" s="229"/>
+      <c r="I9" s="229"/>
+      <c r="J9" s="229"/>
+      <c r="K9" s="229"/>
+      <c r="L9" s="229"/>
+      <c r="M9" s="229"/>
+      <c r="N9" s="229"/>
+      <c r="O9" s="229"/>
+      <c r="P9" s="229"/>
+      <c r="Q9" s="229"/>
     </row>
     <row r="10" spans="2:17" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B10" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C10" s="245" t="s">
+      <c r="C10" s="318" t="s">
         <v>2</v>
       </c>
-      <c r="D10" s="245"/>
+      <c r="D10" s="318"/>
       <c r="E10" s="8" t="s">
         <v>3</v>
       </c>
@@ -10018,10 +10030,10 @@
       </c>
     </row>
     <row r="11" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B11" s="225" t="s">
+      <c r="B11" s="252" t="s">
         <v>16</v>
       </c>
-      <c r="C11" s="225" t="s">
+      <c r="C11" s="252" t="s">
         <v>120</v>
       </c>
       <c r="D11" s="53" t="s">
@@ -10071,8 +10083,8 @@
       </c>
     </row>
     <row r="12" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B12" s="225"/>
-      <c r="C12" s="225"/>
+      <c r="B12" s="252"/>
+      <c r="C12" s="252"/>
       <c r="D12" s="53" t="s">
         <v>24</v>
       </c>
@@ -10120,10 +10132,10 @@
       </c>
     </row>
     <row r="13" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B13" s="225" t="s">
+      <c r="B13" s="252" t="s">
         <v>26</v>
       </c>
-      <c r="C13" s="225" t="s">
+      <c r="C13" s="252" t="s">
         <v>120</v>
       </c>
       <c r="D13" s="53" t="s">
@@ -10173,8 +10185,8 @@
       </c>
     </row>
     <row r="14" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B14" s="225"/>
-      <c r="C14" s="225"/>
+      <c r="B14" s="252"/>
+      <c r="C14" s="252"/>
       <c r="D14" s="53" t="s">
         <v>24</v>
       </c>
@@ -10222,10 +10234,10 @@
       </c>
     </row>
     <row r="15" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B15" s="264" t="s">
+      <c r="B15" s="250" t="s">
         <v>28</v>
       </c>
-      <c r="C15" s="225" t="s">
+      <c r="C15" s="252" t="s">
         <v>120</v>
       </c>
       <c r="D15" s="53" t="s">
@@ -10275,8 +10287,8 @@
       </c>
     </row>
     <row r="16" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B16" s="264"/>
-      <c r="C16" s="225"/>
+      <c r="B16" s="250"/>
+      <c r="C16" s="252"/>
       <c r="D16" s="53" t="s">
         <v>24</v>
       </c>
@@ -10324,10 +10336,10 @@
       </c>
     </row>
     <row r="17" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="B17" s="225" t="s">
+      <c r="B17" s="252" t="s">
         <v>132</v>
       </c>
-      <c r="C17" s="225" t="s">
+      <c r="C17" s="252" t="s">
         <v>120</v>
       </c>
       <c r="D17" s="53" t="s">
@@ -10377,8 +10389,8 @@
       </c>
     </row>
     <row r="18" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="B18" s="225"/>
-      <c r="C18" s="225"/>
+      <c r="B18" s="252"/>
+      <c r="C18" s="252"/>
       <c r="D18" s="53" t="s">
         <v>24</v>
       </c>
@@ -10443,103 +10455,103 @@
       <c r="Q19" s="34"/>
     </row>
     <row r="20" spans="2:18" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B20" s="226" t="s">
+      <c r="B20" s="321" t="s">
         <v>34</v>
       </c>
-      <c r="C20" s="227"/>
-      <c r="D20" s="227"/>
-      <c r="E20" s="227"/>
-      <c r="F20" s="227"/>
-      <c r="G20" s="227"/>
-      <c r="H20" s="227"/>
-      <c r="I20" s="227"/>
-      <c r="J20" s="227"/>
-      <c r="K20" s="227"/>
-      <c r="L20" s="227"/>
-      <c r="M20" s="227"/>
-      <c r="N20" s="227"/>
-      <c r="O20" s="227"/>
-      <c r="P20" s="227"/>
-      <c r="Q20" s="227"/>
-      <c r="R20" s="228"/>
+      <c r="C20" s="322"/>
+      <c r="D20" s="322"/>
+      <c r="E20" s="322"/>
+      <c r="F20" s="322"/>
+      <c r="G20" s="322"/>
+      <c r="H20" s="322"/>
+      <c r="I20" s="322"/>
+      <c r="J20" s="322"/>
+      <c r="K20" s="322"/>
+      <c r="L20" s="322"/>
+      <c r="M20" s="322"/>
+      <c r="N20" s="322"/>
+      <c r="O20" s="322"/>
+      <c r="P20" s="322"/>
+      <c r="Q20" s="322"/>
+      <c r="R20" s="323"/>
     </row>
     <row r="21" spans="2:18" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B21" s="229" t="s">
+      <c r="B21" s="324" t="s">
         <v>35</v>
       </c>
-      <c r="C21" s="230"/>
-      <c r="D21" s="230"/>
-      <c r="E21" s="230"/>
-      <c r="F21" s="230"/>
-      <c r="G21" s="230"/>
-      <c r="H21" s="230"/>
-      <c r="I21" s="230"/>
-      <c r="J21" s="230"/>
-      <c r="K21" s="230"/>
-      <c r="L21" s="230"/>
-      <c r="M21" s="230"/>
-      <c r="N21" s="230"/>
-      <c r="O21" s="230"/>
-      <c r="P21" s="230"/>
-      <c r="Q21" s="230"/>
-      <c r="R21" s="231"/>
+      <c r="C21" s="325"/>
+      <c r="D21" s="325"/>
+      <c r="E21" s="325"/>
+      <c r="F21" s="325"/>
+      <c r="G21" s="325"/>
+      <c r="H21" s="325"/>
+      <c r="I21" s="325"/>
+      <c r="J21" s="325"/>
+      <c r="K21" s="325"/>
+      <c r="L21" s="325"/>
+      <c r="M21" s="325"/>
+      <c r="N21" s="325"/>
+      <c r="O21" s="325"/>
+      <c r="P21" s="325"/>
+      <c r="Q21" s="325"/>
+      <c r="R21" s="326"/>
     </row>
     <row r="22" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="B22" s="232"/>
-      <c r="C22" s="233"/>
-      <c r="D22" s="233"/>
-      <c r="E22" s="233"/>
-      <c r="F22" s="233"/>
-      <c r="G22" s="233"/>
-      <c r="H22" s="233"/>
-      <c r="I22" s="233"/>
-      <c r="J22" s="233"/>
-      <c r="K22" s="233"/>
-      <c r="L22" s="233"/>
-      <c r="M22" s="233"/>
-      <c r="N22" s="233"/>
-      <c r="O22" s="233"/>
-      <c r="P22" s="233"/>
-      <c r="Q22" s="233"/>
-      <c r="R22" s="234"/>
+      <c r="B22" s="327"/>
+      <c r="C22" s="297"/>
+      <c r="D22" s="297"/>
+      <c r="E22" s="297"/>
+      <c r="F22" s="297"/>
+      <c r="G22" s="297"/>
+      <c r="H22" s="297"/>
+      <c r="I22" s="297"/>
+      <c r="J22" s="297"/>
+      <c r="K22" s="297"/>
+      <c r="L22" s="297"/>
+      <c r="M22" s="297"/>
+      <c r="N22" s="297"/>
+      <c r="O22" s="297"/>
+      <c r="P22" s="297"/>
+      <c r="Q22" s="297"/>
+      <c r="R22" s="328"/>
     </row>
     <row r="23" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="B23" s="232"/>
-      <c r="C23" s="233"/>
-      <c r="D23" s="233"/>
-      <c r="E23" s="233"/>
-      <c r="F23" s="233"/>
-      <c r="G23" s="233"/>
-      <c r="H23" s="233"/>
-      <c r="I23" s="233"/>
-      <c r="J23" s="233"/>
-      <c r="K23" s="233"/>
-      <c r="L23" s="233"/>
-      <c r="M23" s="233"/>
-      <c r="N23" s="233"/>
-      <c r="O23" s="233"/>
-      <c r="P23" s="233"/>
-      <c r="Q23" s="233"/>
-      <c r="R23" s="234"/>
+      <c r="B23" s="327"/>
+      <c r="C23" s="297"/>
+      <c r="D23" s="297"/>
+      <c r="E23" s="297"/>
+      <c r="F23" s="297"/>
+      <c r="G23" s="297"/>
+      <c r="H23" s="297"/>
+      <c r="I23" s="297"/>
+      <c r="J23" s="297"/>
+      <c r="K23" s="297"/>
+      <c r="L23" s="297"/>
+      <c r="M23" s="297"/>
+      <c r="N23" s="297"/>
+      <c r="O23" s="297"/>
+      <c r="P23" s="297"/>
+      <c r="Q23" s="297"/>
+      <c r="R23" s="328"/>
     </row>
     <row r="24" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="B24" s="235"/>
-      <c r="C24" s="236"/>
-      <c r="D24" s="236"/>
-      <c r="E24" s="236"/>
-      <c r="F24" s="236"/>
-      <c r="G24" s="236"/>
-      <c r="H24" s="236"/>
-      <c r="I24" s="236"/>
-      <c r="J24" s="236"/>
-      <c r="K24" s="236"/>
-      <c r="L24" s="236"/>
-      <c r="M24" s="236"/>
-      <c r="N24" s="236"/>
-      <c r="O24" s="236"/>
-      <c r="P24" s="236"/>
-      <c r="Q24" s="236"/>
-      <c r="R24" s="237"/>
+      <c r="B24" s="329"/>
+      <c r="C24" s="330"/>
+      <c r="D24" s="330"/>
+      <c r="E24" s="330"/>
+      <c r="F24" s="330"/>
+      <c r="G24" s="330"/>
+      <c r="H24" s="330"/>
+      <c r="I24" s="330"/>
+      <c r="J24" s="330"/>
+      <c r="K24" s="330"/>
+      <c r="L24" s="330"/>
+      <c r="M24" s="330"/>
+      <c r="N24" s="330"/>
+      <c r="O24" s="330"/>
+      <c r="P24" s="330"/>
+      <c r="Q24" s="330"/>
+      <c r="R24" s="331"/>
     </row>
     <row r="25" spans="2:18" x14ac:dyDescent="0.3">
       <c r="B25" s="27"/>
@@ -10695,34 +10707,34 @@
       <c r="Q33" s="34"/>
     </row>
     <row r="34" spans="2:21" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B34" s="256" t="s">
+      <c r="B34" s="253" t="s">
         <v>134</v>
       </c>
-      <c r="C34" s="256"/>
-      <c r="D34" s="256"/>
-      <c r="E34" s="256"/>
-      <c r="F34" s="256"/>
-      <c r="G34" s="256"/>
-      <c r="H34" s="256"/>
-      <c r="I34" s="256"/>
-      <c r="J34" s="256"/>
-      <c r="K34" s="256"/>
-      <c r="L34" s="256"/>
-      <c r="M34" s="256"/>
-      <c r="N34" s="256"/>
-      <c r="O34" s="256"/>
-      <c r="P34" s="256"/>
-      <c r="Q34" s="256"/>
-      <c r="R34" s="256"/>
+      <c r="C34" s="253"/>
+      <c r="D34" s="253"/>
+      <c r="E34" s="253"/>
+      <c r="F34" s="253"/>
+      <c r="G34" s="253"/>
+      <c r="H34" s="253"/>
+      <c r="I34" s="253"/>
+      <c r="J34" s="253"/>
+      <c r="K34" s="253"/>
+      <c r="L34" s="253"/>
+      <c r="M34" s="253"/>
+      <c r="N34" s="253"/>
+      <c r="O34" s="253"/>
+      <c r="P34" s="253"/>
+      <c r="Q34" s="253"/>
+      <c r="R34" s="253"/>
     </row>
     <row r="35" spans="2:21" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B35" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C35" s="245" t="s">
+      <c r="C35" s="318" t="s">
         <v>2</v>
       </c>
-      <c r="D35" s="245"/>
+      <c r="D35" s="318"/>
       <c r="E35" s="127" t="s">
         <v>135</v>
       </c>
@@ -10756,20 +10768,20 @@
       <c r="O35" s="124" t="s">
         <v>127</v>
       </c>
-      <c r="P35" s="243" t="s">
+      <c r="P35" s="230" t="s">
         <v>38</v>
       </c>
-      <c r="Q35" s="243"/>
-      <c r="R35" s="243"/>
+      <c r="Q35" s="230"/>
+      <c r="R35" s="230"/>
       <c r="U35" s="120" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="36" spans="2:21" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B36" s="265" t="s">
+      <c r="B36" s="254" t="s">
         <v>137</v>
       </c>
-      <c r="C36" s="225" t="s">
+      <c r="C36" s="252" t="s">
         <v>120</v>
       </c>
       <c r="D36" s="53" t="s">
@@ -10811,18 +10823,18 @@
       <c r="O36" s="53" t="s">
         <v>129</v>
       </c>
-      <c r="P36" s="266" t="s">
+      <c r="P36" s="255" t="s">
         <v>139</v>
       </c>
-      <c r="Q36" s="267"/>
-      <c r="R36" s="268"/>
+      <c r="Q36" s="313"/>
+      <c r="R36" s="256"/>
       <c r="U36" s="53" t="s">
         <v>140</v>
       </c>
     </row>
     <row r="37" spans="2:21" x14ac:dyDescent="0.3">
-      <c r="B37" s="265"/>
-      <c r="C37" s="225"/>
+      <c r="B37" s="254"/>
+      <c r="C37" s="252"/>
       <c r="D37" s="53" t="s">
         <v>24</v>
       </c>
@@ -10862,9 +10874,9 @@
       <c r="O37" s="53" t="s">
         <v>129</v>
       </c>
-      <c r="P37" s="269"/>
-      <c r="Q37" s="270"/>
-      <c r="R37" s="271"/>
+      <c r="P37" s="314"/>
+      <c r="Q37" s="315"/>
+      <c r="R37" s="316"/>
       <c r="U37" s="53" t="s">
         <v>140</v>
       </c>
@@ -10914,11 +10926,11 @@
       <c r="O38" s="53" t="s">
         <v>143</v>
       </c>
-      <c r="P38" s="257" t="s">
+      <c r="P38" s="310" t="s">
         <v>144</v>
       </c>
-      <c r="Q38" s="258"/>
-      <c r="R38" s="259"/>
+      <c r="Q38" s="311"/>
+      <c r="R38" s="312"/>
       <c r="U38" s="53" t="s">
         <v>145</v>
       </c>
@@ -10969,11 +10981,11 @@
       <c r="O39" s="53" t="s">
         <v>129</v>
       </c>
-      <c r="P39" s="257" t="s">
+      <c r="P39" s="310" t="s">
         <v>144</v>
       </c>
-      <c r="Q39" s="258"/>
-      <c r="R39" s="259"/>
+      <c r="Q39" s="311"/>
+      <c r="R39" s="312"/>
       <c r="U39" s="53" t="s">
         <v>140</v>
       </c>
@@ -11019,86 +11031,86 @@
       <c r="S41" s="7"/>
     </row>
     <row r="42" spans="2:21" x14ac:dyDescent="0.3">
-      <c r="B42" s="254" t="s">
+      <c r="B42" s="237" t="s">
         <v>35</v>
       </c>
-      <c r="C42" s="254"/>
-      <c r="D42" s="254"/>
-      <c r="E42" s="254"/>
-      <c r="F42" s="254"/>
-      <c r="G42" s="254"/>
-      <c r="H42" s="254"/>
-      <c r="I42" s="254"/>
-      <c r="J42" s="254"/>
-      <c r="K42" s="254"/>
-      <c r="L42" s="254"/>
-      <c r="M42" s="254"/>
-      <c r="N42" s="254"/>
-      <c r="O42" s="254"/>
-      <c r="P42" s="254"/>
-      <c r="Q42" s="254"/>
-      <c r="R42" s="254"/>
-      <c r="S42" s="254"/>
+      <c r="C42" s="237"/>
+      <c r="D42" s="237"/>
+      <c r="E42" s="237"/>
+      <c r="F42" s="237"/>
+      <c r="G42" s="237"/>
+      <c r="H42" s="237"/>
+      <c r="I42" s="237"/>
+      <c r="J42" s="237"/>
+      <c r="K42" s="237"/>
+      <c r="L42" s="237"/>
+      <c r="M42" s="237"/>
+      <c r="N42" s="237"/>
+      <c r="O42" s="237"/>
+      <c r="P42" s="237"/>
+      <c r="Q42" s="237"/>
+      <c r="R42" s="237"/>
+      <c r="S42" s="237"/>
     </row>
     <row r="43" spans="2:21" x14ac:dyDescent="0.3">
-      <c r="B43" s="254"/>
-      <c r="C43" s="254"/>
-      <c r="D43" s="254"/>
-      <c r="E43" s="254"/>
-      <c r="F43" s="254"/>
-      <c r="G43" s="254"/>
-      <c r="H43" s="254"/>
-      <c r="I43" s="254"/>
-      <c r="J43" s="254"/>
-      <c r="K43" s="254"/>
-      <c r="L43" s="254"/>
-      <c r="M43" s="254"/>
-      <c r="N43" s="254"/>
-      <c r="O43" s="254"/>
-      <c r="P43" s="254"/>
-      <c r="Q43" s="254"/>
-      <c r="R43" s="254"/>
-      <c r="S43" s="254"/>
+      <c r="B43" s="237"/>
+      <c r="C43" s="237"/>
+      <c r="D43" s="237"/>
+      <c r="E43" s="237"/>
+      <c r="F43" s="237"/>
+      <c r="G43" s="237"/>
+      <c r="H43" s="237"/>
+      <c r="I43" s="237"/>
+      <c r="J43" s="237"/>
+      <c r="K43" s="237"/>
+      <c r="L43" s="237"/>
+      <c r="M43" s="237"/>
+      <c r="N43" s="237"/>
+      <c r="O43" s="237"/>
+      <c r="P43" s="237"/>
+      <c r="Q43" s="237"/>
+      <c r="R43" s="237"/>
+      <c r="S43" s="237"/>
     </row>
     <row r="44" spans="2:21" x14ac:dyDescent="0.3">
-      <c r="B44" s="254"/>
-      <c r="C44" s="254"/>
-      <c r="D44" s="254"/>
-      <c r="E44" s="254"/>
-      <c r="F44" s="254"/>
-      <c r="G44" s="254"/>
-      <c r="H44" s="254"/>
-      <c r="I44" s="254"/>
-      <c r="J44" s="254"/>
-      <c r="K44" s="254"/>
-      <c r="L44" s="254"/>
-      <c r="M44" s="254"/>
-      <c r="N44" s="254"/>
-      <c r="O44" s="254"/>
-      <c r="P44" s="254"/>
-      <c r="Q44" s="254"/>
-      <c r="R44" s="254"/>
-      <c r="S44" s="254"/>
+      <c r="B44" s="237"/>
+      <c r="C44" s="237"/>
+      <c r="D44" s="237"/>
+      <c r="E44" s="237"/>
+      <c r="F44" s="237"/>
+      <c r="G44" s="237"/>
+      <c r="H44" s="237"/>
+      <c r="I44" s="237"/>
+      <c r="J44" s="237"/>
+      <c r="K44" s="237"/>
+      <c r="L44" s="237"/>
+      <c r="M44" s="237"/>
+      <c r="N44" s="237"/>
+      <c r="O44" s="237"/>
+      <c r="P44" s="237"/>
+      <c r="Q44" s="237"/>
+      <c r="R44" s="237"/>
+      <c r="S44" s="237"/>
     </row>
     <row r="45" spans="2:21" x14ac:dyDescent="0.3">
-      <c r="B45" s="255"/>
-      <c r="C45" s="255"/>
-      <c r="D45" s="255"/>
-      <c r="E45" s="255"/>
-      <c r="F45" s="255"/>
-      <c r="G45" s="255"/>
-      <c r="H45" s="255"/>
-      <c r="I45" s="255"/>
-      <c r="J45" s="255"/>
-      <c r="K45" s="255"/>
-      <c r="L45" s="255"/>
-      <c r="M45" s="255"/>
-      <c r="N45" s="255"/>
-      <c r="O45" s="255"/>
-      <c r="P45" s="255"/>
-      <c r="Q45" s="255"/>
-      <c r="R45" s="255"/>
-      <c r="S45" s="255"/>
+      <c r="B45" s="240"/>
+      <c r="C45" s="240"/>
+      <c r="D45" s="240"/>
+      <c r="E45" s="240"/>
+      <c r="F45" s="240"/>
+      <c r="G45" s="240"/>
+      <c r="H45" s="240"/>
+      <c r="I45" s="240"/>
+      <c r="J45" s="240"/>
+      <c r="K45" s="240"/>
+      <c r="L45" s="240"/>
+      <c r="M45" s="240"/>
+      <c r="N45" s="240"/>
+      <c r="O45" s="240"/>
+      <c r="P45" s="240"/>
+      <c r="Q45" s="240"/>
+      <c r="R45" s="240"/>
+      <c r="S45" s="240"/>
     </row>
     <row r="46" spans="2:21" x14ac:dyDescent="0.3">
       <c r="B46" s="42"/>
@@ -11256,33 +11268,33 @@
       <c r="R54" s="126"/>
     </row>
     <row r="55" spans="2:21" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B55" s="242" t="s">
+      <c r="B55" s="245" t="s">
         <v>148</v>
       </c>
-      <c r="C55" s="242"/>
-      <c r="D55" s="242"/>
-      <c r="E55" s="242"/>
-      <c r="F55" s="242"/>
-      <c r="G55" s="242"/>
-      <c r="H55" s="242"/>
-      <c r="I55" s="242"/>
-      <c r="J55" s="242"/>
-      <c r="K55" s="242"/>
-      <c r="L55" s="242"/>
-      <c r="M55" s="242"/>
-      <c r="N55" s="242"/>
-      <c r="O55" s="242"/>
-      <c r="P55" s="242"/>
-      <c r="Q55" s="242"/>
+      <c r="C55" s="245"/>
+      <c r="D55" s="245"/>
+      <c r="E55" s="245"/>
+      <c r="F55" s="245"/>
+      <c r="G55" s="245"/>
+      <c r="H55" s="245"/>
+      <c r="I55" s="245"/>
+      <c r="J55" s="245"/>
+      <c r="K55" s="245"/>
+      <c r="L55" s="245"/>
+      <c r="M55" s="245"/>
+      <c r="N55" s="245"/>
+      <c r="O55" s="245"/>
+      <c r="P55" s="245"/>
+      <c r="Q55" s="245"/>
     </row>
     <row r="56" spans="2:21" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B56" s="97" t="s">
         <v>1</v>
       </c>
-      <c r="C56" s="243" t="s">
+      <c r="C56" s="230" t="s">
         <v>2</v>
       </c>
-      <c r="D56" s="243"/>
+      <c r="D56" s="230"/>
       <c r="E56" s="120" t="s">
         <v>3</v>
       </c>
@@ -11327,10 +11339,10 @@
       </c>
     </row>
     <row r="57" spans="2:21" ht="22.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B57" s="246" t="s">
+      <c r="B57" s="309" t="s">
         <v>152</v>
       </c>
-      <c r="C57" s="247" t="s">
+      <c r="C57" s="317" t="s">
         <v>120</v>
       </c>
       <c r="D57" s="143" t="s">
@@ -11372,7 +11384,7 @@
       <c r="O57" s="208" t="s">
         <v>60</v>
       </c>
-      <c r="P57" s="252" t="s">
+      <c r="P57" s="303" t="s">
         <v>81</v>
       </c>
       <c r="Q57" s="143" t="s">
@@ -11383,8 +11395,8 @@
       </c>
     </row>
     <row r="58" spans="2:21" x14ac:dyDescent="0.3">
-      <c r="B58" s="246"/>
-      <c r="C58" s="247"/>
+      <c r="B58" s="309"/>
+      <c r="C58" s="317"/>
       <c r="D58" s="143" t="s">
         <v>24</v>
       </c>
@@ -11424,7 +11436,7 @@
       <c r="O58" s="208" t="s">
         <v>60</v>
       </c>
-      <c r="P58" s="253"/>
+      <c r="P58" s="304"/>
       <c r="Q58" s="143" t="s">
         <v>130</v>
       </c>
@@ -11433,10 +11445,10 @@
       </c>
     </row>
     <row r="59" spans="2:21" x14ac:dyDescent="0.3">
-      <c r="B59" s="246" t="s">
+      <c r="B59" s="309" t="s">
         <v>154</v>
       </c>
-      <c r="C59" s="247" t="s">
+      <c r="C59" s="317" t="s">
         <v>120</v>
       </c>
       <c r="D59" s="143" t="s">
@@ -11478,15 +11490,15 @@
       <c r="O59" s="208" t="s">
         <v>60</v>
       </c>
-      <c r="P59" s="253"/>
+      <c r="P59" s="304"/>
       <c r="Q59" s="143" t="s">
         <v>130</v>
       </c>
       <c r="U59" s="53"/>
     </row>
     <row r="60" spans="2:21" ht="28.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B60" s="246"/>
-      <c r="C60" s="247"/>
+      <c r="B60" s="309"/>
+      <c r="C60" s="317"/>
       <c r="D60" s="143" t="s">
         <v>24</v>
       </c>
@@ -11526,17 +11538,17 @@
       <c r="O60" s="208" t="s">
         <v>60</v>
       </c>
-      <c r="P60" s="260"/>
+      <c r="P60" s="305"/>
       <c r="Q60" s="143" t="s">
         <v>130</v>
       </c>
       <c r="U60" s="53"/>
     </row>
     <row r="61" spans="2:21" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B61" s="246" t="s">
+      <c r="B61" s="309" t="s">
         <v>155</v>
       </c>
-      <c r="C61" s="247" t="s">
+      <c r="C61" s="317" t="s">
         <v>120</v>
       </c>
       <c r="D61" s="143" t="s">
@@ -11578,7 +11590,7 @@
       <c r="O61" s="208" t="s">
         <v>64</v>
       </c>
-      <c r="P61" s="261" t="s">
+      <c r="P61" s="306" t="s">
         <v>65</v>
       </c>
       <c r="Q61" s="143" t="s">
@@ -11589,8 +11601,8 @@
       </c>
     </row>
     <row r="62" spans="2:21" x14ac:dyDescent="0.3">
-      <c r="B62" s="246"/>
-      <c r="C62" s="247"/>
+      <c r="B62" s="309"/>
+      <c r="C62" s="317"/>
       <c r="D62" s="143" t="s">
         <v>24</v>
       </c>
@@ -11630,7 +11642,7 @@
       <c r="O62" s="208" t="s">
         <v>64</v>
       </c>
-      <c r="P62" s="262"/>
+      <c r="P62" s="307"/>
       <c r="Q62" s="143" t="s">
         <v>156</v>
       </c>
@@ -11639,10 +11651,10 @@
       </c>
     </row>
     <row r="63" spans="2:21" x14ac:dyDescent="0.3">
-      <c r="B63" s="246" t="s">
+      <c r="B63" s="309" t="s">
         <v>158</v>
       </c>
-      <c r="C63" s="247" t="s">
+      <c r="C63" s="317" t="s">
         <v>120</v>
       </c>
       <c r="D63" s="143" t="s">
@@ -11684,7 +11696,7 @@
       <c r="O63" s="208" t="s">
         <v>64</v>
       </c>
-      <c r="P63" s="262"/>
+      <c r="P63" s="307"/>
       <c r="Q63" s="143" t="s">
         <v>156</v>
       </c>
@@ -11693,8 +11705,8 @@
       </c>
     </row>
     <row r="64" spans="2:21" x14ac:dyDescent="0.3">
-      <c r="B64" s="246"/>
-      <c r="C64" s="247"/>
+      <c r="B64" s="309"/>
+      <c r="C64" s="317"/>
       <c r="D64" s="143" t="s">
         <v>24</v>
       </c>
@@ -11734,7 +11746,7 @@
       <c r="O64" s="208" t="s">
         <v>64</v>
       </c>
-      <c r="P64" s="263"/>
+      <c r="P64" s="308"/>
       <c r="Q64" s="143" t="s">
         <v>156</v>
       </c>
@@ -11743,34 +11755,34 @@
       </c>
     </row>
     <row r="65" spans="2:63 3073:12199 12790:15083" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B65" s="248" t="s">
+      <c r="B65" s="225" t="s">
         <v>159</v>
       </c>
-      <c r="C65" s="248"/>
-      <c r="D65" s="249"/>
-      <c r="E65" s="249"/>
-      <c r="F65" s="248"/>
-      <c r="G65" s="249"/>
-      <c r="H65" s="249"/>
-      <c r="I65" s="248"/>
-      <c r="J65" s="249"/>
-      <c r="K65" s="249"/>
-      <c r="L65" s="249"/>
-      <c r="M65" s="248"/>
-      <c r="N65" s="249"/>
-      <c r="O65" s="249"/>
-      <c r="P65" s="249"/>
-      <c r="Q65" s="249"/>
+      <c r="C65" s="225"/>
+      <c r="D65" s="228"/>
+      <c r="E65" s="228"/>
+      <c r="F65" s="225"/>
+      <c r="G65" s="228"/>
+      <c r="H65" s="228"/>
+      <c r="I65" s="225"/>
+      <c r="J65" s="228"/>
+      <c r="K65" s="228"/>
+      <c r="L65" s="228"/>
+      <c r="M65" s="225"/>
+      <c r="N65" s="228"/>
+      <c r="O65" s="228"/>
+      <c r="P65" s="228"/>
+      <c r="Q65" s="228"/>
       <c r="U65" s="53"/>
     </row>
     <row r="66" spans="2:63 3073:12199 12790:15083" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B66" s="97" t="s">
         <v>1</v>
       </c>
-      <c r="C66" s="243" t="s">
+      <c r="C66" s="230" t="s">
         <v>2</v>
       </c>
-      <c r="D66" s="243"/>
+      <c r="D66" s="230"/>
       <c r="E66" s="8" t="s">
         <v>3</v>
       </c>
@@ -11813,7 +11825,7 @@
       <c r="U66" s="53"/>
     </row>
     <row r="67" spans="2:63 3073:12199 12790:15083" x14ac:dyDescent="0.3">
-      <c r="B67" s="250" t="s">
+      <c r="B67" s="289" t="s">
         <v>160</v>
       </c>
       <c r="C67" s="211" t="s">
@@ -11858,7 +11870,7 @@
       <c r="O67" s="208" t="s">
         <v>60</v>
       </c>
-      <c r="P67" s="252" t="s">
+      <c r="P67" s="303" t="s">
         <v>81</v>
       </c>
       <c r="Q67" s="149" t="s">
@@ -43317,7 +43329,7 @@
       </c>
     </row>
     <row r="68" spans="2:63 3073:12199 12790:15083" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B68" s="251"/>
+      <c r="B68" s="319"/>
       <c r="C68" s="211" t="s">
         <v>120</v>
       </c>
@@ -43360,7 +43372,7 @@
       <c r="O68" s="208" t="s">
         <v>60</v>
       </c>
-      <c r="P68" s="253"/>
+      <c r="P68" s="304"/>
       <c r="Q68" s="149" t="s">
         <v>130</v>
       </c>
@@ -54835,34 +54847,34 @@
       <c r="VHC68" s="158"/>
     </row>
     <row r="69" spans="2:63 3073:12199 12790:15083" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B69" s="242" t="s">
+      <c r="B69" s="245" t="s">
         <v>161</v>
       </c>
-      <c r="C69" s="242"/>
-      <c r="D69" s="242"/>
-      <c r="E69" s="242"/>
-      <c r="F69" s="242"/>
-      <c r="G69" s="242"/>
-      <c r="H69" s="242"/>
-      <c r="I69" s="242"/>
-      <c r="J69" s="242"/>
-      <c r="K69" s="242"/>
-      <c r="L69" s="242"/>
-      <c r="M69" s="242"/>
-      <c r="N69" s="242"/>
-      <c r="O69" s="242"/>
-      <c r="P69" s="242"/>
-      <c r="Q69" s="242"/>
+      <c r="C69" s="245"/>
+      <c r="D69" s="245"/>
+      <c r="E69" s="245"/>
+      <c r="F69" s="245"/>
+      <c r="G69" s="245"/>
+      <c r="H69" s="245"/>
+      <c r="I69" s="245"/>
+      <c r="J69" s="245"/>
+      <c r="K69" s="245"/>
+      <c r="L69" s="245"/>
+      <c r="M69" s="245"/>
+      <c r="N69" s="245"/>
+      <c r="O69" s="245"/>
+      <c r="P69" s="245"/>
+      <c r="Q69" s="245"/>
       <c r="U69" s="53"/>
     </row>
     <row r="70" spans="2:63 3073:12199 12790:15083" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B70" s="97" t="s">
         <v>1</v>
       </c>
-      <c r="C70" s="243" t="s">
+      <c r="C70" s="230" t="s">
         <v>2</v>
       </c>
-      <c r="D70" s="243"/>
+      <c r="D70" s="230"/>
       <c r="E70" s="8" t="s">
         <v>3</v>
       </c>
@@ -54905,7 +54917,7 @@
       <c r="U70" s="53"/>
     </row>
     <row r="71" spans="2:63 3073:12199 12790:15083" x14ac:dyDescent="0.3">
-      <c r="B71" s="250" t="s">
+      <c r="B71" s="289" t="s">
         <v>162</v>
       </c>
       <c r="C71" s="211" t="s">
@@ -54950,7 +54962,7 @@
       <c r="O71" s="208" t="s">
         <v>60</v>
       </c>
-      <c r="P71" s="252" t="s">
+      <c r="P71" s="303" t="s">
         <v>81</v>
       </c>
       <c r="Q71" s="149" t="s">
@@ -54959,7 +54971,7 @@
       <c r="U71" s="53"/>
     </row>
     <row r="72" spans="2:63 3073:12199 12790:15083" x14ac:dyDescent="0.3">
-      <c r="B72" s="251"/>
+      <c r="B72" s="319"/>
       <c r="C72" s="211" t="s">
         <v>120</v>
       </c>
@@ -55002,7 +55014,7 @@
       <c r="O72" s="208" t="s">
         <v>60</v>
       </c>
-      <c r="P72" s="253"/>
+      <c r="P72" s="304"/>
       <c r="Q72" s="149" t="s">
         <v>130</v>
       </c>
@@ -55032,121 +55044,121 @@
       <c r="T74" s="6"/>
     </row>
     <row r="75" spans="2:63 3073:12199 12790:15083" x14ac:dyDescent="0.3">
-      <c r="B75" s="241" t="s">
+      <c r="B75" s="263" t="s">
         <v>35</v>
       </c>
-      <c r="C75" s="241"/>
-      <c r="D75" s="241"/>
-      <c r="E75" s="241"/>
-      <c r="F75" s="241"/>
-      <c r="G75" s="241"/>
-      <c r="H75" s="241"/>
-      <c r="I75" s="241"/>
-      <c r="J75" s="241"/>
-      <c r="K75" s="241"/>
-      <c r="L75" s="241"/>
-      <c r="M75" s="241"/>
-      <c r="N75" s="241"/>
-      <c r="O75" s="241"/>
-      <c r="P75" s="241"/>
-      <c r="Q75" s="241"/>
-      <c r="R75" s="241"/>
-      <c r="S75" s="241"/>
-      <c r="T75" s="241"/>
+      <c r="C75" s="263"/>
+      <c r="D75" s="263"/>
+      <c r="E75" s="263"/>
+      <c r="F75" s="263"/>
+      <c r="G75" s="263"/>
+      <c r="H75" s="263"/>
+      <c r="I75" s="263"/>
+      <c r="J75" s="263"/>
+      <c r="K75" s="263"/>
+      <c r="L75" s="263"/>
+      <c r="M75" s="263"/>
+      <c r="N75" s="263"/>
+      <c r="O75" s="263"/>
+      <c r="P75" s="263"/>
+      <c r="Q75" s="263"/>
+      <c r="R75" s="263"/>
+      <c r="S75" s="263"/>
+      <c r="T75" s="263"/>
     </row>
     <row r="76" spans="2:63 3073:12199 12790:15083" x14ac:dyDescent="0.3">
-      <c r="B76" s="241"/>
-      <c r="C76" s="241"/>
-      <c r="D76" s="241"/>
-      <c r="E76" s="241"/>
-      <c r="F76" s="241"/>
-      <c r="G76" s="241"/>
-      <c r="H76" s="241"/>
-      <c r="I76" s="241"/>
-      <c r="J76" s="241"/>
-      <c r="K76" s="241"/>
-      <c r="L76" s="241"/>
-      <c r="M76" s="241"/>
-      <c r="N76" s="241"/>
-      <c r="O76" s="241"/>
-      <c r="P76" s="241"/>
-      <c r="Q76" s="241"/>
-      <c r="R76" s="241"/>
-      <c r="S76" s="241"/>
-      <c r="T76" s="241"/>
+      <c r="B76" s="263"/>
+      <c r="C76" s="263"/>
+      <c r="D76" s="263"/>
+      <c r="E76" s="263"/>
+      <c r="F76" s="263"/>
+      <c r="G76" s="263"/>
+      <c r="H76" s="263"/>
+      <c r="I76" s="263"/>
+      <c r="J76" s="263"/>
+      <c r="K76" s="263"/>
+      <c r="L76" s="263"/>
+      <c r="M76" s="263"/>
+      <c r="N76" s="263"/>
+      <c r="O76" s="263"/>
+      <c r="P76" s="263"/>
+      <c r="Q76" s="263"/>
+      <c r="R76" s="263"/>
+      <c r="S76" s="263"/>
+      <c r="T76" s="263"/>
     </row>
     <row r="77" spans="2:63 3073:12199 12790:15083" x14ac:dyDescent="0.3">
-      <c r="B77" s="241"/>
-      <c r="C77" s="241"/>
-      <c r="D77" s="241"/>
-      <c r="E77" s="241"/>
-      <c r="F77" s="241"/>
-      <c r="G77" s="241"/>
-      <c r="H77" s="241"/>
-      <c r="I77" s="241"/>
-      <c r="J77" s="241"/>
-      <c r="K77" s="241"/>
-      <c r="L77" s="241"/>
-      <c r="M77" s="241"/>
-      <c r="N77" s="241"/>
-      <c r="O77" s="241"/>
-      <c r="P77" s="241"/>
-      <c r="Q77" s="241"/>
-      <c r="R77" s="241"/>
-      <c r="S77" s="241"/>
-      <c r="T77" s="241"/>
+      <c r="B77" s="263"/>
+      <c r="C77" s="263"/>
+      <c r="D77" s="263"/>
+      <c r="E77" s="263"/>
+      <c r="F77" s="263"/>
+      <c r="G77" s="263"/>
+      <c r="H77" s="263"/>
+      <c r="I77" s="263"/>
+      <c r="J77" s="263"/>
+      <c r="K77" s="263"/>
+      <c r="L77" s="263"/>
+      <c r="M77" s="263"/>
+      <c r="N77" s="263"/>
+      <c r="O77" s="263"/>
+      <c r="P77" s="263"/>
+      <c r="Q77" s="263"/>
+      <c r="R77" s="263"/>
+      <c r="S77" s="263"/>
+      <c r="T77" s="263"/>
     </row>
     <row r="78" spans="2:63 3073:12199 12790:15083" x14ac:dyDescent="0.3">
-      <c r="B78" s="241"/>
-      <c r="C78" s="241"/>
-      <c r="D78" s="241"/>
-      <c r="E78" s="241"/>
-      <c r="F78" s="241"/>
-      <c r="G78" s="241"/>
-      <c r="H78" s="241"/>
-      <c r="I78" s="241"/>
-      <c r="J78" s="241"/>
-      <c r="K78" s="241"/>
-      <c r="L78" s="241"/>
-      <c r="M78" s="241"/>
-      <c r="N78" s="241"/>
-      <c r="O78" s="241"/>
-      <c r="P78" s="241"/>
-      <c r="Q78" s="241"/>
-      <c r="R78" s="241"/>
-      <c r="S78" s="241"/>
-      <c r="T78" s="241"/>
+      <c r="B78" s="263"/>
+      <c r="C78" s="263"/>
+      <c r="D78" s="263"/>
+      <c r="E78" s="263"/>
+      <c r="F78" s="263"/>
+      <c r="G78" s="263"/>
+      <c r="H78" s="263"/>
+      <c r="I78" s="263"/>
+      <c r="J78" s="263"/>
+      <c r="K78" s="263"/>
+      <c r="L78" s="263"/>
+      <c r="M78" s="263"/>
+      <c r="N78" s="263"/>
+      <c r="O78" s="263"/>
+      <c r="P78" s="263"/>
+      <c r="Q78" s="263"/>
+      <c r="R78" s="263"/>
+      <c r="S78" s="263"/>
+      <c r="T78" s="263"/>
     </row>
     <row r="87" spans="2:20" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B87" s="244" t="s">
+      <c r="B87" s="229" t="s">
         <v>164</v>
       </c>
-      <c r="C87" s="244"/>
-      <c r="D87" s="244"/>
-      <c r="E87" s="244"/>
-      <c r="F87" s="244"/>
-      <c r="G87" s="244"/>
-      <c r="H87" s="244"/>
-      <c r="I87" s="244"/>
-      <c r="J87" s="244"/>
-      <c r="K87" s="244"/>
-      <c r="L87" s="244"/>
-      <c r="M87" s="244"/>
-      <c r="N87" s="244"/>
-      <c r="O87" s="244"/>
-      <c r="P87" s="244"/>
-      <c r="Q87" s="244"/>
-      <c r="R87" s="244"/>
-      <c r="S87" s="244"/>
+      <c r="C87" s="229"/>
+      <c r="D87" s="229"/>
+      <c r="E87" s="229"/>
+      <c r="F87" s="229"/>
+      <c r="G87" s="229"/>
+      <c r="H87" s="229"/>
+      <c r="I87" s="229"/>
+      <c r="J87" s="229"/>
+      <c r="K87" s="229"/>
+      <c r="L87" s="229"/>
+      <c r="M87" s="229"/>
+      <c r="N87" s="229"/>
+      <c r="O87" s="229"/>
+      <c r="P87" s="229"/>
+      <c r="Q87" s="229"/>
+      <c r="R87" s="229"/>
+      <c r="S87" s="229"/>
     </row>
     <row r="88" spans="2:20" ht="27" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B88" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C88" s="245" t="s">
+      <c r="C88" s="318" t="s">
         <v>2</v>
       </c>
-      <c r="D88" s="245"/>
+      <c r="D88" s="318"/>
       <c r="E88" s="127" t="s">
         <v>135</v>
       </c>
@@ -55183,17 +55195,17 @@
       <c r="P88" s="17" t="s">
         <v>127</v>
       </c>
-      <c r="Q88" s="243" t="s">
+      <c r="Q88" s="230" t="s">
         <v>38</v>
       </c>
-      <c r="R88" s="243"/>
-      <c r="S88" s="243"/>
+      <c r="R88" s="230"/>
+      <c r="S88" s="230"/>
     </row>
     <row r="89" spans="2:20" ht="28.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B89" s="238" t="s">
+      <c r="B89" s="231" t="s">
         <v>99</v>
       </c>
-      <c r="C89" s="225" t="s">
+      <c r="C89" s="252" t="s">
         <v>120</v>
       </c>
       <c r="D89" s="53" t="s">
@@ -55237,15 +55249,15 @@
       <c r="P89" s="53" t="s">
         <v>167</v>
       </c>
-      <c r="Q89" s="240" t="s">
+      <c r="Q89" s="259" t="s">
         <v>47</v>
       </c>
-      <c r="R89" s="240"/>
-      <c r="S89" s="240"/>
+      <c r="R89" s="259"/>
+      <c r="S89" s="259"/>
     </row>
     <row r="90" spans="2:20" x14ac:dyDescent="0.3">
-      <c r="B90" s="239"/>
-      <c r="C90" s="225"/>
+      <c r="B90" s="227"/>
+      <c r="C90" s="252"/>
       <c r="D90" s="53" t="s">
         <v>24</v>
       </c>
@@ -55287,9 +55299,9 @@
       <c r="P90" s="53" t="s">
         <v>167</v>
       </c>
-      <c r="Q90" s="240"/>
-      <c r="R90" s="240"/>
-      <c r="S90" s="240"/>
+      <c r="Q90" s="259"/>
+      <c r="R90" s="259"/>
+      <c r="S90" s="259"/>
     </row>
     <row r="92" spans="2:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B92" s="5" t="s">
@@ -55315,120 +55327,120 @@
       <c r="T92" s="6"/>
     </row>
     <row r="93" spans="2:20" x14ac:dyDescent="0.3">
-      <c r="B93" s="241" t="s">
+      <c r="B93" s="263" t="s">
         <v>35</v>
       </c>
-      <c r="C93" s="241"/>
-      <c r="D93" s="241"/>
-      <c r="E93" s="241"/>
-      <c r="F93" s="241"/>
-      <c r="G93" s="241"/>
-      <c r="H93" s="241"/>
-      <c r="I93" s="241"/>
-      <c r="J93" s="241"/>
-      <c r="K93" s="241"/>
-      <c r="L93" s="241"/>
-      <c r="M93" s="241"/>
-      <c r="N93" s="241"/>
-      <c r="O93" s="241"/>
-      <c r="P93" s="241"/>
-      <c r="Q93" s="241"/>
-      <c r="R93" s="241"/>
-      <c r="S93" s="241"/>
-      <c r="T93" s="241"/>
+      <c r="C93" s="263"/>
+      <c r="D93" s="263"/>
+      <c r="E93" s="263"/>
+      <c r="F93" s="263"/>
+      <c r="G93" s="263"/>
+      <c r="H93" s="263"/>
+      <c r="I93" s="263"/>
+      <c r="J93" s="263"/>
+      <c r="K93" s="263"/>
+      <c r="L93" s="263"/>
+      <c r="M93" s="263"/>
+      <c r="N93" s="263"/>
+      <c r="O93" s="263"/>
+      <c r="P93" s="263"/>
+      <c r="Q93" s="263"/>
+      <c r="R93" s="263"/>
+      <c r="S93" s="263"/>
+      <c r="T93" s="263"/>
     </row>
     <row r="94" spans="2:20" x14ac:dyDescent="0.3">
-      <c r="B94" s="241"/>
-      <c r="C94" s="241"/>
-      <c r="D94" s="241"/>
-      <c r="E94" s="241"/>
-      <c r="F94" s="241"/>
-      <c r="G94" s="241"/>
-      <c r="H94" s="241"/>
-      <c r="I94" s="241"/>
-      <c r="J94" s="241"/>
-      <c r="K94" s="241"/>
-      <c r="L94" s="241"/>
-      <c r="M94" s="241"/>
-      <c r="N94" s="241"/>
-      <c r="O94" s="241"/>
-      <c r="P94" s="241"/>
-      <c r="Q94" s="241"/>
-      <c r="R94" s="241"/>
-      <c r="S94" s="241"/>
-      <c r="T94" s="241"/>
+      <c r="B94" s="263"/>
+      <c r="C94" s="263"/>
+      <c r="D94" s="263"/>
+      <c r="E94" s="263"/>
+      <c r="F94" s="263"/>
+      <c r="G94" s="263"/>
+      <c r="H94" s="263"/>
+      <c r="I94" s="263"/>
+      <c r="J94" s="263"/>
+      <c r="K94" s="263"/>
+      <c r="L94" s="263"/>
+      <c r="M94" s="263"/>
+      <c r="N94" s="263"/>
+      <c r="O94" s="263"/>
+      <c r="P94" s="263"/>
+      <c r="Q94" s="263"/>
+      <c r="R94" s="263"/>
+      <c r="S94" s="263"/>
+      <c r="T94" s="263"/>
     </row>
     <row r="95" spans="2:20" x14ac:dyDescent="0.3">
-      <c r="B95" s="241"/>
-      <c r="C95" s="241"/>
-      <c r="D95" s="241"/>
-      <c r="E95" s="241"/>
-      <c r="F95" s="241"/>
-      <c r="G95" s="241"/>
-      <c r="H95" s="241"/>
-      <c r="I95" s="241"/>
-      <c r="J95" s="241"/>
-      <c r="K95" s="241"/>
-      <c r="L95" s="241"/>
-      <c r="M95" s="241"/>
-      <c r="N95" s="241"/>
-      <c r="O95" s="241"/>
-      <c r="P95" s="241"/>
-      <c r="Q95" s="241"/>
-      <c r="R95" s="241"/>
-      <c r="S95" s="241"/>
-      <c r="T95" s="241"/>
+      <c r="B95" s="263"/>
+      <c r="C95" s="263"/>
+      <c r="D95" s="263"/>
+      <c r="E95" s="263"/>
+      <c r="F95" s="263"/>
+      <c r="G95" s="263"/>
+      <c r="H95" s="263"/>
+      <c r="I95" s="263"/>
+      <c r="J95" s="263"/>
+      <c r="K95" s="263"/>
+      <c r="L95" s="263"/>
+      <c r="M95" s="263"/>
+      <c r="N95" s="263"/>
+      <c r="O95" s="263"/>
+      <c r="P95" s="263"/>
+      <c r="Q95" s="263"/>
+      <c r="R95" s="263"/>
+      <c r="S95" s="263"/>
+      <c r="T95" s="263"/>
     </row>
     <row r="96" spans="2:20" x14ac:dyDescent="0.3">
-      <c r="B96" s="241"/>
-      <c r="C96" s="241"/>
-      <c r="D96" s="241"/>
-      <c r="E96" s="241"/>
-      <c r="F96" s="241"/>
-      <c r="G96" s="241"/>
-      <c r="H96" s="241"/>
-      <c r="I96" s="241"/>
-      <c r="J96" s="241"/>
-      <c r="K96" s="241"/>
-      <c r="L96" s="241"/>
-      <c r="M96" s="241"/>
-      <c r="N96" s="241"/>
-      <c r="O96" s="241"/>
-      <c r="P96" s="241"/>
-      <c r="Q96" s="241"/>
-      <c r="R96" s="241"/>
-      <c r="S96" s="241"/>
-      <c r="T96" s="241"/>
+      <c r="B96" s="263"/>
+      <c r="C96" s="263"/>
+      <c r="D96" s="263"/>
+      <c r="E96" s="263"/>
+      <c r="F96" s="263"/>
+      <c r="G96" s="263"/>
+      <c r="H96" s="263"/>
+      <c r="I96" s="263"/>
+      <c r="J96" s="263"/>
+      <c r="K96" s="263"/>
+      <c r="L96" s="263"/>
+      <c r="M96" s="263"/>
+      <c r="N96" s="263"/>
+      <c r="O96" s="263"/>
+      <c r="P96" s="263"/>
+      <c r="Q96" s="263"/>
+      <c r="R96" s="263"/>
+      <c r="S96" s="263"/>
+      <c r="T96" s="263"/>
     </row>
     <row r="106" spans="2:17" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="107" spans="2:17" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B107" s="242" t="s">
+      <c r="B107" s="245" t="s">
         <v>168</v>
       </c>
-      <c r="C107" s="242"/>
-      <c r="D107" s="242"/>
-      <c r="E107" s="242"/>
-      <c r="F107" s="242"/>
-      <c r="G107" s="242"/>
-      <c r="H107" s="242"/>
-      <c r="I107" s="242"/>
-      <c r="J107" s="242"/>
-      <c r="K107" s="242"/>
-      <c r="L107" s="242"/>
-      <c r="M107" s="242"/>
-      <c r="N107" s="242"/>
-      <c r="O107" s="242"/>
-      <c r="P107" s="242"/>
-      <c r="Q107" s="242"/>
+      <c r="C107" s="245"/>
+      <c r="D107" s="245"/>
+      <c r="E107" s="245"/>
+      <c r="F107" s="245"/>
+      <c r="G107" s="245"/>
+      <c r="H107" s="245"/>
+      <c r="I107" s="245"/>
+      <c r="J107" s="245"/>
+      <c r="K107" s="245"/>
+      <c r="L107" s="245"/>
+      <c r="M107" s="245"/>
+      <c r="N107" s="245"/>
+      <c r="O107" s="245"/>
+      <c r="P107" s="245"/>
+      <c r="Q107" s="245"/>
     </row>
     <row r="108" spans="2:17" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B108" s="97" t="s">
         <v>1</v>
       </c>
-      <c r="C108" s="243" t="s">
+      <c r="C108" s="230" t="s">
         <v>2</v>
       </c>
-      <c r="D108" s="243"/>
+      <c r="D108" s="230"/>
       <c r="E108" s="8" t="s">
         <v>3</v>
       </c>
@@ -55470,10 +55482,10 @@
       </c>
     </row>
     <row r="109" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B109" s="224" t="s">
+      <c r="B109" s="320" t="s">
         <v>169</v>
       </c>
-      <c r="C109" s="225" t="s">
+      <c r="C109" s="252" t="s">
         <v>120</v>
       </c>
       <c r="D109" s="53" t="s">
@@ -55522,8 +55534,8 @@
       </c>
     </row>
     <row r="110" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B110" s="224"/>
-      <c r="C110" s="225"/>
+      <c r="B110" s="320"/>
+      <c r="C110" s="252"/>
       <c r="D110" s="53" t="s">
         <v>24</v>
       </c>
@@ -55571,33 +55583,33 @@
     </row>
     <row r="119" spans="2:17" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="120" spans="2:17" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B120" s="242" t="s">
+      <c r="B120" s="245" t="s">
         <v>173</v>
       </c>
-      <c r="C120" s="242"/>
-      <c r="D120" s="242"/>
-      <c r="E120" s="242"/>
-      <c r="F120" s="242"/>
-      <c r="G120" s="242"/>
-      <c r="H120" s="242"/>
-      <c r="I120" s="242"/>
-      <c r="J120" s="242"/>
-      <c r="K120" s="242"/>
-      <c r="L120" s="242"/>
-      <c r="M120" s="242"/>
-      <c r="N120" s="242"/>
-      <c r="O120" s="242"/>
-      <c r="P120" s="242"/>
-      <c r="Q120" s="242"/>
+      <c r="C120" s="245"/>
+      <c r="D120" s="245"/>
+      <c r="E120" s="245"/>
+      <c r="F120" s="245"/>
+      <c r="G120" s="245"/>
+      <c r="H120" s="245"/>
+      <c r="I120" s="245"/>
+      <c r="J120" s="245"/>
+      <c r="K120" s="245"/>
+      <c r="L120" s="245"/>
+      <c r="M120" s="245"/>
+      <c r="N120" s="245"/>
+      <c r="O120" s="245"/>
+      <c r="P120" s="245"/>
+      <c r="Q120" s="245"/>
     </row>
     <row r="121" spans="2:17" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B121" s="97" t="s">
         <v>1</v>
       </c>
-      <c r="C121" s="243" t="s">
+      <c r="C121" s="230" t="s">
         <v>2</v>
       </c>
-      <c r="D121" s="243"/>
+      <c r="D121" s="230"/>
       <c r="E121" s="8" t="s">
         <v>3</v>
       </c>
@@ -55639,10 +55651,10 @@
       </c>
     </row>
     <row r="122" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B122" s="224" t="s">
+      <c r="B122" s="320" t="s">
         <v>174</v>
       </c>
-      <c r="C122" s="225" t="s">
+      <c r="C122" s="252" t="s">
         <v>120</v>
       </c>
       <c r="D122" s="53" t="s">
@@ -55691,10 +55703,10 @@
       </c>
     </row>
     <row r="123" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B123" s="224" t="s">
+      <c r="B123" s="320" t="s">
         <v>174</v>
       </c>
-      <c r="C123" s="225" t="s">
+      <c r="C123" s="252" t="s">
         <v>120</v>
       </c>
       <c r="D123" s="53" t="s">
@@ -55743,10 +55755,10 @@
       </c>
     </row>
     <row r="124" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B124" s="224" t="s">
+      <c r="B124" s="320" t="s">
         <v>175</v>
       </c>
-      <c r="C124" s="225" t="s">
+      <c r="C124" s="252" t="s">
         <v>120</v>
       </c>
       <c r="D124" s="53" t="s">
@@ -55796,8 +55808,8 @@
       </c>
     </row>
     <row r="125" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B125" s="224"/>
-      <c r="C125" s="225"/>
+      <c r="B125" s="320"/>
+      <c r="C125" s="252"/>
       <c r="D125" s="53" t="s">
         <v>24</v>
       </c>
@@ -55846,19 +55858,36 @@
     </row>
   </sheetData>
   <mergeCells count="59">
-    <mergeCell ref="P57:P60"/>
-    <mergeCell ref="P61:P64"/>
-    <mergeCell ref="B11:B12"/>
-    <mergeCell ref="C11:C12"/>
-    <mergeCell ref="B61:B62"/>
-    <mergeCell ref="P39:R39"/>
-    <mergeCell ref="B15:B16"/>
-    <mergeCell ref="C15:C16"/>
-    <mergeCell ref="B17:B18"/>
-    <mergeCell ref="C17:C18"/>
-    <mergeCell ref="B36:B37"/>
-    <mergeCell ref="C36:C37"/>
-    <mergeCell ref="P36:R37"/>
+    <mergeCell ref="B124:B125"/>
+    <mergeCell ref="C124:C125"/>
+    <mergeCell ref="B122:B123"/>
+    <mergeCell ref="C122:C123"/>
+    <mergeCell ref="B20:R20"/>
+    <mergeCell ref="B21:R24"/>
+    <mergeCell ref="B109:B110"/>
+    <mergeCell ref="C109:C110"/>
+    <mergeCell ref="B89:B90"/>
+    <mergeCell ref="C89:C90"/>
+    <mergeCell ref="Q89:S90"/>
+    <mergeCell ref="B93:T96"/>
+    <mergeCell ref="B107:Q107"/>
+    <mergeCell ref="C108:D108"/>
+    <mergeCell ref="B120:Q120"/>
+    <mergeCell ref="C121:D121"/>
+    <mergeCell ref="Q88:S88"/>
+    <mergeCell ref="B87:S87"/>
+    <mergeCell ref="C88:D88"/>
+    <mergeCell ref="C66:D66"/>
+    <mergeCell ref="B63:B64"/>
+    <mergeCell ref="C63:C64"/>
+    <mergeCell ref="B65:Q65"/>
+    <mergeCell ref="C70:D70"/>
+    <mergeCell ref="B75:T78"/>
+    <mergeCell ref="B67:B68"/>
+    <mergeCell ref="B69:Q69"/>
+    <mergeCell ref="B71:B72"/>
+    <mergeCell ref="P67:P68"/>
+    <mergeCell ref="P71:P72"/>
     <mergeCell ref="B9:Q9"/>
     <mergeCell ref="C61:C62"/>
     <mergeCell ref="B13:B14"/>
@@ -55875,36 +55904,19 @@
     <mergeCell ref="B59:B60"/>
     <mergeCell ref="C59:C60"/>
     <mergeCell ref="C10:D10"/>
-    <mergeCell ref="Q88:S88"/>
-    <mergeCell ref="B87:S87"/>
-    <mergeCell ref="C88:D88"/>
-    <mergeCell ref="C66:D66"/>
-    <mergeCell ref="B63:B64"/>
-    <mergeCell ref="C63:C64"/>
-    <mergeCell ref="B65:Q65"/>
-    <mergeCell ref="C70:D70"/>
-    <mergeCell ref="B75:T78"/>
-    <mergeCell ref="B67:B68"/>
-    <mergeCell ref="B69:Q69"/>
-    <mergeCell ref="B71:B72"/>
-    <mergeCell ref="P67:P68"/>
-    <mergeCell ref="P71:P72"/>
-    <mergeCell ref="B124:B125"/>
-    <mergeCell ref="C124:C125"/>
-    <mergeCell ref="B122:B123"/>
-    <mergeCell ref="C122:C123"/>
-    <mergeCell ref="B20:R20"/>
-    <mergeCell ref="B21:R24"/>
-    <mergeCell ref="B109:B110"/>
-    <mergeCell ref="C109:C110"/>
-    <mergeCell ref="B89:B90"/>
-    <mergeCell ref="C89:C90"/>
-    <mergeCell ref="Q89:S90"/>
-    <mergeCell ref="B93:T96"/>
-    <mergeCell ref="B107:Q107"/>
-    <mergeCell ref="C108:D108"/>
-    <mergeCell ref="B120:Q120"/>
-    <mergeCell ref="C121:D121"/>
+    <mergeCell ref="P57:P60"/>
+    <mergeCell ref="P61:P64"/>
+    <mergeCell ref="B11:B12"/>
+    <mergeCell ref="C11:C12"/>
+    <mergeCell ref="B61:B62"/>
+    <mergeCell ref="P39:R39"/>
+    <mergeCell ref="B15:B16"/>
+    <mergeCell ref="C15:C16"/>
+    <mergeCell ref="B17:B18"/>
+    <mergeCell ref="C17:C18"/>
+    <mergeCell ref="B36:B37"/>
+    <mergeCell ref="C36:C37"/>
+    <mergeCell ref="P36:R37"/>
   </mergeCells>
   <phoneticPr fontId="14" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -55942,8 +55954,8 @@
     <row r="8" spans="2:18" x14ac:dyDescent="0.3">
       <c r="B8" s="126"/>
       <c r="C8" s="126"/>
-      <c r="D8" s="325"/>
-      <c r="E8" s="325"/>
+      <c r="D8" s="334"/>
+      <c r="E8" s="334"/>
       <c r="F8" s="126"/>
       <c r="G8" s="126"/>
       <c r="H8" s="126"/>
@@ -55959,32 +55971,32 @@
       <c r="R8" s="126"/>
     </row>
     <row r="9" spans="2:18" ht="28.8" x14ac:dyDescent="0.55000000000000004">
-      <c r="B9" s="330" t="s">
+      <c r="B9" s="337" t="s">
         <v>176</v>
       </c>
-      <c r="C9" s="330"/>
-      <c r="D9" s="330"/>
-      <c r="E9" s="330"/>
-      <c r="F9" s="330"/>
-      <c r="G9" s="330"/>
-      <c r="H9" s="330"/>
-      <c r="I9" s="330"/>
-      <c r="J9" s="330"/>
-      <c r="K9" s="330"/>
-      <c r="L9" s="330"/>
-      <c r="M9" s="330"/>
-      <c r="N9" s="330"/>
-      <c r="O9" s="330"/>
-      <c r="P9" s="330"/>
+      <c r="C9" s="337"/>
+      <c r="D9" s="337"/>
+      <c r="E9" s="337"/>
+      <c r="F9" s="337"/>
+      <c r="G9" s="337"/>
+      <c r="H9" s="337"/>
+      <c r="I9" s="337"/>
+      <c r="J9" s="337"/>
+      <c r="K9" s="337"/>
+      <c r="L9" s="337"/>
+      <c r="M9" s="337"/>
+      <c r="N9" s="337"/>
+      <c r="O9" s="337"/>
+      <c r="P9" s="337"/>
     </row>
     <row r="10" spans="2:18" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B10" s="127" t="s">
         <v>1</v>
       </c>
-      <c r="C10" s="326" t="s">
+      <c r="C10" s="353" t="s">
         <v>2</v>
       </c>
-      <c r="D10" s="327"/>
+      <c r="D10" s="354"/>
       <c r="E10" s="12" t="s">
         <v>3</v>
       </c>
@@ -56024,10 +56036,10 @@
       <c r="Q10" s="126"/>
     </row>
     <row r="11" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="B11" s="328" t="s">
+      <c r="B11" s="355" t="s">
         <v>179</v>
       </c>
-      <c r="C11" s="328" t="s">
+      <c r="C11" s="355" t="s">
         <v>180</v>
       </c>
       <c r="D11" s="41" t="s">
@@ -56075,8 +56087,8 @@
       <c r="Q11" s="126"/>
     </row>
     <row r="12" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="B12" s="329"/>
-      <c r="C12" s="329"/>
+      <c r="B12" s="356"/>
+      <c r="C12" s="356"/>
       <c r="D12" s="41" t="s">
         <v>24</v>
       </c>
@@ -56122,10 +56134,10 @@
       <c r="Q12" s="126"/>
     </row>
     <row r="13" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="B13" s="328" t="s">
+      <c r="B13" s="355" t="s">
         <v>182</v>
       </c>
-      <c r="C13" s="328" t="s">
+      <c r="C13" s="355" t="s">
         <v>180</v>
       </c>
       <c r="D13" s="41" t="s">
@@ -56173,8 +56185,8 @@
       <c r="Q13" s="126"/>
     </row>
     <row r="14" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="B14" s="329"/>
-      <c r="C14" s="329"/>
+      <c r="B14" s="356"/>
+      <c r="C14" s="356"/>
       <c r="D14" s="41" t="s">
         <v>24</v>
       </c>
@@ -56220,10 +56232,10 @@
       <c r="Q14" s="126"/>
     </row>
     <row r="15" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="B15" s="328" t="s">
+      <c r="B15" s="355" t="s">
         <v>132</v>
       </c>
-      <c r="C15" s="328" t="s">
+      <c r="C15" s="355" t="s">
         <v>180</v>
       </c>
       <c r="D15" s="41" t="s">
@@ -56271,8 +56283,8 @@
       <c r="Q15" s="126"/>
     </row>
     <row r="16" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="B16" s="329"/>
-      <c r="C16" s="329"/>
+      <c r="B16" s="356"/>
+      <c r="C16" s="356"/>
       <c r="D16" s="41" t="s">
         <v>24</v>
       </c>
@@ -56332,93 +56344,93 @@
       <c r="N17" s="34"/>
     </row>
     <row r="18" spans="2:17" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B18" s="334" t="s">
+      <c r="B18" s="359" t="s">
         <v>34</v>
       </c>
-      <c r="C18" s="335"/>
-      <c r="D18" s="335"/>
-      <c r="E18" s="335"/>
-      <c r="F18" s="335"/>
-      <c r="G18" s="335"/>
-      <c r="H18" s="335"/>
-      <c r="I18" s="335"/>
-      <c r="J18" s="335"/>
-      <c r="K18" s="335"/>
-      <c r="L18" s="335"/>
-      <c r="M18" s="335"/>
-      <c r="N18" s="335"/>
-      <c r="O18" s="335"/>
-      <c r="P18" s="336"/>
+      <c r="C18" s="360"/>
+      <c r="D18" s="360"/>
+      <c r="E18" s="360"/>
+      <c r="F18" s="360"/>
+      <c r="G18" s="360"/>
+      <c r="H18" s="360"/>
+      <c r="I18" s="360"/>
+      <c r="J18" s="360"/>
+      <c r="K18" s="360"/>
+      <c r="L18" s="360"/>
+      <c r="M18" s="360"/>
+      <c r="N18" s="360"/>
+      <c r="O18" s="360"/>
+      <c r="P18" s="361"/>
     </row>
     <row r="19" spans="2:17" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B19" s="229" t="s">
+      <c r="B19" s="324" t="s">
         <v>35</v>
       </c>
-      <c r="C19" s="230"/>
-      <c r="D19" s="230"/>
-      <c r="E19" s="230"/>
-      <c r="F19" s="230"/>
-      <c r="G19" s="230"/>
-      <c r="H19" s="230"/>
-      <c r="I19" s="230"/>
-      <c r="J19" s="230"/>
-      <c r="K19" s="230"/>
-      <c r="L19" s="230"/>
-      <c r="M19" s="230"/>
-      <c r="N19" s="230"/>
-      <c r="O19" s="230"/>
-      <c r="P19" s="231"/>
+      <c r="C19" s="325"/>
+      <c r="D19" s="325"/>
+      <c r="E19" s="325"/>
+      <c r="F19" s="325"/>
+      <c r="G19" s="325"/>
+      <c r="H19" s="325"/>
+      <c r="I19" s="325"/>
+      <c r="J19" s="325"/>
+      <c r="K19" s="325"/>
+      <c r="L19" s="325"/>
+      <c r="M19" s="325"/>
+      <c r="N19" s="325"/>
+      <c r="O19" s="325"/>
+      <c r="P19" s="326"/>
     </row>
     <row r="20" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B20" s="232"/>
-      <c r="C20" s="233"/>
-      <c r="D20" s="233"/>
-      <c r="E20" s="233"/>
-      <c r="F20" s="233"/>
-      <c r="G20" s="233"/>
-      <c r="H20" s="233"/>
-      <c r="I20" s="233"/>
-      <c r="J20" s="233"/>
-      <c r="K20" s="233"/>
-      <c r="L20" s="233"/>
-      <c r="M20" s="233"/>
-      <c r="N20" s="233"/>
-      <c r="O20" s="233"/>
-      <c r="P20" s="234"/>
+      <c r="B20" s="327"/>
+      <c r="C20" s="297"/>
+      <c r="D20" s="297"/>
+      <c r="E20" s="297"/>
+      <c r="F20" s="297"/>
+      <c r="G20" s="297"/>
+      <c r="H20" s="297"/>
+      <c r="I20" s="297"/>
+      <c r="J20" s="297"/>
+      <c r="K20" s="297"/>
+      <c r="L20" s="297"/>
+      <c r="M20" s="297"/>
+      <c r="N20" s="297"/>
+      <c r="O20" s="297"/>
+      <c r="P20" s="328"/>
     </row>
     <row r="21" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B21" s="232"/>
-      <c r="C21" s="233"/>
-      <c r="D21" s="233"/>
-      <c r="E21" s="233"/>
-      <c r="F21" s="233"/>
-      <c r="G21" s="233"/>
-      <c r="H21" s="233"/>
-      <c r="I21" s="233"/>
-      <c r="J21" s="233"/>
-      <c r="K21" s="233"/>
-      <c r="L21" s="233"/>
-      <c r="M21" s="233"/>
-      <c r="N21" s="233"/>
-      <c r="O21" s="233"/>
-      <c r="P21" s="234"/>
+      <c r="B21" s="327"/>
+      <c r="C21" s="297"/>
+      <c r="D21" s="297"/>
+      <c r="E21" s="297"/>
+      <c r="F21" s="297"/>
+      <c r="G21" s="297"/>
+      <c r="H21" s="297"/>
+      <c r="I21" s="297"/>
+      <c r="J21" s="297"/>
+      <c r="K21" s="297"/>
+      <c r="L21" s="297"/>
+      <c r="M21" s="297"/>
+      <c r="N21" s="297"/>
+      <c r="O21" s="297"/>
+      <c r="P21" s="328"/>
     </row>
     <row r="22" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B22" s="235"/>
-      <c r="C22" s="236"/>
-      <c r="D22" s="236"/>
-      <c r="E22" s="236"/>
-      <c r="F22" s="236"/>
-      <c r="G22" s="236"/>
-      <c r="H22" s="236"/>
-      <c r="I22" s="236"/>
-      <c r="J22" s="236"/>
-      <c r="K22" s="236"/>
-      <c r="L22" s="236"/>
-      <c r="M22" s="236"/>
-      <c r="N22" s="236"/>
-      <c r="O22" s="236"/>
-      <c r="P22" s="237"/>
+      <c r="B22" s="329"/>
+      <c r="C22" s="330"/>
+      <c r="D22" s="330"/>
+      <c r="E22" s="330"/>
+      <c r="F22" s="330"/>
+      <c r="G22" s="330"/>
+      <c r="H22" s="330"/>
+      <c r="I22" s="330"/>
+      <c r="J22" s="330"/>
+      <c r="K22" s="330"/>
+      <c r="L22" s="330"/>
+      <c r="M22" s="330"/>
+      <c r="N22" s="330"/>
+      <c r="O22" s="330"/>
+      <c r="P22" s="331"/>
     </row>
     <row r="23" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B23" s="27"/>
@@ -56548,33 +56560,33 @@
       <c r="N31" s="34"/>
     </row>
     <row r="32" spans="2:17" ht="28.8" x14ac:dyDescent="0.55000000000000004">
-      <c r="B32" s="331" t="s">
+      <c r="B32" s="357" t="s">
         <v>184</v>
       </c>
-      <c r="C32" s="332"/>
-      <c r="D32" s="332"/>
-      <c r="E32" s="332"/>
-      <c r="F32" s="332"/>
-      <c r="G32" s="332"/>
-      <c r="H32" s="332"/>
-      <c r="I32" s="332"/>
-      <c r="J32" s="332"/>
-      <c r="K32" s="332"/>
-      <c r="L32" s="332"/>
-      <c r="M32" s="332"/>
-      <c r="N32" s="332"/>
-      <c r="O32" s="332"/>
-      <c r="P32" s="332"/>
-      <c r="Q32" s="333"/>
+      <c r="C32" s="336"/>
+      <c r="D32" s="336"/>
+      <c r="E32" s="336"/>
+      <c r="F32" s="336"/>
+      <c r="G32" s="336"/>
+      <c r="H32" s="336"/>
+      <c r="I32" s="336"/>
+      <c r="J32" s="336"/>
+      <c r="K32" s="336"/>
+      <c r="L32" s="336"/>
+      <c r="M32" s="336"/>
+      <c r="N32" s="336"/>
+      <c r="O32" s="336"/>
+      <c r="P32" s="336"/>
+      <c r="Q32" s="358"/>
     </row>
     <row r="33" spans="2:19" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B33" s="127" t="s">
         <v>1</v>
       </c>
-      <c r="C33" s="337" t="s">
+      <c r="C33" s="352" t="s">
         <v>2</v>
       </c>
-      <c r="D33" s="337"/>
+      <c r="D33" s="352"/>
       <c r="E33" s="127" t="s">
         <v>135</v>
       </c>
@@ -56608,19 +56620,19 @@
       <c r="O33" s="127" t="s">
         <v>14</v>
       </c>
-      <c r="P33" s="288" t="s">
+      <c r="P33" s="285" t="s">
         <v>38</v>
       </c>
-      <c r="Q33" s="289"/>
+      <c r="Q33" s="286"/>
       <c r="S33" s="121" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="34" spans="2:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B34" s="342" t="s">
+      <c r="B34" s="350" t="s">
         <v>188</v>
       </c>
-      <c r="C34" s="343" t="s">
+      <c r="C34" s="351" t="s">
         <v>180</v>
       </c>
       <c r="D34" s="40" t="s">
@@ -56661,17 +56673,17 @@
       <c r="O34" s="40" t="s">
         <v>46</v>
       </c>
-      <c r="P34" s="266" t="s">
+      <c r="P34" s="255" t="s">
         <v>189</v>
       </c>
-      <c r="Q34" s="268"/>
+      <c r="Q34" s="256"/>
       <c r="S34" s="53" t="s">
         <v>190</v>
       </c>
     </row>
     <row r="35" spans="2:19" x14ac:dyDescent="0.3">
-      <c r="B35" s="342"/>
-      <c r="C35" s="343"/>
+      <c r="B35" s="350"/>
+      <c r="C35" s="351"/>
       <c r="D35" s="40" t="s">
         <v>24</v>
       </c>
@@ -56710,8 +56722,8 @@
       <c r="O35" s="40" t="s">
         <v>46</v>
       </c>
-      <c r="P35" s="269"/>
-      <c r="Q35" s="271"/>
+      <c r="P35" s="314"/>
+      <c r="Q35" s="316"/>
       <c r="S35" s="53" t="s">
         <v>190</v>
       </c>
@@ -56761,8 +56773,8 @@
       <c r="O36" s="40" t="s">
         <v>46</v>
       </c>
-      <c r="P36" s="309"/>
-      <c r="Q36" s="310"/>
+      <c r="P36" s="257"/>
+      <c r="Q36" s="258"/>
       <c r="S36" s="53" t="s">
         <v>145</v>
       </c>
@@ -56818,74 +56830,74 @@
       <c r="P39" s="7"/>
     </row>
     <row r="40" spans="2:19" x14ac:dyDescent="0.3">
-      <c r="B40" s="254" t="s">
+      <c r="B40" s="237" t="s">
         <v>35</v>
       </c>
-      <c r="C40" s="274"/>
-      <c r="D40" s="274"/>
-      <c r="E40" s="274"/>
-      <c r="F40" s="274"/>
-      <c r="G40" s="274"/>
-      <c r="H40" s="274"/>
-      <c r="I40" s="274"/>
-      <c r="J40" s="274"/>
-      <c r="K40" s="274"/>
-      <c r="L40" s="274"/>
-      <c r="M40" s="274"/>
-      <c r="N40" s="274"/>
-      <c r="O40" s="274"/>
-      <c r="P40" s="275"/>
+      <c r="C40" s="238"/>
+      <c r="D40" s="238"/>
+      <c r="E40" s="238"/>
+      <c r="F40" s="238"/>
+      <c r="G40" s="238"/>
+      <c r="H40" s="238"/>
+      <c r="I40" s="238"/>
+      <c r="J40" s="238"/>
+      <c r="K40" s="238"/>
+      <c r="L40" s="238"/>
+      <c r="M40" s="238"/>
+      <c r="N40" s="238"/>
+      <c r="O40" s="238"/>
+      <c r="P40" s="239"/>
     </row>
     <row r="41" spans="2:19" x14ac:dyDescent="0.3">
-      <c r="B41" s="254"/>
-      <c r="C41" s="274"/>
-      <c r="D41" s="274"/>
-      <c r="E41" s="274"/>
-      <c r="F41" s="274"/>
-      <c r="G41" s="274"/>
-      <c r="H41" s="274"/>
-      <c r="I41" s="274"/>
-      <c r="J41" s="274"/>
-      <c r="K41" s="274"/>
-      <c r="L41" s="274"/>
-      <c r="M41" s="274"/>
-      <c r="N41" s="274"/>
-      <c r="O41" s="274"/>
-      <c r="P41" s="275"/>
+      <c r="B41" s="237"/>
+      <c r="C41" s="238"/>
+      <c r="D41" s="238"/>
+      <c r="E41" s="238"/>
+      <c r="F41" s="238"/>
+      <c r="G41" s="238"/>
+      <c r="H41" s="238"/>
+      <c r="I41" s="238"/>
+      <c r="J41" s="238"/>
+      <c r="K41" s="238"/>
+      <c r="L41" s="238"/>
+      <c r="M41" s="238"/>
+      <c r="N41" s="238"/>
+      <c r="O41" s="238"/>
+      <c r="P41" s="239"/>
     </row>
     <row r="42" spans="2:19" x14ac:dyDescent="0.3">
-      <c r="B42" s="254"/>
-      <c r="C42" s="274"/>
-      <c r="D42" s="274"/>
-      <c r="E42" s="274"/>
-      <c r="F42" s="274"/>
-      <c r="G42" s="274"/>
-      <c r="H42" s="274"/>
-      <c r="I42" s="274"/>
-      <c r="J42" s="274"/>
-      <c r="K42" s="274"/>
-      <c r="L42" s="274"/>
-      <c r="M42" s="274"/>
-      <c r="N42" s="274"/>
-      <c r="O42" s="274"/>
-      <c r="P42" s="275"/>
+      <c r="B42" s="237"/>
+      <c r="C42" s="238"/>
+      <c r="D42" s="238"/>
+      <c r="E42" s="238"/>
+      <c r="F42" s="238"/>
+      <c r="G42" s="238"/>
+      <c r="H42" s="238"/>
+      <c r="I42" s="238"/>
+      <c r="J42" s="238"/>
+      <c r="K42" s="238"/>
+      <c r="L42" s="238"/>
+      <c r="M42" s="238"/>
+      <c r="N42" s="238"/>
+      <c r="O42" s="238"/>
+      <c r="P42" s="239"/>
     </row>
     <row r="43" spans="2:19" x14ac:dyDescent="0.3">
-      <c r="B43" s="255"/>
-      <c r="C43" s="276"/>
-      <c r="D43" s="276"/>
-      <c r="E43" s="276"/>
-      <c r="F43" s="276"/>
-      <c r="G43" s="276"/>
-      <c r="H43" s="276"/>
-      <c r="I43" s="276"/>
-      <c r="J43" s="276"/>
-      <c r="K43" s="276"/>
-      <c r="L43" s="276"/>
-      <c r="M43" s="276"/>
-      <c r="N43" s="276"/>
-      <c r="O43" s="276"/>
-      <c r="P43" s="277"/>
+      <c r="B43" s="240"/>
+      <c r="C43" s="241"/>
+      <c r="D43" s="241"/>
+      <c r="E43" s="241"/>
+      <c r="F43" s="241"/>
+      <c r="G43" s="241"/>
+      <c r="H43" s="241"/>
+      <c r="I43" s="241"/>
+      <c r="J43" s="241"/>
+      <c r="K43" s="241"/>
+      <c r="L43" s="241"/>
+      <c r="M43" s="241"/>
+      <c r="N43" s="241"/>
+      <c r="O43" s="241"/>
+      <c r="P43" s="242"/>
     </row>
     <row r="44" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B44" s="42"/>
@@ -57000,33 +57012,33 @@
       <c r="O51" s="126"/>
     </row>
     <row r="52" spans="2:19" ht="28.8" x14ac:dyDescent="0.55000000000000004">
-      <c r="B52" s="339" t="s">
+      <c r="B52" s="347" t="s">
         <v>195</v>
       </c>
-      <c r="C52" s="340"/>
-      <c r="D52" s="340"/>
-      <c r="E52" s="340"/>
-      <c r="F52" s="340"/>
-      <c r="G52" s="340"/>
-      <c r="H52" s="340"/>
-      <c r="I52" s="340"/>
-      <c r="J52" s="340"/>
-      <c r="K52" s="340"/>
-      <c r="L52" s="340"/>
-      <c r="M52" s="340"/>
-      <c r="N52" s="340"/>
-      <c r="O52" s="340"/>
-      <c r="P52" s="340"/>
-      <c r="Q52" s="341"/>
+      <c r="C52" s="348"/>
+      <c r="D52" s="348"/>
+      <c r="E52" s="348"/>
+      <c r="F52" s="348"/>
+      <c r="G52" s="348"/>
+      <c r="H52" s="348"/>
+      <c r="I52" s="348"/>
+      <c r="J52" s="348"/>
+      <c r="K52" s="348"/>
+      <c r="L52" s="348"/>
+      <c r="M52" s="348"/>
+      <c r="N52" s="348"/>
+      <c r="O52" s="348"/>
+      <c r="P52" s="348"/>
+      <c r="Q52" s="349"/>
     </row>
     <row r="53" spans="2:19" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B53" s="97" t="s">
         <v>1</v>
       </c>
-      <c r="C53" s="243" t="s">
+      <c r="C53" s="230" t="s">
         <v>2</v>
       </c>
-      <c r="D53" s="243"/>
+      <c r="D53" s="230"/>
       <c r="E53" s="120" t="s">
         <v>3</v>
       </c>
@@ -57071,10 +57083,10 @@
       </c>
     </row>
     <row r="54" spans="2:19" ht="40.950000000000003" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B54" s="273" t="s">
+      <c r="B54" s="247" t="s">
         <v>196</v>
       </c>
-      <c r="C54" s="338" t="s">
+      <c r="C54" s="332" t="s">
         <v>180</v>
       </c>
       <c r="D54" s="53" t="s">
@@ -57127,8 +57139,8 @@
       </c>
     </row>
     <row r="55" spans="2:19" ht="42" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B55" s="273"/>
-      <c r="C55" s="338"/>
+      <c r="B55" s="247"/>
+      <c r="C55" s="332"/>
       <c r="D55" s="53" t="s">
         <v>24</v>
       </c>
@@ -57179,34 +57191,34 @@
       </c>
     </row>
     <row r="56" spans="2:19" ht="28.8" x14ac:dyDescent="0.55000000000000004">
-      <c r="B56" s="339" t="s">
+      <c r="B56" s="347" t="s">
         <v>198</v>
       </c>
-      <c r="C56" s="340"/>
-      <c r="D56" s="340"/>
-      <c r="E56" s="340"/>
-      <c r="F56" s="340"/>
-      <c r="G56" s="340"/>
-      <c r="H56" s="340"/>
-      <c r="I56" s="340"/>
-      <c r="J56" s="340"/>
-      <c r="K56" s="340"/>
-      <c r="L56" s="340"/>
-      <c r="M56" s="340"/>
-      <c r="N56" s="340"/>
-      <c r="O56" s="340"/>
-      <c r="P56" s="340"/>
-      <c r="Q56" s="341"/>
+      <c r="C56" s="348"/>
+      <c r="D56" s="348"/>
+      <c r="E56" s="348"/>
+      <c r="F56" s="348"/>
+      <c r="G56" s="348"/>
+      <c r="H56" s="348"/>
+      <c r="I56" s="348"/>
+      <c r="J56" s="348"/>
+      <c r="K56" s="348"/>
+      <c r="L56" s="348"/>
+      <c r="M56" s="348"/>
+      <c r="N56" s="348"/>
+      <c r="O56" s="348"/>
+      <c r="P56" s="348"/>
+      <c r="Q56" s="349"/>
       <c r="S56" s="53"/>
     </row>
     <row r="57" spans="2:19" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B57" s="97" t="s">
         <v>1</v>
       </c>
-      <c r="C57" s="243" t="s">
+      <c r="C57" s="230" t="s">
         <v>2</v>
       </c>
-      <c r="D57" s="243"/>
+      <c r="D57" s="230"/>
       <c r="E57" s="120" t="s">
         <v>3</v>
       </c>
@@ -57249,10 +57261,10 @@
       <c r="S57" s="53"/>
     </row>
     <row r="58" spans="2:19" ht="28.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B58" s="273" t="s">
+      <c r="B58" s="247" t="s">
         <v>79</v>
       </c>
-      <c r="C58" s="338" t="s">
+      <c r="C58" s="332" t="s">
         <v>180</v>
       </c>
       <c r="D58" s="53" t="s">
@@ -57297,7 +57309,7 @@
       <c r="P58" s="53" t="s">
         <v>64</v>
       </c>
-      <c r="Q58" s="347" t="s">
+      <c r="Q58" s="343" t="s">
         <v>199</v>
       </c>
       <c r="S58" s="53" t="s">
@@ -57305,8 +57317,8 @@
       </c>
     </row>
     <row r="59" spans="2:19" x14ac:dyDescent="0.3">
-      <c r="B59" s="273"/>
-      <c r="C59" s="338"/>
+      <c r="B59" s="247"/>
+      <c r="C59" s="332"/>
       <c r="D59" s="53" t="s">
         <v>24</v>
       </c>
@@ -57349,40 +57361,40 @@
       <c r="P59" s="53" t="s">
         <v>64</v>
       </c>
-      <c r="Q59" s="348"/>
+      <c r="Q59" s="344"/>
       <c r="S59" s="53" t="s">
         <v>200</v>
       </c>
     </row>
     <row r="60" spans="2:19" ht="28.8" x14ac:dyDescent="0.55000000000000004">
-      <c r="B60" s="344" t="s">
+      <c r="B60" s="335" t="s">
         <v>201</v>
       </c>
-      <c r="C60" s="332"/>
-      <c r="D60" s="332"/>
-      <c r="E60" s="332"/>
-      <c r="F60" s="332"/>
-      <c r="G60" s="332"/>
-      <c r="H60" s="332"/>
-      <c r="I60" s="332"/>
-      <c r="J60" s="332"/>
-      <c r="K60" s="332"/>
-      <c r="L60" s="332"/>
-      <c r="M60" s="332"/>
-      <c r="N60" s="332"/>
-      <c r="O60" s="332"/>
-      <c r="P60" s="332"/>
-      <c r="Q60" s="345"/>
+      <c r="C60" s="336"/>
+      <c r="D60" s="336"/>
+      <c r="E60" s="336"/>
+      <c r="F60" s="336"/>
+      <c r="G60" s="336"/>
+      <c r="H60" s="336"/>
+      <c r="I60" s="336"/>
+      <c r="J60" s="336"/>
+      <c r="K60" s="336"/>
+      <c r="L60" s="336"/>
+      <c r="M60" s="336"/>
+      <c r="N60" s="336"/>
+      <c r="O60" s="336"/>
+      <c r="P60" s="336"/>
+      <c r="Q60" s="338"/>
       <c r="S60" s="53"/>
     </row>
     <row r="61" spans="2:19" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B61" s="109" t="s">
         <v>1</v>
       </c>
-      <c r="C61" s="245" t="s">
+      <c r="C61" s="318" t="s">
         <v>2</v>
       </c>
-      <c r="D61" s="245"/>
+      <c r="D61" s="318"/>
       <c r="E61" s="8" t="s">
         <v>3</v>
       </c>
@@ -57425,10 +57437,10 @@
       <c r="S61" s="53"/>
     </row>
     <row r="62" spans="2:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B62" s="346" t="s">
+      <c r="B62" s="342" t="s">
         <v>202</v>
       </c>
-      <c r="C62" s="338" t="s">
+      <c r="C62" s="332" t="s">
         <v>180</v>
       </c>
       <c r="D62" s="53" t="s">
@@ -57473,7 +57485,7 @@
       <c r="P62" s="53" t="s">
         <v>64</v>
       </c>
-      <c r="Q62" s="347" t="s">
+      <c r="Q62" s="343" t="s">
         <v>199</v>
       </c>
       <c r="S62" s="53" t="s">
@@ -57481,8 +57493,8 @@
       </c>
     </row>
     <row r="63" spans="2:19" x14ac:dyDescent="0.3">
-      <c r="B63" s="346"/>
-      <c r="C63" s="338"/>
+      <c r="B63" s="342"/>
+      <c r="C63" s="332"/>
       <c r="D63" s="53" t="s">
         <v>24</v>
       </c>
@@ -57525,40 +57537,40 @@
       <c r="P63" s="53" t="s">
         <v>64</v>
       </c>
-      <c r="Q63" s="348"/>
+      <c r="Q63" s="344"/>
       <c r="S63" s="53" t="s">
         <v>200</v>
       </c>
     </row>
     <row r="64" spans="2:19" ht="28.8" x14ac:dyDescent="0.55000000000000004">
-      <c r="B64" s="344" t="s">
+      <c r="B64" s="335" t="s">
         <v>203</v>
       </c>
-      <c r="C64" s="332"/>
-      <c r="D64" s="332"/>
-      <c r="E64" s="332"/>
-      <c r="F64" s="332"/>
-      <c r="G64" s="332"/>
-      <c r="H64" s="332"/>
-      <c r="I64" s="332"/>
-      <c r="J64" s="332"/>
-      <c r="K64" s="332"/>
-      <c r="L64" s="332"/>
-      <c r="M64" s="332"/>
-      <c r="N64" s="332"/>
-      <c r="O64" s="332"/>
-      <c r="P64" s="332"/>
-      <c r="Q64" s="345"/>
+      <c r="C64" s="336"/>
+      <c r="D64" s="336"/>
+      <c r="E64" s="336"/>
+      <c r="F64" s="336"/>
+      <c r="G64" s="336"/>
+      <c r="H64" s="336"/>
+      <c r="I64" s="336"/>
+      <c r="J64" s="336"/>
+      <c r="K64" s="336"/>
+      <c r="L64" s="336"/>
+      <c r="M64" s="336"/>
+      <c r="N64" s="336"/>
+      <c r="O64" s="336"/>
+      <c r="P64" s="336"/>
+      <c r="Q64" s="338"/>
       <c r="S64" s="53"/>
     </row>
     <row r="65" spans="2:19" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B65" s="109" t="s">
         <v>1</v>
       </c>
-      <c r="C65" s="245" t="s">
+      <c r="C65" s="318" t="s">
         <v>2</v>
       </c>
-      <c r="D65" s="245"/>
+      <c r="D65" s="318"/>
       <c r="E65" s="8" t="s">
         <v>3</v>
       </c>
@@ -57601,10 +57613,10 @@
       <c r="S65" s="53"/>
     </row>
     <row r="66" spans="2:19" x14ac:dyDescent="0.3">
-      <c r="B66" s="346" t="s">
+      <c r="B66" s="342" t="s">
         <v>204</v>
       </c>
-      <c r="C66" s="338" t="s">
+      <c r="C66" s="332" t="s">
         <v>180</v>
       </c>
       <c r="D66" s="53" t="s">
@@ -57649,7 +57661,7 @@
       <c r="P66" s="53" t="s">
         <v>64</v>
       </c>
-      <c r="Q66" s="349" t="s">
+      <c r="Q66" s="340" t="s">
         <v>205</v>
       </c>
       <c r="S66" s="53" t="s">
@@ -57657,8 +57669,8 @@
       </c>
     </row>
     <row r="67" spans="2:19" x14ac:dyDescent="0.3">
-      <c r="B67" s="346"/>
-      <c r="C67" s="338"/>
+      <c r="B67" s="342"/>
+      <c r="C67" s="332"/>
       <c r="D67" s="53" t="s">
         <v>24</v>
       </c>
@@ -57701,40 +57713,40 @@
       <c r="P67" s="53" t="s">
         <v>64</v>
       </c>
-      <c r="Q67" s="350"/>
+      <c r="Q67" s="345"/>
       <c r="S67" s="53" t="s">
         <v>200</v>
       </c>
     </row>
     <row r="68" spans="2:19" ht="28.8" x14ac:dyDescent="0.55000000000000004">
-      <c r="B68" s="344" t="s">
+      <c r="B68" s="335" t="s">
         <v>206</v>
       </c>
-      <c r="C68" s="332"/>
-      <c r="D68" s="332"/>
-      <c r="E68" s="332"/>
-      <c r="F68" s="332"/>
-      <c r="G68" s="332"/>
-      <c r="H68" s="332"/>
-      <c r="I68" s="332"/>
-      <c r="J68" s="332"/>
-      <c r="K68" s="332"/>
-      <c r="L68" s="332"/>
-      <c r="M68" s="332"/>
-      <c r="N68" s="332"/>
-      <c r="O68" s="332"/>
-      <c r="P68" s="332"/>
-      <c r="Q68" s="345"/>
+      <c r="C68" s="336"/>
+      <c r="D68" s="336"/>
+      <c r="E68" s="336"/>
+      <c r="F68" s="336"/>
+      <c r="G68" s="336"/>
+      <c r="H68" s="336"/>
+      <c r="I68" s="336"/>
+      <c r="J68" s="336"/>
+      <c r="K68" s="336"/>
+      <c r="L68" s="336"/>
+      <c r="M68" s="336"/>
+      <c r="N68" s="336"/>
+      <c r="O68" s="336"/>
+      <c r="P68" s="336"/>
+      <c r="Q68" s="338"/>
       <c r="S68" s="53"/>
     </row>
     <row r="69" spans="2:19" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B69" s="109" t="s">
         <v>1</v>
       </c>
-      <c r="C69" s="245" t="s">
+      <c r="C69" s="318" t="s">
         <v>2</v>
       </c>
-      <c r="D69" s="245"/>
+      <c r="D69" s="318"/>
       <c r="E69" s="8" t="s">
         <v>3</v>
       </c>
@@ -57777,10 +57789,10 @@
       <c r="S69" s="53"/>
     </row>
     <row r="70" spans="2:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B70" s="273" t="s">
+      <c r="B70" s="247" t="s">
         <v>207</v>
       </c>
-      <c r="C70" s="338" t="s">
+      <c r="C70" s="332" t="s">
         <v>180</v>
       </c>
       <c r="D70" s="53" t="s">
@@ -57825,7 +57837,7 @@
       <c r="P70" s="53" t="s">
         <v>60</v>
       </c>
-      <c r="Q70" s="349" t="s">
+      <c r="Q70" s="340" t="s">
         <v>205</v>
       </c>
       <c r="S70" s="53" t="s">
@@ -57833,8 +57845,8 @@
       </c>
     </row>
     <row r="71" spans="2:19" x14ac:dyDescent="0.3">
-      <c r="B71" s="273"/>
-      <c r="C71" s="338"/>
+      <c r="B71" s="247"/>
+      <c r="C71" s="332"/>
       <c r="D71" s="53" t="s">
         <v>24</v>
       </c>
@@ -57877,39 +57889,39 @@
       <c r="P71" s="53" t="s">
         <v>60</v>
       </c>
-      <c r="Q71" s="351"/>
+      <c r="Q71" s="346"/>
       <c r="S71" s="53" t="s">
         <v>200</v>
       </c>
     </row>
     <row r="72" spans="2:19" ht="28.8" x14ac:dyDescent="0.55000000000000004">
-      <c r="B72" s="344" t="s">
+      <c r="B72" s="335" t="s">
         <v>208</v>
       </c>
-      <c r="C72" s="332"/>
-      <c r="D72" s="332"/>
-      <c r="E72" s="332"/>
-      <c r="F72" s="332"/>
-      <c r="G72" s="332"/>
-      <c r="H72" s="332"/>
-      <c r="I72" s="332"/>
-      <c r="J72" s="332"/>
-      <c r="K72" s="332"/>
-      <c r="L72" s="332"/>
-      <c r="M72" s="332"/>
-      <c r="N72" s="330"/>
-      <c r="O72" s="332"/>
-      <c r="P72" s="332"/>
-      <c r="Q72" s="345"/>
+      <c r="C72" s="336"/>
+      <c r="D72" s="336"/>
+      <c r="E72" s="336"/>
+      <c r="F72" s="336"/>
+      <c r="G72" s="336"/>
+      <c r="H72" s="336"/>
+      <c r="I72" s="336"/>
+      <c r="J72" s="336"/>
+      <c r="K72" s="336"/>
+      <c r="L72" s="336"/>
+      <c r="M72" s="336"/>
+      <c r="N72" s="337"/>
+      <c r="O72" s="336"/>
+      <c r="P72" s="336"/>
+      <c r="Q72" s="338"/>
     </row>
     <row r="73" spans="2:19" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B73" s="109" t="s">
         <v>1</v>
       </c>
-      <c r="C73" s="245" t="s">
+      <c r="C73" s="318" t="s">
         <v>2</v>
       </c>
-      <c r="D73" s="245"/>
+      <c r="D73" s="318"/>
       <c r="E73" s="8" t="s">
         <v>3</v>
       </c>
@@ -57951,10 +57963,10 @@
       </c>
     </row>
     <row r="74" spans="2:19" x14ac:dyDescent="0.3">
-      <c r="B74" s="273" t="s">
+      <c r="B74" s="247" t="s">
         <v>209</v>
       </c>
-      <c r="C74" s="338" t="s">
+      <c r="C74" s="332" t="s">
         <v>180</v>
       </c>
       <c r="D74" s="53" t="s">
@@ -57999,7 +58011,7 @@
       <c r="P74" s="53" t="s">
         <v>64</v>
       </c>
-      <c r="Q74" s="349" t="s">
+      <c r="Q74" s="340" t="s">
         <v>205</v>
       </c>
       <c r="S74" s="53" t="s">
@@ -58007,8 +58019,8 @@
       </c>
     </row>
     <row r="75" spans="2:19" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B75" s="354"/>
-      <c r="C75" s="353"/>
+      <c r="B75" s="339"/>
+      <c r="C75" s="333"/>
       <c r="D75" s="90" t="s">
         <v>24</v>
       </c>
@@ -58051,7 +58063,7 @@
       <c r="P75" s="90" t="s">
         <v>64</v>
       </c>
-      <c r="Q75" s="352"/>
+      <c r="Q75" s="341"/>
       <c r="S75" s="53" t="s">
         <v>200</v>
       </c>
@@ -58059,10 +58071,10 @@
     <row r="76" spans="2:19" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B76" s="126"/>
       <c r="C76" s="126"/>
-      <c r="D76" s="325" t="s">
+      <c r="D76" s="334" t="s">
         <v>210</v>
       </c>
-      <c r="E76" s="325"/>
+      <c r="E76" s="334"/>
       <c r="F76" s="126"/>
       <c r="G76" s="126"/>
       <c r="H76" s="126"/>
@@ -58078,133 +58090,133 @@
       <c r="R76" s="126"/>
     </row>
     <row r="77" spans="2:19" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B77" s="278" t="s">
+      <c r="B77" s="293" t="s">
         <v>34</v>
       </c>
-      <c r="C77" s="279"/>
-      <c r="D77" s="279"/>
-      <c r="E77" s="279"/>
-      <c r="F77" s="279"/>
-      <c r="G77" s="279"/>
-      <c r="H77" s="279"/>
-      <c r="I77" s="279"/>
-      <c r="J77" s="279"/>
-      <c r="K77" s="279"/>
-      <c r="L77" s="279"/>
-      <c r="M77" s="279"/>
-      <c r="N77" s="279"/>
-      <c r="O77" s="279"/>
-      <c r="P77" s="279"/>
-      <c r="Q77" s="279"/>
-      <c r="R77" s="280"/>
+      <c r="C77" s="294"/>
+      <c r="D77" s="294"/>
+      <c r="E77" s="294"/>
+      <c r="F77" s="294"/>
+      <c r="G77" s="294"/>
+      <c r="H77" s="294"/>
+      <c r="I77" s="294"/>
+      <c r="J77" s="294"/>
+      <c r="K77" s="294"/>
+      <c r="L77" s="294"/>
+      <c r="M77" s="294"/>
+      <c r="N77" s="294"/>
+      <c r="O77" s="294"/>
+      <c r="P77" s="294"/>
+      <c r="Q77" s="294"/>
+      <c r="R77" s="295"/>
     </row>
     <row r="78" spans="2:19" x14ac:dyDescent="0.3">
-      <c r="B78" s="281" t="s">
+      <c r="B78" s="296" t="s">
         <v>35</v>
       </c>
-      <c r="C78" s="233"/>
-      <c r="D78" s="233"/>
-      <c r="E78" s="233"/>
-      <c r="F78" s="233"/>
-      <c r="G78" s="233"/>
-      <c r="H78" s="233"/>
-      <c r="I78" s="233"/>
-      <c r="J78" s="233"/>
-      <c r="K78" s="233"/>
-      <c r="L78" s="233"/>
-      <c r="M78" s="233"/>
-      <c r="N78" s="233"/>
-      <c r="O78" s="233"/>
-      <c r="P78" s="233"/>
-      <c r="Q78" s="233"/>
-      <c r="R78" s="282"/>
+      <c r="C78" s="297"/>
+      <c r="D78" s="297"/>
+      <c r="E78" s="297"/>
+      <c r="F78" s="297"/>
+      <c r="G78" s="297"/>
+      <c r="H78" s="297"/>
+      <c r="I78" s="297"/>
+      <c r="J78" s="297"/>
+      <c r="K78" s="297"/>
+      <c r="L78" s="297"/>
+      <c r="M78" s="297"/>
+      <c r="N78" s="297"/>
+      <c r="O78" s="297"/>
+      <c r="P78" s="297"/>
+      <c r="Q78" s="297"/>
+      <c r="R78" s="298"/>
     </row>
     <row r="79" spans="2:19" x14ac:dyDescent="0.3">
-      <c r="B79" s="281"/>
-      <c r="C79" s="233"/>
-      <c r="D79" s="233"/>
-      <c r="E79" s="233"/>
-      <c r="F79" s="233"/>
-      <c r="G79" s="233"/>
-      <c r="H79" s="233"/>
-      <c r="I79" s="233"/>
-      <c r="J79" s="233"/>
-      <c r="K79" s="233"/>
-      <c r="L79" s="233"/>
-      <c r="M79" s="233"/>
-      <c r="N79" s="233"/>
-      <c r="O79" s="233"/>
-      <c r="P79" s="233"/>
-      <c r="Q79" s="233"/>
-      <c r="R79" s="282"/>
+      <c r="B79" s="296"/>
+      <c r="C79" s="297"/>
+      <c r="D79" s="297"/>
+      <c r="E79" s="297"/>
+      <c r="F79" s="297"/>
+      <c r="G79" s="297"/>
+      <c r="H79" s="297"/>
+      <c r="I79" s="297"/>
+      <c r="J79" s="297"/>
+      <c r="K79" s="297"/>
+      <c r="L79" s="297"/>
+      <c r="M79" s="297"/>
+      <c r="N79" s="297"/>
+      <c r="O79" s="297"/>
+      <c r="P79" s="297"/>
+      <c r="Q79" s="297"/>
+      <c r="R79" s="298"/>
     </row>
     <row r="80" spans="2:19" x14ac:dyDescent="0.3">
-      <c r="B80" s="281"/>
-      <c r="C80" s="233"/>
-      <c r="D80" s="233"/>
-      <c r="E80" s="233"/>
-      <c r="F80" s="233"/>
-      <c r="G80" s="233"/>
-      <c r="H80" s="233"/>
-      <c r="I80" s="233"/>
-      <c r="J80" s="233"/>
-      <c r="K80" s="233"/>
-      <c r="L80" s="233"/>
-      <c r="M80" s="233"/>
-      <c r="N80" s="233"/>
-      <c r="O80" s="233"/>
-      <c r="P80" s="233"/>
-      <c r="Q80" s="233"/>
-      <c r="R80" s="282"/>
+      <c r="B80" s="296"/>
+      <c r="C80" s="297"/>
+      <c r="D80" s="297"/>
+      <c r="E80" s="297"/>
+      <c r="F80" s="297"/>
+      <c r="G80" s="297"/>
+      <c r="H80" s="297"/>
+      <c r="I80" s="297"/>
+      <c r="J80" s="297"/>
+      <c r="K80" s="297"/>
+      <c r="L80" s="297"/>
+      <c r="M80" s="297"/>
+      <c r="N80" s="297"/>
+      <c r="O80" s="297"/>
+      <c r="P80" s="297"/>
+      <c r="Q80" s="297"/>
+      <c r="R80" s="298"/>
     </row>
     <row r="81" spans="2:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B81" s="283"/>
-      <c r="C81" s="284"/>
-      <c r="D81" s="284"/>
-      <c r="E81" s="284"/>
-      <c r="F81" s="284"/>
-      <c r="G81" s="284"/>
-      <c r="H81" s="284"/>
-      <c r="I81" s="284"/>
-      <c r="J81" s="284"/>
-      <c r="K81" s="284"/>
-      <c r="L81" s="284"/>
-      <c r="M81" s="284"/>
-      <c r="N81" s="284"/>
-      <c r="O81" s="284"/>
-      <c r="P81" s="284"/>
-      <c r="Q81" s="284"/>
-      <c r="R81" s="285"/>
+      <c r="B81" s="299"/>
+      <c r="C81" s="300"/>
+      <c r="D81" s="300"/>
+      <c r="E81" s="300"/>
+      <c r="F81" s="300"/>
+      <c r="G81" s="300"/>
+      <c r="H81" s="300"/>
+      <c r="I81" s="300"/>
+      <c r="J81" s="300"/>
+      <c r="K81" s="300"/>
+      <c r="L81" s="300"/>
+      <c r="M81" s="300"/>
+      <c r="N81" s="300"/>
+      <c r="O81" s="300"/>
+      <c r="P81" s="300"/>
+      <c r="Q81" s="300"/>
+      <c r="R81" s="301"/>
     </row>
     <row r="89" spans="2:18" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B89" s="286" t="s">
+      <c r="B89" s="302" t="s">
         <v>211</v>
       </c>
-      <c r="C89" s="286"/>
-      <c r="D89" s="286"/>
-      <c r="E89" s="286"/>
-      <c r="F89" s="286"/>
-      <c r="G89" s="286"/>
-      <c r="H89" s="286"/>
-      <c r="I89" s="286"/>
-      <c r="J89" s="286"/>
-      <c r="K89" s="286"/>
-      <c r="L89" s="286"/>
-      <c r="M89" s="286"/>
-      <c r="N89" s="286"/>
-      <c r="O89" s="286"/>
-      <c r="P89" s="286"/>
-      <c r="Q89" s="286"/>
-      <c r="R89" s="286"/>
+      <c r="C89" s="302"/>
+      <c r="D89" s="302"/>
+      <c r="E89" s="302"/>
+      <c r="F89" s="302"/>
+      <c r="G89" s="302"/>
+      <c r="H89" s="302"/>
+      <c r="I89" s="302"/>
+      <c r="J89" s="302"/>
+      <c r="K89" s="302"/>
+      <c r="L89" s="302"/>
+      <c r="M89" s="302"/>
+      <c r="N89" s="302"/>
+      <c r="O89" s="302"/>
+      <c r="P89" s="302"/>
+      <c r="Q89" s="302"/>
+      <c r="R89" s="302"/>
     </row>
     <row r="90" spans="2:18" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B90" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C90" s="245" t="s">
+      <c r="C90" s="318" t="s">
         <v>2</v>
       </c>
-      <c r="D90" s="245"/>
+      <c r="D90" s="318"/>
       <c r="E90" s="127" t="s">
         <v>135</v>
       </c>
@@ -58241,16 +58253,16 @@
       <c r="P90" s="124" t="s">
         <v>127</v>
       </c>
-      <c r="Q90" s="243" t="s">
+      <c r="Q90" s="230" t="s">
         <v>38</v>
       </c>
-      <c r="R90" s="243"/>
+      <c r="R90" s="230"/>
     </row>
     <row r="91" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="B91" s="239" t="s">
+      <c r="B91" s="227" t="s">
         <v>99</v>
       </c>
-      <c r="C91" s="225" t="s">
+      <c r="C91" s="252" t="s">
         <v>180</v>
       </c>
       <c r="D91" s="53" t="s">
@@ -58294,14 +58306,14 @@
       <c r="P91" s="53" t="s">
         <v>167</v>
       </c>
-      <c r="Q91" s="240" t="s">
+      <c r="Q91" s="259" t="s">
         <v>47</v>
       </c>
-      <c r="R91" s="240"/>
+      <c r="R91" s="259"/>
     </row>
     <row r="92" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="B92" s="239"/>
-      <c r="C92" s="225"/>
+      <c r="B92" s="227"/>
+      <c r="C92" s="252"/>
       <c r="D92" s="53" t="s">
         <v>24</v>
       </c>
@@ -58343,8 +58355,8 @@
       <c r="P92" s="53" t="s">
         <v>167</v>
       </c>
-      <c r="Q92" s="240"/>
-      <c r="R92" s="240"/>
+      <c r="Q92" s="259"/>
+      <c r="R92" s="259"/>
     </row>
     <row r="94" spans="2:18" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B94" s="5" t="s">
@@ -58368,82 +58380,82 @@
       <c r="R94" s="6"/>
     </row>
     <row r="95" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="B95" s="241" t="s">
+      <c r="B95" s="263" t="s">
         <v>35</v>
       </c>
-      <c r="C95" s="241"/>
-      <c r="D95" s="241"/>
-      <c r="E95" s="241"/>
-      <c r="F95" s="241"/>
-      <c r="G95" s="241"/>
-      <c r="H95" s="241"/>
-      <c r="I95" s="241"/>
-      <c r="J95" s="241"/>
-      <c r="K95" s="241"/>
-      <c r="L95" s="241"/>
-      <c r="M95" s="241"/>
-      <c r="N95" s="241"/>
-      <c r="O95" s="241"/>
-      <c r="P95" s="241"/>
-      <c r="Q95" s="241"/>
-      <c r="R95" s="241"/>
+      <c r="C95" s="263"/>
+      <c r="D95" s="263"/>
+      <c r="E95" s="263"/>
+      <c r="F95" s="263"/>
+      <c r="G95" s="263"/>
+      <c r="H95" s="263"/>
+      <c r="I95" s="263"/>
+      <c r="J95" s="263"/>
+      <c r="K95" s="263"/>
+      <c r="L95" s="263"/>
+      <c r="M95" s="263"/>
+      <c r="N95" s="263"/>
+      <c r="O95" s="263"/>
+      <c r="P95" s="263"/>
+      <c r="Q95" s="263"/>
+      <c r="R95" s="263"/>
     </row>
     <row r="96" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="B96" s="241"/>
-      <c r="C96" s="241"/>
-      <c r="D96" s="241"/>
-      <c r="E96" s="241"/>
-      <c r="F96" s="241"/>
-      <c r="G96" s="241"/>
-      <c r="H96" s="241"/>
-      <c r="I96" s="241"/>
-      <c r="J96" s="241"/>
-      <c r="K96" s="241"/>
-      <c r="L96" s="241"/>
-      <c r="M96" s="241"/>
-      <c r="N96" s="241"/>
-      <c r="O96" s="241"/>
-      <c r="P96" s="241"/>
-      <c r="Q96" s="241"/>
-      <c r="R96" s="241"/>
+      <c r="B96" s="263"/>
+      <c r="C96" s="263"/>
+      <c r="D96" s="263"/>
+      <c r="E96" s="263"/>
+      <c r="F96" s="263"/>
+      <c r="G96" s="263"/>
+      <c r="H96" s="263"/>
+      <c r="I96" s="263"/>
+      <c r="J96" s="263"/>
+      <c r="K96" s="263"/>
+      <c r="L96" s="263"/>
+      <c r="M96" s="263"/>
+      <c r="N96" s="263"/>
+      <c r="O96" s="263"/>
+      <c r="P96" s="263"/>
+      <c r="Q96" s="263"/>
+      <c r="R96" s="263"/>
     </row>
     <row r="97" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="B97" s="241"/>
-      <c r="C97" s="241"/>
-      <c r="D97" s="241"/>
-      <c r="E97" s="241"/>
-      <c r="F97" s="241"/>
-      <c r="G97" s="241"/>
-      <c r="H97" s="241"/>
-      <c r="I97" s="241"/>
-      <c r="J97" s="241"/>
-      <c r="K97" s="241"/>
-      <c r="L97" s="241"/>
-      <c r="M97" s="241"/>
-      <c r="N97" s="241"/>
-      <c r="O97" s="241"/>
-      <c r="P97" s="241"/>
-      <c r="Q97" s="241"/>
-      <c r="R97" s="241"/>
+      <c r="B97" s="263"/>
+      <c r="C97" s="263"/>
+      <c r="D97" s="263"/>
+      <c r="E97" s="263"/>
+      <c r="F97" s="263"/>
+      <c r="G97" s="263"/>
+      <c r="H97" s="263"/>
+      <c r="I97" s="263"/>
+      <c r="J97" s="263"/>
+      <c r="K97" s="263"/>
+      <c r="L97" s="263"/>
+      <c r="M97" s="263"/>
+      <c r="N97" s="263"/>
+      <c r="O97" s="263"/>
+      <c r="P97" s="263"/>
+      <c r="Q97" s="263"/>
+      <c r="R97" s="263"/>
     </row>
     <row r="98" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="B98" s="241"/>
-      <c r="C98" s="241"/>
-      <c r="D98" s="241"/>
-      <c r="E98" s="241"/>
-      <c r="F98" s="241"/>
-      <c r="G98" s="241"/>
-      <c r="H98" s="241"/>
-      <c r="I98" s="241"/>
-      <c r="J98" s="241"/>
-      <c r="K98" s="241"/>
-      <c r="L98" s="241"/>
-      <c r="M98" s="241"/>
-      <c r="N98" s="241"/>
-      <c r="O98" s="241"/>
-      <c r="P98" s="241"/>
-      <c r="Q98" s="241"/>
-      <c r="R98" s="241"/>
+      <c r="B98" s="263"/>
+      <c r="C98" s="263"/>
+      <c r="D98" s="263"/>
+      <c r="E98" s="263"/>
+      <c r="F98" s="263"/>
+      <c r="G98" s="263"/>
+      <c r="H98" s="263"/>
+      <c r="I98" s="263"/>
+      <c r="J98" s="263"/>
+      <c r="K98" s="263"/>
+      <c r="L98" s="263"/>
+      <c r="M98" s="263"/>
+      <c r="N98" s="263"/>
+      <c r="O98" s="263"/>
+      <c r="P98" s="263"/>
+      <c r="Q98" s="263"/>
+      <c r="R98" s="263"/>
     </row>
     <row r="99" spans="2:18" x14ac:dyDescent="0.3">
       <c r="B99" s="122"/>
@@ -58465,34 +58477,34 @@
       <c r="R99" s="122"/>
     </row>
     <row r="100" spans="2:18" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B100" s="249" t="s">
+      <c r="B100" s="228" t="s">
         <v>214</v>
       </c>
-      <c r="C100" s="244"/>
-      <c r="D100" s="244"/>
-      <c r="E100" s="244"/>
-      <c r="F100" s="244"/>
-      <c r="G100" s="244"/>
-      <c r="H100" s="244"/>
-      <c r="I100" s="244"/>
-      <c r="J100" s="244"/>
-      <c r="K100" s="244"/>
-      <c r="L100" s="244"/>
-      <c r="M100" s="244"/>
-      <c r="N100" s="244"/>
-      <c r="O100" s="244"/>
-      <c r="P100" s="244"/>
-      <c r="Q100" s="244"/>
-      <c r="R100" s="244"/>
+      <c r="C100" s="229"/>
+      <c r="D100" s="229"/>
+      <c r="E100" s="229"/>
+      <c r="F100" s="229"/>
+      <c r="G100" s="229"/>
+      <c r="H100" s="229"/>
+      <c r="I100" s="229"/>
+      <c r="J100" s="229"/>
+      <c r="K100" s="229"/>
+      <c r="L100" s="229"/>
+      <c r="M100" s="229"/>
+      <c r="N100" s="229"/>
+      <c r="O100" s="229"/>
+      <c r="P100" s="229"/>
+      <c r="Q100" s="229"/>
+      <c r="R100" s="229"/>
     </row>
     <row r="101" spans="2:18" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B101" s="97" t="s">
         <v>1</v>
       </c>
-      <c r="C101" s="243" t="s">
+      <c r="C101" s="230" t="s">
         <v>2</v>
       </c>
-      <c r="D101" s="243"/>
+      <c r="D101" s="230"/>
       <c r="E101" s="8" t="s">
         <v>3</v>
       </c>
@@ -58537,10 +58549,10 @@
       </c>
     </row>
     <row r="102" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="B102" s="224" t="s">
+      <c r="B102" s="320" t="s">
         <v>108</v>
       </c>
-      <c r="C102" s="225" t="s">
+      <c r="C102" s="252" t="s">
         <v>180</v>
       </c>
       <c r="D102" s="53" t="s">
@@ -58592,8 +58604,8 @@
       </c>
     </row>
     <row r="103" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="B103" s="224"/>
-      <c r="C103" s="225"/>
+      <c r="B103" s="320"/>
+      <c r="C103" s="252"/>
       <c r="D103" s="53" t="s">
         <v>24</v>
       </c>
@@ -58643,10 +58655,10 @@
       </c>
     </row>
     <row r="104" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="B104" s="224" t="s">
+      <c r="B104" s="320" t="s">
         <v>175</v>
       </c>
-      <c r="C104" s="225" t="s">
+      <c r="C104" s="252" t="s">
         <v>180</v>
       </c>
       <c r="D104" s="53" t="s">
@@ -58699,8 +58711,8 @@
       </c>
     </row>
     <row r="105" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="B105" s="224"/>
-      <c r="C105" s="225"/>
+      <c r="B105" s="320"/>
+      <c r="C105" s="252"/>
       <c r="D105" s="53" t="s">
         <v>24</v>
       </c>
@@ -58752,6 +58764,57 @@
     </row>
   </sheetData>
   <mergeCells count="63">
+    <mergeCell ref="B15:B16"/>
+    <mergeCell ref="C15:C16"/>
+    <mergeCell ref="P33:Q33"/>
+    <mergeCell ref="B32:Q32"/>
+    <mergeCell ref="B18:P18"/>
+    <mergeCell ref="B19:P22"/>
+    <mergeCell ref="D8:E8"/>
+    <mergeCell ref="C10:D10"/>
+    <mergeCell ref="B11:B12"/>
+    <mergeCell ref="C11:C12"/>
+    <mergeCell ref="B13:B14"/>
+    <mergeCell ref="C13:C14"/>
+    <mergeCell ref="B9:P9"/>
+    <mergeCell ref="C33:D33"/>
+    <mergeCell ref="B54:B55"/>
+    <mergeCell ref="C54:C55"/>
+    <mergeCell ref="B102:B103"/>
+    <mergeCell ref="C102:C103"/>
+    <mergeCell ref="B100:R100"/>
+    <mergeCell ref="B56:Q56"/>
+    <mergeCell ref="B34:B35"/>
+    <mergeCell ref="C34:C35"/>
+    <mergeCell ref="B40:P43"/>
+    <mergeCell ref="B52:Q52"/>
+    <mergeCell ref="C53:D53"/>
+    <mergeCell ref="P34:Q36"/>
+    <mergeCell ref="C57:D57"/>
+    <mergeCell ref="B68:Q68"/>
+    <mergeCell ref="C69:D69"/>
+    <mergeCell ref="B70:B71"/>
+    <mergeCell ref="C70:C71"/>
+    <mergeCell ref="B66:B67"/>
+    <mergeCell ref="C66:C67"/>
+    <mergeCell ref="B58:B59"/>
+    <mergeCell ref="Q66:Q67"/>
+    <mergeCell ref="Q70:Q71"/>
+    <mergeCell ref="B64:Q64"/>
+    <mergeCell ref="C65:D65"/>
+    <mergeCell ref="Q58:Q59"/>
+    <mergeCell ref="C58:C59"/>
+    <mergeCell ref="B60:Q60"/>
+    <mergeCell ref="C61:D61"/>
+    <mergeCell ref="B62:B63"/>
+    <mergeCell ref="C62:C63"/>
+    <mergeCell ref="Q62:Q63"/>
+    <mergeCell ref="B72:Q72"/>
+    <mergeCell ref="C73:D73"/>
+    <mergeCell ref="B74:B75"/>
+    <mergeCell ref="C90:D90"/>
+    <mergeCell ref="Q90:R90"/>
+    <mergeCell ref="Q74:Q75"/>
     <mergeCell ref="C101:D101"/>
     <mergeCell ref="B104:B105"/>
     <mergeCell ref="C104:C105"/>
@@ -58760,61 +58823,10 @@
     <mergeCell ref="D76:E76"/>
     <mergeCell ref="B77:R77"/>
     <mergeCell ref="B78:R81"/>
-    <mergeCell ref="B72:Q72"/>
-    <mergeCell ref="C73:D73"/>
-    <mergeCell ref="B74:B75"/>
-    <mergeCell ref="C90:D90"/>
-    <mergeCell ref="Q90:R90"/>
     <mergeCell ref="B91:B92"/>
     <mergeCell ref="C91:C92"/>
     <mergeCell ref="Q91:R92"/>
-    <mergeCell ref="Q74:Q75"/>
     <mergeCell ref="B95:R98"/>
-    <mergeCell ref="C58:C59"/>
-    <mergeCell ref="B60:Q60"/>
-    <mergeCell ref="C61:D61"/>
-    <mergeCell ref="B62:B63"/>
-    <mergeCell ref="C62:C63"/>
-    <mergeCell ref="Q62:Q63"/>
-    <mergeCell ref="B66:B67"/>
-    <mergeCell ref="C66:C67"/>
-    <mergeCell ref="B58:B59"/>
-    <mergeCell ref="Q66:Q67"/>
-    <mergeCell ref="Q70:Q71"/>
-    <mergeCell ref="B64:Q64"/>
-    <mergeCell ref="C65:D65"/>
-    <mergeCell ref="Q58:Q59"/>
-    <mergeCell ref="C57:D57"/>
-    <mergeCell ref="B68:Q68"/>
-    <mergeCell ref="C69:D69"/>
-    <mergeCell ref="B70:B71"/>
-    <mergeCell ref="C70:C71"/>
-    <mergeCell ref="B56:Q56"/>
-    <mergeCell ref="B34:B35"/>
-    <mergeCell ref="C34:C35"/>
-    <mergeCell ref="B40:P43"/>
-    <mergeCell ref="B52:Q52"/>
-    <mergeCell ref="C53:D53"/>
-    <mergeCell ref="P34:Q36"/>
-    <mergeCell ref="C33:D33"/>
-    <mergeCell ref="B54:B55"/>
-    <mergeCell ref="C54:C55"/>
-    <mergeCell ref="B102:B103"/>
-    <mergeCell ref="C102:C103"/>
-    <mergeCell ref="B100:R100"/>
-    <mergeCell ref="D8:E8"/>
-    <mergeCell ref="C10:D10"/>
-    <mergeCell ref="B11:B12"/>
-    <mergeCell ref="C11:C12"/>
-    <mergeCell ref="B13:B14"/>
-    <mergeCell ref="C13:C14"/>
-    <mergeCell ref="B9:P9"/>
-    <mergeCell ref="B15:B16"/>
-    <mergeCell ref="C15:C16"/>
-    <mergeCell ref="P33:Q33"/>
-    <mergeCell ref="B32:Q32"/>
-    <mergeCell ref="B18:P18"/>
-    <mergeCell ref="B19:P22"/>
   </mergeCells>
   <phoneticPr fontId="12" alignment="center"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -58857,33 +58869,33 @@
   </cols>
   <sheetData>
     <row r="8" spans="2:19" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B8" s="249" t="s">
-        <v>215</v>
-      </c>
-      <c r="C8" s="244"/>
-      <c r="D8" s="244"/>
-      <c r="E8" s="244"/>
-      <c r="F8" s="244"/>
-      <c r="G8" s="244"/>
-      <c r="H8" s="244"/>
-      <c r="I8" s="244"/>
-      <c r="J8" s="244"/>
-      <c r="K8" s="244"/>
-      <c r="L8" s="244"/>
-      <c r="M8" s="244"/>
-      <c r="N8" s="244"/>
-      <c r="O8" s="244"/>
-      <c r="P8" s="244"/>
-      <c r="Q8" s="244"/>
+      <c r="B8" s="228" t="s">
+        <v>215</v>
+      </c>
+      <c r="C8" s="229"/>
+      <c r="D8" s="229"/>
+      <c r="E8" s="229"/>
+      <c r="F8" s="229"/>
+      <c r="G8" s="229"/>
+      <c r="H8" s="229"/>
+      <c r="I8" s="229"/>
+      <c r="J8" s="229"/>
+      <c r="K8" s="229"/>
+      <c r="L8" s="229"/>
+      <c r="M8" s="229"/>
+      <c r="N8" s="229"/>
+      <c r="O8" s="229"/>
+      <c r="P8" s="229"/>
+      <c r="Q8" s="229"/>
     </row>
     <row r="9" spans="2:19" ht="57.6" x14ac:dyDescent="0.3">
       <c r="B9" s="97" t="s">
         <v>1</v>
       </c>
-      <c r="C9" s="243" t="s">
+      <c r="C9" s="230" t="s">
         <v>2</v>
       </c>
-      <c r="D9" s="243"/>
+      <c r="D9" s="230"/>
       <c r="E9" s="120" t="s">
         <v>3</v>
       </c>
@@ -58925,10 +58937,10 @@
       </c>
     </row>
     <row r="10" spans="2:19" x14ac:dyDescent="0.3">
-      <c r="B10" s="238" t="s">
+      <c r="B10" s="231" t="s">
         <v>31</v>
       </c>
-      <c r="C10" s="239" t="s">
+      <c r="C10" s="227" t="s">
         <v>120</v>
       </c>
       <c r="D10" s="117" t="s">
@@ -58977,8 +58989,8 @@
       </c>
     </row>
     <row r="11" spans="2:19" x14ac:dyDescent="0.3">
-      <c r="B11" s="308"/>
-      <c r="C11" s="239"/>
+      <c r="B11" s="232"/>
+      <c r="C11" s="227"/>
       <c r="D11" s="117" t="s">
         <v>24</v>
       </c>
@@ -59025,34 +59037,34 @@
       </c>
     </row>
     <row r="12" spans="2:19" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B12" s="249" t="s">
+      <c r="B12" s="228" t="s">
         <v>217</v>
       </c>
-      <c r="C12" s="244"/>
-      <c r="D12" s="244"/>
-      <c r="E12" s="244"/>
-      <c r="F12" s="244"/>
-      <c r="G12" s="244"/>
-      <c r="H12" s="244"/>
-      <c r="I12" s="244"/>
-      <c r="J12" s="244"/>
-      <c r="K12" s="244"/>
-      <c r="L12" s="244"/>
-      <c r="M12" s="244"/>
-      <c r="N12" s="244"/>
-      <c r="O12" s="244"/>
-      <c r="P12" s="244"/>
-      <c r="Q12" s="244"/>
-      <c r="R12" s="244"/>
+      <c r="C12" s="229"/>
+      <c r="D12" s="229"/>
+      <c r="E12" s="229"/>
+      <c r="F12" s="229"/>
+      <c r="G12" s="229"/>
+      <c r="H12" s="229"/>
+      <c r="I12" s="229"/>
+      <c r="J12" s="229"/>
+      <c r="K12" s="229"/>
+      <c r="L12" s="229"/>
+      <c r="M12" s="229"/>
+      <c r="N12" s="229"/>
+      <c r="O12" s="229"/>
+      <c r="P12" s="229"/>
+      <c r="Q12" s="229"/>
+      <c r="R12" s="229"/>
     </row>
     <row r="13" spans="2:19" ht="57.6" x14ac:dyDescent="0.3">
       <c r="B13" s="97" t="s">
         <v>1</v>
       </c>
-      <c r="C13" s="243" t="s">
+      <c r="C13" s="230" t="s">
         <v>2</v>
       </c>
-      <c r="D13" s="243"/>
+      <c r="D13" s="230"/>
       <c r="E13" s="120" t="s">
         <v>3</v>
       </c>
@@ -59100,10 +59112,10 @@
       </c>
     </row>
     <row r="14" spans="2:19" x14ac:dyDescent="0.3">
-      <c r="B14" s="239" t="s">
+      <c r="B14" s="227" t="s">
         <v>31</v>
       </c>
-      <c r="C14" s="239" t="s">
+      <c r="C14" s="227" t="s">
         <v>180</v>
       </c>
       <c r="D14" s="117" t="s">
@@ -59158,8 +59170,8 @@
       </c>
     </row>
     <row r="15" spans="2:19" x14ac:dyDescent="0.3">
-      <c r="B15" s="239"/>
-      <c r="C15" s="239"/>
+      <c r="B15" s="227"/>
+      <c r="C15" s="227"/>
       <c r="D15" s="117" t="s">
         <v>24</v>
       </c>
@@ -59212,33 +59224,33 @@
       </c>
     </row>
     <row r="16" spans="2:19" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B16" s="359" t="s">
+      <c r="B16" s="235" t="s">
         <v>221</v>
       </c>
-      <c r="C16" s="360"/>
-      <c r="D16" s="360"/>
-      <c r="E16" s="360"/>
-      <c r="F16" s="360"/>
-      <c r="G16" s="360"/>
-      <c r="H16" s="360"/>
-      <c r="I16" s="360"/>
-      <c r="J16" s="360"/>
-      <c r="K16" s="360"/>
-      <c r="L16" s="360"/>
-      <c r="M16" s="360"/>
-      <c r="N16" s="360"/>
-      <c r="O16" s="360"/>
-      <c r="P16" s="360"/>
-      <c r="Q16" s="360"/>
+      <c r="C16" s="236"/>
+      <c r="D16" s="236"/>
+      <c r="E16" s="236"/>
+      <c r="F16" s="236"/>
+      <c r="G16" s="236"/>
+      <c r="H16" s="236"/>
+      <c r="I16" s="236"/>
+      <c r="J16" s="236"/>
+      <c r="K16" s="236"/>
+      <c r="L16" s="236"/>
+      <c r="M16" s="236"/>
+      <c r="N16" s="236"/>
+      <c r="O16" s="236"/>
+      <c r="P16" s="236"/>
+      <c r="Q16" s="236"/>
     </row>
     <row r="17" spans="2:17" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B17" s="97" t="s">
         <v>1</v>
       </c>
-      <c r="C17" s="243" t="s">
+      <c r="C17" s="230" t="s">
         <v>2</v>
       </c>
-      <c r="D17" s="243"/>
+      <c r="D17" s="230"/>
       <c r="E17" s="120" t="s">
         <v>3</v>
       </c>
@@ -59272,16 +59284,16 @@
       <c r="O17" s="120" t="s">
         <v>14</v>
       </c>
-      <c r="P17" s="357" t="s">
-        <v>150</v>
-      </c>
-      <c r="Q17" s="358"/>
+      <c r="P17" s="233" t="s">
+        <v>150</v>
+      </c>
+      <c r="Q17" s="234"/>
     </row>
     <row r="18" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B18" s="239" t="s">
+      <c r="B18" s="227" t="s">
         <v>31</v>
       </c>
-      <c r="C18" s="239" t="s">
+      <c r="C18" s="227" t="s">
         <v>222</v>
       </c>
       <c r="D18" s="117" t="s">
@@ -59328,8 +59340,8 @@
       <c r="Q18" s="53"/>
     </row>
     <row r="19" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B19" s="239"/>
-      <c r="C19" s="239"/>
+      <c r="B19" s="227"/>
+      <c r="C19" s="227"/>
       <c r="D19" s="117" t="s">
         <v>24</v>
       </c>
@@ -59374,32 +59386,32 @@
       <c r="Q19" s="53"/>
     </row>
     <row r="20" spans="2:17" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B20" s="248" t="s">
+      <c r="B20" s="225" t="s">
         <v>224</v>
       </c>
-      <c r="C20" s="297"/>
-      <c r="D20" s="297"/>
-      <c r="E20" s="297"/>
-      <c r="F20" s="297"/>
-      <c r="G20" s="297"/>
-      <c r="H20" s="297"/>
-      <c r="I20" s="297"/>
-      <c r="J20" s="297"/>
-      <c r="K20" s="297"/>
-      <c r="L20" s="297"/>
-      <c r="M20" s="297"/>
-      <c r="N20" s="297"/>
-      <c r="O20" s="297"/>
+      <c r="C20" s="226"/>
+      <c r="D20" s="226"/>
+      <c r="E20" s="226"/>
+      <c r="F20" s="226"/>
+      <c r="G20" s="226"/>
+      <c r="H20" s="226"/>
+      <c r="I20" s="226"/>
+      <c r="J20" s="226"/>
+      <c r="K20" s="226"/>
+      <c r="L20" s="226"/>
+      <c r="M20" s="226"/>
+      <c r="N20" s="226"/>
+      <c r="O20" s="226"/>
       <c r="P20" s="222"/>
     </row>
     <row r="21" spans="2:17" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B21" s="97" t="s">
         <v>1</v>
       </c>
-      <c r="C21" s="243" t="s">
+      <c r="C21" s="230" t="s">
         <v>2</v>
       </c>
-      <c r="D21" s="243"/>
+      <c r="D21" s="230"/>
       <c r="E21" s="120" t="s">
         <v>3</v>
       </c>
@@ -59433,14 +59445,14 @@
       <c r="O21" s="120" t="s">
         <v>150</v>
       </c>
-      <c r="P21" s="355"/>
-      <c r="Q21" s="356"/>
+      <c r="P21" s="243"/>
+      <c r="Q21" s="244"/>
     </row>
     <row r="22" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B22" s="239" t="s">
+      <c r="B22" s="224" t="s">
         <v>17</v>
       </c>
-      <c r="C22" s="239" t="s">
+      <c r="C22" s="224" t="s">
         <v>225</v>
       </c>
       <c r="D22" s="117" t="s">
@@ -59486,43 +59498,46 @@
       <c r="Q22" s="174"/>
     </row>
     <row r="23" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B23" s="239"/>
-      <c r="C23" s="239"/>
+      <c r="B23" s="224" t="s">
+        <v>31</v>
+      </c>
+      <c r="C23" s="224" t="s">
+        <v>225</v>
+      </c>
       <c r="D23" s="117" t="s">
         <v>24</v>
       </c>
       <c r="E23" s="140">
-        <f>CEILING((((1200)*1.4)-289),50)</f>
-        <v>1400</v>
+        <v>650</v>
       </c>
       <c r="F23" s="95">
-        <v>355</v>
+        <v>150</v>
       </c>
       <c r="G23" s="95">
-        <v>76.5</v>
+        <v>95.63</v>
       </c>
       <c r="H23" s="95">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="I23" s="96">
         <f>SUM(E23:H23)</f>
-        <v>1881.5</v>
+        <v>895.63</v>
       </c>
       <c r="J23" s="95">
         <v>200</v>
       </c>
       <c r="K23" s="96">
         <f>I23+J23</f>
-        <v>2081.5</v>
+        <v>1095.6300000000001</v>
       </c>
       <c r="L23" s="183" t="s">
-        <v>226</v>
+        <v>242</v>
       </c>
       <c r="M23" s="215" t="s">
-        <v>21</v>
+        <v>243</v>
       </c>
       <c r="N23" s="94" t="s">
-        <v>46</v>
+        <v>244</v>
       </c>
       <c r="O23" s="219" t="s">
         <v>223</v>
@@ -59531,32 +59546,32 @@
       <c r="Q23" s="220"/>
     </row>
     <row r="24" spans="2:17" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B24" s="249" t="s">
+      <c r="B24" s="228" t="s">
         <v>227</v>
       </c>
-      <c r="C24" s="244"/>
-      <c r="D24" s="244"/>
-      <c r="E24" s="244"/>
-      <c r="F24" s="244"/>
-      <c r="G24" s="244"/>
-      <c r="H24" s="244"/>
-      <c r="I24" s="244"/>
-      <c r="J24" s="244"/>
-      <c r="K24" s="244"/>
-      <c r="L24" s="244"/>
-      <c r="M24" s="244"/>
-      <c r="N24" s="244"/>
-      <c r="O24" s="244"/>
+      <c r="C24" s="229"/>
+      <c r="D24" s="229"/>
+      <c r="E24" s="229"/>
+      <c r="F24" s="229"/>
+      <c r="G24" s="229"/>
+      <c r="H24" s="229"/>
+      <c r="I24" s="229"/>
+      <c r="J24" s="229"/>
+      <c r="K24" s="229"/>
+      <c r="L24" s="229"/>
+      <c r="M24" s="229"/>
+      <c r="N24" s="229"/>
+      <c r="O24" s="229"/>
       <c r="P24" s="61"/>
     </row>
     <row r="25" spans="2:17" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B25" s="97" t="s">
         <v>1</v>
       </c>
-      <c r="C25" s="243" t="s">
+      <c r="C25" s="230" t="s">
         <v>2</v>
       </c>
-      <c r="D25" s="243"/>
+      <c r="D25" s="230"/>
       <c r="E25" s="120" t="s">
         <v>3</v>
       </c>
@@ -59594,10 +59609,10 @@
       <c r="Q25" s="223"/>
     </row>
     <row r="26" spans="2:17" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B26" s="239" t="s">
+      <c r="B26" s="227" t="s">
         <v>17</v>
       </c>
-      <c r="C26" s="239" t="s">
+      <c r="C26" s="227" t="s">
         <v>124</v>
       </c>
       <c r="D26" s="117" t="s">
@@ -59643,8 +59658,8 @@
       <c r="P26" s="61"/>
     </row>
     <row r="27" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B27" s="239"/>
-      <c r="C27" s="239"/>
+      <c r="B27" s="227"/>
+      <c r="C27" s="227"/>
       <c r="D27" s="117" t="s">
         <v>24</v>
       </c>
@@ -59708,78 +59723,78 @@
       <c r="Q29" s="7"/>
     </row>
     <row r="30" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B30" s="254" t="s">
+      <c r="B30" s="237" t="s">
         <v>35</v>
       </c>
-      <c r="C30" s="274"/>
-      <c r="D30" s="274"/>
-      <c r="E30" s="274"/>
-      <c r="F30" s="274"/>
-      <c r="G30" s="274"/>
-      <c r="H30" s="274"/>
-      <c r="I30" s="274"/>
-      <c r="J30" s="274"/>
-      <c r="K30" s="274"/>
-      <c r="L30" s="274"/>
-      <c r="M30" s="274"/>
-      <c r="N30" s="274"/>
-      <c r="O30" s="274"/>
-      <c r="P30" s="274"/>
-      <c r="Q30" s="275"/>
+      <c r="C30" s="238"/>
+      <c r="D30" s="238"/>
+      <c r="E30" s="238"/>
+      <c r="F30" s="238"/>
+      <c r="G30" s="238"/>
+      <c r="H30" s="238"/>
+      <c r="I30" s="238"/>
+      <c r="J30" s="238"/>
+      <c r="K30" s="238"/>
+      <c r="L30" s="238"/>
+      <c r="M30" s="238"/>
+      <c r="N30" s="238"/>
+      <c r="O30" s="238"/>
+      <c r="P30" s="238"/>
+      <c r="Q30" s="239"/>
     </row>
     <row r="31" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B31" s="254"/>
-      <c r="C31" s="274"/>
-      <c r="D31" s="274"/>
-      <c r="E31" s="274"/>
-      <c r="F31" s="274"/>
-      <c r="G31" s="274"/>
-      <c r="H31" s="274"/>
-      <c r="I31" s="274"/>
-      <c r="J31" s="274"/>
-      <c r="K31" s="274"/>
-      <c r="L31" s="274"/>
-      <c r="M31" s="274"/>
-      <c r="N31" s="274"/>
-      <c r="O31" s="274"/>
-      <c r="P31" s="274"/>
-      <c r="Q31" s="275"/>
+      <c r="B31" s="237"/>
+      <c r="C31" s="238"/>
+      <c r="D31" s="238"/>
+      <c r="E31" s="238"/>
+      <c r="F31" s="238"/>
+      <c r="G31" s="238"/>
+      <c r="H31" s="238"/>
+      <c r="I31" s="238"/>
+      <c r="J31" s="238"/>
+      <c r="K31" s="238"/>
+      <c r="L31" s="238"/>
+      <c r="M31" s="238"/>
+      <c r="N31" s="238"/>
+      <c r="O31" s="238"/>
+      <c r="P31" s="238"/>
+      <c r="Q31" s="239"/>
     </row>
     <row r="32" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B32" s="254"/>
-      <c r="C32" s="274"/>
-      <c r="D32" s="274"/>
-      <c r="E32" s="274"/>
-      <c r="F32" s="274"/>
-      <c r="G32" s="274"/>
-      <c r="H32" s="274"/>
-      <c r="I32" s="274"/>
-      <c r="J32" s="274"/>
-      <c r="K32" s="274"/>
-      <c r="L32" s="274"/>
-      <c r="M32" s="274"/>
-      <c r="N32" s="274"/>
-      <c r="O32" s="274"/>
-      <c r="P32" s="274"/>
-      <c r="Q32" s="275"/>
+      <c r="B32" s="237"/>
+      <c r="C32" s="238"/>
+      <c r="D32" s="238"/>
+      <c r="E32" s="238"/>
+      <c r="F32" s="238"/>
+      <c r="G32" s="238"/>
+      <c r="H32" s="238"/>
+      <c r="I32" s="238"/>
+      <c r="J32" s="238"/>
+      <c r="K32" s="238"/>
+      <c r="L32" s="238"/>
+      <c r="M32" s="238"/>
+      <c r="N32" s="238"/>
+      <c r="O32" s="238"/>
+      <c r="P32" s="238"/>
+      <c r="Q32" s="239"/>
     </row>
     <row r="33" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B33" s="255"/>
-      <c r="C33" s="276"/>
-      <c r="D33" s="276"/>
-      <c r="E33" s="276"/>
-      <c r="F33" s="276"/>
-      <c r="G33" s="276"/>
-      <c r="H33" s="276"/>
-      <c r="I33" s="276"/>
-      <c r="J33" s="276"/>
-      <c r="K33" s="276"/>
-      <c r="L33" s="276"/>
-      <c r="M33" s="276"/>
-      <c r="N33" s="276"/>
-      <c r="O33" s="276"/>
-      <c r="P33" s="276"/>
-      <c r="Q33" s="277"/>
+      <c r="B33" s="240"/>
+      <c r="C33" s="241"/>
+      <c r="D33" s="241"/>
+      <c r="E33" s="241"/>
+      <c r="F33" s="241"/>
+      <c r="G33" s="241"/>
+      <c r="H33" s="241"/>
+      <c r="I33" s="241"/>
+      <c r="J33" s="241"/>
+      <c r="K33" s="241"/>
+      <c r="L33" s="241"/>
+      <c r="M33" s="241"/>
+      <c r="N33" s="241"/>
+      <c r="O33" s="241"/>
+      <c r="P33" s="241"/>
+      <c r="Q33" s="242"/>
     </row>
     <row r="34" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B34" s="35"/>
@@ -59908,7 +59923,14 @@
       <c r="Q40" s="35"/>
     </row>
   </sheetData>
-  <mergeCells count="23">
+  <mergeCells count="21">
+    <mergeCell ref="B30:Q33"/>
+    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="B24:O24"/>
+    <mergeCell ref="C25:D25"/>
+    <mergeCell ref="B26:B27"/>
+    <mergeCell ref="C26:C27"/>
+    <mergeCell ref="P21:Q21"/>
     <mergeCell ref="B20:O20"/>
     <mergeCell ref="C18:C19"/>
     <mergeCell ref="B14:B15"/>
@@ -59923,15 +59945,6 @@
     <mergeCell ref="B18:B19"/>
     <mergeCell ref="P17:Q17"/>
     <mergeCell ref="B16:Q16"/>
-    <mergeCell ref="B30:Q33"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="B24:O24"/>
-    <mergeCell ref="C25:D25"/>
-    <mergeCell ref="B26:B27"/>
-    <mergeCell ref="C26:C27"/>
-    <mergeCell ref="B22:B23"/>
-    <mergeCell ref="C22:C23"/>
-    <mergeCell ref="P21:Q21"/>
   </mergeCells>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -60118,10 +60131,10 @@
       <c r="B10" s="77" t="s">
         <v>1</v>
       </c>
-      <c r="C10" s="361" t="s">
+      <c r="C10" s="374" t="s">
         <v>2</v>
       </c>
-      <c r="D10" s="361"/>
+      <c r="D10" s="374"/>
       <c r="E10" s="15" t="s">
         <v>3</v>
       </c>
@@ -60160,10 +60173,10 @@
       </c>
     </row>
     <row r="11" spans="2:16" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B11" s="362" t="s">
+      <c r="B11" s="370" t="s">
         <v>229</v>
       </c>
-      <c r="C11" s="365" t="s">
+      <c r="C11" s="372" t="s">
         <v>31</v>
       </c>
       <c r="D11" s="45" t="s">
@@ -60209,8 +60222,8 @@
       </c>
     </row>
     <row r="12" spans="2:16" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B12" s="363"/>
-      <c r="C12" s="365"/>
+      <c r="B12" s="375"/>
+      <c r="C12" s="372"/>
       <c r="D12" s="45" t="s">
         <v>24</v>
       </c>
@@ -60254,8 +60267,8 @@
       </c>
     </row>
     <row r="13" spans="2:16" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B13" s="363"/>
-      <c r="C13" s="365" t="s">
+      <c r="B13" s="375"/>
+      <c r="C13" s="372" t="s">
         <v>17</v>
       </c>
       <c r="D13" s="45" t="s">
@@ -60301,8 +60314,8 @@
       </c>
     </row>
     <row r="14" spans="2:16" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B14" s="363"/>
-      <c r="C14" s="365"/>
+      <c r="B14" s="375"/>
+      <c r="C14" s="372"/>
       <c r="D14" s="45" t="s">
         <v>24</v>
       </c>
@@ -60346,8 +60359,8 @@
       </c>
     </row>
     <row r="15" spans="2:16" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B15" s="363"/>
-      <c r="C15" s="365" t="s">
+      <c r="B15" s="375"/>
+      <c r="C15" s="372" t="s">
         <v>31</v>
       </c>
       <c r="D15" s="45" t="s">
@@ -60393,8 +60406,8 @@
       </c>
     </row>
     <row r="16" spans="2:16" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B16" s="363"/>
-      <c r="C16" s="365"/>
+      <c r="B16" s="375"/>
+      <c r="C16" s="372"/>
       <c r="D16" s="45" t="s">
         <v>24</v>
       </c>
@@ -60438,8 +60451,8 @@
       </c>
     </row>
     <row r="17" spans="2:16" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B17" s="363"/>
-      <c r="C17" s="365" t="s">
+      <c r="B17" s="375"/>
+      <c r="C17" s="372" t="s">
         <v>31</v>
       </c>
       <c r="D17" s="45" t="s">
@@ -60485,8 +60498,8 @@
       </c>
     </row>
     <row r="18" spans="2:16" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B18" s="363"/>
-      <c r="C18" s="365"/>
+      <c r="B18" s="375"/>
+      <c r="C18" s="372"/>
       <c r="D18" s="45" t="s">
         <v>24</v>
       </c>
@@ -60530,8 +60543,8 @@
       </c>
     </row>
     <row r="19" spans="2:16" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="B19" s="363"/>
-      <c r="C19" s="365" t="s">
+      <c r="B19" s="375"/>
+      <c r="C19" s="372" t="s">
         <v>31</v>
       </c>
       <c r="D19" s="45" t="s">
@@ -60577,8 +60590,8 @@
       </c>
     </row>
     <row r="20" spans="2:16" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="B20" s="364"/>
-      <c r="C20" s="365"/>
+      <c r="B20" s="371"/>
+      <c r="C20" s="372"/>
       <c r="D20" s="45" t="s">
         <v>24</v>
       </c>
@@ -60622,10 +60635,10 @@
       </c>
     </row>
     <row r="21" spans="2:16" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B21" s="362" t="s">
+      <c r="B21" s="370" t="s">
         <v>234</v>
       </c>
-      <c r="C21" s="365" t="s">
+      <c r="C21" s="372" t="s">
         <v>31</v>
       </c>
       <c r="D21" s="45" t="s">
@@ -60671,8 +60684,8 @@
       </c>
     </row>
     <row r="22" spans="2:16" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B22" s="364"/>
-      <c r="C22" s="365"/>
+      <c r="B22" s="371"/>
+      <c r="C22" s="372"/>
       <c r="D22" s="45" t="s">
         <v>24</v>
       </c>
@@ -60716,10 +60729,10 @@
       </c>
     </row>
     <row r="23" spans="2:16" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B23" s="362" t="s">
+      <c r="B23" s="370" t="s">
         <v>235</v>
       </c>
-      <c r="C23" s="365" t="s">
+      <c r="C23" s="372" t="s">
         <v>31</v>
       </c>
       <c r="D23" s="45" t="s">
@@ -60765,8 +60778,8 @@
       </c>
     </row>
     <row r="24" spans="2:16" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B24" s="364"/>
-      <c r="C24" s="365"/>
+      <c r="B24" s="371"/>
+      <c r="C24" s="372"/>
       <c r="D24" s="45" t="s">
         <v>24</v>
       </c>
@@ -60810,10 +60823,10 @@
       </c>
     </row>
     <row r="25" spans="2:16" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
-      <c r="B25" s="273" t="s">
+      <c r="B25" s="247" t="s">
         <v>237</v>
       </c>
-      <c r="C25" s="239" t="s">
+      <c r="C25" s="227" t="s">
         <v>31</v>
       </c>
       <c r="D25" s="40" t="s">
@@ -60859,8 +60872,8 @@
       </c>
     </row>
     <row r="26" spans="2:16" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
-      <c r="B26" s="273"/>
-      <c r="C26" s="239"/>
+      <c r="B26" s="247"/>
+      <c r="C26" s="227"/>
       <c r="D26" s="40" t="s">
         <v>24</v>
       </c>
@@ -60904,8 +60917,8 @@
       </c>
     </row>
     <row r="27" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B27" s="354"/>
-      <c r="C27" s="374"/>
+      <c r="B27" s="339"/>
+      <c r="C27" s="373"/>
       <c r="D27" s="84" t="s">
         <v>18</v>
       </c>
@@ -60965,96 +60978,103 @@
       <c r="O28" s="28"/>
     </row>
     <row r="29" spans="2:16" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B29" s="366" t="s">
+      <c r="B29" s="362" t="s">
         <v>34</v>
       </c>
-      <c r="C29" s="367"/>
-      <c r="D29" s="367"/>
-      <c r="E29" s="367"/>
-      <c r="F29" s="367"/>
-      <c r="G29" s="367"/>
-      <c r="H29" s="367"/>
-      <c r="I29" s="367"/>
-      <c r="J29" s="367"/>
-      <c r="K29" s="367"/>
-      <c r="L29" s="367"/>
-      <c r="M29" s="367"/>
-      <c r="N29" s="367"/>
-      <c r="O29" s="367"/>
-      <c r="P29" s="368"/>
+      <c r="C29" s="363"/>
+      <c r="D29" s="363"/>
+      <c r="E29" s="363"/>
+      <c r="F29" s="363"/>
+      <c r="G29" s="363"/>
+      <c r="H29" s="363"/>
+      <c r="I29" s="363"/>
+      <c r="J29" s="363"/>
+      <c r="K29" s="363"/>
+      <c r="L29" s="363"/>
+      <c r="M29" s="363"/>
+      <c r="N29" s="363"/>
+      <c r="O29" s="363"/>
+      <c r="P29" s="364"/>
     </row>
     <row r="30" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="B30" s="369" t="s">
+      <c r="B30" s="365" t="s">
         <v>35</v>
       </c>
-      <c r="C30" s="274"/>
-      <c r="D30" s="274"/>
-      <c r="E30" s="274"/>
-      <c r="F30" s="274"/>
-      <c r="G30" s="274"/>
-      <c r="H30" s="274"/>
-      <c r="I30" s="274"/>
-      <c r="J30" s="274"/>
-      <c r="K30" s="274"/>
-      <c r="L30" s="274"/>
-      <c r="M30" s="274"/>
-      <c r="N30" s="274"/>
-      <c r="O30" s="274"/>
-      <c r="P30" s="370"/>
+      <c r="C30" s="238"/>
+      <c r="D30" s="238"/>
+      <c r="E30" s="238"/>
+      <c r="F30" s="238"/>
+      <c r="G30" s="238"/>
+      <c r="H30" s="238"/>
+      <c r="I30" s="238"/>
+      <c r="J30" s="238"/>
+      <c r="K30" s="238"/>
+      <c r="L30" s="238"/>
+      <c r="M30" s="238"/>
+      <c r="N30" s="238"/>
+      <c r="O30" s="238"/>
+      <c r="P30" s="366"/>
     </row>
     <row r="31" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="B31" s="369"/>
-      <c r="C31" s="274"/>
-      <c r="D31" s="274"/>
-      <c r="E31" s="274"/>
-      <c r="F31" s="274"/>
-      <c r="G31" s="274"/>
-      <c r="H31" s="274"/>
-      <c r="I31" s="274"/>
-      <c r="J31" s="274"/>
-      <c r="K31" s="274"/>
-      <c r="L31" s="274"/>
-      <c r="M31" s="274"/>
-      <c r="N31" s="274"/>
-      <c r="O31" s="274"/>
-      <c r="P31" s="370"/>
+      <c r="B31" s="365"/>
+      <c r="C31" s="238"/>
+      <c r="D31" s="238"/>
+      <c r="E31" s="238"/>
+      <c r="F31" s="238"/>
+      <c r="G31" s="238"/>
+      <c r="H31" s="238"/>
+      <c r="I31" s="238"/>
+      <c r="J31" s="238"/>
+      <c r="K31" s="238"/>
+      <c r="L31" s="238"/>
+      <c r="M31" s="238"/>
+      <c r="N31" s="238"/>
+      <c r="O31" s="238"/>
+      <c r="P31" s="366"/>
     </row>
     <row r="32" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="B32" s="369"/>
-      <c r="C32" s="274"/>
-      <c r="D32" s="274"/>
-      <c r="E32" s="274"/>
-      <c r="F32" s="274"/>
-      <c r="G32" s="274"/>
-      <c r="H32" s="274"/>
-      <c r="I32" s="274"/>
-      <c r="J32" s="274"/>
-      <c r="K32" s="274"/>
-      <c r="L32" s="274"/>
-      <c r="M32" s="274"/>
-      <c r="N32" s="274"/>
-      <c r="O32" s="274"/>
-      <c r="P32" s="370"/>
+      <c r="B32" s="365"/>
+      <c r="C32" s="238"/>
+      <c r="D32" s="238"/>
+      <c r="E32" s="238"/>
+      <c r="F32" s="238"/>
+      <c r="G32" s="238"/>
+      <c r="H32" s="238"/>
+      <c r="I32" s="238"/>
+      <c r="J32" s="238"/>
+      <c r="K32" s="238"/>
+      <c r="L32" s="238"/>
+      <c r="M32" s="238"/>
+      <c r="N32" s="238"/>
+      <c r="O32" s="238"/>
+      <c r="P32" s="366"/>
     </row>
     <row r="33" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B33" s="371"/>
-      <c r="C33" s="372"/>
-      <c r="D33" s="372"/>
-      <c r="E33" s="372"/>
-      <c r="F33" s="372"/>
-      <c r="G33" s="372"/>
-      <c r="H33" s="372"/>
-      <c r="I33" s="372"/>
-      <c r="J33" s="372"/>
-      <c r="K33" s="372"/>
-      <c r="L33" s="372"/>
-      <c r="M33" s="372"/>
-      <c r="N33" s="372"/>
-      <c r="O33" s="372"/>
-      <c r="P33" s="373"/>
+      <c r="B33" s="367"/>
+      <c r="C33" s="368"/>
+      <c r="D33" s="368"/>
+      <c r="E33" s="368"/>
+      <c r="F33" s="368"/>
+      <c r="G33" s="368"/>
+      <c r="H33" s="368"/>
+      <c r="I33" s="368"/>
+      <c r="J33" s="368"/>
+      <c r="K33" s="368"/>
+      <c r="L33" s="368"/>
+      <c r="M33" s="368"/>
+      <c r="N33" s="368"/>
+      <c r="O33" s="368"/>
+      <c r="P33" s="369"/>
     </row>
   </sheetData>
   <mergeCells count="15">
+    <mergeCell ref="C10:D10"/>
+    <mergeCell ref="B11:B20"/>
+    <mergeCell ref="C11:C12"/>
+    <mergeCell ref="C13:C14"/>
+    <mergeCell ref="C15:C16"/>
+    <mergeCell ref="C17:C18"/>
+    <mergeCell ref="C19:C20"/>
     <mergeCell ref="B29:P29"/>
     <mergeCell ref="B30:P33"/>
     <mergeCell ref="B21:B22"/>
@@ -61063,13 +61083,6 @@
     <mergeCell ref="C23:C24"/>
     <mergeCell ref="B25:B27"/>
     <mergeCell ref="C25:C27"/>
-    <mergeCell ref="C10:D10"/>
-    <mergeCell ref="B11:B20"/>
-    <mergeCell ref="C11:C12"/>
-    <mergeCell ref="C13:C14"/>
-    <mergeCell ref="C15:C16"/>
-    <mergeCell ref="C17:C18"/>
-    <mergeCell ref="C19:C20"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup scale="67" orientation="landscape" r:id="rId1"/>
@@ -61078,17 +61091,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="8bf418b7-79e0-4993-aa07-d31c53a64380">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="268ad1c4-fabf-4dd0-b894-8fd5403102c0" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100BF631F92D611394D900040A4BC36CE07" ma:contentTypeVersion="13" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="711a2ec75ffd0c152903cfa2dedf38be">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="8bf418b7-79e0-4993-aa07-d31c53a64380" xmlns:ns3="268ad1c4-fabf-4dd0-b894-8fd5403102c0" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="0628c710989f2757c815e19c03677863" ns2:_="" ns3:_="">
     <xsd:import namespace="8bf418b7-79e0-4993-aa07-d31c53a64380"/>
@@ -61311,6 +61313,17 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="8bf418b7-79e0-4993-aa07-d31c53a64380">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="268ad1c4-fabf-4dd0-b894-8fd5403102c0" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
@@ -61321,17 +61334,6 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{900DAED1-575B-462E-9521-61C8D8B6DAE7}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="8bf418b7-79e0-4993-aa07-d31c53a64380"/>
-    <ds:schemaRef ds:uri="268ad1c4-fabf-4dd0-b894-8fd5403102c0"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1A722593-7143-4ACD-9A00-2A0E70214590}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -61350,6 +61352,17 @@
 </ds:datastoreItem>
 </file>
 
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{900DAED1-575B-462E-9521-61C8D8B6DAE7}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="8bf418b7-79e0-4993-aa07-d31c53a64380"/>
+    <ds:schemaRef ds:uri="268ad1c4-fabf-4dd0-b894-8fd5403102c0"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6AAFA3EB-B8AB-4135-B122-0B0233A6C07D}">
   <ds:schemaRefs>

--- a/Customer Rate Tariff Template_Week 29_2026.xlsx
+++ b/Customer Rate Tariff Template_Week 29_2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\stephanie.galera.RAMPSLOGISTICS\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{59108480-641A-42DC-AA8C-47A54E412526}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C5A211DB-B627-4298-A23B-D3C7B90E8BCA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{493693A0-0616-4273-B364-7C8DEB21885C}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4480" uniqueCount="245">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4478" uniqueCount="242">
   <si>
     <t>USA / TRINIDAD SHIPPING TARIFF</t>
   </si>
@@ -772,15 +772,6 @@
   </si>
   <si>
     <t>Foshan/Gaoming</t>
-  </si>
-  <si>
-    <t>7-9 days</t>
-  </si>
-  <si>
-    <t>17/07/2026</t>
-  </si>
-  <si>
-    <t>ZIM</t>
   </si>
 </sst>
 </file>
@@ -1819,7 +1810,7 @@
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="376">
+  <cellXfs count="375">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -2342,16 +2333,25 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2360,7 +2360,19 @@
     <xf numFmtId="0" fontId="5" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2381,30 +2393,6 @@
     <xf numFmtId="0" fontId="5" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2413,141 +2401,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="36" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="46" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="47" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="61" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="60" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="60" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="59" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="45" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="66" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="63" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2579,56 +2432,140 @@
     <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="59" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="45" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="66" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="63" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="36" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="60" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="60" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="61" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="60" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="46" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="47" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="36" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2666,48 +2603,86 @@
     <xf numFmtId="0" fontId="0" fillId="5" borderId="58" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="36" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="60" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="11" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="38" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="61" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="65" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="61" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="62" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="62" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="64" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="3" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -2722,25 +2697,53 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="61" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="62" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="64" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="61" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="62" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="38" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="65" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="26" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="27" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="29" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -2766,23 +2769,8 @@
     <xf numFmtId="0" fontId="0" fillId="5" borderId="35" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="26" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="29" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="5" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="27" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -4244,23 +4232,23 @@
       <c r="P7" s="18"/>
     </row>
     <row r="8" spans="2:20" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B8" s="229" t="s">
+      <c r="B8" s="232" t="s">
         <v>0</v>
       </c>
-      <c r="C8" s="229"/>
-      <c r="D8" s="229"/>
-      <c r="E8" s="229"/>
-      <c r="F8" s="229"/>
-      <c r="G8" s="229"/>
-      <c r="H8" s="229"/>
-      <c r="I8" s="229"/>
-      <c r="J8" s="229"/>
-      <c r="K8" s="229"/>
-      <c r="L8" s="229"/>
-      <c r="M8" s="229"/>
-      <c r="N8" s="229"/>
-      <c r="O8" s="229"/>
-      <c r="P8" s="229"/>
+      <c r="C8" s="232"/>
+      <c r="D8" s="232"/>
+      <c r="E8" s="232"/>
+      <c r="F8" s="232"/>
+      <c r="G8" s="232"/>
+      <c r="H8" s="232"/>
+      <c r="I8" s="232"/>
+      <c r="J8" s="232"/>
+      <c r="K8" s="232"/>
+      <c r="L8" s="232"/>
+      <c r="M8" s="232"/>
+      <c r="N8" s="232"/>
+      <c r="O8" s="232"/>
+      <c r="P8" s="232"/>
     </row>
     <row r="9" spans="2:20" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B9" s="4" t="s">
@@ -4311,10 +4299,10 @@
       </c>
     </row>
     <row r="10" spans="2:20" x14ac:dyDescent="0.3">
-      <c r="B10" s="248" t="s">
+      <c r="B10" s="295" t="s">
         <v>16</v>
       </c>
-      <c r="C10" s="248" t="s">
+      <c r="C10" s="295" t="s">
         <v>17</v>
       </c>
       <c r="D10" s="20" t="s">
@@ -4363,8 +4351,8 @@
       </c>
     </row>
     <row r="11" spans="2:20" x14ac:dyDescent="0.3">
-      <c r="B11" s="249"/>
-      <c r="C11" s="249"/>
+      <c r="B11" s="296"/>
+      <c r="C11" s="296"/>
       <c r="D11" s="20" t="s">
         <v>24</v>
       </c>
@@ -4411,8 +4399,8 @@
       </c>
     </row>
     <row r="12" spans="2:20" x14ac:dyDescent="0.3">
-      <c r="B12" s="249"/>
-      <c r="C12" s="248" t="s">
+      <c r="B12" s="296"/>
+      <c r="C12" s="295" t="s">
         <v>17</v>
       </c>
       <c r="D12" s="111" t="s">
@@ -4462,8 +4450,8 @@
       </c>
     </row>
     <row r="13" spans="2:20" x14ac:dyDescent="0.3">
-      <c r="B13" s="249"/>
-      <c r="C13" s="249"/>
+      <c r="B13" s="296"/>
+      <c r="C13" s="296"/>
       <c r="D13" s="111" t="s">
         <v>24</v>
       </c>
@@ -4512,10 +4500,10 @@
       </c>
     </row>
     <row r="14" spans="2:20" x14ac:dyDescent="0.3">
-      <c r="B14" s="250" t="s">
+      <c r="B14" s="297" t="s">
         <v>26</v>
       </c>
-      <c r="C14" s="252" t="s">
+      <c r="C14" s="257" t="s">
         <v>17</v>
       </c>
       <c r="D14" s="20" t="s">
@@ -4565,8 +4553,8 @@
       </c>
     </row>
     <row r="15" spans="2:20" x14ac:dyDescent="0.3">
-      <c r="B15" s="251"/>
-      <c r="C15" s="252"/>
+      <c r="B15" s="298"/>
+      <c r="C15" s="257"/>
       <c r="D15" s="20" t="s">
         <v>24</v>
       </c>
@@ -4614,10 +4602,10 @@
       </c>
     </row>
     <row r="16" spans="2:20" x14ac:dyDescent="0.3">
-      <c r="B16" s="250" t="s">
+      <c r="B16" s="297" t="s">
         <v>28</v>
       </c>
-      <c r="C16" s="250" t="s">
+      <c r="C16" s="297" t="s">
         <v>17</v>
       </c>
       <c r="D16" s="20" t="s">
@@ -4667,8 +4655,8 @@
       </c>
     </row>
     <row r="17" spans="2:20" x14ac:dyDescent="0.3">
-      <c r="B17" s="251"/>
-      <c r="C17" s="251"/>
+      <c r="B17" s="298"/>
+      <c r="C17" s="298"/>
       <c r="D17" s="20" t="s">
         <v>24</v>
       </c>
@@ -4716,10 +4704,10 @@
       </c>
     </row>
     <row r="18" spans="2:20" x14ac:dyDescent="0.3">
-      <c r="B18" s="250" t="s">
+      <c r="B18" s="297" t="s">
         <v>30</v>
       </c>
-      <c r="C18" s="252" t="s">
+      <c r="C18" s="257" t="s">
         <v>31</v>
       </c>
       <c r="D18" s="20" t="s">
@@ -4770,8 +4758,8 @@
       </c>
     </row>
     <row r="19" spans="2:20" x14ac:dyDescent="0.3">
-      <c r="B19" s="260"/>
-      <c r="C19" s="252"/>
+      <c r="B19" s="301"/>
+      <c r="C19" s="257"/>
       <c r="D19" s="20" t="s">
         <v>24</v>
       </c>
@@ -4820,8 +4808,8 @@
       </c>
     </row>
     <row r="20" spans="2:20" x14ac:dyDescent="0.3">
-      <c r="B20" s="260"/>
-      <c r="C20" s="252" t="s">
+      <c r="B20" s="301"/>
+      <c r="C20" s="257" t="s">
         <v>17</v>
       </c>
       <c r="D20" s="20" t="s">
@@ -4871,8 +4859,8 @@
       </c>
     </row>
     <row r="21" spans="2:20" x14ac:dyDescent="0.3">
-      <c r="B21" s="251"/>
-      <c r="C21" s="252"/>
+      <c r="B21" s="298"/>
+      <c r="C21" s="257"/>
       <c r="D21" s="20" t="s">
         <v>24</v>
       </c>
@@ -4957,74 +4945,74 @@
       <c r="P23" s="192"/>
     </row>
     <row r="24" spans="2:20" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B24" s="263" t="s">
+      <c r="B24" s="292" t="s">
         <v>35</v>
       </c>
-      <c r="C24" s="263"/>
-      <c r="D24" s="263"/>
-      <c r="E24" s="263"/>
-      <c r="F24" s="263"/>
-      <c r="G24" s="263"/>
-      <c r="H24" s="263"/>
-      <c r="I24" s="263"/>
-      <c r="J24" s="263"/>
-      <c r="K24" s="263"/>
-      <c r="L24" s="263"/>
-      <c r="M24" s="263"/>
-      <c r="N24" s="263"/>
-      <c r="O24" s="263"/>
-      <c r="P24" s="263"/>
+      <c r="C24" s="292"/>
+      <c r="D24" s="292"/>
+      <c r="E24" s="292"/>
+      <c r="F24" s="292"/>
+      <c r="G24" s="292"/>
+      <c r="H24" s="292"/>
+      <c r="I24" s="292"/>
+      <c r="J24" s="292"/>
+      <c r="K24" s="292"/>
+      <c r="L24" s="292"/>
+      <c r="M24" s="292"/>
+      <c r="N24" s="292"/>
+      <c r="O24" s="292"/>
+      <c r="P24" s="292"/>
     </row>
     <row r="25" spans="2:20" x14ac:dyDescent="0.3">
-      <c r="B25" s="263"/>
-      <c r="C25" s="263"/>
-      <c r="D25" s="263"/>
-      <c r="E25" s="263"/>
-      <c r="F25" s="263"/>
-      <c r="G25" s="263"/>
-      <c r="H25" s="263"/>
-      <c r="I25" s="263"/>
-      <c r="J25" s="263"/>
-      <c r="K25" s="263"/>
-      <c r="L25" s="263"/>
-      <c r="M25" s="263"/>
-      <c r="N25" s="263"/>
-      <c r="O25" s="263"/>
-      <c r="P25" s="263"/>
+      <c r="B25" s="292"/>
+      <c r="C25" s="292"/>
+      <c r="D25" s="292"/>
+      <c r="E25" s="292"/>
+      <c r="F25" s="292"/>
+      <c r="G25" s="292"/>
+      <c r="H25" s="292"/>
+      <c r="I25" s="292"/>
+      <c r="J25" s="292"/>
+      <c r="K25" s="292"/>
+      <c r="L25" s="292"/>
+      <c r="M25" s="292"/>
+      <c r="N25" s="292"/>
+      <c r="O25" s="292"/>
+      <c r="P25" s="292"/>
     </row>
     <row r="26" spans="2:20" x14ac:dyDescent="0.3">
-      <c r="B26" s="263"/>
-      <c r="C26" s="263"/>
-      <c r="D26" s="263"/>
-      <c r="E26" s="263"/>
-      <c r="F26" s="263"/>
-      <c r="G26" s="263"/>
-      <c r="H26" s="263"/>
-      <c r="I26" s="263"/>
-      <c r="J26" s="263"/>
-      <c r="K26" s="263"/>
-      <c r="L26" s="263"/>
-      <c r="M26" s="263"/>
-      <c r="N26" s="263"/>
-      <c r="O26" s="263"/>
-      <c r="P26" s="263"/>
+      <c r="B26" s="292"/>
+      <c r="C26" s="292"/>
+      <c r="D26" s="292"/>
+      <c r="E26" s="292"/>
+      <c r="F26" s="292"/>
+      <c r="G26" s="292"/>
+      <c r="H26" s="292"/>
+      <c r="I26" s="292"/>
+      <c r="J26" s="292"/>
+      <c r="K26" s="292"/>
+      <c r="L26" s="292"/>
+      <c r="M26" s="292"/>
+      <c r="N26" s="292"/>
+      <c r="O26" s="292"/>
+      <c r="P26" s="292"/>
     </row>
     <row r="27" spans="2:20" x14ac:dyDescent="0.3">
-      <c r="B27" s="263"/>
-      <c r="C27" s="263"/>
-      <c r="D27" s="263"/>
-      <c r="E27" s="263"/>
-      <c r="F27" s="263"/>
-      <c r="G27" s="263"/>
-      <c r="H27" s="263"/>
-      <c r="I27" s="263"/>
-      <c r="J27" s="263"/>
-      <c r="K27" s="263"/>
-      <c r="L27" s="263"/>
-      <c r="M27" s="263"/>
-      <c r="N27" s="263"/>
-      <c r="O27" s="263"/>
-      <c r="P27" s="263"/>
+      <c r="B27" s="292"/>
+      <c r="C27" s="292"/>
+      <c r="D27" s="292"/>
+      <c r="E27" s="292"/>
+      <c r="F27" s="292"/>
+      <c r="G27" s="292"/>
+      <c r="H27" s="292"/>
+      <c r="I27" s="292"/>
+      <c r="J27" s="292"/>
+      <c r="K27" s="292"/>
+      <c r="L27" s="292"/>
+      <c r="M27" s="292"/>
+      <c r="N27" s="292"/>
+      <c r="O27" s="292"/>
+      <c r="P27" s="292"/>
     </row>
     <row r="28" spans="2:20" x14ac:dyDescent="0.3">
       <c r="B28" s="35"/>
@@ -5153,23 +5141,23 @@
       <c r="Q34" s="28"/>
     </row>
     <row r="35" spans="2:20" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B35" s="253" t="s">
+      <c r="B35" s="299" t="s">
         <v>36</v>
       </c>
-      <c r="C35" s="226"/>
-      <c r="D35" s="226"/>
-      <c r="E35" s="226"/>
-      <c r="F35" s="226"/>
-      <c r="G35" s="226"/>
-      <c r="H35" s="226"/>
-      <c r="I35" s="226"/>
-      <c r="J35" s="226"/>
-      <c r="K35" s="226"/>
-      <c r="L35" s="226"/>
-      <c r="M35" s="226"/>
-      <c r="N35" s="226"/>
-      <c r="O35" s="226"/>
-      <c r="P35" s="226"/>
+      <c r="C35" s="237"/>
+      <c r="D35" s="237"/>
+      <c r="E35" s="237"/>
+      <c r="F35" s="237"/>
+      <c r="G35" s="237"/>
+      <c r="H35" s="237"/>
+      <c r="I35" s="237"/>
+      <c r="J35" s="237"/>
+      <c r="K35" s="237"/>
+      <c r="L35" s="237"/>
+      <c r="M35" s="237"/>
+      <c r="N35" s="237"/>
+      <c r="O35" s="237"/>
+      <c r="P35" s="237"/>
     </row>
     <row r="36" spans="2:20" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B36" s="120" t="s">
@@ -5218,7 +5206,7 @@
       </c>
     </row>
     <row r="37" spans="2:20" x14ac:dyDescent="0.3">
-      <c r="B37" s="254" t="s">
+      <c r="B37" s="300" t="s">
         <v>39</v>
       </c>
       <c r="C37" s="138" t="s">
@@ -5260,16 +5248,16 @@
       <c r="N37" s="94" t="s">
         <v>41</v>
       </c>
-      <c r="O37" s="255" t="s">
+      <c r="O37" s="281" t="s">
         <v>42</v>
       </c>
-      <c r="P37" s="256"/>
+      <c r="P37" s="282"/>
       <c r="T37" s="53" t="s">
         <v>43</v>
       </c>
     </row>
     <row r="38" spans="2:20" x14ac:dyDescent="0.3">
-      <c r="B38" s="254"/>
+      <c r="B38" s="300"/>
       <c r="C38" s="138" t="s">
         <v>17</v>
       </c>
@@ -5309,8 +5297,8 @@
       <c r="N38" s="94" t="s">
         <v>41</v>
       </c>
-      <c r="O38" s="257"/>
-      <c r="P38" s="258"/>
+      <c r="O38" s="283"/>
+      <c r="P38" s="284"/>
       <c r="T38" s="53" t="s">
         <v>43</v>
       </c>
@@ -5357,10 +5345,10 @@
       <c r="N39" s="94" t="s">
         <v>46</v>
       </c>
-      <c r="O39" s="259" t="s">
+      <c r="O39" s="258" t="s">
         <v>47</v>
       </c>
-      <c r="P39" s="259"/>
+      <c r="P39" s="258"/>
       <c r="T39" s="53" t="s">
         <v>48</v>
       </c>
@@ -5408,10 +5396,10 @@
       <c r="N40" s="94" t="s">
         <v>41</v>
       </c>
-      <c r="O40" s="259" t="s">
+      <c r="O40" s="258" t="s">
         <v>47</v>
       </c>
-      <c r="P40" s="259"/>
+      <c r="P40" s="258"/>
       <c r="T40" s="53" t="s">
         <v>43</v>
       </c>
@@ -5455,78 +5443,78 @@
       <c r="Q42" s="7"/>
     </row>
     <row r="43" spans="2:20" x14ac:dyDescent="0.3">
-      <c r="B43" s="237" t="s">
+      <c r="B43" s="224" t="s">
         <v>35</v>
       </c>
-      <c r="C43" s="238"/>
-      <c r="D43" s="238"/>
-      <c r="E43" s="238"/>
-      <c r="F43" s="238"/>
-      <c r="G43" s="238"/>
-      <c r="H43" s="238"/>
-      <c r="I43" s="238"/>
-      <c r="J43" s="238"/>
-      <c r="K43" s="238"/>
-      <c r="L43" s="238"/>
-      <c r="M43" s="238"/>
-      <c r="N43" s="238"/>
-      <c r="O43" s="238"/>
-      <c r="P43" s="238"/>
-      <c r="Q43" s="239"/>
+      <c r="C43" s="225"/>
+      <c r="D43" s="225"/>
+      <c r="E43" s="225"/>
+      <c r="F43" s="225"/>
+      <c r="G43" s="225"/>
+      <c r="H43" s="225"/>
+      <c r="I43" s="225"/>
+      <c r="J43" s="225"/>
+      <c r="K43" s="225"/>
+      <c r="L43" s="225"/>
+      <c r="M43" s="225"/>
+      <c r="N43" s="225"/>
+      <c r="O43" s="225"/>
+      <c r="P43" s="225"/>
+      <c r="Q43" s="226"/>
     </row>
     <row r="44" spans="2:20" x14ac:dyDescent="0.3">
-      <c r="B44" s="237"/>
-      <c r="C44" s="238"/>
-      <c r="D44" s="238"/>
-      <c r="E44" s="238"/>
-      <c r="F44" s="238"/>
-      <c r="G44" s="238"/>
-      <c r="H44" s="238"/>
-      <c r="I44" s="238"/>
-      <c r="J44" s="238"/>
-      <c r="K44" s="238"/>
-      <c r="L44" s="238"/>
-      <c r="M44" s="238"/>
-      <c r="N44" s="238"/>
-      <c r="O44" s="238"/>
-      <c r="P44" s="238"/>
-      <c r="Q44" s="239"/>
+      <c r="B44" s="224"/>
+      <c r="C44" s="225"/>
+      <c r="D44" s="225"/>
+      <c r="E44" s="225"/>
+      <c r="F44" s="225"/>
+      <c r="G44" s="225"/>
+      <c r="H44" s="225"/>
+      <c r="I44" s="225"/>
+      <c r="J44" s="225"/>
+      <c r="K44" s="225"/>
+      <c r="L44" s="225"/>
+      <c r="M44" s="225"/>
+      <c r="N44" s="225"/>
+      <c r="O44" s="225"/>
+      <c r="P44" s="225"/>
+      <c r="Q44" s="226"/>
     </row>
     <row r="45" spans="2:20" x14ac:dyDescent="0.3">
-      <c r="B45" s="237"/>
-      <c r="C45" s="238"/>
-      <c r="D45" s="238"/>
-      <c r="E45" s="238"/>
-      <c r="F45" s="238"/>
-      <c r="G45" s="238"/>
-      <c r="H45" s="238"/>
-      <c r="I45" s="238"/>
-      <c r="J45" s="238"/>
-      <c r="K45" s="238"/>
-      <c r="L45" s="238"/>
-      <c r="M45" s="238"/>
-      <c r="N45" s="238"/>
-      <c r="O45" s="238"/>
-      <c r="P45" s="238"/>
-      <c r="Q45" s="239"/>
+      <c r="B45" s="224"/>
+      <c r="C45" s="225"/>
+      <c r="D45" s="225"/>
+      <c r="E45" s="225"/>
+      <c r="F45" s="225"/>
+      <c r="G45" s="225"/>
+      <c r="H45" s="225"/>
+      <c r="I45" s="225"/>
+      <c r="J45" s="225"/>
+      <c r="K45" s="225"/>
+      <c r="L45" s="225"/>
+      <c r="M45" s="225"/>
+      <c r="N45" s="225"/>
+      <c r="O45" s="225"/>
+      <c r="P45" s="225"/>
+      <c r="Q45" s="226"/>
     </row>
     <row r="46" spans="2:20" x14ac:dyDescent="0.3">
-      <c r="B46" s="240"/>
-      <c r="C46" s="241"/>
-      <c r="D46" s="241"/>
-      <c r="E46" s="241"/>
-      <c r="F46" s="241"/>
-      <c r="G46" s="241"/>
-      <c r="H46" s="241"/>
-      <c r="I46" s="241"/>
-      <c r="J46" s="241"/>
-      <c r="K46" s="241"/>
-      <c r="L46" s="241"/>
-      <c r="M46" s="241"/>
-      <c r="N46" s="241"/>
-      <c r="O46" s="241"/>
-      <c r="P46" s="241"/>
-      <c r="Q46" s="242"/>
+      <c r="B46" s="227"/>
+      <c r="C46" s="228"/>
+      <c r="D46" s="228"/>
+      <c r="E46" s="228"/>
+      <c r="F46" s="228"/>
+      <c r="G46" s="228"/>
+      <c r="H46" s="228"/>
+      <c r="I46" s="228"/>
+      <c r="J46" s="228"/>
+      <c r="K46" s="228"/>
+      <c r="L46" s="228"/>
+      <c r="M46" s="228"/>
+      <c r="N46" s="228"/>
+      <c r="O46" s="228"/>
+      <c r="P46" s="228"/>
+      <c r="Q46" s="229"/>
     </row>
     <row r="47" spans="2:20" x14ac:dyDescent="0.3">
       <c r="B47" s="35"/>
@@ -5692,26 +5680,26 @@
       <c r="R55" s="28"/>
     </row>
     <row r="56" spans="2:20" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B56" s="245" t="s">
+      <c r="B56" s="244" t="s">
         <v>50</v>
       </c>
-      <c r="C56" s="246"/>
-      <c r="D56" s="246"/>
-      <c r="E56" s="246"/>
-      <c r="F56" s="246"/>
-      <c r="G56" s="246"/>
-      <c r="H56" s="246"/>
-      <c r="I56" s="246"/>
-      <c r="J56" s="246"/>
-      <c r="K56" s="246"/>
-      <c r="L56" s="246"/>
-      <c r="M56" s="246"/>
-      <c r="N56" s="246"/>
-      <c r="O56" s="246"/>
-      <c r="P56" s="246"/>
-      <c r="Q56" s="246"/>
-      <c r="R56" s="246"/>
-      <c r="S56" s="264"/>
+      <c r="C56" s="245"/>
+      <c r="D56" s="245"/>
+      <c r="E56" s="245"/>
+      <c r="F56" s="245"/>
+      <c r="G56" s="245"/>
+      <c r="H56" s="245"/>
+      <c r="I56" s="245"/>
+      <c r="J56" s="245"/>
+      <c r="K56" s="245"/>
+      <c r="L56" s="245"/>
+      <c r="M56" s="245"/>
+      <c r="N56" s="245"/>
+      <c r="O56" s="245"/>
+      <c r="P56" s="245"/>
+      <c r="Q56" s="245"/>
+      <c r="R56" s="245"/>
+      <c r="S56" s="272"/>
     </row>
     <row r="57" spans="2:20" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B57" s="97" t="s">
@@ -5760,19 +5748,19 @@
       <c r="Q57" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="R57" s="265" t="s">
+      <c r="R57" s="293" t="s">
         <v>38</v>
       </c>
-      <c r="S57" s="266"/>
+      <c r="S57" s="294"/>
       <c r="T57" s="129" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="58" spans="2:20" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B58" s="261" t="s">
+      <c r="B58" s="262" t="s">
         <v>55</v>
       </c>
-      <c r="C58" s="262" t="s">
+      <c r="C58" s="263" t="s">
         <v>56</v>
       </c>
       <c r="D58" s="139" t="s">
@@ -5820,17 +5808,17 @@
       <c r="Q58" s="142" t="s">
         <v>60</v>
       </c>
-      <c r="R58" s="267" t="s">
+      <c r="R58" s="264" t="s">
         <v>61</v>
       </c>
-      <c r="S58" s="268"/>
+      <c r="S58" s="265"/>
       <c r="T58" s="130" t="s">
         <v>62</v>
       </c>
     </row>
     <row r="59" spans="2:20" x14ac:dyDescent="0.3">
-      <c r="B59" s="261"/>
-      <c r="C59" s="262"/>
+      <c r="B59" s="262"/>
+      <c r="C59" s="263"/>
       <c r="D59" s="139" t="s">
         <v>24</v>
       </c>
@@ -5876,17 +5864,17 @@
       <c r="Q59" s="142" t="s">
         <v>60</v>
       </c>
-      <c r="R59" s="269"/>
-      <c r="S59" s="270"/>
+      <c r="R59" s="266"/>
+      <c r="S59" s="267"/>
       <c r="T59" s="130" t="s">
         <v>62</v>
       </c>
     </row>
     <row r="60" spans="2:20" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B60" s="261" t="s">
+      <c r="B60" s="262" t="s">
         <v>241</v>
       </c>
-      <c r="C60" s="262" t="s">
+      <c r="C60" s="263" t="s">
         <v>56</v>
       </c>
       <c r="D60" s="139" t="s">
@@ -5934,15 +5922,15 @@
       <c r="Q60" s="142" t="s">
         <v>60</v>
       </c>
-      <c r="R60" s="269"/>
-      <c r="S60" s="270"/>
+      <c r="R60" s="266"/>
+      <c r="S60" s="267"/>
       <c r="T60" s="130" t="s">
         <v>62</v>
       </c>
     </row>
     <row r="61" spans="2:20" x14ac:dyDescent="0.3">
-      <c r="B61" s="261"/>
-      <c r="C61" s="262"/>
+      <c r="B61" s="262"/>
+      <c r="C61" s="263"/>
       <c r="D61" s="139" t="s">
         <v>24</v>
       </c>
@@ -5988,17 +5976,17 @@
       <c r="Q61" s="142" t="s">
         <v>60</v>
       </c>
-      <c r="R61" s="271"/>
-      <c r="S61" s="272"/>
+      <c r="R61" s="288"/>
+      <c r="S61" s="289"/>
       <c r="T61" s="130" t="s">
         <v>62</v>
       </c>
     </row>
     <row r="62" spans="2:20" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B62" s="278" t="s">
+      <c r="B62" s="279" t="s">
         <v>63</v>
       </c>
-      <c r="C62" s="231" t="s">
+      <c r="C62" s="238" t="s">
         <v>31</v>
       </c>
       <c r="D62" s="117" t="s">
@@ -6046,17 +6034,17 @@
       <c r="Q62" s="94" t="s">
         <v>64</v>
       </c>
-      <c r="R62" s="255" t="s">
+      <c r="R62" s="281" t="s">
         <v>65</v>
       </c>
-      <c r="S62" s="256"/>
+      <c r="S62" s="282"/>
       <c r="T62" s="130" t="s">
         <v>66</v>
       </c>
     </row>
     <row r="63" spans="2:20" x14ac:dyDescent="0.3">
-      <c r="B63" s="279"/>
-      <c r="C63" s="232"/>
+      <c r="B63" s="280"/>
+      <c r="C63" s="239"/>
       <c r="D63" s="117" t="s">
         <v>24</v>
       </c>
@@ -6102,17 +6090,17 @@
       <c r="Q63" s="94" t="s">
         <v>64</v>
       </c>
-      <c r="R63" s="257"/>
-      <c r="S63" s="258"/>
+      <c r="R63" s="283"/>
+      <c r="S63" s="284"/>
       <c r="T63" s="130" t="s">
         <v>66</v>
       </c>
     </row>
     <row r="64" spans="2:20" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B64" s="261" t="s">
+      <c r="B64" s="262" t="s">
         <v>67</v>
       </c>
-      <c r="C64" s="262" t="s">
+      <c r="C64" s="263" t="s">
         <v>56</v>
       </c>
       <c r="D64" s="139" t="s">
@@ -6160,17 +6148,17 @@
       <c r="Q64" s="142" t="s">
         <v>60</v>
       </c>
-      <c r="R64" s="267" t="s">
+      <c r="R64" s="264" t="s">
         <v>61</v>
       </c>
-      <c r="S64" s="268"/>
+      <c r="S64" s="265"/>
       <c r="T64" s="130" t="s">
         <v>62</v>
       </c>
     </row>
     <row r="65" spans="2:20" x14ac:dyDescent="0.3">
-      <c r="B65" s="261"/>
-      <c r="C65" s="262"/>
+      <c r="B65" s="262"/>
+      <c r="C65" s="263"/>
       <c r="D65" s="139" t="s">
         <v>24</v>
       </c>
@@ -6216,17 +6204,17 @@
       <c r="Q65" s="142" t="s">
         <v>60</v>
       </c>
-      <c r="R65" s="269"/>
-      <c r="S65" s="270"/>
+      <c r="R65" s="266"/>
+      <c r="S65" s="267"/>
       <c r="T65" s="130" t="s">
         <v>62</v>
       </c>
     </row>
     <row r="66" spans="2:20" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B66" s="278" t="s">
+      <c r="B66" s="279" t="s">
         <v>68</v>
       </c>
-      <c r="C66" s="231" t="s">
+      <c r="C66" s="238" t="s">
         <v>31</v>
       </c>
       <c r="D66" s="117" t="s">
@@ -6274,17 +6262,17 @@
       <c r="Q66" s="94" t="s">
         <v>64</v>
       </c>
-      <c r="R66" s="255" t="s">
+      <c r="R66" s="281" t="s">
         <v>65</v>
       </c>
-      <c r="S66" s="256"/>
+      <c r="S66" s="282"/>
       <c r="T66" s="130" t="s">
         <v>66</v>
       </c>
     </row>
     <row r="67" spans="2:20" x14ac:dyDescent="0.3">
-      <c r="B67" s="279"/>
-      <c r="C67" s="232"/>
+      <c r="B67" s="280"/>
+      <c r="C67" s="239"/>
       <c r="D67" s="117" t="s">
         <v>24</v>
       </c>
@@ -6330,17 +6318,17 @@
       <c r="Q67" s="94" t="s">
         <v>64</v>
       </c>
-      <c r="R67" s="257"/>
-      <c r="S67" s="258"/>
+      <c r="R67" s="283"/>
+      <c r="S67" s="284"/>
       <c r="T67" s="130" t="s">
         <v>66</v>
       </c>
     </row>
     <row r="68" spans="2:20" x14ac:dyDescent="0.3">
-      <c r="B68" s="283" t="s">
+      <c r="B68" s="290" t="s">
         <v>69</v>
       </c>
-      <c r="C68" s="262" t="s">
+      <c r="C68" s="263" t="s">
         <v>56</v>
       </c>
       <c r="D68" s="139" t="s">
@@ -6388,17 +6376,17 @@
       <c r="Q68" s="142" t="s">
         <v>60</v>
       </c>
-      <c r="R68" s="267" t="s">
+      <c r="R68" s="264" t="s">
         <v>61</v>
       </c>
-      <c r="S68" s="268"/>
+      <c r="S68" s="265"/>
       <c r="T68" s="130" t="s">
         <v>62</v>
       </c>
     </row>
     <row r="69" spans="2:20" x14ac:dyDescent="0.3">
-      <c r="B69" s="284"/>
-      <c r="C69" s="262"/>
+      <c r="B69" s="291"/>
+      <c r="C69" s="263"/>
       <c r="D69" s="139" t="s">
         <v>24</v>
       </c>
@@ -6444,17 +6432,17 @@
       <c r="Q69" s="142" t="s">
         <v>60</v>
       </c>
-      <c r="R69" s="269"/>
-      <c r="S69" s="270"/>
+      <c r="R69" s="266"/>
+      <c r="S69" s="267"/>
       <c r="T69" s="130" t="s">
         <v>62</v>
       </c>
     </row>
     <row r="70" spans="2:20" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B70" s="261" t="s">
+      <c r="B70" s="262" t="s">
         <v>70</v>
       </c>
-      <c r="C70" s="262" t="s">
+      <c r="C70" s="263" t="s">
         <v>56</v>
       </c>
       <c r="D70" s="139" t="s">
@@ -6502,15 +6490,15 @@
       <c r="Q70" s="142" t="s">
         <v>60</v>
       </c>
-      <c r="R70" s="269"/>
-      <c r="S70" s="270"/>
+      <c r="R70" s="266"/>
+      <c r="S70" s="267"/>
       <c r="T70" s="130" t="s">
         <v>62</v>
       </c>
     </row>
     <row r="71" spans="2:20" x14ac:dyDescent="0.3">
-      <c r="B71" s="261"/>
-      <c r="C71" s="262"/>
+      <c r="B71" s="262"/>
+      <c r="C71" s="263"/>
       <c r="D71" s="139" t="s">
         <v>24</v>
       </c>
@@ -6556,17 +6544,17 @@
       <c r="Q71" s="142" t="s">
         <v>60</v>
       </c>
-      <c r="R71" s="271"/>
-      <c r="S71" s="272"/>
+      <c r="R71" s="288"/>
+      <c r="S71" s="289"/>
       <c r="T71" s="130" t="s">
         <v>62</v>
       </c>
     </row>
     <row r="72" spans="2:20" x14ac:dyDescent="0.3">
-      <c r="B72" s="280" t="s">
+      <c r="B72" s="285" t="s">
         <v>71</v>
       </c>
-      <c r="C72" s="281" t="s">
+      <c r="C72" s="286" t="s">
         <v>31</v>
       </c>
       <c r="D72" s="185" t="s">
@@ -6614,17 +6602,17 @@
       <c r="Q72" s="187" t="s">
         <v>72</v>
       </c>
-      <c r="R72" s="274" t="s">
+      <c r="R72" s="268" t="s">
         <v>73</v>
       </c>
-      <c r="S72" s="275"/>
+      <c r="S72" s="269"/>
       <c r="T72" s="130" t="s">
         <v>74</v>
       </c>
     </row>
     <row r="73" spans="2:20" x14ac:dyDescent="0.3">
-      <c r="B73" s="280"/>
-      <c r="C73" s="282"/>
+      <c r="B73" s="285"/>
+      <c r="C73" s="287"/>
       <c r="D73" s="185" t="s">
         <v>24</v>
       </c>
@@ -6670,17 +6658,17 @@
       <c r="Q73" s="187" t="s">
         <v>72</v>
       </c>
-      <c r="R73" s="276"/>
-      <c r="S73" s="277"/>
+      <c r="R73" s="270"/>
+      <c r="S73" s="271"/>
       <c r="T73" s="130" t="s">
         <v>74</v>
       </c>
     </row>
     <row r="74" spans="2:20" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B74" s="261" t="s">
-        <v>75</v>
-      </c>
-      <c r="C74" s="262" t="s">
+      <c r="B74" s="262" t="s">
+        <v>75</v>
+      </c>
+      <c r="C74" s="263" t="s">
         <v>56</v>
       </c>
       <c r="D74" s="139" t="s">
@@ -6728,17 +6716,17 @@
       <c r="Q74" s="142" t="s">
         <v>60</v>
       </c>
-      <c r="R74" s="267" t="s">
+      <c r="R74" s="264" t="s">
         <v>61</v>
       </c>
-      <c r="S74" s="268"/>
+      <c r="S74" s="265"/>
       <c r="T74" s="130" t="s">
         <v>62</v>
       </c>
     </row>
     <row r="75" spans="2:20" x14ac:dyDescent="0.3">
-      <c r="B75" s="261"/>
-      <c r="C75" s="262"/>
+      <c r="B75" s="262"/>
+      <c r="C75" s="263"/>
       <c r="D75" s="139" t="s">
         <v>24</v>
       </c>
@@ -6784,17 +6772,17 @@
       <c r="Q75" s="142" t="s">
         <v>60</v>
       </c>
-      <c r="R75" s="269"/>
-      <c r="S75" s="270"/>
+      <c r="R75" s="266"/>
+      <c r="S75" s="267"/>
       <c r="T75" s="130" t="s">
         <v>62</v>
       </c>
     </row>
     <row r="76" spans="2:20" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B76" s="261" t="s">
+      <c r="B76" s="262" t="s">
         <v>76</v>
       </c>
-      <c r="C76" s="262" t="s">
+      <c r="C76" s="263" t="s">
         <v>56</v>
       </c>
       <c r="D76" s="139" t="s">
@@ -6842,15 +6830,15 @@
       <c r="Q76" s="142" t="s">
         <v>60</v>
       </c>
-      <c r="R76" s="269"/>
-      <c r="S76" s="270"/>
+      <c r="R76" s="266"/>
+      <c r="S76" s="267"/>
       <c r="T76" s="130" t="s">
         <v>62</v>
       </c>
     </row>
     <row r="77" spans="2:20" x14ac:dyDescent="0.3">
-      <c r="B77" s="261"/>
-      <c r="C77" s="262"/>
+      <c r="B77" s="262"/>
+      <c r="C77" s="263"/>
       <c r="D77" s="139" t="s">
         <v>24</v>
       </c>
@@ -6896,17 +6884,17 @@
       <c r="Q77" s="142" t="s">
         <v>60</v>
       </c>
-      <c r="R77" s="269"/>
-      <c r="S77" s="270"/>
+      <c r="R77" s="266"/>
+      <c r="S77" s="267"/>
       <c r="T77" s="130" t="s">
         <v>62</v>
       </c>
     </row>
     <row r="78" spans="2:20" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B78" s="261" t="s">
+      <c r="B78" s="262" t="s">
         <v>77</v>
       </c>
-      <c r="C78" s="262" t="s">
+      <c r="C78" s="263" t="s">
         <v>56</v>
       </c>
       <c r="D78" s="139" t="s">
@@ -6954,15 +6942,15 @@
       <c r="Q78" s="142" t="s">
         <v>60</v>
       </c>
-      <c r="R78" s="269"/>
-      <c r="S78" s="270"/>
+      <c r="R78" s="266"/>
+      <c r="S78" s="267"/>
       <c r="T78" s="130" t="s">
         <v>62</v>
       </c>
     </row>
     <row r="79" spans="2:20" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B79" s="261"/>
-      <c r="C79" s="262"/>
+      <c r="B79" s="262"/>
+      <c r="C79" s="263"/>
       <c r="D79" s="139" t="s">
         <v>24</v>
       </c>
@@ -7008,43 +6996,43 @@
       <c r="Q79" s="142" t="s">
         <v>60</v>
       </c>
-      <c r="R79" s="271"/>
-      <c r="S79" s="272"/>
+      <c r="R79" s="288"/>
+      <c r="S79" s="289"/>
       <c r="T79" s="130" t="s">
         <v>62</v>
       </c>
     </row>
     <row r="80" spans="2:20" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B80" s="245" t="s">
+      <c r="B80" s="244" t="s">
         <v>78</v>
       </c>
-      <c r="C80" s="246"/>
-      <c r="D80" s="246"/>
-      <c r="E80" s="246"/>
-      <c r="F80" s="246"/>
-      <c r="G80" s="246"/>
-      <c r="H80" s="246"/>
-      <c r="I80" s="246"/>
-      <c r="J80" s="246"/>
-      <c r="K80" s="246"/>
-      <c r="L80" s="246"/>
-      <c r="M80" s="246"/>
-      <c r="N80" s="246"/>
-      <c r="O80" s="246"/>
-      <c r="P80" s="246"/>
-      <c r="Q80" s="246"/>
-      <c r="R80" s="229"/>
-      <c r="S80" s="288"/>
+      <c r="C80" s="245"/>
+      <c r="D80" s="245"/>
+      <c r="E80" s="245"/>
+      <c r="F80" s="245"/>
+      <c r="G80" s="245"/>
+      <c r="H80" s="245"/>
+      <c r="I80" s="245"/>
+      <c r="J80" s="245"/>
+      <c r="K80" s="245"/>
+      <c r="L80" s="245"/>
+      <c r="M80" s="245"/>
+      <c r="N80" s="245"/>
+      <c r="O80" s="245"/>
+      <c r="P80" s="245"/>
+      <c r="Q80" s="245"/>
+      <c r="R80" s="232"/>
+      <c r="S80" s="273"/>
       <c r="T80" s="130"/>
     </row>
     <row r="81" spans="2:20" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B81" s="97" t="s">
         <v>1</v>
       </c>
-      <c r="C81" s="285" t="s">
+      <c r="C81" s="259" t="s">
         <v>2</v>
       </c>
-      <c r="D81" s="286"/>
+      <c r="D81" s="260"/>
       <c r="E81" s="120" t="s">
         <v>3</v>
       </c>
@@ -7084,17 +7072,17 @@
       <c r="Q81" s="120" t="s">
         <v>14</v>
       </c>
-      <c r="R81" s="285" t="s">
+      <c r="R81" s="259" t="s">
         <v>38</v>
       </c>
-      <c r="S81" s="287"/>
+      <c r="S81" s="261"/>
       <c r="T81" s="130"/>
     </row>
     <row r="82" spans="2:20" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B82" s="289" t="s">
+      <c r="B82" s="274" t="s">
         <v>79</v>
       </c>
-      <c r="C82" s="291" t="s">
+      <c r="C82" s="276" t="s">
         <v>80</v>
       </c>
       <c r="D82" s="139" t="s">
@@ -7142,17 +7130,17 @@
       <c r="Q82" s="142" t="s">
         <v>60</v>
       </c>
-      <c r="R82" s="274" t="s">
+      <c r="R82" s="268" t="s">
         <v>81</v>
       </c>
-      <c r="S82" s="275"/>
+      <c r="S82" s="269"/>
       <c r="T82" s="130" t="s">
         <v>74</v>
       </c>
     </row>
     <row r="83" spans="2:20" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B83" s="290"/>
-      <c r="C83" s="292"/>
+      <c r="B83" s="275"/>
+      <c r="C83" s="277"/>
       <c r="D83" s="139" t="s">
         <v>24</v>
       </c>
@@ -7198,43 +7186,43 @@
       <c r="Q83" s="142" t="s">
         <v>60</v>
       </c>
-      <c r="R83" s="276"/>
-      <c r="S83" s="277"/>
+      <c r="R83" s="270"/>
+      <c r="S83" s="271"/>
       <c r="T83" s="130" t="s">
         <v>74</v>
       </c>
     </row>
     <row r="84" spans="2:20" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B84" s="245" t="s">
+      <c r="B84" s="244" t="s">
         <v>82</v>
       </c>
-      <c r="C84" s="246"/>
-      <c r="D84" s="246"/>
-      <c r="E84" s="246"/>
-      <c r="F84" s="246"/>
-      <c r="G84" s="246"/>
-      <c r="H84" s="246"/>
-      <c r="I84" s="246"/>
-      <c r="J84" s="246"/>
-      <c r="K84" s="246"/>
-      <c r="L84" s="246"/>
-      <c r="M84" s="246"/>
-      <c r="N84" s="246"/>
-      <c r="O84" s="246"/>
-      <c r="P84" s="246"/>
-      <c r="Q84" s="246"/>
-      <c r="R84" s="246"/>
-      <c r="S84" s="264"/>
+      <c r="C84" s="245"/>
+      <c r="D84" s="245"/>
+      <c r="E84" s="245"/>
+      <c r="F84" s="245"/>
+      <c r="G84" s="245"/>
+      <c r="H84" s="245"/>
+      <c r="I84" s="245"/>
+      <c r="J84" s="245"/>
+      <c r="K84" s="245"/>
+      <c r="L84" s="245"/>
+      <c r="M84" s="245"/>
+      <c r="N84" s="245"/>
+      <c r="O84" s="245"/>
+      <c r="P84" s="245"/>
+      <c r="Q84" s="245"/>
+      <c r="R84" s="245"/>
+      <c r="S84" s="272"/>
       <c r="T84" s="130"/>
     </row>
     <row r="85" spans="2:20" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B85" s="97" t="s">
         <v>1</v>
       </c>
-      <c r="C85" s="285" t="s">
+      <c r="C85" s="259" t="s">
         <v>2</v>
       </c>
-      <c r="D85" s="286"/>
+      <c r="D85" s="260"/>
       <c r="E85" s="120" t="s">
         <v>3</v>
       </c>
@@ -7274,17 +7262,17 @@
       <c r="Q85" s="120" t="s">
         <v>14</v>
       </c>
-      <c r="R85" s="285" t="s">
+      <c r="R85" s="259" t="s">
         <v>38</v>
       </c>
-      <c r="S85" s="287"/>
+      <c r="S85" s="261"/>
       <c r="T85" s="130"/>
     </row>
     <row r="86" spans="2:20" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B86" s="261" t="s">
+      <c r="B86" s="262" t="s">
         <v>83</v>
       </c>
-      <c r="C86" s="262" t="s">
+      <c r="C86" s="263" t="s">
         <v>80</v>
       </c>
       <c r="D86" s="139" t="s">
@@ -7332,17 +7320,17 @@
       <c r="Q86" s="142" t="s">
         <v>60</v>
       </c>
-      <c r="R86" s="274" t="s">
+      <c r="R86" s="268" t="s">
         <v>81</v>
       </c>
-      <c r="S86" s="275"/>
+      <c r="S86" s="269"/>
       <c r="T86" s="130" t="s">
         <v>62</v>
       </c>
     </row>
     <row r="87" spans="2:20" x14ac:dyDescent="0.3">
-      <c r="B87" s="261"/>
-      <c r="C87" s="262"/>
+      <c r="B87" s="262"/>
+      <c r="C87" s="263"/>
       <c r="D87" s="139" t="s">
         <v>24</v>
       </c>
@@ -7388,43 +7376,43 @@
       <c r="Q87" s="142" t="s">
         <v>60</v>
       </c>
-      <c r="R87" s="276"/>
-      <c r="S87" s="277"/>
+      <c r="R87" s="270"/>
+      <c r="S87" s="271"/>
       <c r="T87" s="130" t="s">
         <v>62</v>
       </c>
     </row>
     <row r="88" spans="2:20" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B88" s="225" t="s">
-        <v>85</v>
-      </c>
-      <c r="C88" s="226"/>
-      <c r="D88" s="226"/>
-      <c r="E88" s="226"/>
-      <c r="F88" s="226"/>
-      <c r="G88" s="226"/>
-      <c r="H88" s="226"/>
-      <c r="I88" s="226"/>
-      <c r="J88" s="226"/>
-      <c r="K88" s="226"/>
-      <c r="L88" s="226"/>
-      <c r="M88" s="226"/>
-      <c r="N88" s="226"/>
-      <c r="O88" s="226"/>
-      <c r="P88" s="226"/>
-      <c r="Q88" s="226"/>
-      <c r="R88" s="226"/>
-      <c r="S88" s="273"/>
+      <c r="B88" s="236" t="s">
+        <v>85</v>
+      </c>
+      <c r="C88" s="237"/>
+      <c r="D88" s="237"/>
+      <c r="E88" s="237"/>
+      <c r="F88" s="237"/>
+      <c r="G88" s="237"/>
+      <c r="H88" s="237"/>
+      <c r="I88" s="237"/>
+      <c r="J88" s="237"/>
+      <c r="K88" s="237"/>
+      <c r="L88" s="237"/>
+      <c r="M88" s="237"/>
+      <c r="N88" s="237"/>
+      <c r="O88" s="237"/>
+      <c r="P88" s="237"/>
+      <c r="Q88" s="237"/>
+      <c r="R88" s="237"/>
+      <c r="S88" s="278"/>
       <c r="T88" s="130"/>
     </row>
     <row r="89" spans="2:20" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B89" s="97" t="s">
         <v>1</v>
       </c>
-      <c r="C89" s="285" t="s">
+      <c r="C89" s="259" t="s">
         <v>2</v>
       </c>
-      <c r="D89" s="286"/>
+      <c r="D89" s="260"/>
       <c r="E89" s="120" t="s">
         <v>3</v>
       </c>
@@ -7464,17 +7452,17 @@
       <c r="Q89" s="120" t="s">
         <v>14</v>
       </c>
-      <c r="R89" s="285" t="s">
+      <c r="R89" s="259" t="s">
         <v>38</v>
       </c>
-      <c r="S89" s="287"/>
+      <c r="S89" s="261"/>
       <c r="T89" s="130"/>
     </row>
     <row r="90" spans="2:20" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B90" s="261" t="s">
+      <c r="B90" s="262" t="s">
         <v>86</v>
       </c>
-      <c r="C90" s="262" t="s">
+      <c r="C90" s="263" t="s">
         <v>80</v>
       </c>
       <c r="D90" s="139" t="s">
@@ -7522,17 +7510,17 @@
       <c r="Q90" s="142" t="s">
         <v>60</v>
       </c>
-      <c r="R90" s="274" t="s">
+      <c r="R90" s="268" t="s">
         <v>81</v>
       </c>
-      <c r="S90" s="275"/>
+      <c r="S90" s="269"/>
       <c r="T90" s="130" t="s">
         <v>62</v>
       </c>
     </row>
     <row r="91" spans="2:20" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B91" s="261"/>
-      <c r="C91" s="262"/>
+      <c r="B91" s="262"/>
+      <c r="C91" s="263"/>
       <c r="D91" s="139" t="s">
         <v>24</v>
       </c>
@@ -7578,43 +7566,43 @@
       <c r="Q91" s="142" t="s">
         <v>60</v>
       </c>
-      <c r="R91" s="276"/>
-      <c r="S91" s="277"/>
+      <c r="R91" s="270"/>
+      <c r="S91" s="271"/>
       <c r="T91" s="130" t="s">
         <v>62</v>
       </c>
     </row>
     <row r="92" spans="2:20" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B92" s="225" t="s">
+      <c r="B92" s="236" t="s">
         <v>87</v>
       </c>
-      <c r="C92" s="226"/>
-      <c r="D92" s="226"/>
-      <c r="E92" s="226"/>
-      <c r="F92" s="226"/>
-      <c r="G92" s="226"/>
-      <c r="H92" s="226"/>
-      <c r="I92" s="226"/>
-      <c r="J92" s="226"/>
-      <c r="K92" s="226"/>
-      <c r="L92" s="226"/>
-      <c r="M92" s="226"/>
-      <c r="N92" s="226"/>
-      <c r="O92" s="226"/>
-      <c r="P92" s="226"/>
-      <c r="Q92" s="226"/>
-      <c r="R92" s="226"/>
-      <c r="S92" s="273"/>
+      <c r="C92" s="237"/>
+      <c r="D92" s="237"/>
+      <c r="E92" s="237"/>
+      <c r="F92" s="237"/>
+      <c r="G92" s="237"/>
+      <c r="H92" s="237"/>
+      <c r="I92" s="237"/>
+      <c r="J92" s="237"/>
+      <c r="K92" s="237"/>
+      <c r="L92" s="237"/>
+      <c r="M92" s="237"/>
+      <c r="N92" s="237"/>
+      <c r="O92" s="237"/>
+      <c r="P92" s="237"/>
+      <c r="Q92" s="237"/>
+      <c r="R92" s="237"/>
+      <c r="S92" s="278"/>
       <c r="T92" s="130"/>
     </row>
     <row r="93" spans="2:20" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B93" s="97" t="s">
         <v>1</v>
       </c>
-      <c r="C93" s="285" t="s">
+      <c r="C93" s="259" t="s">
         <v>2</v>
       </c>
-      <c r="D93" s="286"/>
+      <c r="D93" s="260"/>
       <c r="E93" s="120" t="s">
         <v>3</v>
       </c>
@@ -7654,17 +7642,17 @@
       <c r="Q93" s="120" t="s">
         <v>14</v>
       </c>
-      <c r="R93" s="285" t="s">
+      <c r="R93" s="259" t="s">
         <v>38</v>
       </c>
-      <c r="S93" s="287"/>
+      <c r="S93" s="261"/>
       <c r="T93" s="130"/>
     </row>
     <row r="94" spans="2:20" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B94" s="261" t="s">
+      <c r="B94" s="262" t="s">
         <v>88</v>
       </c>
-      <c r="C94" s="262" t="s">
+      <c r="C94" s="263" t="s">
         <v>80</v>
       </c>
       <c r="D94" s="139" t="s">
@@ -7712,17 +7700,17 @@
       <c r="Q94" s="142" t="s">
         <v>60</v>
       </c>
-      <c r="R94" s="274" t="s">
+      <c r="R94" s="268" t="s">
         <v>81</v>
       </c>
-      <c r="S94" s="275"/>
+      <c r="S94" s="269"/>
       <c r="T94" s="130" t="s">
         <v>62</v>
       </c>
     </row>
     <row r="95" spans="2:20" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B95" s="261"/>
-      <c r="C95" s="262"/>
+      <c r="B95" s="262"/>
+      <c r="C95" s="263"/>
       <c r="D95" s="139" t="s">
         <v>24</v>
       </c>
@@ -7768,42 +7756,42 @@
       <c r="Q95" s="142" t="s">
         <v>60</v>
       </c>
-      <c r="R95" s="276"/>
-      <c r="S95" s="277"/>
+      <c r="R95" s="270"/>
+      <c r="S95" s="271"/>
       <c r="T95" s="130" t="s">
         <v>62</v>
       </c>
     </row>
     <row r="96" spans="2:20" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B96" s="245" t="s">
+      <c r="B96" s="244" t="s">
         <v>91</v>
       </c>
-      <c r="C96" s="246"/>
-      <c r="D96" s="246"/>
-      <c r="E96" s="246"/>
-      <c r="F96" s="246"/>
-      <c r="G96" s="246"/>
-      <c r="H96" s="246"/>
-      <c r="I96" s="246"/>
-      <c r="J96" s="246"/>
-      <c r="K96" s="246"/>
-      <c r="L96" s="246"/>
-      <c r="M96" s="246"/>
-      <c r="N96" s="246"/>
-      <c r="O96" s="246"/>
-      <c r="P96" s="246"/>
-      <c r="Q96" s="246"/>
-      <c r="R96" s="229"/>
-      <c r="S96" s="229"/>
+      <c r="C96" s="245"/>
+      <c r="D96" s="245"/>
+      <c r="E96" s="245"/>
+      <c r="F96" s="245"/>
+      <c r="G96" s="245"/>
+      <c r="H96" s="245"/>
+      <c r="I96" s="245"/>
+      <c r="J96" s="245"/>
+      <c r="K96" s="245"/>
+      <c r="L96" s="245"/>
+      <c r="M96" s="245"/>
+      <c r="N96" s="245"/>
+      <c r="O96" s="245"/>
+      <c r="P96" s="245"/>
+      <c r="Q96" s="245"/>
+      <c r="R96" s="232"/>
+      <c r="S96" s="232"/>
     </row>
     <row r="97" spans="2:21" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B97" s="97" t="s">
         <v>1</v>
       </c>
-      <c r="C97" s="285" t="s">
+      <c r="C97" s="259" t="s">
         <v>2</v>
       </c>
-      <c r="D97" s="286"/>
+      <c r="D97" s="260"/>
       <c r="E97" s="120" t="s">
         <v>3</v>
       </c>
@@ -7843,16 +7831,16 @@
       <c r="Q97" s="120" t="s">
         <v>14</v>
       </c>
-      <c r="R97" s="285" t="s">
+      <c r="R97" s="259" t="s">
         <v>38</v>
       </c>
-      <c r="S97" s="287"/>
+      <c r="S97" s="261"/>
     </row>
     <row r="98" spans="2:21" x14ac:dyDescent="0.3">
-      <c r="B98" s="261" t="s">
+      <c r="B98" s="262" t="s">
         <v>92</v>
       </c>
-      <c r="C98" s="262" t="s">
+      <c r="C98" s="263" t="s">
         <v>80</v>
       </c>
       <c r="D98" s="139" t="s">
@@ -7900,18 +7888,18 @@
       <c r="Q98" s="142" t="s">
         <v>60</v>
       </c>
-      <c r="R98" s="267" t="s">
+      <c r="R98" s="264" t="s">
         <v>93</v>
       </c>
-      <c r="S98" s="268"/>
+      <c r="S98" s="265"/>
       <c r="T98" s="130" t="s">
         <v>62</v>
       </c>
       <c r="U98"/>
     </row>
     <row r="99" spans="2:21" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B99" s="261"/>
-      <c r="C99" s="262"/>
+      <c r="B99" s="262"/>
+      <c r="C99" s="263"/>
       <c r="D99" s="139" t="s">
         <v>24</v>
       </c>
@@ -7957,43 +7945,43 @@
       <c r="Q99" s="142" t="s">
         <v>60</v>
       </c>
-      <c r="R99" s="269"/>
-      <c r="S99" s="270"/>
+      <c r="R99" s="266"/>
+      <c r="S99" s="267"/>
       <c r="T99" s="130" t="s">
         <v>62</v>
       </c>
       <c r="U99"/>
     </row>
     <row r="100" spans="2:21" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B100" s="245" t="s">
+      <c r="B100" s="244" t="s">
         <v>94</v>
       </c>
-      <c r="C100" s="246"/>
-      <c r="D100" s="246"/>
-      <c r="E100" s="246"/>
-      <c r="F100" s="246"/>
-      <c r="G100" s="246"/>
-      <c r="H100" s="246"/>
-      <c r="I100" s="246"/>
-      <c r="J100" s="246"/>
-      <c r="K100" s="246"/>
-      <c r="L100" s="246"/>
-      <c r="M100" s="246"/>
-      <c r="N100" s="246"/>
-      <c r="O100" s="246"/>
-      <c r="P100" s="246"/>
-      <c r="Q100" s="246"/>
-      <c r="R100" s="246"/>
-      <c r="S100" s="264"/>
+      <c r="C100" s="245"/>
+      <c r="D100" s="245"/>
+      <c r="E100" s="245"/>
+      <c r="F100" s="245"/>
+      <c r="G100" s="245"/>
+      <c r="H100" s="245"/>
+      <c r="I100" s="245"/>
+      <c r="J100" s="245"/>
+      <c r="K100" s="245"/>
+      <c r="L100" s="245"/>
+      <c r="M100" s="245"/>
+      <c r="N100" s="245"/>
+      <c r="O100" s="245"/>
+      <c r="P100" s="245"/>
+      <c r="Q100" s="245"/>
+      <c r="R100" s="245"/>
+      <c r="S100" s="272"/>
     </row>
     <row r="101" spans="2:21" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B101" s="97" t="s">
         <v>1</v>
       </c>
-      <c r="C101" s="285" t="s">
+      <c r="C101" s="259" t="s">
         <v>2</v>
       </c>
-      <c r="D101" s="286"/>
+      <c r="D101" s="260"/>
       <c r="E101" s="120" t="s">
         <v>3</v>
       </c>
@@ -8033,16 +8021,16 @@
       <c r="Q101" s="120" t="s">
         <v>14</v>
       </c>
-      <c r="R101" s="285" t="s">
+      <c r="R101" s="259" t="s">
         <v>38</v>
       </c>
-      <c r="S101" s="287"/>
+      <c r="S101" s="261"/>
     </row>
     <row r="102" spans="2:21" x14ac:dyDescent="0.3">
-      <c r="B102" s="261" t="s">
+      <c r="B102" s="262" t="s">
         <v>95</v>
       </c>
-      <c r="C102" s="262" t="s">
+      <c r="C102" s="263" t="s">
         <v>31</v>
       </c>
       <c r="D102" s="139" t="s">
@@ -8090,18 +8078,18 @@
       <c r="Q102" s="142" t="s">
         <v>60</v>
       </c>
-      <c r="R102" s="267" t="s">
+      <c r="R102" s="264" t="s">
         <v>93</v>
       </c>
-      <c r="S102" s="268"/>
+      <c r="S102" s="265"/>
       <c r="T102" s="184" t="s">
         <v>96</v>
       </c>
       <c r="U102"/>
     </row>
     <row r="103" spans="2:21" x14ac:dyDescent="0.3">
-      <c r="B103" s="261"/>
-      <c r="C103" s="262"/>
+      <c r="B103" s="262"/>
+      <c r="C103" s="263"/>
       <c r="D103" s="139" t="s">
         <v>24</v>
       </c>
@@ -8147,8 +8135,8 @@
       <c r="Q103" s="142" t="s">
         <v>60</v>
       </c>
-      <c r="R103" s="269"/>
-      <c r="S103" s="270"/>
+      <c r="R103" s="266"/>
+      <c r="S103" s="267"/>
       <c r="T103" s="184" t="s">
         <v>96</v>
       </c>
@@ -8175,127 +8163,127 @@
       <c r="S104" s="136"/>
     </row>
     <row r="105" spans="2:21" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B105" s="293" t="s">
+      <c r="B105" s="247" t="s">
         <v>34</v>
       </c>
-      <c r="C105" s="294"/>
-      <c r="D105" s="294"/>
-      <c r="E105" s="294"/>
-      <c r="F105" s="294"/>
-      <c r="G105" s="294"/>
-      <c r="H105" s="294"/>
-      <c r="I105" s="294"/>
-      <c r="J105" s="294"/>
-      <c r="K105" s="294"/>
-      <c r="L105" s="294"/>
-      <c r="M105" s="294"/>
-      <c r="N105" s="294"/>
-      <c r="O105" s="294"/>
-      <c r="P105" s="294"/>
-      <c r="Q105" s="294"/>
-      <c r="R105" s="294"/>
-      <c r="S105" s="295"/>
+      <c r="C105" s="248"/>
+      <c r="D105" s="248"/>
+      <c r="E105" s="248"/>
+      <c r="F105" s="248"/>
+      <c r="G105" s="248"/>
+      <c r="H105" s="248"/>
+      <c r="I105" s="248"/>
+      <c r="J105" s="248"/>
+      <c r="K105" s="248"/>
+      <c r="L105" s="248"/>
+      <c r="M105" s="248"/>
+      <c r="N105" s="248"/>
+      <c r="O105" s="248"/>
+      <c r="P105" s="248"/>
+      <c r="Q105" s="248"/>
+      <c r="R105" s="248"/>
+      <c r="S105" s="249"/>
     </row>
     <row r="106" spans="2:21" x14ac:dyDescent="0.3">
-      <c r="B106" s="296" t="s">
+      <c r="B106" s="250" t="s">
         <v>35</v>
       </c>
-      <c r="C106" s="297"/>
-      <c r="D106" s="297"/>
-      <c r="E106" s="297"/>
-      <c r="F106" s="297"/>
-      <c r="G106" s="297"/>
-      <c r="H106" s="297"/>
-      <c r="I106" s="297"/>
-      <c r="J106" s="297"/>
-      <c r="K106" s="297"/>
-      <c r="L106" s="297"/>
-      <c r="M106" s="297"/>
-      <c r="N106" s="297"/>
-      <c r="O106" s="297"/>
-      <c r="P106" s="297"/>
-      <c r="Q106" s="297"/>
-      <c r="R106" s="297"/>
-      <c r="S106" s="298"/>
+      <c r="C106" s="251"/>
+      <c r="D106" s="251"/>
+      <c r="E106" s="251"/>
+      <c r="F106" s="251"/>
+      <c r="G106" s="251"/>
+      <c r="H106" s="251"/>
+      <c r="I106" s="251"/>
+      <c r="J106" s="251"/>
+      <c r="K106" s="251"/>
+      <c r="L106" s="251"/>
+      <c r="M106" s="251"/>
+      <c r="N106" s="251"/>
+      <c r="O106" s="251"/>
+      <c r="P106" s="251"/>
+      <c r="Q106" s="251"/>
+      <c r="R106" s="251"/>
+      <c r="S106" s="252"/>
     </row>
     <row r="107" spans="2:21" x14ac:dyDescent="0.3">
-      <c r="B107" s="296"/>
-      <c r="C107" s="297"/>
-      <c r="D107" s="297"/>
-      <c r="E107" s="297"/>
-      <c r="F107" s="297"/>
-      <c r="G107" s="297"/>
-      <c r="H107" s="297"/>
-      <c r="I107" s="297"/>
-      <c r="J107" s="297"/>
-      <c r="K107" s="297"/>
-      <c r="L107" s="297"/>
-      <c r="M107" s="297"/>
-      <c r="N107" s="297"/>
-      <c r="O107" s="297"/>
-      <c r="P107" s="297"/>
-      <c r="Q107" s="297"/>
-      <c r="R107" s="297"/>
-      <c r="S107" s="298"/>
+      <c r="B107" s="250"/>
+      <c r="C107" s="251"/>
+      <c r="D107" s="251"/>
+      <c r="E107" s="251"/>
+      <c r="F107" s="251"/>
+      <c r="G107" s="251"/>
+      <c r="H107" s="251"/>
+      <c r="I107" s="251"/>
+      <c r="J107" s="251"/>
+      <c r="K107" s="251"/>
+      <c r="L107" s="251"/>
+      <c r="M107" s="251"/>
+      <c r="N107" s="251"/>
+      <c r="O107" s="251"/>
+      <c r="P107" s="251"/>
+      <c r="Q107" s="251"/>
+      <c r="R107" s="251"/>
+      <c r="S107" s="252"/>
     </row>
     <row r="108" spans="2:21" x14ac:dyDescent="0.3">
-      <c r="B108" s="296"/>
-      <c r="C108" s="297"/>
-      <c r="D108" s="297"/>
-      <c r="E108" s="297"/>
-      <c r="F108" s="297"/>
-      <c r="G108" s="297"/>
-      <c r="H108" s="297"/>
-      <c r="I108" s="297"/>
-      <c r="J108" s="297"/>
-      <c r="K108" s="297"/>
-      <c r="L108" s="297"/>
-      <c r="M108" s="297"/>
-      <c r="N108" s="297"/>
-      <c r="O108" s="297"/>
-      <c r="P108" s="297"/>
-      <c r="Q108" s="297"/>
-      <c r="R108" s="297"/>
-      <c r="S108" s="298"/>
+      <c r="B108" s="250"/>
+      <c r="C108" s="251"/>
+      <c r="D108" s="251"/>
+      <c r="E108" s="251"/>
+      <c r="F108" s="251"/>
+      <c r="G108" s="251"/>
+      <c r="H108" s="251"/>
+      <c r="I108" s="251"/>
+      <c r="J108" s="251"/>
+      <c r="K108" s="251"/>
+      <c r="L108" s="251"/>
+      <c r="M108" s="251"/>
+      <c r="N108" s="251"/>
+      <c r="O108" s="251"/>
+      <c r="P108" s="251"/>
+      <c r="Q108" s="251"/>
+      <c r="R108" s="251"/>
+      <c r="S108" s="252"/>
     </row>
     <row r="109" spans="2:21" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B109" s="299"/>
-      <c r="C109" s="300"/>
-      <c r="D109" s="300"/>
-      <c r="E109" s="300"/>
-      <c r="F109" s="300"/>
-      <c r="G109" s="300"/>
-      <c r="H109" s="300"/>
-      <c r="I109" s="300"/>
-      <c r="J109" s="300"/>
-      <c r="K109" s="300"/>
-      <c r="L109" s="300"/>
-      <c r="M109" s="300"/>
-      <c r="N109" s="300"/>
-      <c r="O109" s="300"/>
-      <c r="P109" s="300"/>
-      <c r="Q109" s="300"/>
-      <c r="R109" s="300"/>
-      <c r="S109" s="301"/>
+      <c r="B109" s="253"/>
+      <c r="C109" s="254"/>
+      <c r="D109" s="254"/>
+      <c r="E109" s="254"/>
+      <c r="F109" s="254"/>
+      <c r="G109" s="254"/>
+      <c r="H109" s="254"/>
+      <c r="I109" s="254"/>
+      <c r="J109" s="254"/>
+      <c r="K109" s="254"/>
+      <c r="L109" s="254"/>
+      <c r="M109" s="254"/>
+      <c r="N109" s="254"/>
+      <c r="O109" s="254"/>
+      <c r="P109" s="254"/>
+      <c r="Q109" s="254"/>
+      <c r="R109" s="254"/>
+      <c r="S109" s="255"/>
     </row>
     <row r="118" spans="2:20" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B118" s="302" t="s">
+      <c r="B118" s="256" t="s">
         <v>97</v>
       </c>
-      <c r="C118" s="302"/>
-      <c r="D118" s="302"/>
-      <c r="E118" s="302"/>
-      <c r="F118" s="302"/>
-      <c r="G118" s="302"/>
-      <c r="H118" s="302"/>
-      <c r="I118" s="302"/>
-      <c r="J118" s="302"/>
-      <c r="K118" s="302"/>
-      <c r="L118" s="302"/>
-      <c r="M118" s="302"/>
-      <c r="N118" s="302"/>
-      <c r="O118" s="302"/>
-      <c r="P118" s="302"/>
+      <c r="C118" s="256"/>
+      <c r="D118" s="256"/>
+      <c r="E118" s="256"/>
+      <c r="F118" s="256"/>
+      <c r="G118" s="256"/>
+      <c r="H118" s="256"/>
+      <c r="I118" s="256"/>
+      <c r="J118" s="256"/>
+      <c r="K118" s="256"/>
+      <c r="L118" s="256"/>
+      <c r="M118" s="256"/>
+      <c r="N118" s="256"/>
+      <c r="O118" s="256"/>
+      <c r="P118" s="256"/>
       <c r="Q118" s="131"/>
     </row>
     <row r="119" spans="2:20" ht="28.8" x14ac:dyDescent="0.3">
@@ -8346,10 +8334,10 @@
       </c>
     </row>
     <row r="120" spans="2:20" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B120" s="227" t="s">
+      <c r="B120" s="233" t="s">
         <v>99</v>
       </c>
-      <c r="C120" s="252" t="s">
+      <c r="C120" s="257" t="s">
         <v>17</v>
       </c>
       <c r="D120" s="20" t="s">
@@ -8387,18 +8375,18 @@
       <c r="N120" s="20" t="s">
         <v>41</v>
       </c>
-      <c r="O120" s="259" t="s">
+      <c r="O120" s="258" t="s">
         <v>47</v>
       </c>
-      <c r="P120" s="259"/>
-      <c r="Q120" s="259"/>
+      <c r="P120" s="258"/>
+      <c r="Q120" s="258"/>
       <c r="T120" s="130" t="s">
         <v>100</v>
       </c>
     </row>
     <row r="121" spans="2:20" x14ac:dyDescent="0.3">
-      <c r="B121" s="227"/>
-      <c r="C121" s="252"/>
+      <c r="B121" s="233"/>
+      <c r="C121" s="257"/>
       <c r="D121" s="20" t="s">
         <v>24</v>
       </c>
@@ -8434,9 +8422,9 @@
       <c r="N121" s="20" t="s">
         <v>41</v>
       </c>
-      <c r="O121" s="259"/>
-      <c r="P121" s="259"/>
-      <c r="Q121" s="259"/>
+      <c r="O121" s="258"/>
+      <c r="P121" s="258"/>
+      <c r="Q121" s="258"/>
       <c r="T121" s="130" t="s">
         <v>100</v>
       </c>
@@ -8480,78 +8468,78 @@
       <c r="Q123" s="7"/>
     </row>
     <row r="124" spans="2:20" x14ac:dyDescent="0.3">
-      <c r="B124" s="237" t="s">
+      <c r="B124" s="224" t="s">
         <v>35</v>
       </c>
-      <c r="C124" s="238"/>
-      <c r="D124" s="238"/>
-      <c r="E124" s="238"/>
-      <c r="F124" s="238"/>
-      <c r="G124" s="238"/>
-      <c r="H124" s="238"/>
-      <c r="I124" s="238"/>
-      <c r="J124" s="238"/>
-      <c r="K124" s="238"/>
-      <c r="L124" s="238"/>
-      <c r="M124" s="238"/>
-      <c r="N124" s="238"/>
-      <c r="O124" s="238"/>
-      <c r="P124" s="238"/>
-      <c r="Q124" s="239"/>
+      <c r="C124" s="225"/>
+      <c r="D124" s="225"/>
+      <c r="E124" s="225"/>
+      <c r="F124" s="225"/>
+      <c r="G124" s="225"/>
+      <c r="H124" s="225"/>
+      <c r="I124" s="225"/>
+      <c r="J124" s="225"/>
+      <c r="K124" s="225"/>
+      <c r="L124" s="225"/>
+      <c r="M124" s="225"/>
+      <c r="N124" s="225"/>
+      <c r="O124" s="225"/>
+      <c r="P124" s="225"/>
+      <c r="Q124" s="226"/>
     </row>
     <row r="125" spans="2:20" x14ac:dyDescent="0.3">
-      <c r="B125" s="237"/>
-      <c r="C125" s="238"/>
-      <c r="D125" s="238"/>
-      <c r="E125" s="238"/>
-      <c r="F125" s="238"/>
-      <c r="G125" s="238"/>
-      <c r="H125" s="238"/>
-      <c r="I125" s="238"/>
-      <c r="J125" s="238"/>
-      <c r="K125" s="238"/>
-      <c r="L125" s="238"/>
-      <c r="M125" s="238"/>
-      <c r="N125" s="238"/>
-      <c r="O125" s="238"/>
-      <c r="P125" s="238"/>
-      <c r="Q125" s="239"/>
+      <c r="B125" s="224"/>
+      <c r="C125" s="225"/>
+      <c r="D125" s="225"/>
+      <c r="E125" s="225"/>
+      <c r="F125" s="225"/>
+      <c r="G125" s="225"/>
+      <c r="H125" s="225"/>
+      <c r="I125" s="225"/>
+      <c r="J125" s="225"/>
+      <c r="K125" s="225"/>
+      <c r="L125" s="225"/>
+      <c r="M125" s="225"/>
+      <c r="N125" s="225"/>
+      <c r="O125" s="225"/>
+      <c r="P125" s="225"/>
+      <c r="Q125" s="226"/>
     </row>
     <row r="126" spans="2:20" x14ac:dyDescent="0.3">
-      <c r="B126" s="237"/>
-      <c r="C126" s="238"/>
-      <c r="D126" s="238"/>
-      <c r="E126" s="238"/>
-      <c r="F126" s="238"/>
-      <c r="G126" s="238"/>
-      <c r="H126" s="238"/>
-      <c r="I126" s="238"/>
-      <c r="J126" s="238"/>
-      <c r="K126" s="238"/>
-      <c r="L126" s="238"/>
-      <c r="M126" s="238"/>
-      <c r="N126" s="238"/>
-      <c r="O126" s="238"/>
-      <c r="P126" s="238"/>
-      <c r="Q126" s="239"/>
+      <c r="B126" s="224"/>
+      <c r="C126" s="225"/>
+      <c r="D126" s="225"/>
+      <c r="E126" s="225"/>
+      <c r="F126" s="225"/>
+      <c r="G126" s="225"/>
+      <c r="H126" s="225"/>
+      <c r="I126" s="225"/>
+      <c r="J126" s="225"/>
+      <c r="K126" s="225"/>
+      <c r="L126" s="225"/>
+      <c r="M126" s="225"/>
+      <c r="N126" s="225"/>
+      <c r="O126" s="225"/>
+      <c r="P126" s="225"/>
+      <c r="Q126" s="226"/>
     </row>
     <row r="127" spans="2:20" x14ac:dyDescent="0.3">
-      <c r="B127" s="240"/>
-      <c r="C127" s="241"/>
-      <c r="D127" s="241"/>
-      <c r="E127" s="241"/>
-      <c r="F127" s="241"/>
-      <c r="G127" s="241"/>
-      <c r="H127" s="241"/>
-      <c r="I127" s="241"/>
-      <c r="J127" s="241"/>
-      <c r="K127" s="241"/>
-      <c r="L127" s="241"/>
-      <c r="M127" s="241"/>
-      <c r="N127" s="241"/>
-      <c r="O127" s="241"/>
-      <c r="P127" s="241"/>
-      <c r="Q127" s="242"/>
+      <c r="B127" s="227"/>
+      <c r="C127" s="228"/>
+      <c r="D127" s="228"/>
+      <c r="E127" s="228"/>
+      <c r="F127" s="228"/>
+      <c r="G127" s="228"/>
+      <c r="H127" s="228"/>
+      <c r="I127" s="228"/>
+      <c r="J127" s="228"/>
+      <c r="K127" s="228"/>
+      <c r="L127" s="228"/>
+      <c r="M127" s="228"/>
+      <c r="N127" s="228"/>
+      <c r="O127" s="228"/>
+      <c r="P127" s="228"/>
+      <c r="Q127" s="229"/>
     </row>
     <row r="128" spans="2:20" x14ac:dyDescent="0.3">
       <c r="B128" s="35"/>
@@ -8574,23 +8562,23 @@
     <row r="129" spans="2:20" ht="13.8" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="133" spans="2:20" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="134" spans="2:20" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B134" s="245" t="s">
+      <c r="B134" s="244" t="s">
         <v>101</v>
       </c>
-      <c r="C134" s="246"/>
-      <c r="D134" s="246"/>
-      <c r="E134" s="246"/>
-      <c r="F134" s="246"/>
-      <c r="G134" s="246"/>
-      <c r="H134" s="246"/>
-      <c r="I134" s="246"/>
-      <c r="J134" s="246"/>
-      <c r="K134" s="246"/>
-      <c r="L134" s="246"/>
-      <c r="M134" s="246"/>
-      <c r="N134" s="246"/>
-      <c r="O134" s="246"/>
-      <c r="P134" s="246"/>
+      <c r="C134" s="245"/>
+      <c r="D134" s="245"/>
+      <c r="E134" s="245"/>
+      <c r="F134" s="245"/>
+      <c r="G134" s="245"/>
+      <c r="H134" s="245"/>
+      <c r="I134" s="245"/>
+      <c r="J134" s="245"/>
+      <c r="K134" s="245"/>
+      <c r="L134" s="245"/>
+      <c r="M134" s="245"/>
+      <c r="N134" s="245"/>
+      <c r="O134" s="245"/>
+      <c r="P134" s="245"/>
     </row>
     <row r="135" spans="2:20" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B135" s="97" t="s">
@@ -8693,10 +8681,10 @@
       </c>
     </row>
     <row r="137" spans="2:20" x14ac:dyDescent="0.3">
-      <c r="B137" s="247" t="s">
+      <c r="B137" s="246" t="s">
         <v>106</v>
       </c>
-      <c r="C137" s="227" t="s">
+      <c r="C137" s="233" t="s">
         <v>31</v>
       </c>
       <c r="D137" s="117" t="s">
@@ -8746,8 +8734,8 @@
       </c>
     </row>
     <row r="138" spans="2:20" x14ac:dyDescent="0.3">
-      <c r="B138" s="247"/>
-      <c r="C138" s="227"/>
+      <c r="B138" s="246"/>
+      <c r="C138" s="233"/>
       <c r="D138" s="117" t="s">
         <v>24</v>
       </c>
@@ -8796,23 +8784,23 @@
     </row>
     <row r="140" spans="2:20" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="141" spans="2:20" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B141" s="245" t="s">
+      <c r="B141" s="244" t="s">
         <v>107</v>
       </c>
-      <c r="C141" s="246"/>
-      <c r="D141" s="246"/>
-      <c r="E141" s="246"/>
-      <c r="F141" s="246"/>
-      <c r="G141" s="246"/>
-      <c r="H141" s="246"/>
-      <c r="I141" s="246"/>
-      <c r="J141" s="246"/>
-      <c r="K141" s="246"/>
-      <c r="L141" s="246"/>
-      <c r="M141" s="246"/>
-      <c r="N141" s="246"/>
-      <c r="O141" s="246"/>
-      <c r="P141" s="246"/>
+      <c r="C141" s="245"/>
+      <c r="D141" s="245"/>
+      <c r="E141" s="245"/>
+      <c r="F141" s="245"/>
+      <c r="G141" s="245"/>
+      <c r="H141" s="245"/>
+      <c r="I141" s="245"/>
+      <c r="J141" s="245"/>
+      <c r="K141" s="245"/>
+      <c r="L141" s="245"/>
+      <c r="M141" s="245"/>
+      <c r="N141" s="245"/>
+      <c r="O141" s="245"/>
+      <c r="P141" s="245"/>
     </row>
     <row r="142" spans="2:20" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B142" s="97" t="s">
@@ -8860,10 +8848,10 @@
       </c>
     </row>
     <row r="143" spans="2:20" x14ac:dyDescent="0.3">
-      <c r="B143" s="227" t="s">
+      <c r="B143" s="233" t="s">
         <v>108</v>
       </c>
-      <c r="C143" s="227" t="s">
+      <c r="C143" s="233" t="s">
         <v>17</v>
       </c>
       <c r="D143" s="117" t="s">
@@ -8909,8 +8897,8 @@
       </c>
     </row>
     <row r="144" spans="2:20" x14ac:dyDescent="0.3">
-      <c r="B144" s="227"/>
-      <c r="C144" s="227"/>
+      <c r="B144" s="233"/>
+      <c r="C144" s="233"/>
       <c r="D144" s="117" t="s">
         <v>24</v>
       </c>
@@ -8954,10 +8942,10 @@
       </c>
     </row>
     <row r="145" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B145" s="227" t="s">
+      <c r="B145" s="233" t="s">
         <v>110</v>
       </c>
-      <c r="C145" s="227" t="s">
+      <c r="C145" s="233" t="s">
         <v>31</v>
       </c>
       <c r="D145" s="117" t="s">
@@ -9003,8 +8991,8 @@
       </c>
     </row>
     <row r="146" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B146" s="227"/>
-      <c r="C146" s="227"/>
+      <c r="B146" s="233"/>
+      <c r="C146" s="233"/>
       <c r="D146" s="117" t="s">
         <v>24</v>
       </c>
@@ -9074,78 +9062,78 @@
       <c r="Q148" s="7"/>
     </row>
     <row r="149" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B149" s="237" t="s">
+      <c r="B149" s="224" t="s">
         <v>35</v>
       </c>
-      <c r="C149" s="238"/>
-      <c r="D149" s="238"/>
-      <c r="E149" s="238"/>
-      <c r="F149" s="238"/>
-      <c r="G149" s="238"/>
-      <c r="H149" s="238"/>
-      <c r="I149" s="238"/>
-      <c r="J149" s="238"/>
-      <c r="K149" s="238"/>
-      <c r="L149" s="238"/>
-      <c r="M149" s="238"/>
-      <c r="N149" s="238"/>
-      <c r="O149" s="238"/>
-      <c r="P149" s="238"/>
-      <c r="Q149" s="239"/>
+      <c r="C149" s="225"/>
+      <c r="D149" s="225"/>
+      <c r="E149" s="225"/>
+      <c r="F149" s="225"/>
+      <c r="G149" s="225"/>
+      <c r="H149" s="225"/>
+      <c r="I149" s="225"/>
+      <c r="J149" s="225"/>
+      <c r="K149" s="225"/>
+      <c r="L149" s="225"/>
+      <c r="M149" s="225"/>
+      <c r="N149" s="225"/>
+      <c r="O149" s="225"/>
+      <c r="P149" s="225"/>
+      <c r="Q149" s="226"/>
     </row>
     <row r="150" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B150" s="237"/>
-      <c r="C150" s="238"/>
-      <c r="D150" s="238"/>
-      <c r="E150" s="238"/>
-      <c r="F150" s="238"/>
-      <c r="G150" s="238"/>
-      <c r="H150" s="238"/>
-      <c r="I150" s="238"/>
-      <c r="J150" s="238"/>
-      <c r="K150" s="238"/>
-      <c r="L150" s="238"/>
-      <c r="M150" s="238"/>
-      <c r="N150" s="238"/>
-      <c r="O150" s="238"/>
-      <c r="P150" s="238"/>
-      <c r="Q150" s="239"/>
+      <c r="B150" s="224"/>
+      <c r="C150" s="225"/>
+      <c r="D150" s="225"/>
+      <c r="E150" s="225"/>
+      <c r="F150" s="225"/>
+      <c r="G150" s="225"/>
+      <c r="H150" s="225"/>
+      <c r="I150" s="225"/>
+      <c r="J150" s="225"/>
+      <c r="K150" s="225"/>
+      <c r="L150" s="225"/>
+      <c r="M150" s="225"/>
+      <c r="N150" s="225"/>
+      <c r="O150" s="225"/>
+      <c r="P150" s="225"/>
+      <c r="Q150" s="226"/>
     </row>
     <row r="151" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B151" s="237"/>
-      <c r="C151" s="238"/>
-      <c r="D151" s="238"/>
-      <c r="E151" s="238"/>
-      <c r="F151" s="238"/>
-      <c r="G151" s="238"/>
-      <c r="H151" s="238"/>
-      <c r="I151" s="238"/>
-      <c r="J151" s="238"/>
-      <c r="K151" s="238"/>
-      <c r="L151" s="238"/>
-      <c r="M151" s="238"/>
-      <c r="N151" s="238"/>
-      <c r="O151" s="238"/>
-      <c r="P151" s="238"/>
-      <c r="Q151" s="239"/>
+      <c r="B151" s="224"/>
+      <c r="C151" s="225"/>
+      <c r="D151" s="225"/>
+      <c r="E151" s="225"/>
+      <c r="F151" s="225"/>
+      <c r="G151" s="225"/>
+      <c r="H151" s="225"/>
+      <c r="I151" s="225"/>
+      <c r="J151" s="225"/>
+      <c r="K151" s="225"/>
+      <c r="L151" s="225"/>
+      <c r="M151" s="225"/>
+      <c r="N151" s="225"/>
+      <c r="O151" s="225"/>
+      <c r="P151" s="225"/>
+      <c r="Q151" s="226"/>
     </row>
     <row r="152" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B152" s="240"/>
-      <c r="C152" s="241"/>
-      <c r="D152" s="241"/>
-      <c r="E152" s="241"/>
-      <c r="F152" s="241"/>
-      <c r="G152" s="241"/>
-      <c r="H152" s="241"/>
-      <c r="I152" s="241"/>
-      <c r="J152" s="241"/>
-      <c r="K152" s="241"/>
-      <c r="L152" s="241"/>
-      <c r="M152" s="241"/>
-      <c r="N152" s="241"/>
-      <c r="O152" s="241"/>
-      <c r="P152" s="241"/>
-      <c r="Q152" s="242"/>
+      <c r="B152" s="227"/>
+      <c r="C152" s="228"/>
+      <c r="D152" s="228"/>
+      <c r="E152" s="228"/>
+      <c r="F152" s="228"/>
+      <c r="G152" s="228"/>
+      <c r="H152" s="228"/>
+      <c r="I152" s="228"/>
+      <c r="J152" s="228"/>
+      <c r="K152" s="228"/>
+      <c r="L152" s="228"/>
+      <c r="M152" s="228"/>
+      <c r="N152" s="228"/>
+      <c r="O152" s="228"/>
+      <c r="P152" s="228"/>
+      <c r="Q152" s="229"/>
     </row>
     <row r="154" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B154" s="35"/>
@@ -9166,23 +9154,23 @@
     </row>
     <row r="159" spans="2:17" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="160" spans="2:17" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B160" s="245" t="s">
+      <c r="B160" s="244" t="s">
         <v>111</v>
       </c>
-      <c r="C160" s="246"/>
-      <c r="D160" s="246"/>
-      <c r="E160" s="246"/>
-      <c r="F160" s="246"/>
-      <c r="G160" s="246"/>
-      <c r="H160" s="246"/>
-      <c r="I160" s="246"/>
-      <c r="J160" s="246"/>
-      <c r="K160" s="246"/>
-      <c r="L160" s="246"/>
-      <c r="M160" s="246"/>
-      <c r="N160" s="246"/>
-      <c r="O160" s="246"/>
-      <c r="P160" s="246"/>
+      <c r="C160" s="245"/>
+      <c r="D160" s="245"/>
+      <c r="E160" s="245"/>
+      <c r="F160" s="245"/>
+      <c r="G160" s="245"/>
+      <c r="H160" s="245"/>
+      <c r="I160" s="245"/>
+      <c r="J160" s="245"/>
+      <c r="K160" s="245"/>
+      <c r="L160" s="245"/>
+      <c r="M160" s="245"/>
+      <c r="N160" s="245"/>
+      <c r="O160" s="245"/>
+      <c r="P160" s="245"/>
     </row>
     <row r="161" spans="2:17" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B161" s="97" t="s">
@@ -9230,10 +9218,10 @@
       </c>
     </row>
     <row r="162" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B162" s="247" t="s">
+      <c r="B162" s="246" t="s">
         <v>112</v>
       </c>
-      <c r="C162" s="227" t="s">
+      <c r="C162" s="233" t="s">
         <v>113</v>
       </c>
       <c r="D162" s="117" t="s">
@@ -9279,8 +9267,8 @@
       </c>
     </row>
     <row r="163" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B163" s="247"/>
-      <c r="C163" s="227"/>
+      <c r="B163" s="246"/>
+      <c r="C163" s="233"/>
       <c r="D163" s="117" t="s">
         <v>24</v>
       </c>
@@ -9344,78 +9332,78 @@
       <c r="Q165" s="7"/>
     </row>
     <row r="166" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B166" s="237" t="s">
+      <c r="B166" s="224" t="s">
         <v>35</v>
       </c>
-      <c r="C166" s="238"/>
-      <c r="D166" s="238"/>
-      <c r="E166" s="238"/>
-      <c r="F166" s="238"/>
-      <c r="G166" s="238"/>
-      <c r="H166" s="238"/>
-      <c r="I166" s="238"/>
-      <c r="J166" s="238"/>
-      <c r="K166" s="238"/>
-      <c r="L166" s="238"/>
-      <c r="M166" s="238"/>
-      <c r="N166" s="238"/>
-      <c r="O166" s="238"/>
-      <c r="P166" s="238"/>
-      <c r="Q166" s="239"/>
+      <c r="C166" s="225"/>
+      <c r="D166" s="225"/>
+      <c r="E166" s="225"/>
+      <c r="F166" s="225"/>
+      <c r="G166" s="225"/>
+      <c r="H166" s="225"/>
+      <c r="I166" s="225"/>
+      <c r="J166" s="225"/>
+      <c r="K166" s="225"/>
+      <c r="L166" s="225"/>
+      <c r="M166" s="225"/>
+      <c r="N166" s="225"/>
+      <c r="O166" s="225"/>
+      <c r="P166" s="225"/>
+      <c r="Q166" s="226"/>
     </row>
     <row r="167" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B167" s="237"/>
-      <c r="C167" s="238"/>
-      <c r="D167" s="238"/>
-      <c r="E167" s="238"/>
-      <c r="F167" s="238"/>
-      <c r="G167" s="238"/>
-      <c r="H167" s="238"/>
-      <c r="I167" s="238"/>
-      <c r="J167" s="238"/>
-      <c r="K167" s="238"/>
-      <c r="L167" s="238"/>
-      <c r="M167" s="238"/>
-      <c r="N167" s="238"/>
-      <c r="O167" s="238"/>
-      <c r="P167" s="238"/>
-      <c r="Q167" s="239"/>
+      <c r="B167" s="224"/>
+      <c r="C167" s="225"/>
+      <c r="D167" s="225"/>
+      <c r="E167" s="225"/>
+      <c r="F167" s="225"/>
+      <c r="G167" s="225"/>
+      <c r="H167" s="225"/>
+      <c r="I167" s="225"/>
+      <c r="J167" s="225"/>
+      <c r="K167" s="225"/>
+      <c r="L167" s="225"/>
+      <c r="M167" s="225"/>
+      <c r="N167" s="225"/>
+      <c r="O167" s="225"/>
+      <c r="P167" s="225"/>
+      <c r="Q167" s="226"/>
     </row>
     <row r="168" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B168" s="237"/>
-      <c r="C168" s="238"/>
-      <c r="D168" s="238"/>
-      <c r="E168" s="238"/>
-      <c r="F168" s="238"/>
-      <c r="G168" s="238"/>
-      <c r="H168" s="238"/>
-      <c r="I168" s="238"/>
-      <c r="J168" s="238"/>
-      <c r="K168" s="238"/>
-      <c r="L168" s="238"/>
-      <c r="M168" s="238"/>
-      <c r="N168" s="238"/>
-      <c r="O168" s="238"/>
-      <c r="P168" s="238"/>
-      <c r="Q168" s="239"/>
+      <c r="B168" s="224"/>
+      <c r="C168" s="225"/>
+      <c r="D168" s="225"/>
+      <c r="E168" s="225"/>
+      <c r="F168" s="225"/>
+      <c r="G168" s="225"/>
+      <c r="H168" s="225"/>
+      <c r="I168" s="225"/>
+      <c r="J168" s="225"/>
+      <c r="K168" s="225"/>
+      <c r="L168" s="225"/>
+      <c r="M168" s="225"/>
+      <c r="N168" s="225"/>
+      <c r="O168" s="225"/>
+      <c r="P168" s="225"/>
+      <c r="Q168" s="226"/>
     </row>
     <row r="169" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B169" s="240"/>
-      <c r="C169" s="241"/>
-      <c r="D169" s="241"/>
-      <c r="E169" s="241"/>
-      <c r="F169" s="241"/>
-      <c r="G169" s="241"/>
-      <c r="H169" s="241"/>
-      <c r="I169" s="241"/>
-      <c r="J169" s="241"/>
-      <c r="K169" s="241"/>
-      <c r="L169" s="241"/>
-      <c r="M169" s="241"/>
-      <c r="N169" s="241"/>
-      <c r="O169" s="241"/>
-      <c r="P169" s="241"/>
-      <c r="Q169" s="242"/>
+      <c r="B169" s="227"/>
+      <c r="C169" s="228"/>
+      <c r="D169" s="228"/>
+      <c r="E169" s="228"/>
+      <c r="F169" s="228"/>
+      <c r="G169" s="228"/>
+      <c r="H169" s="228"/>
+      <c r="I169" s="228"/>
+      <c r="J169" s="228"/>
+      <c r="K169" s="228"/>
+      <c r="L169" s="228"/>
+      <c r="M169" s="228"/>
+      <c r="N169" s="228"/>
+      <c r="O169" s="228"/>
+      <c r="P169" s="228"/>
+      <c r="Q169" s="229"/>
     </row>
     <row r="170" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B170" s="35"/>
@@ -9454,24 +9442,24 @@
       <c r="Q171" s="35"/>
     </row>
     <row r="173" spans="2:17" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B173" s="228" t="s">
+      <c r="B173" s="231" t="s">
         <v>114</v>
       </c>
-      <c r="C173" s="229"/>
-      <c r="D173" s="229"/>
-      <c r="E173" s="229"/>
-      <c r="F173" s="229"/>
-      <c r="G173" s="229"/>
-      <c r="H173" s="229"/>
-      <c r="I173" s="229"/>
-      <c r="J173" s="229"/>
-      <c r="K173" s="229"/>
-      <c r="L173" s="229"/>
-      <c r="M173" s="229"/>
-      <c r="N173" s="229"/>
-      <c r="O173" s="229"/>
-      <c r="P173" s="229"/>
-      <c r="Q173" s="229"/>
+      <c r="C173" s="232"/>
+      <c r="D173" s="232"/>
+      <c r="E173" s="232"/>
+      <c r="F173" s="232"/>
+      <c r="G173" s="232"/>
+      <c r="H173" s="232"/>
+      <c r="I173" s="232"/>
+      <c r="J173" s="232"/>
+      <c r="K173" s="232"/>
+      <c r="L173" s="232"/>
+      <c r="M173" s="232"/>
+      <c r="N173" s="232"/>
+      <c r="O173" s="232"/>
+      <c r="P173" s="232"/>
+      <c r="Q173" s="232"/>
     </row>
     <row r="174" spans="2:17" ht="43.2" x14ac:dyDescent="0.3">
       <c r="B174" s="97" t="s">
@@ -9522,10 +9510,10 @@
       </c>
     </row>
     <row r="175" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B175" s="231" t="s">
+      <c r="B175" s="238" t="s">
         <v>120</v>
       </c>
-      <c r="C175" s="227" t="s">
+      <c r="C175" s="233" t="s">
         <v>31</v>
       </c>
       <c r="D175" s="117" t="s">
@@ -9574,8 +9562,8 @@
       </c>
     </row>
     <row r="176" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B176" s="232"/>
-      <c r="C176" s="227"/>
+      <c r="B176" s="239"/>
+      <c r="C176" s="233"/>
       <c r="D176" s="117" t="s">
         <v>24</v>
       </c>
@@ -9640,23 +9628,23 @@
     </row>
     <row r="185" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="186" spans="2:16" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B186" s="245" t="s">
+      <c r="B186" s="244" t="s">
         <v>122</v>
       </c>
-      <c r="C186" s="246"/>
-      <c r="D186" s="246"/>
-      <c r="E186" s="246"/>
-      <c r="F186" s="246"/>
-      <c r="G186" s="246"/>
-      <c r="H186" s="246"/>
-      <c r="I186" s="246"/>
-      <c r="J186" s="246"/>
-      <c r="K186" s="246"/>
-      <c r="L186" s="246"/>
-      <c r="M186" s="246"/>
-      <c r="N186" s="246"/>
-      <c r="O186" s="246"/>
-      <c r="P186" s="246"/>
+      <c r="C186" s="245"/>
+      <c r="D186" s="245"/>
+      <c r="E186" s="245"/>
+      <c r="F186" s="245"/>
+      <c r="G186" s="245"/>
+      <c r="H186" s="245"/>
+      <c r="I186" s="245"/>
+      <c r="J186" s="245"/>
+      <c r="K186" s="245"/>
+      <c r="L186" s="245"/>
+      <c r="M186" s="245"/>
+      <c r="N186" s="245"/>
+      <c r="O186" s="245"/>
+      <c r="P186" s="245"/>
     </row>
     <row r="187" spans="2:16" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B187" s="97" t="s">
@@ -9704,10 +9692,10 @@
       </c>
     </row>
     <row r="188" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="B188" s="247" t="s">
+      <c r="B188" s="246" t="s">
         <v>124</v>
       </c>
-      <c r="C188" s="227" t="s">
+      <c r="C188" s="233" t="s">
         <v>89</v>
       </c>
       <c r="D188" s="117" t="s">
@@ -9753,8 +9741,8 @@
       </c>
     </row>
     <row r="189" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="B189" s="247"/>
-      <c r="C189" s="227"/>
+      <c r="B189" s="246"/>
+      <c r="C189" s="233"/>
       <c r="D189" s="117" t="s">
         <v>24</v>
       </c>
@@ -9802,62 +9790,48 @@
     </row>
   </sheetData>
   <mergeCells count="122">
-    <mergeCell ref="B160:P160"/>
-    <mergeCell ref="C161:D161"/>
-    <mergeCell ref="B162:B163"/>
-    <mergeCell ref="C162:C163"/>
-    <mergeCell ref="B166:Q169"/>
-    <mergeCell ref="C142:D142"/>
-    <mergeCell ref="B145:B146"/>
-    <mergeCell ref="C145:C146"/>
-    <mergeCell ref="B149:Q152"/>
-    <mergeCell ref="B124:Q127"/>
-    <mergeCell ref="B134:P134"/>
-    <mergeCell ref="C135:D135"/>
-    <mergeCell ref="B137:B138"/>
-    <mergeCell ref="C137:C138"/>
-    <mergeCell ref="B141:P141"/>
-    <mergeCell ref="B143:B144"/>
-    <mergeCell ref="C143:C144"/>
-    <mergeCell ref="B105:S105"/>
-    <mergeCell ref="B106:S109"/>
-    <mergeCell ref="B118:P118"/>
-    <mergeCell ref="C119:D119"/>
-    <mergeCell ref="O119:Q119"/>
-    <mergeCell ref="B120:B121"/>
-    <mergeCell ref="C120:C121"/>
-    <mergeCell ref="O120:Q121"/>
-    <mergeCell ref="C101:D101"/>
-    <mergeCell ref="R101:S101"/>
-    <mergeCell ref="B102:B103"/>
-    <mergeCell ref="C102:C103"/>
-    <mergeCell ref="R102:S103"/>
-    <mergeCell ref="B96:S96"/>
-    <mergeCell ref="C97:D97"/>
-    <mergeCell ref="R97:S97"/>
-    <mergeCell ref="B98:B99"/>
-    <mergeCell ref="C98:C99"/>
-    <mergeCell ref="R98:S99"/>
-    <mergeCell ref="B94:B95"/>
-    <mergeCell ref="C94:C95"/>
-    <mergeCell ref="R94:S95"/>
-    <mergeCell ref="C89:D89"/>
-    <mergeCell ref="R89:S89"/>
-    <mergeCell ref="B90:B91"/>
-    <mergeCell ref="C90:C91"/>
-    <mergeCell ref="R90:S91"/>
-    <mergeCell ref="B100:S100"/>
-    <mergeCell ref="R86:S87"/>
-    <mergeCell ref="B80:S80"/>
-    <mergeCell ref="C81:D81"/>
-    <mergeCell ref="R81:S81"/>
-    <mergeCell ref="B82:B83"/>
-    <mergeCell ref="C82:C83"/>
-    <mergeCell ref="R82:S83"/>
-    <mergeCell ref="B92:S92"/>
-    <mergeCell ref="C93:D93"/>
-    <mergeCell ref="R93:S93"/>
-    <mergeCell ref="B88:S88"/>
+    <mergeCell ref="B186:P186"/>
+    <mergeCell ref="C187:D187"/>
+    <mergeCell ref="B188:B189"/>
+    <mergeCell ref="C188:C189"/>
+    <mergeCell ref="C174:D174"/>
+    <mergeCell ref="B175:B176"/>
+    <mergeCell ref="C175:C176"/>
+    <mergeCell ref="B8:P8"/>
+    <mergeCell ref="C9:D9"/>
+    <mergeCell ref="B10:B13"/>
+    <mergeCell ref="C10:C11"/>
+    <mergeCell ref="C12:C13"/>
+    <mergeCell ref="B14:B15"/>
+    <mergeCell ref="C14:C15"/>
+    <mergeCell ref="B35:P35"/>
+    <mergeCell ref="C36:D36"/>
+    <mergeCell ref="O36:P36"/>
+    <mergeCell ref="B37:B38"/>
+    <mergeCell ref="O37:P38"/>
+    <mergeCell ref="O39:P39"/>
+    <mergeCell ref="B16:B17"/>
+    <mergeCell ref="C16:C17"/>
+    <mergeCell ref="B18:B21"/>
+    <mergeCell ref="C18:C19"/>
+    <mergeCell ref="C78:C79"/>
+    <mergeCell ref="C20:C21"/>
+    <mergeCell ref="B24:P27"/>
+    <mergeCell ref="O40:P40"/>
+    <mergeCell ref="B43:Q46"/>
+    <mergeCell ref="B56:S56"/>
+    <mergeCell ref="C57:D57"/>
+    <mergeCell ref="R57:S57"/>
+    <mergeCell ref="B58:B59"/>
+    <mergeCell ref="C58:C59"/>
+    <mergeCell ref="R58:S61"/>
+    <mergeCell ref="B60:B61"/>
+    <mergeCell ref="C60:C61"/>
+    <mergeCell ref="R74:S79"/>
+    <mergeCell ref="B74:B75"/>
+    <mergeCell ref="C74:C75"/>
+    <mergeCell ref="B76:B77"/>
+    <mergeCell ref="C76:C77"/>
     <mergeCell ref="B173:Q173"/>
     <mergeCell ref="R72:S73"/>
     <mergeCell ref="B62:B63"/>
@@ -9882,48 +9856,62 @@
     <mergeCell ref="B86:B87"/>
     <mergeCell ref="C86:C87"/>
     <mergeCell ref="B78:B79"/>
-    <mergeCell ref="C78:C79"/>
-    <mergeCell ref="C20:C21"/>
-    <mergeCell ref="B24:P27"/>
-    <mergeCell ref="O40:P40"/>
-    <mergeCell ref="B43:Q46"/>
-    <mergeCell ref="B56:S56"/>
-    <mergeCell ref="C57:D57"/>
-    <mergeCell ref="R57:S57"/>
-    <mergeCell ref="B58:B59"/>
-    <mergeCell ref="C58:C59"/>
-    <mergeCell ref="R58:S61"/>
-    <mergeCell ref="B60:B61"/>
-    <mergeCell ref="C60:C61"/>
-    <mergeCell ref="R74:S79"/>
-    <mergeCell ref="B74:B75"/>
-    <mergeCell ref="C74:C75"/>
-    <mergeCell ref="B76:B77"/>
-    <mergeCell ref="C76:C77"/>
-    <mergeCell ref="B186:P186"/>
-    <mergeCell ref="C187:D187"/>
-    <mergeCell ref="B188:B189"/>
-    <mergeCell ref="C188:C189"/>
-    <mergeCell ref="C174:D174"/>
-    <mergeCell ref="B175:B176"/>
-    <mergeCell ref="C175:C176"/>
-    <mergeCell ref="B8:P8"/>
-    <mergeCell ref="C9:D9"/>
-    <mergeCell ref="B10:B13"/>
-    <mergeCell ref="C10:C11"/>
-    <mergeCell ref="C12:C13"/>
-    <mergeCell ref="B14:B15"/>
-    <mergeCell ref="C14:C15"/>
-    <mergeCell ref="B35:P35"/>
-    <mergeCell ref="C36:D36"/>
-    <mergeCell ref="O36:P36"/>
-    <mergeCell ref="B37:B38"/>
-    <mergeCell ref="O37:P38"/>
-    <mergeCell ref="O39:P39"/>
-    <mergeCell ref="B16:B17"/>
-    <mergeCell ref="C16:C17"/>
-    <mergeCell ref="B18:B21"/>
-    <mergeCell ref="C18:C19"/>
+    <mergeCell ref="R86:S87"/>
+    <mergeCell ref="B80:S80"/>
+    <mergeCell ref="C81:D81"/>
+    <mergeCell ref="R81:S81"/>
+    <mergeCell ref="B82:B83"/>
+    <mergeCell ref="C82:C83"/>
+    <mergeCell ref="R82:S83"/>
+    <mergeCell ref="B92:S92"/>
+    <mergeCell ref="C93:D93"/>
+    <mergeCell ref="R93:S93"/>
+    <mergeCell ref="B88:S88"/>
+    <mergeCell ref="B94:B95"/>
+    <mergeCell ref="C94:C95"/>
+    <mergeCell ref="R94:S95"/>
+    <mergeCell ref="C89:D89"/>
+    <mergeCell ref="R89:S89"/>
+    <mergeCell ref="B90:B91"/>
+    <mergeCell ref="C90:C91"/>
+    <mergeCell ref="R90:S91"/>
+    <mergeCell ref="B100:S100"/>
+    <mergeCell ref="C101:D101"/>
+    <mergeCell ref="R101:S101"/>
+    <mergeCell ref="B102:B103"/>
+    <mergeCell ref="C102:C103"/>
+    <mergeCell ref="R102:S103"/>
+    <mergeCell ref="B96:S96"/>
+    <mergeCell ref="C97:D97"/>
+    <mergeCell ref="R97:S97"/>
+    <mergeCell ref="B98:B99"/>
+    <mergeCell ref="C98:C99"/>
+    <mergeCell ref="R98:S99"/>
+    <mergeCell ref="B124:Q127"/>
+    <mergeCell ref="B134:P134"/>
+    <mergeCell ref="C135:D135"/>
+    <mergeCell ref="B137:B138"/>
+    <mergeCell ref="C137:C138"/>
+    <mergeCell ref="B141:P141"/>
+    <mergeCell ref="B143:B144"/>
+    <mergeCell ref="C143:C144"/>
+    <mergeCell ref="B105:S105"/>
+    <mergeCell ref="B106:S109"/>
+    <mergeCell ref="B118:P118"/>
+    <mergeCell ref="C119:D119"/>
+    <mergeCell ref="O119:Q119"/>
+    <mergeCell ref="B120:B121"/>
+    <mergeCell ref="C120:C121"/>
+    <mergeCell ref="O120:Q121"/>
+    <mergeCell ref="B160:P160"/>
+    <mergeCell ref="C161:D161"/>
+    <mergeCell ref="B162:B163"/>
+    <mergeCell ref="C162:C163"/>
+    <mergeCell ref="B166:Q169"/>
+    <mergeCell ref="C142:D142"/>
+    <mergeCell ref="B145:B146"/>
+    <mergeCell ref="C145:C146"/>
+    <mergeCell ref="B149:Q152"/>
   </mergeCells>
   <phoneticPr fontId="14" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -9962,33 +9950,33 @@
   <sheetData>
     <row r="6" spans="2:17" ht="12" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="9" spans="2:17" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B9" s="229" t="s">
+      <c r="B9" s="232" t="s">
         <v>126</v>
       </c>
-      <c r="C9" s="229"/>
-      <c r="D9" s="229"/>
-      <c r="E9" s="229"/>
-      <c r="F9" s="229"/>
-      <c r="G9" s="229"/>
-      <c r="H9" s="229"/>
-      <c r="I9" s="229"/>
-      <c r="J9" s="229"/>
-      <c r="K9" s="229"/>
-      <c r="L9" s="229"/>
-      <c r="M9" s="229"/>
-      <c r="N9" s="229"/>
-      <c r="O9" s="229"/>
-      <c r="P9" s="229"/>
-      <c r="Q9" s="229"/>
+      <c r="C9" s="232"/>
+      <c r="D9" s="232"/>
+      <c r="E9" s="232"/>
+      <c r="F9" s="232"/>
+      <c r="G9" s="232"/>
+      <c r="H9" s="232"/>
+      <c r="I9" s="232"/>
+      <c r="J9" s="232"/>
+      <c r="K9" s="232"/>
+      <c r="L9" s="232"/>
+      <c r="M9" s="232"/>
+      <c r="N9" s="232"/>
+      <c r="O9" s="232"/>
+      <c r="P9" s="232"/>
+      <c r="Q9" s="232"/>
     </row>
     <row r="10" spans="2:17" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B10" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C10" s="318" t="s">
+      <c r="C10" s="314" t="s">
         <v>2</v>
       </c>
-      <c r="D10" s="318"/>
+      <c r="D10" s="314"/>
       <c r="E10" s="8" t="s">
         <v>3</v>
       </c>
@@ -10030,10 +10018,10 @@
       </c>
     </row>
     <row r="11" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B11" s="252" t="s">
+      <c r="B11" s="257" t="s">
         <v>16</v>
       </c>
-      <c r="C11" s="252" t="s">
+      <c r="C11" s="257" t="s">
         <v>120</v>
       </c>
       <c r="D11" s="53" t="s">
@@ -10083,8 +10071,8 @@
       </c>
     </row>
     <row r="12" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B12" s="252"/>
-      <c r="C12" s="252"/>
+      <c r="B12" s="257"/>
+      <c r="C12" s="257"/>
       <c r="D12" s="53" t="s">
         <v>24</v>
       </c>
@@ -10132,10 +10120,10 @@
       </c>
     </row>
     <row r="13" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B13" s="252" t="s">
+      <c r="B13" s="257" t="s">
         <v>26</v>
       </c>
-      <c r="C13" s="252" t="s">
+      <c r="C13" s="257" t="s">
         <v>120</v>
       </c>
       <c r="D13" s="53" t="s">
@@ -10185,8 +10173,8 @@
       </c>
     </row>
     <row r="14" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B14" s="252"/>
-      <c r="C14" s="252"/>
+      <c r="B14" s="257"/>
+      <c r="C14" s="257"/>
       <c r="D14" s="53" t="s">
         <v>24</v>
       </c>
@@ -10234,10 +10222,10 @@
       </c>
     </row>
     <row r="15" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B15" s="250" t="s">
+      <c r="B15" s="297" t="s">
         <v>28</v>
       </c>
-      <c r="C15" s="252" t="s">
+      <c r="C15" s="257" t="s">
         <v>120</v>
       </c>
       <c r="D15" s="53" t="s">
@@ -10287,8 +10275,8 @@
       </c>
     </row>
     <row r="16" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B16" s="250"/>
-      <c r="C16" s="252"/>
+      <c r="B16" s="297"/>
+      <c r="C16" s="257"/>
       <c r="D16" s="53" t="s">
         <v>24</v>
       </c>
@@ -10336,10 +10324,10 @@
       </c>
     </row>
     <row r="17" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="B17" s="252" t="s">
+      <c r="B17" s="257" t="s">
         <v>132</v>
       </c>
-      <c r="C17" s="252" t="s">
+      <c r="C17" s="257" t="s">
         <v>120</v>
       </c>
       <c r="D17" s="53" t="s">
@@ -10389,8 +10377,8 @@
       </c>
     </row>
     <row r="18" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="B18" s="252"/>
-      <c r="C18" s="252"/>
+      <c r="B18" s="257"/>
+      <c r="C18" s="257"/>
       <c r="D18" s="53" t="s">
         <v>24</v>
       </c>
@@ -10455,103 +10443,103 @@
       <c r="Q19" s="34"/>
     </row>
     <row r="20" spans="2:18" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B20" s="321" t="s">
+      <c r="B20" s="303" t="s">
         <v>34</v>
       </c>
-      <c r="C20" s="322"/>
-      <c r="D20" s="322"/>
-      <c r="E20" s="322"/>
-      <c r="F20" s="322"/>
-      <c r="G20" s="322"/>
-      <c r="H20" s="322"/>
-      <c r="I20" s="322"/>
-      <c r="J20" s="322"/>
-      <c r="K20" s="322"/>
-      <c r="L20" s="322"/>
-      <c r="M20" s="322"/>
-      <c r="N20" s="322"/>
-      <c r="O20" s="322"/>
-      <c r="P20" s="322"/>
-      <c r="Q20" s="322"/>
-      <c r="R20" s="323"/>
+      <c r="C20" s="304"/>
+      <c r="D20" s="304"/>
+      <c r="E20" s="304"/>
+      <c r="F20" s="304"/>
+      <c r="G20" s="304"/>
+      <c r="H20" s="304"/>
+      <c r="I20" s="304"/>
+      <c r="J20" s="304"/>
+      <c r="K20" s="304"/>
+      <c r="L20" s="304"/>
+      <c r="M20" s="304"/>
+      <c r="N20" s="304"/>
+      <c r="O20" s="304"/>
+      <c r="P20" s="304"/>
+      <c r="Q20" s="304"/>
+      <c r="R20" s="305"/>
     </row>
     <row r="21" spans="2:18" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B21" s="324" t="s">
+      <c r="B21" s="306" t="s">
         <v>35</v>
       </c>
-      <c r="C21" s="325"/>
-      <c r="D21" s="325"/>
-      <c r="E21" s="325"/>
-      <c r="F21" s="325"/>
-      <c r="G21" s="325"/>
-      <c r="H21" s="325"/>
-      <c r="I21" s="325"/>
-      <c r="J21" s="325"/>
-      <c r="K21" s="325"/>
-      <c r="L21" s="325"/>
-      <c r="M21" s="325"/>
-      <c r="N21" s="325"/>
-      <c r="O21" s="325"/>
-      <c r="P21" s="325"/>
-      <c r="Q21" s="325"/>
-      <c r="R21" s="326"/>
+      <c r="C21" s="307"/>
+      <c r="D21" s="307"/>
+      <c r="E21" s="307"/>
+      <c r="F21" s="307"/>
+      <c r="G21" s="307"/>
+      <c r="H21" s="307"/>
+      <c r="I21" s="307"/>
+      <c r="J21" s="307"/>
+      <c r="K21" s="307"/>
+      <c r="L21" s="307"/>
+      <c r="M21" s="307"/>
+      <c r="N21" s="307"/>
+      <c r="O21" s="307"/>
+      <c r="P21" s="307"/>
+      <c r="Q21" s="307"/>
+      <c r="R21" s="308"/>
     </row>
     <row r="22" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="B22" s="327"/>
-      <c r="C22" s="297"/>
-      <c r="D22" s="297"/>
-      <c r="E22" s="297"/>
-      <c r="F22" s="297"/>
-      <c r="G22" s="297"/>
-      <c r="H22" s="297"/>
-      <c r="I22" s="297"/>
-      <c r="J22" s="297"/>
-      <c r="K22" s="297"/>
-      <c r="L22" s="297"/>
-      <c r="M22" s="297"/>
-      <c r="N22" s="297"/>
-      <c r="O22" s="297"/>
-      <c r="P22" s="297"/>
-      <c r="Q22" s="297"/>
-      <c r="R22" s="328"/>
+      <c r="B22" s="309"/>
+      <c r="C22" s="251"/>
+      <c r="D22" s="251"/>
+      <c r="E22" s="251"/>
+      <c r="F22" s="251"/>
+      <c r="G22" s="251"/>
+      <c r="H22" s="251"/>
+      <c r="I22" s="251"/>
+      <c r="J22" s="251"/>
+      <c r="K22" s="251"/>
+      <c r="L22" s="251"/>
+      <c r="M22" s="251"/>
+      <c r="N22" s="251"/>
+      <c r="O22" s="251"/>
+      <c r="P22" s="251"/>
+      <c r="Q22" s="251"/>
+      <c r="R22" s="310"/>
     </row>
     <row r="23" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="B23" s="327"/>
-      <c r="C23" s="297"/>
-      <c r="D23" s="297"/>
-      <c r="E23" s="297"/>
-      <c r="F23" s="297"/>
-      <c r="G23" s="297"/>
-      <c r="H23" s="297"/>
-      <c r="I23" s="297"/>
-      <c r="J23" s="297"/>
-      <c r="K23" s="297"/>
-      <c r="L23" s="297"/>
-      <c r="M23" s="297"/>
-      <c r="N23" s="297"/>
-      <c r="O23" s="297"/>
-      <c r="P23" s="297"/>
-      <c r="Q23" s="297"/>
-      <c r="R23" s="328"/>
+      <c r="B23" s="309"/>
+      <c r="C23" s="251"/>
+      <c r="D23" s="251"/>
+      <c r="E23" s="251"/>
+      <c r="F23" s="251"/>
+      <c r="G23" s="251"/>
+      <c r="H23" s="251"/>
+      <c r="I23" s="251"/>
+      <c r="J23" s="251"/>
+      <c r="K23" s="251"/>
+      <c r="L23" s="251"/>
+      <c r="M23" s="251"/>
+      <c r="N23" s="251"/>
+      <c r="O23" s="251"/>
+      <c r="P23" s="251"/>
+      <c r="Q23" s="251"/>
+      <c r="R23" s="310"/>
     </row>
     <row r="24" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="B24" s="329"/>
-      <c r="C24" s="330"/>
-      <c r="D24" s="330"/>
-      <c r="E24" s="330"/>
-      <c r="F24" s="330"/>
-      <c r="G24" s="330"/>
-      <c r="H24" s="330"/>
-      <c r="I24" s="330"/>
-      <c r="J24" s="330"/>
-      <c r="K24" s="330"/>
-      <c r="L24" s="330"/>
-      <c r="M24" s="330"/>
-      <c r="N24" s="330"/>
-      <c r="O24" s="330"/>
-      <c r="P24" s="330"/>
-      <c r="Q24" s="330"/>
-      <c r="R24" s="331"/>
+      <c r="B24" s="311"/>
+      <c r="C24" s="312"/>
+      <c r="D24" s="312"/>
+      <c r="E24" s="312"/>
+      <c r="F24" s="312"/>
+      <c r="G24" s="312"/>
+      <c r="H24" s="312"/>
+      <c r="I24" s="312"/>
+      <c r="J24" s="312"/>
+      <c r="K24" s="312"/>
+      <c r="L24" s="312"/>
+      <c r="M24" s="312"/>
+      <c r="N24" s="312"/>
+      <c r="O24" s="312"/>
+      <c r="P24" s="312"/>
+      <c r="Q24" s="312"/>
+      <c r="R24" s="313"/>
     </row>
     <row r="25" spans="2:18" x14ac:dyDescent="0.3">
       <c r="B25" s="27"/>
@@ -10707,34 +10695,34 @@
       <c r="Q33" s="34"/>
     </row>
     <row r="34" spans="2:21" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B34" s="253" t="s">
+      <c r="B34" s="299" t="s">
         <v>134</v>
       </c>
-      <c r="C34" s="253"/>
-      <c r="D34" s="253"/>
-      <c r="E34" s="253"/>
-      <c r="F34" s="253"/>
-      <c r="G34" s="253"/>
-      <c r="H34" s="253"/>
-      <c r="I34" s="253"/>
-      <c r="J34" s="253"/>
-      <c r="K34" s="253"/>
-      <c r="L34" s="253"/>
-      <c r="M34" s="253"/>
-      <c r="N34" s="253"/>
-      <c r="O34" s="253"/>
-      <c r="P34" s="253"/>
-      <c r="Q34" s="253"/>
-      <c r="R34" s="253"/>
+      <c r="C34" s="299"/>
+      <c r="D34" s="299"/>
+      <c r="E34" s="299"/>
+      <c r="F34" s="299"/>
+      <c r="G34" s="299"/>
+      <c r="H34" s="299"/>
+      <c r="I34" s="299"/>
+      <c r="J34" s="299"/>
+      <c r="K34" s="299"/>
+      <c r="L34" s="299"/>
+      <c r="M34" s="299"/>
+      <c r="N34" s="299"/>
+      <c r="O34" s="299"/>
+      <c r="P34" s="299"/>
+      <c r="Q34" s="299"/>
+      <c r="R34" s="299"/>
     </row>
     <row r="35" spans="2:21" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B35" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C35" s="318" t="s">
+      <c r="C35" s="314" t="s">
         <v>2</v>
       </c>
-      <c r="D35" s="318"/>
+      <c r="D35" s="314"/>
       <c r="E35" s="127" t="s">
         <v>135</v>
       </c>
@@ -10778,10 +10766,10 @@
       </c>
     </row>
     <row r="36" spans="2:21" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B36" s="254" t="s">
+      <c r="B36" s="300" t="s">
         <v>137</v>
       </c>
-      <c r="C36" s="252" t="s">
+      <c r="C36" s="257" t="s">
         <v>120</v>
       </c>
       <c r="D36" s="53" t="s">
@@ -10823,18 +10811,18 @@
       <c r="O36" s="53" t="s">
         <v>129</v>
       </c>
-      <c r="P36" s="255" t="s">
+      <c r="P36" s="281" t="s">
         <v>139</v>
       </c>
-      <c r="Q36" s="313"/>
-      <c r="R36" s="256"/>
+      <c r="Q36" s="327"/>
+      <c r="R36" s="282"/>
       <c r="U36" s="53" t="s">
         <v>140</v>
       </c>
     </row>
     <row r="37" spans="2:21" x14ac:dyDescent="0.3">
-      <c r="B37" s="254"/>
-      <c r="C37" s="252"/>
+      <c r="B37" s="300"/>
+      <c r="C37" s="257"/>
       <c r="D37" s="53" t="s">
         <v>24</v>
       </c>
@@ -10874,9 +10862,9 @@
       <c r="O37" s="53" t="s">
         <v>129</v>
       </c>
-      <c r="P37" s="314"/>
-      <c r="Q37" s="315"/>
-      <c r="R37" s="316"/>
+      <c r="P37" s="328"/>
+      <c r="Q37" s="329"/>
+      <c r="R37" s="330"/>
       <c r="U37" s="53" t="s">
         <v>140</v>
       </c>
@@ -10926,11 +10914,11 @@
       <c r="O38" s="53" t="s">
         <v>143</v>
       </c>
-      <c r="P38" s="310" t="s">
+      <c r="P38" s="320" t="s">
         <v>144</v>
       </c>
-      <c r="Q38" s="311"/>
-      <c r="R38" s="312"/>
+      <c r="Q38" s="321"/>
+      <c r="R38" s="322"/>
       <c r="U38" s="53" t="s">
         <v>145</v>
       </c>
@@ -10981,11 +10969,11 @@
       <c r="O39" s="53" t="s">
         <v>129</v>
       </c>
-      <c r="P39" s="310" t="s">
+      <c r="P39" s="320" t="s">
         <v>144</v>
       </c>
-      <c r="Q39" s="311"/>
-      <c r="R39" s="312"/>
+      <c r="Q39" s="321"/>
+      <c r="R39" s="322"/>
       <c r="U39" s="53" t="s">
         <v>140</v>
       </c>
@@ -11031,86 +11019,86 @@
       <c r="S41" s="7"/>
     </row>
     <row r="42" spans="2:21" x14ac:dyDescent="0.3">
-      <c r="B42" s="237" t="s">
+      <c r="B42" s="224" t="s">
         <v>35</v>
       </c>
-      <c r="C42" s="237"/>
-      <c r="D42" s="237"/>
-      <c r="E42" s="237"/>
-      <c r="F42" s="237"/>
-      <c r="G42" s="237"/>
-      <c r="H42" s="237"/>
-      <c r="I42" s="237"/>
-      <c r="J42" s="237"/>
-      <c r="K42" s="237"/>
-      <c r="L42" s="237"/>
-      <c r="M42" s="237"/>
-      <c r="N42" s="237"/>
-      <c r="O42" s="237"/>
-      <c r="P42" s="237"/>
-      <c r="Q42" s="237"/>
-      <c r="R42" s="237"/>
-      <c r="S42" s="237"/>
+      <c r="C42" s="224"/>
+      <c r="D42" s="224"/>
+      <c r="E42" s="224"/>
+      <c r="F42" s="224"/>
+      <c r="G42" s="224"/>
+      <c r="H42" s="224"/>
+      <c r="I42" s="224"/>
+      <c r="J42" s="224"/>
+      <c r="K42" s="224"/>
+      <c r="L42" s="224"/>
+      <c r="M42" s="224"/>
+      <c r="N42" s="224"/>
+      <c r="O42" s="224"/>
+      <c r="P42" s="224"/>
+      <c r="Q42" s="224"/>
+      <c r="R42" s="224"/>
+      <c r="S42" s="224"/>
     </row>
     <row r="43" spans="2:21" x14ac:dyDescent="0.3">
-      <c r="B43" s="237"/>
-      <c r="C43" s="237"/>
-      <c r="D43" s="237"/>
-      <c r="E43" s="237"/>
-      <c r="F43" s="237"/>
-      <c r="G43" s="237"/>
-      <c r="H43" s="237"/>
-      <c r="I43" s="237"/>
-      <c r="J43" s="237"/>
-      <c r="K43" s="237"/>
-      <c r="L43" s="237"/>
-      <c r="M43" s="237"/>
-      <c r="N43" s="237"/>
-      <c r="O43" s="237"/>
-      <c r="P43" s="237"/>
-      <c r="Q43" s="237"/>
-      <c r="R43" s="237"/>
-      <c r="S43" s="237"/>
+      <c r="B43" s="224"/>
+      <c r="C43" s="224"/>
+      <c r="D43" s="224"/>
+      <c r="E43" s="224"/>
+      <c r="F43" s="224"/>
+      <c r="G43" s="224"/>
+      <c r="H43" s="224"/>
+      <c r="I43" s="224"/>
+      <c r="J43" s="224"/>
+      <c r="K43" s="224"/>
+      <c r="L43" s="224"/>
+      <c r="M43" s="224"/>
+      <c r="N43" s="224"/>
+      <c r="O43" s="224"/>
+      <c r="P43" s="224"/>
+      <c r="Q43" s="224"/>
+      <c r="R43" s="224"/>
+      <c r="S43" s="224"/>
     </row>
     <row r="44" spans="2:21" x14ac:dyDescent="0.3">
-      <c r="B44" s="237"/>
-      <c r="C44" s="237"/>
-      <c r="D44" s="237"/>
-      <c r="E44" s="237"/>
-      <c r="F44" s="237"/>
-      <c r="G44" s="237"/>
-      <c r="H44" s="237"/>
-      <c r="I44" s="237"/>
-      <c r="J44" s="237"/>
-      <c r="K44" s="237"/>
-      <c r="L44" s="237"/>
-      <c r="M44" s="237"/>
-      <c r="N44" s="237"/>
-      <c r="O44" s="237"/>
-      <c r="P44" s="237"/>
-      <c r="Q44" s="237"/>
-      <c r="R44" s="237"/>
-      <c r="S44" s="237"/>
+      <c r="B44" s="224"/>
+      <c r="C44" s="224"/>
+      <c r="D44" s="224"/>
+      <c r="E44" s="224"/>
+      <c r="F44" s="224"/>
+      <c r="G44" s="224"/>
+      <c r="H44" s="224"/>
+      <c r="I44" s="224"/>
+      <c r="J44" s="224"/>
+      <c r="K44" s="224"/>
+      <c r="L44" s="224"/>
+      <c r="M44" s="224"/>
+      <c r="N44" s="224"/>
+      <c r="O44" s="224"/>
+      <c r="P44" s="224"/>
+      <c r="Q44" s="224"/>
+      <c r="R44" s="224"/>
+      <c r="S44" s="224"/>
     </row>
     <row r="45" spans="2:21" x14ac:dyDescent="0.3">
-      <c r="B45" s="240"/>
-      <c r="C45" s="240"/>
-      <c r="D45" s="240"/>
-      <c r="E45" s="240"/>
-      <c r="F45" s="240"/>
-      <c r="G45" s="240"/>
-      <c r="H45" s="240"/>
-      <c r="I45" s="240"/>
-      <c r="J45" s="240"/>
-      <c r="K45" s="240"/>
-      <c r="L45" s="240"/>
-      <c r="M45" s="240"/>
-      <c r="N45" s="240"/>
-      <c r="O45" s="240"/>
-      <c r="P45" s="240"/>
-      <c r="Q45" s="240"/>
-      <c r="R45" s="240"/>
-      <c r="S45" s="240"/>
+      <c r="B45" s="227"/>
+      <c r="C45" s="227"/>
+      <c r="D45" s="227"/>
+      <c r="E45" s="227"/>
+      <c r="F45" s="227"/>
+      <c r="G45" s="227"/>
+      <c r="H45" s="227"/>
+      <c r="I45" s="227"/>
+      <c r="J45" s="227"/>
+      <c r="K45" s="227"/>
+      <c r="L45" s="227"/>
+      <c r="M45" s="227"/>
+      <c r="N45" s="227"/>
+      <c r="O45" s="227"/>
+      <c r="P45" s="227"/>
+      <c r="Q45" s="227"/>
+      <c r="R45" s="227"/>
+      <c r="S45" s="227"/>
     </row>
     <row r="46" spans="2:21" x14ac:dyDescent="0.3">
       <c r="B46" s="42"/>
@@ -11268,24 +11256,24 @@
       <c r="R54" s="126"/>
     </row>
     <row r="55" spans="2:21" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B55" s="245" t="s">
+      <c r="B55" s="244" t="s">
         <v>148</v>
       </c>
-      <c r="C55" s="245"/>
-      <c r="D55" s="245"/>
-      <c r="E55" s="245"/>
-      <c r="F55" s="245"/>
-      <c r="G55" s="245"/>
-      <c r="H55" s="245"/>
-      <c r="I55" s="245"/>
-      <c r="J55" s="245"/>
-      <c r="K55" s="245"/>
-      <c r="L55" s="245"/>
-      <c r="M55" s="245"/>
-      <c r="N55" s="245"/>
-      <c r="O55" s="245"/>
-      <c r="P55" s="245"/>
-      <c r="Q55" s="245"/>
+      <c r="C55" s="244"/>
+      <c r="D55" s="244"/>
+      <c r="E55" s="244"/>
+      <c r="F55" s="244"/>
+      <c r="G55" s="244"/>
+      <c r="H55" s="244"/>
+      <c r="I55" s="244"/>
+      <c r="J55" s="244"/>
+      <c r="K55" s="244"/>
+      <c r="L55" s="244"/>
+      <c r="M55" s="244"/>
+      <c r="N55" s="244"/>
+      <c r="O55" s="244"/>
+      <c r="P55" s="244"/>
+      <c r="Q55" s="244"/>
     </row>
     <row r="56" spans="2:21" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B56" s="97" t="s">
@@ -11339,10 +11327,10 @@
       </c>
     </row>
     <row r="57" spans="2:21" ht="22.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B57" s="309" t="s">
+      <c r="B57" s="315" t="s">
         <v>152</v>
       </c>
-      <c r="C57" s="317" t="s">
+      <c r="C57" s="316" t="s">
         <v>120</v>
       </c>
       <c r="D57" s="143" t="s">
@@ -11384,7 +11372,7 @@
       <c r="O57" s="208" t="s">
         <v>60</v>
       </c>
-      <c r="P57" s="303" t="s">
+      <c r="P57" s="318" t="s">
         <v>81</v>
       </c>
       <c r="Q57" s="143" t="s">
@@ -11395,8 +11383,8 @@
       </c>
     </row>
     <row r="58" spans="2:21" x14ac:dyDescent="0.3">
-      <c r="B58" s="309"/>
-      <c r="C58" s="317"/>
+      <c r="B58" s="315"/>
+      <c r="C58" s="316"/>
       <c r="D58" s="143" t="s">
         <v>24</v>
       </c>
@@ -11436,7 +11424,7 @@
       <c r="O58" s="208" t="s">
         <v>60</v>
       </c>
-      <c r="P58" s="304"/>
+      <c r="P58" s="319"/>
       <c r="Q58" s="143" t="s">
         <v>130</v>
       </c>
@@ -11445,10 +11433,10 @@
       </c>
     </row>
     <row r="59" spans="2:21" x14ac:dyDescent="0.3">
-      <c r="B59" s="309" t="s">
+      <c r="B59" s="315" t="s">
         <v>154</v>
       </c>
-      <c r="C59" s="317" t="s">
+      <c r="C59" s="316" t="s">
         <v>120</v>
       </c>
       <c r="D59" s="143" t="s">
@@ -11490,15 +11478,15 @@
       <c r="O59" s="208" t="s">
         <v>60</v>
       </c>
-      <c r="P59" s="304"/>
+      <c r="P59" s="319"/>
       <c r="Q59" s="143" t="s">
         <v>130</v>
       </c>
       <c r="U59" s="53"/>
     </row>
     <row r="60" spans="2:21" ht="28.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B60" s="309"/>
-      <c r="C60" s="317"/>
+      <c r="B60" s="315"/>
+      <c r="C60" s="316"/>
       <c r="D60" s="143" t="s">
         <v>24</v>
       </c>
@@ -11538,17 +11526,17 @@
       <c r="O60" s="208" t="s">
         <v>60</v>
       </c>
-      <c r="P60" s="305"/>
+      <c r="P60" s="323"/>
       <c r="Q60" s="143" t="s">
         <v>130</v>
       </c>
       <c r="U60" s="53"/>
     </row>
     <row r="61" spans="2:21" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B61" s="309" t="s">
+      <c r="B61" s="315" t="s">
         <v>155</v>
       </c>
-      <c r="C61" s="317" t="s">
+      <c r="C61" s="316" t="s">
         <v>120</v>
       </c>
       <c r="D61" s="143" t="s">
@@ -11590,7 +11578,7 @@
       <c r="O61" s="208" t="s">
         <v>64</v>
       </c>
-      <c r="P61" s="306" t="s">
+      <c r="P61" s="324" t="s">
         <v>65</v>
       </c>
       <c r="Q61" s="143" t="s">
@@ -11601,8 +11589,8 @@
       </c>
     </row>
     <row r="62" spans="2:21" x14ac:dyDescent="0.3">
-      <c r="B62" s="309"/>
-      <c r="C62" s="317"/>
+      <c r="B62" s="315"/>
+      <c r="C62" s="316"/>
       <c r="D62" s="143" t="s">
         <v>24</v>
       </c>
@@ -11642,7 +11630,7 @@
       <c r="O62" s="208" t="s">
         <v>64</v>
       </c>
-      <c r="P62" s="307"/>
+      <c r="P62" s="325"/>
       <c r="Q62" s="143" t="s">
         <v>156</v>
       </c>
@@ -11651,10 +11639,10 @@
       </c>
     </row>
     <row r="63" spans="2:21" x14ac:dyDescent="0.3">
-      <c r="B63" s="309" t="s">
+      <c r="B63" s="315" t="s">
         <v>158</v>
       </c>
-      <c r="C63" s="317" t="s">
+      <c r="C63" s="316" t="s">
         <v>120</v>
       </c>
       <c r="D63" s="143" t="s">
@@ -11696,7 +11684,7 @@
       <c r="O63" s="208" t="s">
         <v>64</v>
       </c>
-      <c r="P63" s="307"/>
+      <c r="P63" s="325"/>
       <c r="Q63" s="143" t="s">
         <v>156</v>
       </c>
@@ -11705,8 +11693,8 @@
       </c>
     </row>
     <row r="64" spans="2:21" x14ac:dyDescent="0.3">
-      <c r="B64" s="309"/>
-      <c r="C64" s="317"/>
+      <c r="B64" s="315"/>
+      <c r="C64" s="316"/>
       <c r="D64" s="143" t="s">
         <v>24</v>
       </c>
@@ -11746,7 +11734,7 @@
       <c r="O64" s="208" t="s">
         <v>64</v>
       </c>
-      <c r="P64" s="308"/>
+      <c r="P64" s="326"/>
       <c r="Q64" s="143" t="s">
         <v>156</v>
       </c>
@@ -11755,24 +11743,24 @@
       </c>
     </row>
     <row r="65" spans="2:63 3073:12199 12790:15083" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B65" s="225" t="s">
+      <c r="B65" s="236" t="s">
         <v>159</v>
       </c>
-      <c r="C65" s="225"/>
-      <c r="D65" s="228"/>
-      <c r="E65" s="228"/>
-      <c r="F65" s="225"/>
-      <c r="G65" s="228"/>
-      <c r="H65" s="228"/>
-      <c r="I65" s="225"/>
-      <c r="J65" s="228"/>
-      <c r="K65" s="228"/>
-      <c r="L65" s="228"/>
-      <c r="M65" s="225"/>
-      <c r="N65" s="228"/>
-      <c r="O65" s="228"/>
-      <c r="P65" s="228"/>
-      <c r="Q65" s="228"/>
+      <c r="C65" s="236"/>
+      <c r="D65" s="231"/>
+      <c r="E65" s="231"/>
+      <c r="F65" s="236"/>
+      <c r="G65" s="231"/>
+      <c r="H65" s="231"/>
+      <c r="I65" s="236"/>
+      <c r="J65" s="231"/>
+      <c r="K65" s="231"/>
+      <c r="L65" s="231"/>
+      <c r="M65" s="236"/>
+      <c r="N65" s="231"/>
+      <c r="O65" s="231"/>
+      <c r="P65" s="231"/>
+      <c r="Q65" s="231"/>
       <c r="U65" s="53"/>
     </row>
     <row r="66" spans="2:63 3073:12199 12790:15083" ht="28.8" x14ac:dyDescent="0.3">
@@ -11825,7 +11813,7 @@
       <c r="U66" s="53"/>
     </row>
     <row r="67" spans="2:63 3073:12199 12790:15083" x14ac:dyDescent="0.3">
-      <c r="B67" s="289" t="s">
+      <c r="B67" s="274" t="s">
         <v>160</v>
       </c>
       <c r="C67" s="211" t="s">
@@ -11870,7 +11858,7 @@
       <c r="O67" s="208" t="s">
         <v>60</v>
       </c>
-      <c r="P67" s="303" t="s">
+      <c r="P67" s="318" t="s">
         <v>81</v>
       </c>
       <c r="Q67" s="149" t="s">
@@ -43329,7 +43317,7 @@
       </c>
     </row>
     <row r="68" spans="2:63 3073:12199 12790:15083" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B68" s="319"/>
+      <c r="B68" s="317"/>
       <c r="C68" s="211" t="s">
         <v>120</v>
       </c>
@@ -43372,7 +43360,7 @@
       <c r="O68" s="208" t="s">
         <v>60</v>
       </c>
-      <c r="P68" s="304"/>
+      <c r="P68" s="319"/>
       <c r="Q68" s="149" t="s">
         <v>130</v>
       </c>
@@ -54847,24 +54835,24 @@
       <c r="VHC68" s="158"/>
     </row>
     <row r="69" spans="2:63 3073:12199 12790:15083" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B69" s="245" t="s">
+      <c r="B69" s="244" t="s">
         <v>161</v>
       </c>
-      <c r="C69" s="245"/>
-      <c r="D69" s="245"/>
-      <c r="E69" s="245"/>
-      <c r="F69" s="245"/>
-      <c r="G69" s="245"/>
-      <c r="H69" s="245"/>
-      <c r="I69" s="245"/>
-      <c r="J69" s="245"/>
-      <c r="K69" s="245"/>
-      <c r="L69" s="245"/>
-      <c r="M69" s="245"/>
-      <c r="N69" s="245"/>
-      <c r="O69" s="245"/>
-      <c r="P69" s="245"/>
-      <c r="Q69" s="245"/>
+      <c r="C69" s="244"/>
+      <c r="D69" s="244"/>
+      <c r="E69" s="244"/>
+      <c r="F69" s="244"/>
+      <c r="G69" s="244"/>
+      <c r="H69" s="244"/>
+      <c r="I69" s="244"/>
+      <c r="J69" s="244"/>
+      <c r="K69" s="244"/>
+      <c r="L69" s="244"/>
+      <c r="M69" s="244"/>
+      <c r="N69" s="244"/>
+      <c r="O69" s="244"/>
+      <c r="P69" s="244"/>
+      <c r="Q69" s="244"/>
       <c r="U69" s="53"/>
     </row>
     <row r="70" spans="2:63 3073:12199 12790:15083" ht="28.8" x14ac:dyDescent="0.3">
@@ -54917,7 +54905,7 @@
       <c r="U70" s="53"/>
     </row>
     <row r="71" spans="2:63 3073:12199 12790:15083" x14ac:dyDescent="0.3">
-      <c r="B71" s="289" t="s">
+      <c r="B71" s="274" t="s">
         <v>162</v>
       </c>
       <c r="C71" s="211" t="s">
@@ -54962,7 +54950,7 @@
       <c r="O71" s="208" t="s">
         <v>60</v>
       </c>
-      <c r="P71" s="303" t="s">
+      <c r="P71" s="318" t="s">
         <v>81</v>
       </c>
       <c r="Q71" s="149" t="s">
@@ -54971,7 +54959,7 @@
       <c r="U71" s="53"/>
     </row>
     <row r="72" spans="2:63 3073:12199 12790:15083" x14ac:dyDescent="0.3">
-      <c r="B72" s="319"/>
+      <c r="B72" s="317"/>
       <c r="C72" s="211" t="s">
         <v>120</v>
       </c>
@@ -55014,7 +55002,7 @@
       <c r="O72" s="208" t="s">
         <v>60</v>
       </c>
-      <c r="P72" s="304"/>
+      <c r="P72" s="319"/>
       <c r="Q72" s="149" t="s">
         <v>130</v>
       </c>
@@ -55044,121 +55032,121 @@
       <c r="T74" s="6"/>
     </row>
     <row r="75" spans="2:63 3073:12199 12790:15083" x14ac:dyDescent="0.3">
-      <c r="B75" s="263" t="s">
+      <c r="B75" s="292" t="s">
         <v>35</v>
       </c>
-      <c r="C75" s="263"/>
-      <c r="D75" s="263"/>
-      <c r="E75" s="263"/>
-      <c r="F75" s="263"/>
-      <c r="G75" s="263"/>
-      <c r="H75" s="263"/>
-      <c r="I75" s="263"/>
-      <c r="J75" s="263"/>
-      <c r="K75" s="263"/>
-      <c r="L75" s="263"/>
-      <c r="M75" s="263"/>
-      <c r="N75" s="263"/>
-      <c r="O75" s="263"/>
-      <c r="P75" s="263"/>
-      <c r="Q75" s="263"/>
-      <c r="R75" s="263"/>
-      <c r="S75" s="263"/>
-      <c r="T75" s="263"/>
+      <c r="C75" s="292"/>
+      <c r="D75" s="292"/>
+      <c r="E75" s="292"/>
+      <c r="F75" s="292"/>
+      <c r="G75" s="292"/>
+      <c r="H75" s="292"/>
+      <c r="I75" s="292"/>
+      <c r="J75" s="292"/>
+      <c r="K75" s="292"/>
+      <c r="L75" s="292"/>
+      <c r="M75" s="292"/>
+      <c r="N75" s="292"/>
+      <c r="O75" s="292"/>
+      <c r="P75" s="292"/>
+      <c r="Q75" s="292"/>
+      <c r="R75" s="292"/>
+      <c r="S75" s="292"/>
+      <c r="T75" s="292"/>
     </row>
     <row r="76" spans="2:63 3073:12199 12790:15083" x14ac:dyDescent="0.3">
-      <c r="B76" s="263"/>
-      <c r="C76" s="263"/>
-      <c r="D76" s="263"/>
-      <c r="E76" s="263"/>
-      <c r="F76" s="263"/>
-      <c r="G76" s="263"/>
-      <c r="H76" s="263"/>
-      <c r="I76" s="263"/>
-      <c r="J76" s="263"/>
-      <c r="K76" s="263"/>
-      <c r="L76" s="263"/>
-      <c r="M76" s="263"/>
-      <c r="N76" s="263"/>
-      <c r="O76" s="263"/>
-      <c r="P76" s="263"/>
-      <c r="Q76" s="263"/>
-      <c r="R76" s="263"/>
-      <c r="S76" s="263"/>
-      <c r="T76" s="263"/>
+      <c r="B76" s="292"/>
+      <c r="C76" s="292"/>
+      <c r="D76" s="292"/>
+      <c r="E76" s="292"/>
+      <c r="F76" s="292"/>
+      <c r="G76" s="292"/>
+      <c r="H76" s="292"/>
+      <c r="I76" s="292"/>
+      <c r="J76" s="292"/>
+      <c r="K76" s="292"/>
+      <c r="L76" s="292"/>
+      <c r="M76" s="292"/>
+      <c r="N76" s="292"/>
+      <c r="O76" s="292"/>
+      <c r="P76" s="292"/>
+      <c r="Q76" s="292"/>
+      <c r="R76" s="292"/>
+      <c r="S76" s="292"/>
+      <c r="T76" s="292"/>
     </row>
     <row r="77" spans="2:63 3073:12199 12790:15083" x14ac:dyDescent="0.3">
-      <c r="B77" s="263"/>
-      <c r="C77" s="263"/>
-      <c r="D77" s="263"/>
-      <c r="E77" s="263"/>
-      <c r="F77" s="263"/>
-      <c r="G77" s="263"/>
-      <c r="H77" s="263"/>
-      <c r="I77" s="263"/>
-      <c r="J77" s="263"/>
-      <c r="K77" s="263"/>
-      <c r="L77" s="263"/>
-      <c r="M77" s="263"/>
-      <c r="N77" s="263"/>
-      <c r="O77" s="263"/>
-      <c r="P77" s="263"/>
-      <c r="Q77" s="263"/>
-      <c r="R77" s="263"/>
-      <c r="S77" s="263"/>
-      <c r="T77" s="263"/>
+      <c r="B77" s="292"/>
+      <c r="C77" s="292"/>
+      <c r="D77" s="292"/>
+      <c r="E77" s="292"/>
+      <c r="F77" s="292"/>
+      <c r="G77" s="292"/>
+      <c r="H77" s="292"/>
+      <c r="I77" s="292"/>
+      <c r="J77" s="292"/>
+      <c r="K77" s="292"/>
+      <c r="L77" s="292"/>
+      <c r="M77" s="292"/>
+      <c r="N77" s="292"/>
+      <c r="O77" s="292"/>
+      <c r="P77" s="292"/>
+      <c r="Q77" s="292"/>
+      <c r="R77" s="292"/>
+      <c r="S77" s="292"/>
+      <c r="T77" s="292"/>
     </row>
     <row r="78" spans="2:63 3073:12199 12790:15083" x14ac:dyDescent="0.3">
-      <c r="B78" s="263"/>
-      <c r="C78" s="263"/>
-      <c r="D78" s="263"/>
-      <c r="E78" s="263"/>
-      <c r="F78" s="263"/>
-      <c r="G78" s="263"/>
-      <c r="H78" s="263"/>
-      <c r="I78" s="263"/>
-      <c r="J78" s="263"/>
-      <c r="K78" s="263"/>
-      <c r="L78" s="263"/>
-      <c r="M78" s="263"/>
-      <c r="N78" s="263"/>
-      <c r="O78" s="263"/>
-      <c r="P78" s="263"/>
-      <c r="Q78" s="263"/>
-      <c r="R78" s="263"/>
-      <c r="S78" s="263"/>
-      <c r="T78" s="263"/>
+      <c r="B78" s="292"/>
+      <c r="C78" s="292"/>
+      <c r="D78" s="292"/>
+      <c r="E78" s="292"/>
+      <c r="F78" s="292"/>
+      <c r="G78" s="292"/>
+      <c r="H78" s="292"/>
+      <c r="I78" s="292"/>
+      <c r="J78" s="292"/>
+      <c r="K78" s="292"/>
+      <c r="L78" s="292"/>
+      <c r="M78" s="292"/>
+      <c r="N78" s="292"/>
+      <c r="O78" s="292"/>
+      <c r="P78" s="292"/>
+      <c r="Q78" s="292"/>
+      <c r="R78" s="292"/>
+      <c r="S78" s="292"/>
+      <c r="T78" s="292"/>
     </row>
     <row r="87" spans="2:20" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B87" s="229" t="s">
+      <c r="B87" s="232" t="s">
         <v>164</v>
       </c>
-      <c r="C87" s="229"/>
-      <c r="D87" s="229"/>
-      <c r="E87" s="229"/>
-      <c r="F87" s="229"/>
-      <c r="G87" s="229"/>
-      <c r="H87" s="229"/>
-      <c r="I87" s="229"/>
-      <c r="J87" s="229"/>
-      <c r="K87" s="229"/>
-      <c r="L87" s="229"/>
-      <c r="M87" s="229"/>
-      <c r="N87" s="229"/>
-      <c r="O87" s="229"/>
-      <c r="P87" s="229"/>
-      <c r="Q87" s="229"/>
-      <c r="R87" s="229"/>
-      <c r="S87" s="229"/>
+      <c r="C87" s="232"/>
+      <c r="D87" s="232"/>
+      <c r="E87" s="232"/>
+      <c r="F87" s="232"/>
+      <c r="G87" s="232"/>
+      <c r="H87" s="232"/>
+      <c r="I87" s="232"/>
+      <c r="J87" s="232"/>
+      <c r="K87" s="232"/>
+      <c r="L87" s="232"/>
+      <c r="M87" s="232"/>
+      <c r="N87" s="232"/>
+      <c r="O87" s="232"/>
+      <c r="P87" s="232"/>
+      <c r="Q87" s="232"/>
+      <c r="R87" s="232"/>
+      <c r="S87" s="232"/>
     </row>
     <row r="88" spans="2:20" ht="27" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B88" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C88" s="318" t="s">
+      <c r="C88" s="314" t="s">
         <v>2</v>
       </c>
-      <c r="D88" s="318"/>
+      <c r="D88" s="314"/>
       <c r="E88" s="127" t="s">
         <v>135</v>
       </c>
@@ -55202,10 +55190,10 @@
       <c r="S88" s="230"/>
     </row>
     <row r="89" spans="2:20" ht="28.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B89" s="231" t="s">
+      <c r="B89" s="238" t="s">
         <v>99</v>
       </c>
-      <c r="C89" s="252" t="s">
+      <c r="C89" s="257" t="s">
         <v>120</v>
       </c>
       <c r="D89" s="53" t="s">
@@ -55249,15 +55237,15 @@
       <c r="P89" s="53" t="s">
         <v>167</v>
       </c>
-      <c r="Q89" s="259" t="s">
+      <c r="Q89" s="258" t="s">
         <v>47</v>
       </c>
-      <c r="R89" s="259"/>
-      <c r="S89" s="259"/>
+      <c r="R89" s="258"/>
+      <c r="S89" s="258"/>
     </row>
     <row r="90" spans="2:20" x14ac:dyDescent="0.3">
-      <c r="B90" s="227"/>
-      <c r="C90" s="252"/>
+      <c r="B90" s="233"/>
+      <c r="C90" s="257"/>
       <c r="D90" s="53" t="s">
         <v>24</v>
       </c>
@@ -55299,9 +55287,9 @@
       <c r="P90" s="53" t="s">
         <v>167</v>
       </c>
-      <c r="Q90" s="259"/>
-      <c r="R90" s="259"/>
-      <c r="S90" s="259"/>
+      <c r="Q90" s="258"/>
+      <c r="R90" s="258"/>
+      <c r="S90" s="258"/>
     </row>
     <row r="92" spans="2:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B92" s="5" t="s">
@@ -55327,111 +55315,111 @@
       <c r="T92" s="6"/>
     </row>
     <row r="93" spans="2:20" x14ac:dyDescent="0.3">
-      <c r="B93" s="263" t="s">
+      <c r="B93" s="292" t="s">
         <v>35</v>
       </c>
-      <c r="C93" s="263"/>
-      <c r="D93" s="263"/>
-      <c r="E93" s="263"/>
-      <c r="F93" s="263"/>
-      <c r="G93" s="263"/>
-      <c r="H93" s="263"/>
-      <c r="I93" s="263"/>
-      <c r="J93" s="263"/>
-      <c r="K93" s="263"/>
-      <c r="L93" s="263"/>
-      <c r="M93" s="263"/>
-      <c r="N93" s="263"/>
-      <c r="O93" s="263"/>
-      <c r="P93" s="263"/>
-      <c r="Q93" s="263"/>
-      <c r="R93" s="263"/>
-      <c r="S93" s="263"/>
-      <c r="T93" s="263"/>
+      <c r="C93" s="292"/>
+      <c r="D93" s="292"/>
+      <c r="E93" s="292"/>
+      <c r="F93" s="292"/>
+      <c r="G93" s="292"/>
+      <c r="H93" s="292"/>
+      <c r="I93" s="292"/>
+      <c r="J93" s="292"/>
+      <c r="K93" s="292"/>
+      <c r="L93" s="292"/>
+      <c r="M93" s="292"/>
+      <c r="N93" s="292"/>
+      <c r="O93" s="292"/>
+      <c r="P93" s="292"/>
+      <c r="Q93" s="292"/>
+      <c r="R93" s="292"/>
+      <c r="S93" s="292"/>
+      <c r="T93" s="292"/>
     </row>
     <row r="94" spans="2:20" x14ac:dyDescent="0.3">
-      <c r="B94" s="263"/>
-      <c r="C94" s="263"/>
-      <c r="D94" s="263"/>
-      <c r="E94" s="263"/>
-      <c r="F94" s="263"/>
-      <c r="G94" s="263"/>
-      <c r="H94" s="263"/>
-      <c r="I94" s="263"/>
-      <c r="J94" s="263"/>
-      <c r="K94" s="263"/>
-      <c r="L94" s="263"/>
-      <c r="M94" s="263"/>
-      <c r="N94" s="263"/>
-      <c r="O94" s="263"/>
-      <c r="P94" s="263"/>
-      <c r="Q94" s="263"/>
-      <c r="R94" s="263"/>
-      <c r="S94" s="263"/>
-      <c r="T94" s="263"/>
+      <c r="B94" s="292"/>
+      <c r="C94" s="292"/>
+      <c r="D94" s="292"/>
+      <c r="E94" s="292"/>
+      <c r="F94" s="292"/>
+      <c r="G94" s="292"/>
+      <c r="H94" s="292"/>
+      <c r="I94" s="292"/>
+      <c r="J94" s="292"/>
+      <c r="K94" s="292"/>
+      <c r="L94" s="292"/>
+      <c r="M94" s="292"/>
+      <c r="N94" s="292"/>
+      <c r="O94" s="292"/>
+      <c r="P94" s="292"/>
+      <c r="Q94" s="292"/>
+      <c r="R94" s="292"/>
+      <c r="S94" s="292"/>
+      <c r="T94" s="292"/>
     </row>
     <row r="95" spans="2:20" x14ac:dyDescent="0.3">
-      <c r="B95" s="263"/>
-      <c r="C95" s="263"/>
-      <c r="D95" s="263"/>
-      <c r="E95" s="263"/>
-      <c r="F95" s="263"/>
-      <c r="G95" s="263"/>
-      <c r="H95" s="263"/>
-      <c r="I95" s="263"/>
-      <c r="J95" s="263"/>
-      <c r="K95" s="263"/>
-      <c r="L95" s="263"/>
-      <c r="M95" s="263"/>
-      <c r="N95" s="263"/>
-      <c r="O95" s="263"/>
-      <c r="P95" s="263"/>
-      <c r="Q95" s="263"/>
-      <c r="R95" s="263"/>
-      <c r="S95" s="263"/>
-      <c r="T95" s="263"/>
+      <c r="B95" s="292"/>
+      <c r="C95" s="292"/>
+      <c r="D95" s="292"/>
+      <c r="E95" s="292"/>
+      <c r="F95" s="292"/>
+      <c r="G95" s="292"/>
+      <c r="H95" s="292"/>
+      <c r="I95" s="292"/>
+      <c r="J95" s="292"/>
+      <c r="K95" s="292"/>
+      <c r="L95" s="292"/>
+      <c r="M95" s="292"/>
+      <c r="N95" s="292"/>
+      <c r="O95" s="292"/>
+      <c r="P95" s="292"/>
+      <c r="Q95" s="292"/>
+      <c r="R95" s="292"/>
+      <c r="S95" s="292"/>
+      <c r="T95" s="292"/>
     </row>
     <row r="96" spans="2:20" x14ac:dyDescent="0.3">
-      <c r="B96" s="263"/>
-      <c r="C96" s="263"/>
-      <c r="D96" s="263"/>
-      <c r="E96" s="263"/>
-      <c r="F96" s="263"/>
-      <c r="G96" s="263"/>
-      <c r="H96" s="263"/>
-      <c r="I96" s="263"/>
-      <c r="J96" s="263"/>
-      <c r="K96" s="263"/>
-      <c r="L96" s="263"/>
-      <c r="M96" s="263"/>
-      <c r="N96" s="263"/>
-      <c r="O96" s="263"/>
-      <c r="P96" s="263"/>
-      <c r="Q96" s="263"/>
-      <c r="R96" s="263"/>
-      <c r="S96" s="263"/>
-      <c r="T96" s="263"/>
+      <c r="B96" s="292"/>
+      <c r="C96" s="292"/>
+      <c r="D96" s="292"/>
+      <c r="E96" s="292"/>
+      <c r="F96" s="292"/>
+      <c r="G96" s="292"/>
+      <c r="H96" s="292"/>
+      <c r="I96" s="292"/>
+      <c r="J96" s="292"/>
+      <c r="K96" s="292"/>
+      <c r="L96" s="292"/>
+      <c r="M96" s="292"/>
+      <c r="N96" s="292"/>
+      <c r="O96" s="292"/>
+      <c r="P96" s="292"/>
+      <c r="Q96" s="292"/>
+      <c r="R96" s="292"/>
+      <c r="S96" s="292"/>
+      <c r="T96" s="292"/>
     </row>
     <row r="106" spans="2:17" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="107" spans="2:17" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B107" s="245" t="s">
+      <c r="B107" s="244" t="s">
         <v>168</v>
       </c>
-      <c r="C107" s="245"/>
-      <c r="D107" s="245"/>
-      <c r="E107" s="245"/>
-      <c r="F107" s="245"/>
-      <c r="G107" s="245"/>
-      <c r="H107" s="245"/>
-      <c r="I107" s="245"/>
-      <c r="J107" s="245"/>
-      <c r="K107" s="245"/>
-      <c r="L107" s="245"/>
-      <c r="M107" s="245"/>
-      <c r="N107" s="245"/>
-      <c r="O107" s="245"/>
-      <c r="P107" s="245"/>
-      <c r="Q107" s="245"/>
+      <c r="C107" s="244"/>
+      <c r="D107" s="244"/>
+      <c r="E107" s="244"/>
+      <c r="F107" s="244"/>
+      <c r="G107" s="244"/>
+      <c r="H107" s="244"/>
+      <c r="I107" s="244"/>
+      <c r="J107" s="244"/>
+      <c r="K107" s="244"/>
+      <c r="L107" s="244"/>
+      <c r="M107" s="244"/>
+      <c r="N107" s="244"/>
+      <c r="O107" s="244"/>
+      <c r="P107" s="244"/>
+      <c r="Q107" s="244"/>
     </row>
     <row r="108" spans="2:17" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B108" s="97" t="s">
@@ -55482,10 +55470,10 @@
       </c>
     </row>
     <row r="109" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B109" s="320" t="s">
+      <c r="B109" s="302" t="s">
         <v>169</v>
       </c>
-      <c r="C109" s="252" t="s">
+      <c r="C109" s="257" t="s">
         <v>120</v>
       </c>
       <c r="D109" s="53" t="s">
@@ -55534,8 +55522,8 @@
       </c>
     </row>
     <row r="110" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B110" s="320"/>
-      <c r="C110" s="252"/>
+      <c r="B110" s="302"/>
+      <c r="C110" s="257"/>
       <c r="D110" s="53" t="s">
         <v>24</v>
       </c>
@@ -55583,24 +55571,24 @@
     </row>
     <row r="119" spans="2:17" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="120" spans="2:17" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B120" s="245" t="s">
+      <c r="B120" s="244" t="s">
         <v>173</v>
       </c>
-      <c r="C120" s="245"/>
-      <c r="D120" s="245"/>
-      <c r="E120" s="245"/>
-      <c r="F120" s="245"/>
-      <c r="G120" s="245"/>
-      <c r="H120" s="245"/>
-      <c r="I120" s="245"/>
-      <c r="J120" s="245"/>
-      <c r="K120" s="245"/>
-      <c r="L120" s="245"/>
-      <c r="M120" s="245"/>
-      <c r="N120" s="245"/>
-      <c r="O120" s="245"/>
-      <c r="P120" s="245"/>
-      <c r="Q120" s="245"/>
+      <c r="C120" s="244"/>
+      <c r="D120" s="244"/>
+      <c r="E120" s="244"/>
+      <c r="F120" s="244"/>
+      <c r="G120" s="244"/>
+      <c r="H120" s="244"/>
+      <c r="I120" s="244"/>
+      <c r="J120" s="244"/>
+      <c r="K120" s="244"/>
+      <c r="L120" s="244"/>
+      <c r="M120" s="244"/>
+      <c r="N120" s="244"/>
+      <c r="O120" s="244"/>
+      <c r="P120" s="244"/>
+      <c r="Q120" s="244"/>
     </row>
     <row r="121" spans="2:17" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B121" s="97" t="s">
@@ -55651,10 +55639,10 @@
       </c>
     </row>
     <row r="122" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B122" s="320" t="s">
+      <c r="B122" s="302" t="s">
         <v>174</v>
       </c>
-      <c r="C122" s="252" t="s">
+      <c r="C122" s="257" t="s">
         <v>120</v>
       </c>
       <c r="D122" s="53" t="s">
@@ -55703,10 +55691,10 @@
       </c>
     </row>
     <row r="123" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B123" s="320" t="s">
+      <c r="B123" s="302" t="s">
         <v>174</v>
       </c>
-      <c r="C123" s="252" t="s">
+      <c r="C123" s="257" t="s">
         <v>120</v>
       </c>
       <c r="D123" s="53" t="s">
@@ -55755,10 +55743,10 @@
       </c>
     </row>
     <row r="124" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B124" s="320" t="s">
+      <c r="B124" s="302" t="s">
         <v>175</v>
       </c>
-      <c r="C124" s="252" t="s">
+      <c r="C124" s="257" t="s">
         <v>120</v>
       </c>
       <c r="D124" s="53" t="s">
@@ -55808,8 +55796,8 @@
       </c>
     </row>
     <row r="125" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B125" s="320"/>
-      <c r="C125" s="252"/>
+      <c r="B125" s="302"/>
+      <c r="C125" s="257"/>
       <c r="D125" s="53" t="s">
         <v>24</v>
       </c>
@@ -55858,6 +55846,49 @@
     </row>
   </sheetData>
   <mergeCells count="59">
+    <mergeCell ref="P57:P60"/>
+    <mergeCell ref="P61:P64"/>
+    <mergeCell ref="B11:B12"/>
+    <mergeCell ref="C11:C12"/>
+    <mergeCell ref="B61:B62"/>
+    <mergeCell ref="P39:R39"/>
+    <mergeCell ref="B15:B16"/>
+    <mergeCell ref="C15:C16"/>
+    <mergeCell ref="B17:B18"/>
+    <mergeCell ref="C17:C18"/>
+    <mergeCell ref="B36:B37"/>
+    <mergeCell ref="C36:C37"/>
+    <mergeCell ref="P36:R37"/>
+    <mergeCell ref="B9:Q9"/>
+    <mergeCell ref="C61:C62"/>
+    <mergeCell ref="B13:B14"/>
+    <mergeCell ref="C13:C14"/>
+    <mergeCell ref="B57:B58"/>
+    <mergeCell ref="C57:C58"/>
+    <mergeCell ref="B42:S45"/>
+    <mergeCell ref="B55:Q55"/>
+    <mergeCell ref="C56:D56"/>
+    <mergeCell ref="B34:R34"/>
+    <mergeCell ref="C35:D35"/>
+    <mergeCell ref="P35:R35"/>
+    <mergeCell ref="P38:R38"/>
+    <mergeCell ref="B59:B60"/>
+    <mergeCell ref="C59:C60"/>
+    <mergeCell ref="C10:D10"/>
+    <mergeCell ref="Q88:S88"/>
+    <mergeCell ref="B87:S87"/>
+    <mergeCell ref="C88:D88"/>
+    <mergeCell ref="C66:D66"/>
+    <mergeCell ref="B63:B64"/>
+    <mergeCell ref="C63:C64"/>
+    <mergeCell ref="B65:Q65"/>
+    <mergeCell ref="C70:D70"/>
+    <mergeCell ref="B75:T78"/>
+    <mergeCell ref="B67:B68"/>
+    <mergeCell ref="B69:Q69"/>
+    <mergeCell ref="B71:B72"/>
+    <mergeCell ref="P67:P68"/>
+    <mergeCell ref="P71:P72"/>
     <mergeCell ref="B124:B125"/>
     <mergeCell ref="C124:C125"/>
     <mergeCell ref="B122:B123"/>
@@ -55874,49 +55905,6 @@
     <mergeCell ref="C108:D108"/>
     <mergeCell ref="B120:Q120"/>
     <mergeCell ref="C121:D121"/>
-    <mergeCell ref="Q88:S88"/>
-    <mergeCell ref="B87:S87"/>
-    <mergeCell ref="C88:D88"/>
-    <mergeCell ref="C66:D66"/>
-    <mergeCell ref="B63:B64"/>
-    <mergeCell ref="C63:C64"/>
-    <mergeCell ref="B65:Q65"/>
-    <mergeCell ref="C70:D70"/>
-    <mergeCell ref="B75:T78"/>
-    <mergeCell ref="B67:B68"/>
-    <mergeCell ref="B69:Q69"/>
-    <mergeCell ref="B71:B72"/>
-    <mergeCell ref="P67:P68"/>
-    <mergeCell ref="P71:P72"/>
-    <mergeCell ref="B9:Q9"/>
-    <mergeCell ref="C61:C62"/>
-    <mergeCell ref="B13:B14"/>
-    <mergeCell ref="C13:C14"/>
-    <mergeCell ref="B57:B58"/>
-    <mergeCell ref="C57:C58"/>
-    <mergeCell ref="B42:S45"/>
-    <mergeCell ref="B55:Q55"/>
-    <mergeCell ref="C56:D56"/>
-    <mergeCell ref="B34:R34"/>
-    <mergeCell ref="C35:D35"/>
-    <mergeCell ref="P35:R35"/>
-    <mergeCell ref="P38:R38"/>
-    <mergeCell ref="B59:B60"/>
-    <mergeCell ref="C59:C60"/>
-    <mergeCell ref="C10:D10"/>
-    <mergeCell ref="P57:P60"/>
-    <mergeCell ref="P61:P64"/>
-    <mergeCell ref="B11:B12"/>
-    <mergeCell ref="C11:C12"/>
-    <mergeCell ref="B61:B62"/>
-    <mergeCell ref="P39:R39"/>
-    <mergeCell ref="B15:B16"/>
-    <mergeCell ref="C15:C16"/>
-    <mergeCell ref="B17:B18"/>
-    <mergeCell ref="C17:C18"/>
-    <mergeCell ref="B36:B37"/>
-    <mergeCell ref="C36:C37"/>
-    <mergeCell ref="P36:R37"/>
   </mergeCells>
   <phoneticPr fontId="14" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -55954,8 +55942,8 @@
     <row r="8" spans="2:18" x14ac:dyDescent="0.3">
       <c r="B8" s="126"/>
       <c r="C8" s="126"/>
-      <c r="D8" s="334"/>
-      <c r="E8" s="334"/>
+      <c r="D8" s="339"/>
+      <c r="E8" s="339"/>
       <c r="F8" s="126"/>
       <c r="G8" s="126"/>
       <c r="H8" s="126"/>
@@ -55971,32 +55959,32 @@
       <c r="R8" s="126"/>
     </row>
     <row r="9" spans="2:18" ht="28.8" x14ac:dyDescent="0.55000000000000004">
-      <c r="B9" s="337" t="s">
+      <c r="B9" s="342" t="s">
         <v>176</v>
       </c>
-      <c r="C9" s="337"/>
-      <c r="D9" s="337"/>
-      <c r="E9" s="337"/>
-      <c r="F9" s="337"/>
-      <c r="G9" s="337"/>
-      <c r="H9" s="337"/>
-      <c r="I9" s="337"/>
-      <c r="J9" s="337"/>
-      <c r="K9" s="337"/>
-      <c r="L9" s="337"/>
-      <c r="M9" s="337"/>
-      <c r="N9" s="337"/>
-      <c r="O9" s="337"/>
-      <c r="P9" s="337"/>
+      <c r="C9" s="342"/>
+      <c r="D9" s="342"/>
+      <c r="E9" s="342"/>
+      <c r="F9" s="342"/>
+      <c r="G9" s="342"/>
+      <c r="H9" s="342"/>
+      <c r="I9" s="342"/>
+      <c r="J9" s="342"/>
+      <c r="K9" s="342"/>
+      <c r="L9" s="342"/>
+      <c r="M9" s="342"/>
+      <c r="N9" s="342"/>
+      <c r="O9" s="342"/>
+      <c r="P9" s="342"/>
     </row>
     <row r="10" spans="2:18" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B10" s="127" t="s">
         <v>1</v>
       </c>
-      <c r="C10" s="353" t="s">
+      <c r="C10" s="340" t="s">
         <v>2</v>
       </c>
-      <c r="D10" s="354"/>
+      <c r="D10" s="341"/>
       <c r="E10" s="12" t="s">
         <v>3</v>
       </c>
@@ -56036,10 +56024,10 @@
       <c r="Q10" s="126"/>
     </row>
     <row r="11" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="B11" s="355" t="s">
+      <c r="B11" s="331" t="s">
         <v>179</v>
       </c>
-      <c r="C11" s="355" t="s">
+      <c r="C11" s="331" t="s">
         <v>180</v>
       </c>
       <c r="D11" s="41" t="s">
@@ -56087,8 +56075,8 @@
       <c r="Q11" s="126"/>
     </row>
     <row r="12" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="B12" s="356"/>
-      <c r="C12" s="356"/>
+      <c r="B12" s="332"/>
+      <c r="C12" s="332"/>
       <c r="D12" s="41" t="s">
         <v>24</v>
       </c>
@@ -56134,10 +56122,10 @@
       <c r="Q12" s="126"/>
     </row>
     <row r="13" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="B13" s="355" t="s">
+      <c r="B13" s="331" t="s">
         <v>182</v>
       </c>
-      <c r="C13" s="355" t="s">
+      <c r="C13" s="331" t="s">
         <v>180</v>
       </c>
       <c r="D13" s="41" t="s">
@@ -56185,8 +56173,8 @@
       <c r="Q13" s="126"/>
     </row>
     <row r="14" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="B14" s="356"/>
-      <c r="C14" s="356"/>
+      <c r="B14" s="332"/>
+      <c r="C14" s="332"/>
       <c r="D14" s="41" t="s">
         <v>24</v>
       </c>
@@ -56232,10 +56220,10 @@
       <c r="Q14" s="126"/>
     </row>
     <row r="15" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="B15" s="355" t="s">
+      <c r="B15" s="331" t="s">
         <v>132</v>
       </c>
-      <c r="C15" s="355" t="s">
+      <c r="C15" s="331" t="s">
         <v>180</v>
       </c>
       <c r="D15" s="41" t="s">
@@ -56283,8 +56271,8 @@
       <c r="Q15" s="126"/>
     </row>
     <row r="16" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="B16" s="356"/>
-      <c r="C16" s="356"/>
+      <c r="B16" s="332"/>
+      <c r="C16" s="332"/>
       <c r="D16" s="41" t="s">
         <v>24</v>
       </c>
@@ -56344,93 +56332,93 @@
       <c r="N17" s="34"/>
     </row>
     <row r="18" spans="2:17" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B18" s="359" t="s">
+      <c r="B18" s="336" t="s">
         <v>34</v>
       </c>
-      <c r="C18" s="360"/>
-      <c r="D18" s="360"/>
-      <c r="E18" s="360"/>
-      <c r="F18" s="360"/>
-      <c r="G18" s="360"/>
-      <c r="H18" s="360"/>
-      <c r="I18" s="360"/>
-      <c r="J18" s="360"/>
-      <c r="K18" s="360"/>
-      <c r="L18" s="360"/>
-      <c r="M18" s="360"/>
-      <c r="N18" s="360"/>
-      <c r="O18" s="360"/>
-      <c r="P18" s="361"/>
+      <c r="C18" s="337"/>
+      <c r="D18" s="337"/>
+      <c r="E18" s="337"/>
+      <c r="F18" s="337"/>
+      <c r="G18" s="337"/>
+      <c r="H18" s="337"/>
+      <c r="I18" s="337"/>
+      <c r="J18" s="337"/>
+      <c r="K18" s="337"/>
+      <c r="L18" s="337"/>
+      <c r="M18" s="337"/>
+      <c r="N18" s="337"/>
+      <c r="O18" s="337"/>
+      <c r="P18" s="338"/>
     </row>
     <row r="19" spans="2:17" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B19" s="324" t="s">
+      <c r="B19" s="306" t="s">
         <v>35</v>
       </c>
-      <c r="C19" s="325"/>
-      <c r="D19" s="325"/>
-      <c r="E19" s="325"/>
-      <c r="F19" s="325"/>
-      <c r="G19" s="325"/>
-      <c r="H19" s="325"/>
-      <c r="I19" s="325"/>
-      <c r="J19" s="325"/>
-      <c r="K19" s="325"/>
-      <c r="L19" s="325"/>
-      <c r="M19" s="325"/>
-      <c r="N19" s="325"/>
-      <c r="O19" s="325"/>
-      <c r="P19" s="326"/>
+      <c r="C19" s="307"/>
+      <c r="D19" s="307"/>
+      <c r="E19" s="307"/>
+      <c r="F19" s="307"/>
+      <c r="G19" s="307"/>
+      <c r="H19" s="307"/>
+      <c r="I19" s="307"/>
+      <c r="J19" s="307"/>
+      <c r="K19" s="307"/>
+      <c r="L19" s="307"/>
+      <c r="M19" s="307"/>
+      <c r="N19" s="307"/>
+      <c r="O19" s="307"/>
+      <c r="P19" s="308"/>
     </row>
     <row r="20" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B20" s="327"/>
-      <c r="C20" s="297"/>
-      <c r="D20" s="297"/>
-      <c r="E20" s="297"/>
-      <c r="F20" s="297"/>
-      <c r="G20" s="297"/>
-      <c r="H20" s="297"/>
-      <c r="I20" s="297"/>
-      <c r="J20" s="297"/>
-      <c r="K20" s="297"/>
-      <c r="L20" s="297"/>
-      <c r="M20" s="297"/>
-      <c r="N20" s="297"/>
-      <c r="O20" s="297"/>
-      <c r="P20" s="328"/>
+      <c r="B20" s="309"/>
+      <c r="C20" s="251"/>
+      <c r="D20" s="251"/>
+      <c r="E20" s="251"/>
+      <c r="F20" s="251"/>
+      <c r="G20" s="251"/>
+      <c r="H20" s="251"/>
+      <c r="I20" s="251"/>
+      <c r="J20" s="251"/>
+      <c r="K20" s="251"/>
+      <c r="L20" s="251"/>
+      <c r="M20" s="251"/>
+      <c r="N20" s="251"/>
+      <c r="O20" s="251"/>
+      <c r="P20" s="310"/>
     </row>
     <row r="21" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B21" s="327"/>
-      <c r="C21" s="297"/>
-      <c r="D21" s="297"/>
-      <c r="E21" s="297"/>
-      <c r="F21" s="297"/>
-      <c r="G21" s="297"/>
-      <c r="H21" s="297"/>
-      <c r="I21" s="297"/>
-      <c r="J21" s="297"/>
-      <c r="K21" s="297"/>
-      <c r="L21" s="297"/>
-      <c r="M21" s="297"/>
-      <c r="N21" s="297"/>
-      <c r="O21" s="297"/>
-      <c r="P21" s="328"/>
+      <c r="B21" s="309"/>
+      <c r="C21" s="251"/>
+      <c r="D21" s="251"/>
+      <c r="E21" s="251"/>
+      <c r="F21" s="251"/>
+      <c r="G21" s="251"/>
+      <c r="H21" s="251"/>
+      <c r="I21" s="251"/>
+      <c r="J21" s="251"/>
+      <c r="K21" s="251"/>
+      <c r="L21" s="251"/>
+      <c r="M21" s="251"/>
+      <c r="N21" s="251"/>
+      <c r="O21" s="251"/>
+      <c r="P21" s="310"/>
     </row>
     <row r="22" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B22" s="329"/>
-      <c r="C22" s="330"/>
-      <c r="D22" s="330"/>
-      <c r="E22" s="330"/>
-      <c r="F22" s="330"/>
-      <c r="G22" s="330"/>
-      <c r="H22" s="330"/>
-      <c r="I22" s="330"/>
-      <c r="J22" s="330"/>
-      <c r="K22" s="330"/>
-      <c r="L22" s="330"/>
-      <c r="M22" s="330"/>
-      <c r="N22" s="330"/>
-      <c r="O22" s="330"/>
-      <c r="P22" s="331"/>
+      <c r="B22" s="311"/>
+      <c r="C22" s="312"/>
+      <c r="D22" s="312"/>
+      <c r="E22" s="312"/>
+      <c r="F22" s="312"/>
+      <c r="G22" s="312"/>
+      <c r="H22" s="312"/>
+      <c r="I22" s="312"/>
+      <c r="J22" s="312"/>
+      <c r="K22" s="312"/>
+      <c r="L22" s="312"/>
+      <c r="M22" s="312"/>
+      <c r="N22" s="312"/>
+      <c r="O22" s="312"/>
+      <c r="P22" s="313"/>
     </row>
     <row r="23" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B23" s="27"/>
@@ -56560,33 +56548,33 @@
       <c r="N31" s="34"/>
     </row>
     <row r="32" spans="2:17" ht="28.8" x14ac:dyDescent="0.55000000000000004">
-      <c r="B32" s="357" t="s">
+      <c r="B32" s="333" t="s">
         <v>184</v>
       </c>
-      <c r="C32" s="336"/>
-      <c r="D32" s="336"/>
-      <c r="E32" s="336"/>
-      <c r="F32" s="336"/>
-      <c r="G32" s="336"/>
-      <c r="H32" s="336"/>
-      <c r="I32" s="336"/>
-      <c r="J32" s="336"/>
-      <c r="K32" s="336"/>
-      <c r="L32" s="336"/>
-      <c r="M32" s="336"/>
-      <c r="N32" s="336"/>
-      <c r="O32" s="336"/>
-      <c r="P32" s="336"/>
-      <c r="Q32" s="358"/>
+      <c r="C32" s="334"/>
+      <c r="D32" s="334"/>
+      <c r="E32" s="334"/>
+      <c r="F32" s="334"/>
+      <c r="G32" s="334"/>
+      <c r="H32" s="334"/>
+      <c r="I32" s="334"/>
+      <c r="J32" s="334"/>
+      <c r="K32" s="334"/>
+      <c r="L32" s="334"/>
+      <c r="M32" s="334"/>
+      <c r="N32" s="334"/>
+      <c r="O32" s="334"/>
+      <c r="P32" s="334"/>
+      <c r="Q32" s="335"/>
     </row>
     <row r="33" spans="2:19" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B33" s="127" t="s">
         <v>1</v>
       </c>
-      <c r="C33" s="352" t="s">
+      <c r="C33" s="343" t="s">
         <v>2</v>
       </c>
-      <c r="D33" s="352"/>
+      <c r="D33" s="343"/>
       <c r="E33" s="127" t="s">
         <v>135</v>
       </c>
@@ -56620,19 +56608,19 @@
       <c r="O33" s="127" t="s">
         <v>14</v>
       </c>
-      <c r="P33" s="285" t="s">
+      <c r="P33" s="259" t="s">
         <v>38</v>
       </c>
-      <c r="Q33" s="286"/>
+      <c r="Q33" s="260"/>
       <c r="S33" s="121" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="34" spans="2:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B34" s="350" t="s">
+      <c r="B34" s="348" t="s">
         <v>188</v>
       </c>
-      <c r="C34" s="351" t="s">
+      <c r="C34" s="349" t="s">
         <v>180</v>
       </c>
       <c r="D34" s="40" t="s">
@@ -56673,17 +56661,17 @@
       <c r="O34" s="40" t="s">
         <v>46</v>
       </c>
-      <c r="P34" s="255" t="s">
+      <c r="P34" s="281" t="s">
         <v>189</v>
       </c>
-      <c r="Q34" s="256"/>
+      <c r="Q34" s="282"/>
       <c r="S34" s="53" t="s">
         <v>190</v>
       </c>
     </row>
     <row r="35" spans="2:19" x14ac:dyDescent="0.3">
-      <c r="B35" s="350"/>
-      <c r="C35" s="351"/>
+      <c r="B35" s="348"/>
+      <c r="C35" s="349"/>
       <c r="D35" s="40" t="s">
         <v>24</v>
       </c>
@@ -56722,8 +56710,8 @@
       <c r="O35" s="40" t="s">
         <v>46</v>
       </c>
-      <c r="P35" s="314"/>
-      <c r="Q35" s="316"/>
+      <c r="P35" s="328"/>
+      <c r="Q35" s="330"/>
       <c r="S35" s="53" t="s">
         <v>190</v>
       </c>
@@ -56773,8 +56761,8 @@
       <c r="O36" s="40" t="s">
         <v>46</v>
       </c>
-      <c r="P36" s="257"/>
-      <c r="Q36" s="258"/>
+      <c r="P36" s="283"/>
+      <c r="Q36" s="284"/>
       <c r="S36" s="53" t="s">
         <v>145</v>
       </c>
@@ -56830,74 +56818,74 @@
       <c r="P39" s="7"/>
     </row>
     <row r="40" spans="2:19" x14ac:dyDescent="0.3">
-      <c r="B40" s="237" t="s">
+      <c r="B40" s="224" t="s">
         <v>35</v>
       </c>
-      <c r="C40" s="238"/>
-      <c r="D40" s="238"/>
-      <c r="E40" s="238"/>
-      <c r="F40" s="238"/>
-      <c r="G40" s="238"/>
-      <c r="H40" s="238"/>
-      <c r="I40" s="238"/>
-      <c r="J40" s="238"/>
-      <c r="K40" s="238"/>
-      <c r="L40" s="238"/>
-      <c r="M40" s="238"/>
-      <c r="N40" s="238"/>
-      <c r="O40" s="238"/>
-      <c r="P40" s="239"/>
+      <c r="C40" s="225"/>
+      <c r="D40" s="225"/>
+      <c r="E40" s="225"/>
+      <c r="F40" s="225"/>
+      <c r="G40" s="225"/>
+      <c r="H40" s="225"/>
+      <c r="I40" s="225"/>
+      <c r="J40" s="225"/>
+      <c r="K40" s="225"/>
+      <c r="L40" s="225"/>
+      <c r="M40" s="225"/>
+      <c r="N40" s="225"/>
+      <c r="O40" s="225"/>
+      <c r="P40" s="226"/>
     </row>
     <row r="41" spans="2:19" x14ac:dyDescent="0.3">
-      <c r="B41" s="237"/>
-      <c r="C41" s="238"/>
-      <c r="D41" s="238"/>
-      <c r="E41" s="238"/>
-      <c r="F41" s="238"/>
-      <c r="G41" s="238"/>
-      <c r="H41" s="238"/>
-      <c r="I41" s="238"/>
-      <c r="J41" s="238"/>
-      <c r="K41" s="238"/>
-      <c r="L41" s="238"/>
-      <c r="M41" s="238"/>
-      <c r="N41" s="238"/>
-      <c r="O41" s="238"/>
-      <c r="P41" s="239"/>
+      <c r="B41" s="224"/>
+      <c r="C41" s="225"/>
+      <c r="D41" s="225"/>
+      <c r="E41" s="225"/>
+      <c r="F41" s="225"/>
+      <c r="G41" s="225"/>
+      <c r="H41" s="225"/>
+      <c r="I41" s="225"/>
+      <c r="J41" s="225"/>
+      <c r="K41" s="225"/>
+      <c r="L41" s="225"/>
+      <c r="M41" s="225"/>
+      <c r="N41" s="225"/>
+      <c r="O41" s="225"/>
+      <c r="P41" s="226"/>
     </row>
     <row r="42" spans="2:19" x14ac:dyDescent="0.3">
-      <c r="B42" s="237"/>
-      <c r="C42" s="238"/>
-      <c r="D42" s="238"/>
-      <c r="E42" s="238"/>
-      <c r="F42" s="238"/>
-      <c r="G42" s="238"/>
-      <c r="H42" s="238"/>
-      <c r="I42" s="238"/>
-      <c r="J42" s="238"/>
-      <c r="K42" s="238"/>
-      <c r="L42" s="238"/>
-      <c r="M42" s="238"/>
-      <c r="N42" s="238"/>
-      <c r="O42" s="238"/>
-      <c r="P42" s="239"/>
+      <c r="B42" s="224"/>
+      <c r="C42" s="225"/>
+      <c r="D42" s="225"/>
+      <c r="E42" s="225"/>
+      <c r="F42" s="225"/>
+      <c r="G42" s="225"/>
+      <c r="H42" s="225"/>
+      <c r="I42" s="225"/>
+      <c r="J42" s="225"/>
+      <c r="K42" s="225"/>
+      <c r="L42" s="225"/>
+      <c r="M42" s="225"/>
+      <c r="N42" s="225"/>
+      <c r="O42" s="225"/>
+      <c r="P42" s="226"/>
     </row>
     <row r="43" spans="2:19" x14ac:dyDescent="0.3">
-      <c r="B43" s="240"/>
-      <c r="C43" s="241"/>
-      <c r="D43" s="241"/>
-      <c r="E43" s="241"/>
-      <c r="F43" s="241"/>
-      <c r="G43" s="241"/>
-      <c r="H43" s="241"/>
-      <c r="I43" s="241"/>
-      <c r="J43" s="241"/>
-      <c r="K43" s="241"/>
-      <c r="L43" s="241"/>
-      <c r="M43" s="241"/>
-      <c r="N43" s="241"/>
-      <c r="O43" s="241"/>
-      <c r="P43" s="242"/>
+      <c r="B43" s="227"/>
+      <c r="C43" s="228"/>
+      <c r="D43" s="228"/>
+      <c r="E43" s="228"/>
+      <c r="F43" s="228"/>
+      <c r="G43" s="228"/>
+      <c r="H43" s="228"/>
+      <c r="I43" s="228"/>
+      <c r="J43" s="228"/>
+      <c r="K43" s="228"/>
+      <c r="L43" s="228"/>
+      <c r="M43" s="228"/>
+      <c r="N43" s="228"/>
+      <c r="O43" s="228"/>
+      <c r="P43" s="229"/>
     </row>
     <row r="44" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B44" s="42"/>
@@ -57012,24 +57000,24 @@
       <c r="O51" s="126"/>
     </row>
     <row r="52" spans="2:19" ht="28.8" x14ac:dyDescent="0.55000000000000004">
-      <c r="B52" s="347" t="s">
+      <c r="B52" s="345" t="s">
         <v>195</v>
       </c>
-      <c r="C52" s="348"/>
-      <c r="D52" s="348"/>
-      <c r="E52" s="348"/>
-      <c r="F52" s="348"/>
-      <c r="G52" s="348"/>
-      <c r="H52" s="348"/>
-      <c r="I52" s="348"/>
-      <c r="J52" s="348"/>
-      <c r="K52" s="348"/>
-      <c r="L52" s="348"/>
-      <c r="M52" s="348"/>
-      <c r="N52" s="348"/>
-      <c r="O52" s="348"/>
-      <c r="P52" s="348"/>
-      <c r="Q52" s="349"/>
+      <c r="C52" s="346"/>
+      <c r="D52" s="346"/>
+      <c r="E52" s="346"/>
+      <c r="F52" s="346"/>
+      <c r="G52" s="346"/>
+      <c r="H52" s="346"/>
+      <c r="I52" s="346"/>
+      <c r="J52" s="346"/>
+      <c r="K52" s="346"/>
+      <c r="L52" s="346"/>
+      <c r="M52" s="346"/>
+      <c r="N52" s="346"/>
+      <c r="O52" s="346"/>
+      <c r="P52" s="346"/>
+      <c r="Q52" s="347"/>
     </row>
     <row r="53" spans="2:19" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B53" s="97" t="s">
@@ -57083,10 +57071,10 @@
       </c>
     </row>
     <row r="54" spans="2:19" ht="40.950000000000003" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B54" s="247" t="s">
+      <c r="B54" s="246" t="s">
         <v>196</v>
       </c>
-      <c r="C54" s="332" t="s">
+      <c r="C54" s="344" t="s">
         <v>180</v>
       </c>
       <c r="D54" s="53" t="s">
@@ -57139,8 +57127,8 @@
       </c>
     </row>
     <row r="55" spans="2:19" ht="42" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B55" s="247"/>
-      <c r="C55" s="332"/>
+      <c r="B55" s="246"/>
+      <c r="C55" s="344"/>
       <c r="D55" s="53" t="s">
         <v>24</v>
       </c>
@@ -57191,24 +57179,24 @@
       </c>
     </row>
     <row r="56" spans="2:19" ht="28.8" x14ac:dyDescent="0.55000000000000004">
-      <c r="B56" s="347" t="s">
+      <c r="B56" s="345" t="s">
         <v>198</v>
       </c>
-      <c r="C56" s="348"/>
-      <c r="D56" s="348"/>
-      <c r="E56" s="348"/>
-      <c r="F56" s="348"/>
-      <c r="G56" s="348"/>
-      <c r="H56" s="348"/>
-      <c r="I56" s="348"/>
-      <c r="J56" s="348"/>
-      <c r="K56" s="348"/>
-      <c r="L56" s="348"/>
-      <c r="M56" s="348"/>
-      <c r="N56" s="348"/>
-      <c r="O56" s="348"/>
-      <c r="P56" s="348"/>
-      <c r="Q56" s="349"/>
+      <c r="C56" s="346"/>
+      <c r="D56" s="346"/>
+      <c r="E56" s="346"/>
+      <c r="F56" s="346"/>
+      <c r="G56" s="346"/>
+      <c r="H56" s="346"/>
+      <c r="I56" s="346"/>
+      <c r="J56" s="346"/>
+      <c r="K56" s="346"/>
+      <c r="L56" s="346"/>
+      <c r="M56" s="346"/>
+      <c r="N56" s="346"/>
+      <c r="O56" s="346"/>
+      <c r="P56" s="346"/>
+      <c r="Q56" s="347"/>
       <c r="S56" s="53"/>
     </row>
     <row r="57" spans="2:19" ht="28.8" x14ac:dyDescent="0.3">
@@ -57261,10 +57249,10 @@
       <c r="S57" s="53"/>
     </row>
     <row r="58" spans="2:19" ht="28.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B58" s="247" t="s">
+      <c r="B58" s="246" t="s">
         <v>79</v>
       </c>
-      <c r="C58" s="332" t="s">
+      <c r="C58" s="344" t="s">
         <v>180</v>
       </c>
       <c r="D58" s="53" t="s">
@@ -57309,7 +57297,7 @@
       <c r="P58" s="53" t="s">
         <v>64</v>
       </c>
-      <c r="Q58" s="343" t="s">
+      <c r="Q58" s="356" t="s">
         <v>199</v>
       </c>
       <c r="S58" s="53" t="s">
@@ -57317,8 +57305,8 @@
       </c>
     </row>
     <row r="59" spans="2:19" x14ac:dyDescent="0.3">
-      <c r="B59" s="247"/>
-      <c r="C59" s="332"/>
+      <c r="B59" s="246"/>
+      <c r="C59" s="344"/>
       <c r="D59" s="53" t="s">
         <v>24</v>
       </c>
@@ -57361,40 +57349,40 @@
       <c r="P59" s="53" t="s">
         <v>64</v>
       </c>
-      <c r="Q59" s="344"/>
+      <c r="Q59" s="357"/>
       <c r="S59" s="53" t="s">
         <v>200</v>
       </c>
     </row>
     <row r="60" spans="2:19" ht="28.8" x14ac:dyDescent="0.55000000000000004">
-      <c r="B60" s="335" t="s">
+      <c r="B60" s="350" t="s">
         <v>201</v>
       </c>
-      <c r="C60" s="336"/>
-      <c r="D60" s="336"/>
-      <c r="E60" s="336"/>
-      <c r="F60" s="336"/>
-      <c r="G60" s="336"/>
-      <c r="H60" s="336"/>
-      <c r="I60" s="336"/>
-      <c r="J60" s="336"/>
-      <c r="K60" s="336"/>
-      <c r="L60" s="336"/>
-      <c r="M60" s="336"/>
-      <c r="N60" s="336"/>
-      <c r="O60" s="336"/>
-      <c r="P60" s="336"/>
-      <c r="Q60" s="338"/>
+      <c r="C60" s="334"/>
+      <c r="D60" s="334"/>
+      <c r="E60" s="334"/>
+      <c r="F60" s="334"/>
+      <c r="G60" s="334"/>
+      <c r="H60" s="334"/>
+      <c r="I60" s="334"/>
+      <c r="J60" s="334"/>
+      <c r="K60" s="334"/>
+      <c r="L60" s="334"/>
+      <c r="M60" s="334"/>
+      <c r="N60" s="334"/>
+      <c r="O60" s="334"/>
+      <c r="P60" s="334"/>
+      <c r="Q60" s="351"/>
       <c r="S60" s="53"/>
     </row>
     <row r="61" spans="2:19" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B61" s="109" t="s">
         <v>1</v>
       </c>
-      <c r="C61" s="318" t="s">
+      <c r="C61" s="314" t="s">
         <v>2</v>
       </c>
-      <c r="D61" s="318"/>
+      <c r="D61" s="314"/>
       <c r="E61" s="8" t="s">
         <v>3</v>
       </c>
@@ -57437,10 +57425,10 @@
       <c r="S61" s="53"/>
     </row>
     <row r="62" spans="2:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B62" s="342" t="s">
+      <c r="B62" s="352" t="s">
         <v>202</v>
       </c>
-      <c r="C62" s="332" t="s">
+      <c r="C62" s="344" t="s">
         <v>180</v>
       </c>
       <c r="D62" s="53" t="s">
@@ -57485,7 +57473,7 @@
       <c r="P62" s="53" t="s">
         <v>64</v>
       </c>
-      <c r="Q62" s="343" t="s">
+      <c r="Q62" s="356" t="s">
         <v>199</v>
       </c>
       <c r="S62" s="53" t="s">
@@ -57493,8 +57481,8 @@
       </c>
     </row>
     <row r="63" spans="2:19" x14ac:dyDescent="0.3">
-      <c r="B63" s="342"/>
-      <c r="C63" s="332"/>
+      <c r="B63" s="352"/>
+      <c r="C63" s="344"/>
       <c r="D63" s="53" t="s">
         <v>24</v>
       </c>
@@ -57537,40 +57525,40 @@
       <c r="P63" s="53" t="s">
         <v>64</v>
       </c>
-      <c r="Q63" s="344"/>
+      <c r="Q63" s="357"/>
       <c r="S63" s="53" t="s">
         <v>200</v>
       </c>
     </row>
     <row r="64" spans="2:19" ht="28.8" x14ac:dyDescent="0.55000000000000004">
-      <c r="B64" s="335" t="s">
+      <c r="B64" s="350" t="s">
         <v>203</v>
       </c>
-      <c r="C64" s="336"/>
-      <c r="D64" s="336"/>
-      <c r="E64" s="336"/>
-      <c r="F64" s="336"/>
-      <c r="G64" s="336"/>
-      <c r="H64" s="336"/>
-      <c r="I64" s="336"/>
-      <c r="J64" s="336"/>
-      <c r="K64" s="336"/>
-      <c r="L64" s="336"/>
-      <c r="M64" s="336"/>
-      <c r="N64" s="336"/>
-      <c r="O64" s="336"/>
-      <c r="P64" s="336"/>
-      <c r="Q64" s="338"/>
+      <c r="C64" s="334"/>
+      <c r="D64" s="334"/>
+      <c r="E64" s="334"/>
+      <c r="F64" s="334"/>
+      <c r="G64" s="334"/>
+      <c r="H64" s="334"/>
+      <c r="I64" s="334"/>
+      <c r="J64" s="334"/>
+      <c r="K64" s="334"/>
+      <c r="L64" s="334"/>
+      <c r="M64" s="334"/>
+      <c r="N64" s="334"/>
+      <c r="O64" s="334"/>
+      <c r="P64" s="334"/>
+      <c r="Q64" s="351"/>
       <c r="S64" s="53"/>
     </row>
     <row r="65" spans="2:19" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B65" s="109" t="s">
         <v>1</v>
       </c>
-      <c r="C65" s="318" t="s">
+      <c r="C65" s="314" t="s">
         <v>2</v>
       </c>
-      <c r="D65" s="318"/>
+      <c r="D65" s="314"/>
       <c r="E65" s="8" t="s">
         <v>3</v>
       </c>
@@ -57613,10 +57601,10 @@
       <c r="S65" s="53"/>
     </row>
     <row r="66" spans="2:19" x14ac:dyDescent="0.3">
-      <c r="B66" s="342" t="s">
+      <c r="B66" s="352" t="s">
         <v>204</v>
       </c>
-      <c r="C66" s="332" t="s">
+      <c r="C66" s="344" t="s">
         <v>180</v>
       </c>
       <c r="D66" s="53" t="s">
@@ -57661,7 +57649,7 @@
       <c r="P66" s="53" t="s">
         <v>64</v>
       </c>
-      <c r="Q66" s="340" t="s">
+      <c r="Q66" s="353" t="s">
         <v>205</v>
       </c>
       <c r="S66" s="53" t="s">
@@ -57669,8 +57657,8 @@
       </c>
     </row>
     <row r="67" spans="2:19" x14ac:dyDescent="0.3">
-      <c r="B67" s="342"/>
-      <c r="C67" s="332"/>
+      <c r="B67" s="352"/>
+      <c r="C67" s="344"/>
       <c r="D67" s="53" t="s">
         <v>24</v>
       </c>
@@ -57713,40 +57701,40 @@
       <c r="P67" s="53" t="s">
         <v>64</v>
       </c>
-      <c r="Q67" s="345"/>
+      <c r="Q67" s="354"/>
       <c r="S67" s="53" t="s">
         <v>200</v>
       </c>
     </row>
     <row r="68" spans="2:19" ht="28.8" x14ac:dyDescent="0.55000000000000004">
-      <c r="B68" s="335" t="s">
+      <c r="B68" s="350" t="s">
         <v>206</v>
       </c>
-      <c r="C68" s="336"/>
-      <c r="D68" s="336"/>
-      <c r="E68" s="336"/>
-      <c r="F68" s="336"/>
-      <c r="G68" s="336"/>
-      <c r="H68" s="336"/>
-      <c r="I68" s="336"/>
-      <c r="J68" s="336"/>
-      <c r="K68" s="336"/>
-      <c r="L68" s="336"/>
-      <c r="M68" s="336"/>
-      <c r="N68" s="336"/>
-      <c r="O68" s="336"/>
-      <c r="P68" s="336"/>
-      <c r="Q68" s="338"/>
+      <c r="C68" s="334"/>
+      <c r="D68" s="334"/>
+      <c r="E68" s="334"/>
+      <c r="F68" s="334"/>
+      <c r="G68" s="334"/>
+      <c r="H68" s="334"/>
+      <c r="I68" s="334"/>
+      <c r="J68" s="334"/>
+      <c r="K68" s="334"/>
+      <c r="L68" s="334"/>
+      <c r="M68" s="334"/>
+      <c r="N68" s="334"/>
+      <c r="O68" s="334"/>
+      <c r="P68" s="334"/>
+      <c r="Q68" s="351"/>
       <c r="S68" s="53"/>
     </row>
     <row r="69" spans="2:19" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B69" s="109" t="s">
         <v>1</v>
       </c>
-      <c r="C69" s="318" t="s">
+      <c r="C69" s="314" t="s">
         <v>2</v>
       </c>
-      <c r="D69" s="318"/>
+      <c r="D69" s="314"/>
       <c r="E69" s="8" t="s">
         <v>3</v>
       </c>
@@ -57789,10 +57777,10 @@
       <c r="S69" s="53"/>
     </row>
     <row r="70" spans="2:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B70" s="247" t="s">
+      <c r="B70" s="246" t="s">
         <v>207</v>
       </c>
-      <c r="C70" s="332" t="s">
+      <c r="C70" s="344" t="s">
         <v>180</v>
       </c>
       <c r="D70" s="53" t="s">
@@ -57837,7 +57825,7 @@
       <c r="P70" s="53" t="s">
         <v>60</v>
       </c>
-      <c r="Q70" s="340" t="s">
+      <c r="Q70" s="353" t="s">
         <v>205</v>
       </c>
       <c r="S70" s="53" t="s">
@@ -57845,8 +57833,8 @@
       </c>
     </row>
     <row r="71" spans="2:19" x14ac:dyDescent="0.3">
-      <c r="B71" s="247"/>
-      <c r="C71" s="332"/>
+      <c r="B71" s="246"/>
+      <c r="C71" s="344"/>
       <c r="D71" s="53" t="s">
         <v>24</v>
       </c>
@@ -57889,39 +57877,39 @@
       <c r="P71" s="53" t="s">
         <v>60</v>
       </c>
-      <c r="Q71" s="346"/>
+      <c r="Q71" s="355"/>
       <c r="S71" s="53" t="s">
         <v>200</v>
       </c>
     </row>
     <row r="72" spans="2:19" ht="28.8" x14ac:dyDescent="0.55000000000000004">
-      <c r="B72" s="335" t="s">
+      <c r="B72" s="350" t="s">
         <v>208</v>
       </c>
-      <c r="C72" s="336"/>
-      <c r="D72" s="336"/>
-      <c r="E72" s="336"/>
-      <c r="F72" s="336"/>
-      <c r="G72" s="336"/>
-      <c r="H72" s="336"/>
-      <c r="I72" s="336"/>
-      <c r="J72" s="336"/>
-      <c r="K72" s="336"/>
-      <c r="L72" s="336"/>
-      <c r="M72" s="336"/>
-      <c r="N72" s="337"/>
-      <c r="O72" s="336"/>
-      <c r="P72" s="336"/>
-      <c r="Q72" s="338"/>
+      <c r="C72" s="334"/>
+      <c r="D72" s="334"/>
+      <c r="E72" s="334"/>
+      <c r="F72" s="334"/>
+      <c r="G72" s="334"/>
+      <c r="H72" s="334"/>
+      <c r="I72" s="334"/>
+      <c r="J72" s="334"/>
+      <c r="K72" s="334"/>
+      <c r="L72" s="334"/>
+      <c r="M72" s="334"/>
+      <c r="N72" s="342"/>
+      <c r="O72" s="334"/>
+      <c r="P72" s="334"/>
+      <c r="Q72" s="351"/>
     </row>
     <row r="73" spans="2:19" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B73" s="109" t="s">
         <v>1</v>
       </c>
-      <c r="C73" s="318" t="s">
+      <c r="C73" s="314" t="s">
         <v>2</v>
       </c>
-      <c r="D73" s="318"/>
+      <c r="D73" s="314"/>
       <c r="E73" s="8" t="s">
         <v>3</v>
       </c>
@@ -57963,10 +57951,10 @@
       </c>
     </row>
     <row r="74" spans="2:19" x14ac:dyDescent="0.3">
-      <c r="B74" s="247" t="s">
+      <c r="B74" s="246" t="s">
         <v>209</v>
       </c>
-      <c r="C74" s="332" t="s">
+      <c r="C74" s="344" t="s">
         <v>180</v>
       </c>
       <c r="D74" s="53" t="s">
@@ -58011,7 +57999,7 @@
       <c r="P74" s="53" t="s">
         <v>64</v>
       </c>
-      <c r="Q74" s="340" t="s">
+      <c r="Q74" s="353" t="s">
         <v>205</v>
       </c>
       <c r="S74" s="53" t="s">
@@ -58019,8 +58007,8 @@
       </c>
     </row>
     <row r="75" spans="2:19" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B75" s="339"/>
-      <c r="C75" s="333"/>
+      <c r="B75" s="358"/>
+      <c r="C75" s="360"/>
       <c r="D75" s="90" t="s">
         <v>24</v>
       </c>
@@ -58063,7 +58051,7 @@
       <c r="P75" s="90" t="s">
         <v>64</v>
       </c>
-      <c r="Q75" s="341"/>
+      <c r="Q75" s="359"/>
       <c r="S75" s="53" t="s">
         <v>200</v>
       </c>
@@ -58071,10 +58059,10 @@
     <row r="76" spans="2:19" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B76" s="126"/>
       <c r="C76" s="126"/>
-      <c r="D76" s="334" t="s">
+      <c r="D76" s="339" t="s">
         <v>210</v>
       </c>
-      <c r="E76" s="334"/>
+      <c r="E76" s="339"/>
       <c r="F76" s="126"/>
       <c r="G76" s="126"/>
       <c r="H76" s="126"/>
@@ -58090,133 +58078,133 @@
       <c r="R76" s="126"/>
     </row>
     <row r="77" spans="2:19" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B77" s="293" t="s">
+      <c r="B77" s="247" t="s">
         <v>34</v>
       </c>
-      <c r="C77" s="294"/>
-      <c r="D77" s="294"/>
-      <c r="E77" s="294"/>
-      <c r="F77" s="294"/>
-      <c r="G77" s="294"/>
-      <c r="H77" s="294"/>
-      <c r="I77" s="294"/>
-      <c r="J77" s="294"/>
-      <c r="K77" s="294"/>
-      <c r="L77" s="294"/>
-      <c r="M77" s="294"/>
-      <c r="N77" s="294"/>
-      <c r="O77" s="294"/>
-      <c r="P77" s="294"/>
-      <c r="Q77" s="294"/>
-      <c r="R77" s="295"/>
+      <c r="C77" s="248"/>
+      <c r="D77" s="248"/>
+      <c r="E77" s="248"/>
+      <c r="F77" s="248"/>
+      <c r="G77" s="248"/>
+      <c r="H77" s="248"/>
+      <c r="I77" s="248"/>
+      <c r="J77" s="248"/>
+      <c r="K77" s="248"/>
+      <c r="L77" s="248"/>
+      <c r="M77" s="248"/>
+      <c r="N77" s="248"/>
+      <c r="O77" s="248"/>
+      <c r="P77" s="248"/>
+      <c r="Q77" s="248"/>
+      <c r="R77" s="249"/>
     </row>
     <row r="78" spans="2:19" x14ac:dyDescent="0.3">
-      <c r="B78" s="296" t="s">
+      <c r="B78" s="250" t="s">
         <v>35</v>
       </c>
-      <c r="C78" s="297"/>
-      <c r="D78" s="297"/>
-      <c r="E78" s="297"/>
-      <c r="F78" s="297"/>
-      <c r="G78" s="297"/>
-      <c r="H78" s="297"/>
-      <c r="I78" s="297"/>
-      <c r="J78" s="297"/>
-      <c r="K78" s="297"/>
-      <c r="L78" s="297"/>
-      <c r="M78" s="297"/>
-      <c r="N78" s="297"/>
-      <c r="O78" s="297"/>
-      <c r="P78" s="297"/>
-      <c r="Q78" s="297"/>
-      <c r="R78" s="298"/>
+      <c r="C78" s="251"/>
+      <c r="D78" s="251"/>
+      <c r="E78" s="251"/>
+      <c r="F78" s="251"/>
+      <c r="G78" s="251"/>
+      <c r="H78" s="251"/>
+      <c r="I78" s="251"/>
+      <c r="J78" s="251"/>
+      <c r="K78" s="251"/>
+      <c r="L78" s="251"/>
+      <c r="M78" s="251"/>
+      <c r="N78" s="251"/>
+      <c r="O78" s="251"/>
+      <c r="P78" s="251"/>
+      <c r="Q78" s="251"/>
+      <c r="R78" s="252"/>
     </row>
     <row r="79" spans="2:19" x14ac:dyDescent="0.3">
-      <c r="B79" s="296"/>
-      <c r="C79" s="297"/>
-      <c r="D79" s="297"/>
-      <c r="E79" s="297"/>
-      <c r="F79" s="297"/>
-      <c r="G79" s="297"/>
-      <c r="H79" s="297"/>
-      <c r="I79" s="297"/>
-      <c r="J79" s="297"/>
-      <c r="K79" s="297"/>
-      <c r="L79" s="297"/>
-      <c r="M79" s="297"/>
-      <c r="N79" s="297"/>
-      <c r="O79" s="297"/>
-      <c r="P79" s="297"/>
-      <c r="Q79" s="297"/>
-      <c r="R79" s="298"/>
+      <c r="B79" s="250"/>
+      <c r="C79" s="251"/>
+      <c r="D79" s="251"/>
+      <c r="E79" s="251"/>
+      <c r="F79" s="251"/>
+      <c r="G79" s="251"/>
+      <c r="H79" s="251"/>
+      <c r="I79" s="251"/>
+      <c r="J79" s="251"/>
+      <c r="K79" s="251"/>
+      <c r="L79" s="251"/>
+      <c r="M79" s="251"/>
+      <c r="N79" s="251"/>
+      <c r="O79" s="251"/>
+      <c r="P79" s="251"/>
+      <c r="Q79" s="251"/>
+      <c r="R79" s="252"/>
     </row>
     <row r="80" spans="2:19" x14ac:dyDescent="0.3">
-      <c r="B80" s="296"/>
-      <c r="C80" s="297"/>
-      <c r="D80" s="297"/>
-      <c r="E80" s="297"/>
-      <c r="F80" s="297"/>
-      <c r="G80" s="297"/>
-      <c r="H80" s="297"/>
-      <c r="I80" s="297"/>
-      <c r="J80" s="297"/>
-      <c r="K80" s="297"/>
-      <c r="L80" s="297"/>
-      <c r="M80" s="297"/>
-      <c r="N80" s="297"/>
-      <c r="O80" s="297"/>
-      <c r="P80" s="297"/>
-      <c r="Q80" s="297"/>
-      <c r="R80" s="298"/>
+      <c r="B80" s="250"/>
+      <c r="C80" s="251"/>
+      <c r="D80" s="251"/>
+      <c r="E80" s="251"/>
+      <c r="F80" s="251"/>
+      <c r="G80" s="251"/>
+      <c r="H80" s="251"/>
+      <c r="I80" s="251"/>
+      <c r="J80" s="251"/>
+      <c r="K80" s="251"/>
+      <c r="L80" s="251"/>
+      <c r="M80" s="251"/>
+      <c r="N80" s="251"/>
+      <c r="O80" s="251"/>
+      <c r="P80" s="251"/>
+      <c r="Q80" s="251"/>
+      <c r="R80" s="252"/>
     </row>
     <row r="81" spans="2:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B81" s="299"/>
-      <c r="C81" s="300"/>
-      <c r="D81" s="300"/>
-      <c r="E81" s="300"/>
-      <c r="F81" s="300"/>
-      <c r="G81" s="300"/>
-      <c r="H81" s="300"/>
-      <c r="I81" s="300"/>
-      <c r="J81" s="300"/>
-      <c r="K81" s="300"/>
-      <c r="L81" s="300"/>
-      <c r="M81" s="300"/>
-      <c r="N81" s="300"/>
-      <c r="O81" s="300"/>
-      <c r="P81" s="300"/>
-      <c r="Q81" s="300"/>
-      <c r="R81" s="301"/>
+      <c r="B81" s="253"/>
+      <c r="C81" s="254"/>
+      <c r="D81" s="254"/>
+      <c r="E81" s="254"/>
+      <c r="F81" s="254"/>
+      <c r="G81" s="254"/>
+      <c r="H81" s="254"/>
+      <c r="I81" s="254"/>
+      <c r="J81" s="254"/>
+      <c r="K81" s="254"/>
+      <c r="L81" s="254"/>
+      <c r="M81" s="254"/>
+      <c r="N81" s="254"/>
+      <c r="O81" s="254"/>
+      <c r="P81" s="254"/>
+      <c r="Q81" s="254"/>
+      <c r="R81" s="255"/>
     </row>
     <row r="89" spans="2:18" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B89" s="302" t="s">
+      <c r="B89" s="256" t="s">
         <v>211</v>
       </c>
-      <c r="C89" s="302"/>
-      <c r="D89" s="302"/>
-      <c r="E89" s="302"/>
-      <c r="F89" s="302"/>
-      <c r="G89" s="302"/>
-      <c r="H89" s="302"/>
-      <c r="I89" s="302"/>
-      <c r="J89" s="302"/>
-      <c r="K89" s="302"/>
-      <c r="L89" s="302"/>
-      <c r="M89" s="302"/>
-      <c r="N89" s="302"/>
-      <c r="O89" s="302"/>
-      <c r="P89" s="302"/>
-      <c r="Q89" s="302"/>
-      <c r="R89" s="302"/>
+      <c r="C89" s="256"/>
+      <c r="D89" s="256"/>
+      <c r="E89" s="256"/>
+      <c r="F89" s="256"/>
+      <c r="G89" s="256"/>
+      <c r="H89" s="256"/>
+      <c r="I89" s="256"/>
+      <c r="J89" s="256"/>
+      <c r="K89" s="256"/>
+      <c r="L89" s="256"/>
+      <c r="M89" s="256"/>
+      <c r="N89" s="256"/>
+      <c r="O89" s="256"/>
+      <c r="P89" s="256"/>
+      <c r="Q89" s="256"/>
+      <c r="R89" s="256"/>
     </row>
     <row r="90" spans="2:18" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B90" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C90" s="318" t="s">
+      <c r="C90" s="314" t="s">
         <v>2</v>
       </c>
-      <c r="D90" s="318"/>
+      <c r="D90" s="314"/>
       <c r="E90" s="127" t="s">
         <v>135</v>
       </c>
@@ -58259,10 +58247,10 @@
       <c r="R90" s="230"/>
     </row>
     <row r="91" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="B91" s="227" t="s">
+      <c r="B91" s="233" t="s">
         <v>99</v>
       </c>
-      <c r="C91" s="252" t="s">
+      <c r="C91" s="257" t="s">
         <v>180</v>
       </c>
       <c r="D91" s="53" t="s">
@@ -58306,14 +58294,14 @@
       <c r="P91" s="53" t="s">
         <v>167</v>
       </c>
-      <c r="Q91" s="259" t="s">
+      <c r="Q91" s="258" t="s">
         <v>47</v>
       </c>
-      <c r="R91" s="259"/>
+      <c r="R91" s="258"/>
     </row>
     <row r="92" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="B92" s="227"/>
-      <c r="C92" s="252"/>
+      <c r="B92" s="233"/>
+      <c r="C92" s="257"/>
       <c r="D92" s="53" t="s">
         <v>24</v>
       </c>
@@ -58355,8 +58343,8 @@
       <c r="P92" s="53" t="s">
         <v>167</v>
       </c>
-      <c r="Q92" s="259"/>
-      <c r="R92" s="259"/>
+      <c r="Q92" s="258"/>
+      <c r="R92" s="258"/>
     </row>
     <row r="94" spans="2:18" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B94" s="5" t="s">
@@ -58380,82 +58368,82 @@
       <c r="R94" s="6"/>
     </row>
     <row r="95" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="B95" s="263" t="s">
+      <c r="B95" s="292" t="s">
         <v>35</v>
       </c>
-      <c r="C95" s="263"/>
-      <c r="D95" s="263"/>
-      <c r="E95" s="263"/>
-      <c r="F95" s="263"/>
-      <c r="G95" s="263"/>
-      <c r="H95" s="263"/>
-      <c r="I95" s="263"/>
-      <c r="J95" s="263"/>
-      <c r="K95" s="263"/>
-      <c r="L95" s="263"/>
-      <c r="M95" s="263"/>
-      <c r="N95" s="263"/>
-      <c r="O95" s="263"/>
-      <c r="P95" s="263"/>
-      <c r="Q95" s="263"/>
-      <c r="R95" s="263"/>
+      <c r="C95" s="292"/>
+      <c r="D95" s="292"/>
+      <c r="E95" s="292"/>
+      <c r="F95" s="292"/>
+      <c r="G95" s="292"/>
+      <c r="H95" s="292"/>
+      <c r="I95" s="292"/>
+      <c r="J95" s="292"/>
+      <c r="K95" s="292"/>
+      <c r="L95" s="292"/>
+      <c r="M95" s="292"/>
+      <c r="N95" s="292"/>
+      <c r="O95" s="292"/>
+      <c r="P95" s="292"/>
+      <c r="Q95" s="292"/>
+      <c r="R95" s="292"/>
     </row>
     <row r="96" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="B96" s="263"/>
-      <c r="C96" s="263"/>
-      <c r="D96" s="263"/>
-      <c r="E96" s="263"/>
-      <c r="F96" s="263"/>
-      <c r="G96" s="263"/>
-      <c r="H96" s="263"/>
-      <c r="I96" s="263"/>
-      <c r="J96" s="263"/>
-      <c r="K96" s="263"/>
-      <c r="L96" s="263"/>
-      <c r="M96" s="263"/>
-      <c r="N96" s="263"/>
-      <c r="O96" s="263"/>
-      <c r="P96" s="263"/>
-      <c r="Q96" s="263"/>
-      <c r="R96" s="263"/>
+      <c r="B96" s="292"/>
+      <c r="C96" s="292"/>
+      <c r="D96" s="292"/>
+      <c r="E96" s="292"/>
+      <c r="F96" s="292"/>
+      <c r="G96" s="292"/>
+      <c r="H96" s="292"/>
+      <c r="I96" s="292"/>
+      <c r="J96" s="292"/>
+      <c r="K96" s="292"/>
+      <c r="L96" s="292"/>
+      <c r="M96" s="292"/>
+      <c r="N96" s="292"/>
+      <c r="O96" s="292"/>
+      <c r="P96" s="292"/>
+      <c r="Q96" s="292"/>
+      <c r="R96" s="292"/>
     </row>
     <row r="97" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="B97" s="263"/>
-      <c r="C97" s="263"/>
-      <c r="D97" s="263"/>
-      <c r="E97" s="263"/>
-      <c r="F97" s="263"/>
-      <c r="G97" s="263"/>
-      <c r="H97" s="263"/>
-      <c r="I97" s="263"/>
-      <c r="J97" s="263"/>
-      <c r="K97" s="263"/>
-      <c r="L97" s="263"/>
-      <c r="M97" s="263"/>
-      <c r="N97" s="263"/>
-      <c r="O97" s="263"/>
-      <c r="P97" s="263"/>
-      <c r="Q97" s="263"/>
-      <c r="R97" s="263"/>
+      <c r="B97" s="292"/>
+      <c r="C97" s="292"/>
+      <c r="D97" s="292"/>
+      <c r="E97" s="292"/>
+      <c r="F97" s="292"/>
+      <c r="G97" s="292"/>
+      <c r="H97" s="292"/>
+      <c r="I97" s="292"/>
+      <c r="J97" s="292"/>
+      <c r="K97" s="292"/>
+      <c r="L97" s="292"/>
+      <c r="M97" s="292"/>
+      <c r="N97" s="292"/>
+      <c r="O97" s="292"/>
+      <c r="P97" s="292"/>
+      <c r="Q97" s="292"/>
+      <c r="R97" s="292"/>
     </row>
     <row r="98" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="B98" s="263"/>
-      <c r="C98" s="263"/>
-      <c r="D98" s="263"/>
-      <c r="E98" s="263"/>
-      <c r="F98" s="263"/>
-      <c r="G98" s="263"/>
-      <c r="H98" s="263"/>
-      <c r="I98" s="263"/>
-      <c r="J98" s="263"/>
-      <c r="K98" s="263"/>
-      <c r="L98" s="263"/>
-      <c r="M98" s="263"/>
-      <c r="N98" s="263"/>
-      <c r="O98" s="263"/>
-      <c r="P98" s="263"/>
-      <c r="Q98" s="263"/>
-      <c r="R98" s="263"/>
+      <c r="B98" s="292"/>
+      <c r="C98" s="292"/>
+      <c r="D98" s="292"/>
+      <c r="E98" s="292"/>
+      <c r="F98" s="292"/>
+      <c r="G98" s="292"/>
+      <c r="H98" s="292"/>
+      <c r="I98" s="292"/>
+      <c r="J98" s="292"/>
+      <c r="K98" s="292"/>
+      <c r="L98" s="292"/>
+      <c r="M98" s="292"/>
+      <c r="N98" s="292"/>
+      <c r="O98" s="292"/>
+      <c r="P98" s="292"/>
+      <c r="Q98" s="292"/>
+      <c r="R98" s="292"/>
     </row>
     <row r="99" spans="2:18" x14ac:dyDescent="0.3">
       <c r="B99" s="122"/>
@@ -58477,25 +58465,25 @@
       <c r="R99" s="122"/>
     </row>
     <row r="100" spans="2:18" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B100" s="228" t="s">
+      <c r="B100" s="231" t="s">
         <v>214</v>
       </c>
-      <c r="C100" s="229"/>
-      <c r="D100" s="229"/>
-      <c r="E100" s="229"/>
-      <c r="F100" s="229"/>
-      <c r="G100" s="229"/>
-      <c r="H100" s="229"/>
-      <c r="I100" s="229"/>
-      <c r="J100" s="229"/>
-      <c r="K100" s="229"/>
-      <c r="L100" s="229"/>
-      <c r="M100" s="229"/>
-      <c r="N100" s="229"/>
-      <c r="O100" s="229"/>
-      <c r="P100" s="229"/>
-      <c r="Q100" s="229"/>
-      <c r="R100" s="229"/>
+      <c r="C100" s="232"/>
+      <c r="D100" s="232"/>
+      <c r="E100" s="232"/>
+      <c r="F100" s="232"/>
+      <c r="G100" s="232"/>
+      <c r="H100" s="232"/>
+      <c r="I100" s="232"/>
+      <c r="J100" s="232"/>
+      <c r="K100" s="232"/>
+      <c r="L100" s="232"/>
+      <c r="M100" s="232"/>
+      <c r="N100" s="232"/>
+      <c r="O100" s="232"/>
+      <c r="P100" s="232"/>
+      <c r="Q100" s="232"/>
+      <c r="R100" s="232"/>
     </row>
     <row r="101" spans="2:18" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B101" s="97" t="s">
@@ -58549,10 +58537,10 @@
       </c>
     </row>
     <row r="102" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="B102" s="320" t="s">
+      <c r="B102" s="302" t="s">
         <v>108</v>
       </c>
-      <c r="C102" s="252" t="s">
+      <c r="C102" s="257" t="s">
         <v>180</v>
       </c>
       <c r="D102" s="53" t="s">
@@ -58604,8 +58592,8 @@
       </c>
     </row>
     <row r="103" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="B103" s="320"/>
-      <c r="C103" s="252"/>
+      <c r="B103" s="302"/>
+      <c r="C103" s="257"/>
       <c r="D103" s="53" t="s">
         <v>24</v>
       </c>
@@ -58655,10 +58643,10 @@
       </c>
     </row>
     <row r="104" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="B104" s="320" t="s">
+      <c r="B104" s="302" t="s">
         <v>175</v>
       </c>
-      <c r="C104" s="252" t="s">
+      <c r="C104" s="257" t="s">
         <v>180</v>
       </c>
       <c r="D104" s="53" t="s">
@@ -58711,8 +58699,8 @@
       </c>
     </row>
     <row r="105" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="B105" s="320"/>
-      <c r="C105" s="252"/>
+      <c r="B105" s="302"/>
+      <c r="C105" s="257"/>
       <c r="D105" s="53" t="s">
         <v>24</v>
       </c>
@@ -58764,57 +58752,6 @@
     </row>
   </sheetData>
   <mergeCells count="63">
-    <mergeCell ref="B15:B16"/>
-    <mergeCell ref="C15:C16"/>
-    <mergeCell ref="P33:Q33"/>
-    <mergeCell ref="B32:Q32"/>
-    <mergeCell ref="B18:P18"/>
-    <mergeCell ref="B19:P22"/>
-    <mergeCell ref="D8:E8"/>
-    <mergeCell ref="C10:D10"/>
-    <mergeCell ref="B11:B12"/>
-    <mergeCell ref="C11:C12"/>
-    <mergeCell ref="B13:B14"/>
-    <mergeCell ref="C13:C14"/>
-    <mergeCell ref="B9:P9"/>
-    <mergeCell ref="C33:D33"/>
-    <mergeCell ref="B54:B55"/>
-    <mergeCell ref="C54:C55"/>
-    <mergeCell ref="B102:B103"/>
-    <mergeCell ref="C102:C103"/>
-    <mergeCell ref="B100:R100"/>
-    <mergeCell ref="B56:Q56"/>
-    <mergeCell ref="B34:B35"/>
-    <mergeCell ref="C34:C35"/>
-    <mergeCell ref="B40:P43"/>
-    <mergeCell ref="B52:Q52"/>
-    <mergeCell ref="C53:D53"/>
-    <mergeCell ref="P34:Q36"/>
-    <mergeCell ref="C57:D57"/>
-    <mergeCell ref="B68:Q68"/>
-    <mergeCell ref="C69:D69"/>
-    <mergeCell ref="B70:B71"/>
-    <mergeCell ref="C70:C71"/>
-    <mergeCell ref="B66:B67"/>
-    <mergeCell ref="C66:C67"/>
-    <mergeCell ref="B58:B59"/>
-    <mergeCell ref="Q66:Q67"/>
-    <mergeCell ref="Q70:Q71"/>
-    <mergeCell ref="B64:Q64"/>
-    <mergeCell ref="C65:D65"/>
-    <mergeCell ref="Q58:Q59"/>
-    <mergeCell ref="C58:C59"/>
-    <mergeCell ref="B60:Q60"/>
-    <mergeCell ref="C61:D61"/>
-    <mergeCell ref="B62:B63"/>
-    <mergeCell ref="C62:C63"/>
-    <mergeCell ref="Q62:Q63"/>
-    <mergeCell ref="B72:Q72"/>
-    <mergeCell ref="C73:D73"/>
-    <mergeCell ref="B74:B75"/>
-    <mergeCell ref="C90:D90"/>
-    <mergeCell ref="Q90:R90"/>
-    <mergeCell ref="Q74:Q75"/>
     <mergeCell ref="C101:D101"/>
     <mergeCell ref="B104:B105"/>
     <mergeCell ref="C104:C105"/>
@@ -58827,6 +58764,57 @@
     <mergeCell ref="C91:C92"/>
     <mergeCell ref="Q91:R92"/>
     <mergeCell ref="B95:R98"/>
+    <mergeCell ref="B72:Q72"/>
+    <mergeCell ref="C73:D73"/>
+    <mergeCell ref="B74:B75"/>
+    <mergeCell ref="C90:D90"/>
+    <mergeCell ref="Q90:R90"/>
+    <mergeCell ref="Q74:Q75"/>
+    <mergeCell ref="B64:Q64"/>
+    <mergeCell ref="C65:D65"/>
+    <mergeCell ref="Q58:Q59"/>
+    <mergeCell ref="C58:C59"/>
+    <mergeCell ref="B60:Q60"/>
+    <mergeCell ref="C61:D61"/>
+    <mergeCell ref="B62:B63"/>
+    <mergeCell ref="C62:C63"/>
+    <mergeCell ref="Q62:Q63"/>
+    <mergeCell ref="B34:B35"/>
+    <mergeCell ref="C34:C35"/>
+    <mergeCell ref="B40:P43"/>
+    <mergeCell ref="B52:Q52"/>
+    <mergeCell ref="C53:D53"/>
+    <mergeCell ref="P34:Q36"/>
+    <mergeCell ref="B54:B55"/>
+    <mergeCell ref="C54:C55"/>
+    <mergeCell ref="B102:B103"/>
+    <mergeCell ref="C102:C103"/>
+    <mergeCell ref="B100:R100"/>
+    <mergeCell ref="B56:Q56"/>
+    <mergeCell ref="C57:D57"/>
+    <mergeCell ref="B68:Q68"/>
+    <mergeCell ref="C69:D69"/>
+    <mergeCell ref="B70:B71"/>
+    <mergeCell ref="C70:C71"/>
+    <mergeCell ref="B66:B67"/>
+    <mergeCell ref="C66:C67"/>
+    <mergeCell ref="B58:B59"/>
+    <mergeCell ref="Q66:Q67"/>
+    <mergeCell ref="Q70:Q71"/>
+    <mergeCell ref="D8:E8"/>
+    <mergeCell ref="C10:D10"/>
+    <mergeCell ref="B11:B12"/>
+    <mergeCell ref="C11:C12"/>
+    <mergeCell ref="B13:B14"/>
+    <mergeCell ref="C13:C14"/>
+    <mergeCell ref="B9:P9"/>
+    <mergeCell ref="B15:B16"/>
+    <mergeCell ref="C15:C16"/>
+    <mergeCell ref="P33:Q33"/>
+    <mergeCell ref="B32:Q32"/>
+    <mergeCell ref="B18:P18"/>
+    <mergeCell ref="B19:P22"/>
+    <mergeCell ref="C33:D33"/>
   </mergeCells>
   <phoneticPr fontId="12" alignment="center"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -58869,24 +58857,24 @@
   </cols>
   <sheetData>
     <row r="8" spans="2:19" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B8" s="228" t="s">
-        <v>215</v>
-      </c>
-      <c r="C8" s="229"/>
-      <c r="D8" s="229"/>
-      <c r="E8" s="229"/>
-      <c r="F8" s="229"/>
-      <c r="G8" s="229"/>
-      <c r="H8" s="229"/>
-      <c r="I8" s="229"/>
-      <c r="J8" s="229"/>
-      <c r="K8" s="229"/>
-      <c r="L8" s="229"/>
-      <c r="M8" s="229"/>
-      <c r="N8" s="229"/>
-      <c r="O8" s="229"/>
-      <c r="P8" s="229"/>
-      <c r="Q8" s="229"/>
+      <c r="B8" s="231" t="s">
+        <v>215</v>
+      </c>
+      <c r="C8" s="232"/>
+      <c r="D8" s="232"/>
+      <c r="E8" s="232"/>
+      <c r="F8" s="232"/>
+      <c r="G8" s="232"/>
+      <c r="H8" s="232"/>
+      <c r="I8" s="232"/>
+      <c r="J8" s="232"/>
+      <c r="K8" s="232"/>
+      <c r="L8" s="232"/>
+      <c r="M8" s="232"/>
+      <c r="N8" s="232"/>
+      <c r="O8" s="232"/>
+      <c r="P8" s="232"/>
+      <c r="Q8" s="232"/>
     </row>
     <row r="9" spans="2:19" ht="57.6" x14ac:dyDescent="0.3">
       <c r="B9" s="97" t="s">
@@ -58937,10 +58925,10 @@
       </c>
     </row>
     <row r="10" spans="2:19" x14ac:dyDescent="0.3">
-      <c r="B10" s="231" t="s">
+      <c r="B10" s="238" t="s">
         <v>31</v>
       </c>
-      <c r="C10" s="227" t="s">
+      <c r="C10" s="233" t="s">
         <v>120</v>
       </c>
       <c r="D10" s="117" t="s">
@@ -58989,8 +58977,8 @@
       </c>
     </row>
     <row r="11" spans="2:19" x14ac:dyDescent="0.3">
-      <c r="B11" s="232"/>
-      <c r="C11" s="227"/>
+      <c r="B11" s="239"/>
+      <c r="C11" s="233"/>
       <c r="D11" s="117" t="s">
         <v>24</v>
       </c>
@@ -59037,25 +59025,25 @@
       </c>
     </row>
     <row r="12" spans="2:19" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B12" s="228" t="s">
+      <c r="B12" s="231" t="s">
         <v>217</v>
       </c>
-      <c r="C12" s="229"/>
-      <c r="D12" s="229"/>
-      <c r="E12" s="229"/>
-      <c r="F12" s="229"/>
-      <c r="G12" s="229"/>
-      <c r="H12" s="229"/>
-      <c r="I12" s="229"/>
-      <c r="J12" s="229"/>
-      <c r="K12" s="229"/>
-      <c r="L12" s="229"/>
-      <c r="M12" s="229"/>
-      <c r="N12" s="229"/>
-      <c r="O12" s="229"/>
-      <c r="P12" s="229"/>
-      <c r="Q12" s="229"/>
-      <c r="R12" s="229"/>
+      <c r="C12" s="232"/>
+      <c r="D12" s="232"/>
+      <c r="E12" s="232"/>
+      <c r="F12" s="232"/>
+      <c r="G12" s="232"/>
+      <c r="H12" s="232"/>
+      <c r="I12" s="232"/>
+      <c r="J12" s="232"/>
+      <c r="K12" s="232"/>
+      <c r="L12" s="232"/>
+      <c r="M12" s="232"/>
+      <c r="N12" s="232"/>
+      <c r="O12" s="232"/>
+      <c r="P12" s="232"/>
+      <c r="Q12" s="232"/>
+      <c r="R12" s="232"/>
     </row>
     <row r="13" spans="2:19" ht="57.6" x14ac:dyDescent="0.3">
       <c r="B13" s="97" t="s">
@@ -59112,10 +59100,10 @@
       </c>
     </row>
     <row r="14" spans="2:19" x14ac:dyDescent="0.3">
-      <c r="B14" s="227" t="s">
+      <c r="B14" s="233" t="s">
         <v>31</v>
       </c>
-      <c r="C14" s="227" t="s">
+      <c r="C14" s="233" t="s">
         <v>180</v>
       </c>
       <c r="D14" s="117" t="s">
@@ -59170,8 +59158,8 @@
       </c>
     </row>
     <row r="15" spans="2:19" x14ac:dyDescent="0.3">
-      <c r="B15" s="227"/>
-      <c r="C15" s="227"/>
+      <c r="B15" s="233"/>
+      <c r="C15" s="233"/>
       <c r="D15" s="117" t="s">
         <v>24</v>
       </c>
@@ -59224,24 +59212,24 @@
       </c>
     </row>
     <row r="16" spans="2:19" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B16" s="235" t="s">
+      <c r="B16" s="242" t="s">
         <v>221</v>
       </c>
-      <c r="C16" s="236"/>
-      <c r="D16" s="236"/>
-      <c r="E16" s="236"/>
-      <c r="F16" s="236"/>
-      <c r="G16" s="236"/>
-      <c r="H16" s="236"/>
-      <c r="I16" s="236"/>
-      <c r="J16" s="236"/>
-      <c r="K16" s="236"/>
-      <c r="L16" s="236"/>
-      <c r="M16" s="236"/>
-      <c r="N16" s="236"/>
-      <c r="O16" s="236"/>
-      <c r="P16" s="236"/>
-      <c r="Q16" s="236"/>
+      <c r="C16" s="243"/>
+      <c r="D16" s="243"/>
+      <c r="E16" s="243"/>
+      <c r="F16" s="243"/>
+      <c r="G16" s="243"/>
+      <c r="H16" s="243"/>
+      <c r="I16" s="243"/>
+      <c r="J16" s="243"/>
+      <c r="K16" s="243"/>
+      <c r="L16" s="243"/>
+      <c r="M16" s="243"/>
+      <c r="N16" s="243"/>
+      <c r="O16" s="243"/>
+      <c r="P16" s="243"/>
+      <c r="Q16" s="243"/>
     </row>
     <row r="17" spans="2:17" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B17" s="97" t="s">
@@ -59284,16 +59272,16 @@
       <c r="O17" s="120" t="s">
         <v>14</v>
       </c>
-      <c r="P17" s="233" t="s">
-        <v>150</v>
-      </c>
-      <c r="Q17" s="234"/>
+      <c r="P17" s="240" t="s">
+        <v>150</v>
+      </c>
+      <c r="Q17" s="241"/>
     </row>
     <row r="18" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B18" s="227" t="s">
+      <c r="B18" s="233" t="s">
         <v>31</v>
       </c>
-      <c r="C18" s="227" t="s">
+      <c r="C18" s="233" t="s">
         <v>222</v>
       </c>
       <c r="D18" s="117" t="s">
@@ -59340,8 +59328,8 @@
       <c r="Q18" s="53"/>
     </row>
     <row r="19" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B19" s="227"/>
-      <c r="C19" s="227"/>
+      <c r="B19" s="233"/>
+      <c r="C19" s="233"/>
       <c r="D19" s="117" t="s">
         <v>24</v>
       </c>
@@ -59386,22 +59374,22 @@
       <c r="Q19" s="53"/>
     </row>
     <row r="20" spans="2:17" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B20" s="225" t="s">
+      <c r="B20" s="236" t="s">
         <v>224</v>
       </c>
-      <c r="C20" s="226"/>
-      <c r="D20" s="226"/>
-      <c r="E20" s="226"/>
-      <c r="F20" s="226"/>
-      <c r="G20" s="226"/>
-      <c r="H20" s="226"/>
-      <c r="I20" s="226"/>
-      <c r="J20" s="226"/>
-      <c r="K20" s="226"/>
-      <c r="L20" s="226"/>
-      <c r="M20" s="226"/>
-      <c r="N20" s="226"/>
-      <c r="O20" s="226"/>
+      <c r="C20" s="237"/>
+      <c r="D20" s="237"/>
+      <c r="E20" s="237"/>
+      <c r="F20" s="237"/>
+      <c r="G20" s="237"/>
+      <c r="H20" s="237"/>
+      <c r="I20" s="237"/>
+      <c r="J20" s="237"/>
+      <c r="K20" s="237"/>
+      <c r="L20" s="237"/>
+      <c r="M20" s="237"/>
+      <c r="N20" s="237"/>
+      <c r="O20" s="237"/>
       <c r="P20" s="222"/>
     </row>
     <row r="21" spans="2:17" ht="28.8" x14ac:dyDescent="0.3">
@@ -59445,14 +59433,14 @@
       <c r="O21" s="120" t="s">
         <v>150</v>
       </c>
-      <c r="P21" s="243"/>
-      <c r="Q21" s="244"/>
+      <c r="P21" s="234"/>
+      <c r="Q21" s="235"/>
     </row>
     <row r="22" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B22" s="224" t="s">
+      <c r="B22" s="238" t="s">
         <v>17</v>
       </c>
-      <c r="C22" s="224" t="s">
+      <c r="C22" s="238" t="s">
         <v>225</v>
       </c>
       <c r="D22" s="117" t="s">
@@ -59498,46 +59486,42 @@
       <c r="Q22" s="174"/>
     </row>
     <row r="23" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B23" s="224" t="s">
-        <v>31</v>
-      </c>
-      <c r="C23" s="224" t="s">
-        <v>225</v>
-      </c>
+      <c r="B23" s="239"/>
+      <c r="C23" s="239"/>
       <c r="D23" s="117" t="s">
         <v>24</v>
       </c>
       <c r="E23" s="140">
-        <v>650</v>
+        <v>1400</v>
       </c>
       <c r="F23" s="95">
-        <v>150</v>
+        <v>355</v>
       </c>
       <c r="G23" s="95">
-        <v>95.63</v>
+        <v>76.5</v>
       </c>
       <c r="H23" s="95">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="I23" s="96">
         <f>SUM(E23:H23)</f>
-        <v>895.63</v>
+        <v>1881.5</v>
       </c>
       <c r="J23" s="95">
         <v>200</v>
       </c>
       <c r="K23" s="96">
         <f>I23+J23</f>
-        <v>1095.6300000000001</v>
+        <v>2081.5</v>
       </c>
       <c r="L23" s="183" t="s">
-        <v>242</v>
+        <v>226</v>
       </c>
       <c r="M23" s="215" t="s">
-        <v>243</v>
+        <v>21</v>
       </c>
       <c r="N23" s="94" t="s">
-        <v>244</v>
+        <v>46</v>
       </c>
       <c r="O23" s="219" t="s">
         <v>223</v>
@@ -59546,22 +59530,22 @@
       <c r="Q23" s="220"/>
     </row>
     <row r="24" spans="2:17" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B24" s="228" t="s">
+      <c r="B24" s="231" t="s">
         <v>227</v>
       </c>
-      <c r="C24" s="229"/>
-      <c r="D24" s="229"/>
-      <c r="E24" s="229"/>
-      <c r="F24" s="229"/>
-      <c r="G24" s="229"/>
-      <c r="H24" s="229"/>
-      <c r="I24" s="229"/>
-      <c r="J24" s="229"/>
-      <c r="K24" s="229"/>
-      <c r="L24" s="229"/>
-      <c r="M24" s="229"/>
-      <c r="N24" s="229"/>
-      <c r="O24" s="229"/>
+      <c r="C24" s="232"/>
+      <c r="D24" s="232"/>
+      <c r="E24" s="232"/>
+      <c r="F24" s="232"/>
+      <c r="G24" s="232"/>
+      <c r="H24" s="232"/>
+      <c r="I24" s="232"/>
+      <c r="J24" s="232"/>
+      <c r="K24" s="232"/>
+      <c r="L24" s="232"/>
+      <c r="M24" s="232"/>
+      <c r="N24" s="232"/>
+      <c r="O24" s="232"/>
       <c r="P24" s="61"/>
     </row>
     <row r="25" spans="2:17" ht="28.8" x14ac:dyDescent="0.3">
@@ -59609,10 +59593,10 @@
       <c r="Q25" s="223"/>
     </row>
     <row r="26" spans="2:17" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B26" s="227" t="s">
+      <c r="B26" s="233" t="s">
         <v>17</v>
       </c>
-      <c r="C26" s="227" t="s">
+      <c r="C26" s="233" t="s">
         <v>124</v>
       </c>
       <c r="D26" s="117" t="s">
@@ -59658,8 +59642,8 @@
       <c r="P26" s="61"/>
     </row>
     <row r="27" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B27" s="227"/>
-      <c r="C27" s="227"/>
+      <c r="B27" s="233"/>
+      <c r="C27" s="233"/>
       <c r="D27" s="117" t="s">
         <v>24</v>
       </c>
@@ -59723,78 +59707,78 @@
       <c r="Q29" s="7"/>
     </row>
     <row r="30" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B30" s="237" t="s">
+      <c r="B30" s="224" t="s">
         <v>35</v>
       </c>
-      <c r="C30" s="238"/>
-      <c r="D30" s="238"/>
-      <c r="E30" s="238"/>
-      <c r="F30" s="238"/>
-      <c r="G30" s="238"/>
-      <c r="H30" s="238"/>
-      <c r="I30" s="238"/>
-      <c r="J30" s="238"/>
-      <c r="K30" s="238"/>
-      <c r="L30" s="238"/>
-      <c r="M30" s="238"/>
-      <c r="N30" s="238"/>
-      <c r="O30" s="238"/>
-      <c r="P30" s="238"/>
-      <c r="Q30" s="239"/>
+      <c r="C30" s="225"/>
+      <c r="D30" s="225"/>
+      <c r="E30" s="225"/>
+      <c r="F30" s="225"/>
+      <c r="G30" s="225"/>
+      <c r="H30" s="225"/>
+      <c r="I30" s="225"/>
+      <c r="J30" s="225"/>
+      <c r="K30" s="225"/>
+      <c r="L30" s="225"/>
+      <c r="M30" s="225"/>
+      <c r="N30" s="225"/>
+      <c r="O30" s="225"/>
+      <c r="P30" s="225"/>
+      <c r="Q30" s="226"/>
     </row>
     <row r="31" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B31" s="237"/>
-      <c r="C31" s="238"/>
-      <c r="D31" s="238"/>
-      <c r="E31" s="238"/>
-      <c r="F31" s="238"/>
-      <c r="G31" s="238"/>
-      <c r="H31" s="238"/>
-      <c r="I31" s="238"/>
-      <c r="J31" s="238"/>
-      <c r="K31" s="238"/>
-      <c r="L31" s="238"/>
-      <c r="M31" s="238"/>
-      <c r="N31" s="238"/>
-      <c r="O31" s="238"/>
-      <c r="P31" s="238"/>
-      <c r="Q31" s="239"/>
+      <c r="B31" s="224"/>
+      <c r="C31" s="225"/>
+      <c r="D31" s="225"/>
+      <c r="E31" s="225"/>
+      <c r="F31" s="225"/>
+      <c r="G31" s="225"/>
+      <c r="H31" s="225"/>
+      <c r="I31" s="225"/>
+      <c r="J31" s="225"/>
+      <c r="K31" s="225"/>
+      <c r="L31" s="225"/>
+      <c r="M31" s="225"/>
+      <c r="N31" s="225"/>
+      <c r="O31" s="225"/>
+      <c r="P31" s="225"/>
+      <c r="Q31" s="226"/>
     </row>
     <row r="32" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B32" s="237"/>
-      <c r="C32" s="238"/>
-      <c r="D32" s="238"/>
-      <c r="E32" s="238"/>
-      <c r="F32" s="238"/>
-      <c r="G32" s="238"/>
-      <c r="H32" s="238"/>
-      <c r="I32" s="238"/>
-      <c r="J32" s="238"/>
-      <c r="K32" s="238"/>
-      <c r="L32" s="238"/>
-      <c r="M32" s="238"/>
-      <c r="N32" s="238"/>
-      <c r="O32" s="238"/>
-      <c r="P32" s="238"/>
-      <c r="Q32" s="239"/>
+      <c r="B32" s="224"/>
+      <c r="C32" s="225"/>
+      <c r="D32" s="225"/>
+      <c r="E32" s="225"/>
+      <c r="F32" s="225"/>
+      <c r="G32" s="225"/>
+      <c r="H32" s="225"/>
+      <c r="I32" s="225"/>
+      <c r="J32" s="225"/>
+      <c r="K32" s="225"/>
+      <c r="L32" s="225"/>
+      <c r="M32" s="225"/>
+      <c r="N32" s="225"/>
+      <c r="O32" s="225"/>
+      <c r="P32" s="225"/>
+      <c r="Q32" s="226"/>
     </row>
     <row r="33" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B33" s="240"/>
-      <c r="C33" s="241"/>
-      <c r="D33" s="241"/>
-      <c r="E33" s="241"/>
-      <c r="F33" s="241"/>
-      <c r="G33" s="241"/>
-      <c r="H33" s="241"/>
-      <c r="I33" s="241"/>
-      <c r="J33" s="241"/>
-      <c r="K33" s="241"/>
-      <c r="L33" s="241"/>
-      <c r="M33" s="241"/>
-      <c r="N33" s="241"/>
-      <c r="O33" s="241"/>
-      <c r="P33" s="241"/>
-      <c r="Q33" s="242"/>
+      <c r="B33" s="227"/>
+      <c r="C33" s="228"/>
+      <c r="D33" s="228"/>
+      <c r="E33" s="228"/>
+      <c r="F33" s="228"/>
+      <c r="G33" s="228"/>
+      <c r="H33" s="228"/>
+      <c r="I33" s="228"/>
+      <c r="J33" s="228"/>
+      <c r="K33" s="228"/>
+      <c r="L33" s="228"/>
+      <c r="M33" s="228"/>
+      <c r="N33" s="228"/>
+      <c r="O33" s="228"/>
+      <c r="P33" s="228"/>
+      <c r="Q33" s="229"/>
     </row>
     <row r="34" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B34" s="35"/>
@@ -59923,14 +59907,7 @@
       <c r="Q40" s="35"/>
     </row>
   </sheetData>
-  <mergeCells count="21">
-    <mergeCell ref="B30:Q33"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="B24:O24"/>
-    <mergeCell ref="C25:D25"/>
-    <mergeCell ref="B26:B27"/>
-    <mergeCell ref="C26:C27"/>
-    <mergeCell ref="P21:Q21"/>
+  <mergeCells count="23">
     <mergeCell ref="B20:O20"/>
     <mergeCell ref="C18:C19"/>
     <mergeCell ref="B14:B15"/>
@@ -59945,7 +59922,17 @@
     <mergeCell ref="B18:B19"/>
     <mergeCell ref="P17:Q17"/>
     <mergeCell ref="B16:Q16"/>
+    <mergeCell ref="B30:Q33"/>
+    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="B24:O24"/>
+    <mergeCell ref="C25:D25"/>
+    <mergeCell ref="B26:B27"/>
+    <mergeCell ref="C26:C27"/>
+    <mergeCell ref="P21:Q21"/>
+    <mergeCell ref="B22:B23"/>
+    <mergeCell ref="C22:C23"/>
   </mergeCells>
+  <phoneticPr fontId="14" type="noConversion"/>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="5" scale="54" orientation="landscape" r:id="rId1"/>
@@ -60131,10 +60118,10 @@
       <c r="B10" s="77" t="s">
         <v>1</v>
       </c>
-      <c r="C10" s="374" t="s">
+      <c r="C10" s="361" t="s">
         <v>2</v>
       </c>
-      <c r="D10" s="374"/>
+      <c r="D10" s="361"/>
       <c r="E10" s="15" t="s">
         <v>3</v>
       </c>
@@ -60173,10 +60160,10 @@
       </c>
     </row>
     <row r="11" spans="2:16" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B11" s="370" t="s">
+      <c r="B11" s="362" t="s">
         <v>229</v>
       </c>
-      <c r="C11" s="372" t="s">
+      <c r="C11" s="365" t="s">
         <v>31</v>
       </c>
       <c r="D11" s="45" t="s">
@@ -60222,8 +60209,8 @@
       </c>
     </row>
     <row r="12" spans="2:16" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B12" s="375"/>
-      <c r="C12" s="372"/>
+      <c r="B12" s="363"/>
+      <c r="C12" s="365"/>
       <c r="D12" s="45" t="s">
         <v>24</v>
       </c>
@@ -60267,8 +60254,8 @@
       </c>
     </row>
     <row r="13" spans="2:16" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B13" s="375"/>
-      <c r="C13" s="372" t="s">
+      <c r="B13" s="363"/>
+      <c r="C13" s="365" t="s">
         <v>17</v>
       </c>
       <c r="D13" s="45" t="s">
@@ -60314,8 +60301,8 @@
       </c>
     </row>
     <row r="14" spans="2:16" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B14" s="375"/>
-      <c r="C14" s="372"/>
+      <c r="B14" s="363"/>
+      <c r="C14" s="365"/>
       <c r="D14" s="45" t="s">
         <v>24</v>
       </c>
@@ -60359,8 +60346,8 @@
       </c>
     </row>
     <row r="15" spans="2:16" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B15" s="375"/>
-      <c r="C15" s="372" t="s">
+      <c r="B15" s="363"/>
+      <c r="C15" s="365" t="s">
         <v>31</v>
       </c>
       <c r="D15" s="45" t="s">
@@ -60406,8 +60393,8 @@
       </c>
     </row>
     <row r="16" spans="2:16" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B16" s="375"/>
-      <c r="C16" s="372"/>
+      <c r="B16" s="363"/>
+      <c r="C16" s="365"/>
       <c r="D16" s="45" t="s">
         <v>24</v>
       </c>
@@ -60451,8 +60438,8 @@
       </c>
     </row>
     <row r="17" spans="2:16" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B17" s="375"/>
-      <c r="C17" s="372" t="s">
+      <c r="B17" s="363"/>
+      <c r="C17" s="365" t="s">
         <v>31</v>
       </c>
       <c r="D17" s="45" t="s">
@@ -60498,8 +60485,8 @@
       </c>
     </row>
     <row r="18" spans="2:16" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B18" s="375"/>
-      <c r="C18" s="372"/>
+      <c r="B18" s="363"/>
+      <c r="C18" s="365"/>
       <c r="D18" s="45" t="s">
         <v>24</v>
       </c>
@@ -60543,8 +60530,8 @@
       </c>
     </row>
     <row r="19" spans="2:16" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="B19" s="375"/>
-      <c r="C19" s="372" t="s">
+      <c r="B19" s="363"/>
+      <c r="C19" s="365" t="s">
         <v>31</v>
       </c>
       <c r="D19" s="45" t="s">
@@ -60590,8 +60577,8 @@
       </c>
     </row>
     <row r="20" spans="2:16" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="B20" s="371"/>
-      <c r="C20" s="372"/>
+      <c r="B20" s="364"/>
+      <c r="C20" s="365"/>
       <c r="D20" s="45" t="s">
         <v>24</v>
       </c>
@@ -60635,10 +60622,10 @@
       </c>
     </row>
     <row r="21" spans="2:16" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B21" s="370" t="s">
+      <c r="B21" s="362" t="s">
         <v>234</v>
       </c>
-      <c r="C21" s="372" t="s">
+      <c r="C21" s="365" t="s">
         <v>31</v>
       </c>
       <c r="D21" s="45" t="s">
@@ -60684,8 +60671,8 @@
       </c>
     </row>
     <row r="22" spans="2:16" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B22" s="371"/>
-      <c r="C22" s="372"/>
+      <c r="B22" s="364"/>
+      <c r="C22" s="365"/>
       <c r="D22" s="45" t="s">
         <v>24</v>
       </c>
@@ -60729,10 +60716,10 @@
       </c>
     </row>
     <row r="23" spans="2:16" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B23" s="370" t="s">
+      <c r="B23" s="362" t="s">
         <v>235</v>
       </c>
-      <c r="C23" s="372" t="s">
+      <c r="C23" s="365" t="s">
         <v>31</v>
       </c>
       <c r="D23" s="45" t="s">
@@ -60778,8 +60765,8 @@
       </c>
     </row>
     <row r="24" spans="2:16" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B24" s="371"/>
-      <c r="C24" s="372"/>
+      <c r="B24" s="364"/>
+      <c r="C24" s="365"/>
       <c r="D24" s="45" t="s">
         <v>24</v>
       </c>
@@ -60823,10 +60810,10 @@
       </c>
     </row>
     <row r="25" spans="2:16" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
-      <c r="B25" s="247" t="s">
+      <c r="B25" s="246" t="s">
         <v>237</v>
       </c>
-      <c r="C25" s="227" t="s">
+      <c r="C25" s="233" t="s">
         <v>31</v>
       </c>
       <c r="D25" s="40" t="s">
@@ -60872,8 +60859,8 @@
       </c>
     </row>
     <row r="26" spans="2:16" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
-      <c r="B26" s="247"/>
-      <c r="C26" s="227"/>
+      <c r="B26" s="246"/>
+      <c r="C26" s="233"/>
       <c r="D26" s="40" t="s">
         <v>24</v>
       </c>
@@ -60917,8 +60904,8 @@
       </c>
     </row>
     <row r="27" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B27" s="339"/>
-      <c r="C27" s="373"/>
+      <c r="B27" s="358"/>
+      <c r="C27" s="374"/>
       <c r="D27" s="84" t="s">
         <v>18</v>
       </c>
@@ -60978,103 +60965,96 @@
       <c r="O28" s="28"/>
     </row>
     <row r="29" spans="2:16" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B29" s="362" t="s">
+      <c r="B29" s="366" t="s">
         <v>34</v>
       </c>
-      <c r="C29" s="363"/>
-      <c r="D29" s="363"/>
-      <c r="E29" s="363"/>
-      <c r="F29" s="363"/>
-      <c r="G29" s="363"/>
-      <c r="H29" s="363"/>
-      <c r="I29" s="363"/>
-      <c r="J29" s="363"/>
-      <c r="K29" s="363"/>
-      <c r="L29" s="363"/>
-      <c r="M29" s="363"/>
-      <c r="N29" s="363"/>
-      <c r="O29" s="363"/>
-      <c r="P29" s="364"/>
+      <c r="C29" s="367"/>
+      <c r="D29" s="367"/>
+      <c r="E29" s="367"/>
+      <c r="F29" s="367"/>
+      <c r="G29" s="367"/>
+      <c r="H29" s="367"/>
+      <c r="I29" s="367"/>
+      <c r="J29" s="367"/>
+      <c r="K29" s="367"/>
+      <c r="L29" s="367"/>
+      <c r="M29" s="367"/>
+      <c r="N29" s="367"/>
+      <c r="O29" s="367"/>
+      <c r="P29" s="368"/>
     </row>
     <row r="30" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="B30" s="365" t="s">
+      <c r="B30" s="369" t="s">
         <v>35</v>
       </c>
-      <c r="C30" s="238"/>
-      <c r="D30" s="238"/>
-      <c r="E30" s="238"/>
-      <c r="F30" s="238"/>
-      <c r="G30" s="238"/>
-      <c r="H30" s="238"/>
-      <c r="I30" s="238"/>
-      <c r="J30" s="238"/>
-      <c r="K30" s="238"/>
-      <c r="L30" s="238"/>
-      <c r="M30" s="238"/>
-      <c r="N30" s="238"/>
-      <c r="O30" s="238"/>
-      <c r="P30" s="366"/>
+      <c r="C30" s="225"/>
+      <c r="D30" s="225"/>
+      <c r="E30" s="225"/>
+      <c r="F30" s="225"/>
+      <c r="G30" s="225"/>
+      <c r="H30" s="225"/>
+      <c r="I30" s="225"/>
+      <c r="J30" s="225"/>
+      <c r="K30" s="225"/>
+      <c r="L30" s="225"/>
+      <c r="M30" s="225"/>
+      <c r="N30" s="225"/>
+      <c r="O30" s="225"/>
+      <c r="P30" s="370"/>
     </row>
     <row r="31" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="B31" s="365"/>
-      <c r="C31" s="238"/>
-      <c r="D31" s="238"/>
-      <c r="E31" s="238"/>
-      <c r="F31" s="238"/>
-      <c r="G31" s="238"/>
-      <c r="H31" s="238"/>
-      <c r="I31" s="238"/>
-      <c r="J31" s="238"/>
-      <c r="K31" s="238"/>
-      <c r="L31" s="238"/>
-      <c r="M31" s="238"/>
-      <c r="N31" s="238"/>
-      <c r="O31" s="238"/>
-      <c r="P31" s="366"/>
+      <c r="B31" s="369"/>
+      <c r="C31" s="225"/>
+      <c r="D31" s="225"/>
+      <c r="E31" s="225"/>
+      <c r="F31" s="225"/>
+      <c r="G31" s="225"/>
+      <c r="H31" s="225"/>
+      <c r="I31" s="225"/>
+      <c r="J31" s="225"/>
+      <c r="K31" s="225"/>
+      <c r="L31" s="225"/>
+      <c r="M31" s="225"/>
+      <c r="N31" s="225"/>
+      <c r="O31" s="225"/>
+      <c r="P31" s="370"/>
     </row>
     <row r="32" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="B32" s="365"/>
-      <c r="C32" s="238"/>
-      <c r="D32" s="238"/>
-      <c r="E32" s="238"/>
-      <c r="F32" s="238"/>
-      <c r="G32" s="238"/>
-      <c r="H32" s="238"/>
-      <c r="I32" s="238"/>
-      <c r="J32" s="238"/>
-      <c r="K32" s="238"/>
-      <c r="L32" s="238"/>
-      <c r="M32" s="238"/>
-      <c r="N32" s="238"/>
-      <c r="O32" s="238"/>
-      <c r="P32" s="366"/>
+      <c r="B32" s="369"/>
+      <c r="C32" s="225"/>
+      <c r="D32" s="225"/>
+      <c r="E32" s="225"/>
+      <c r="F32" s="225"/>
+      <c r="G32" s="225"/>
+      <c r="H32" s="225"/>
+      <c r="I32" s="225"/>
+      <c r="J32" s="225"/>
+      <c r="K32" s="225"/>
+      <c r="L32" s="225"/>
+      <c r="M32" s="225"/>
+      <c r="N32" s="225"/>
+      <c r="O32" s="225"/>
+      <c r="P32" s="370"/>
     </row>
     <row r="33" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B33" s="367"/>
-      <c r="C33" s="368"/>
-      <c r="D33" s="368"/>
-      <c r="E33" s="368"/>
-      <c r="F33" s="368"/>
-      <c r="G33" s="368"/>
-      <c r="H33" s="368"/>
-      <c r="I33" s="368"/>
-      <c r="J33" s="368"/>
-      <c r="K33" s="368"/>
-      <c r="L33" s="368"/>
-      <c r="M33" s="368"/>
-      <c r="N33" s="368"/>
-      <c r="O33" s="368"/>
-      <c r="P33" s="369"/>
+      <c r="B33" s="371"/>
+      <c r="C33" s="372"/>
+      <c r="D33" s="372"/>
+      <c r="E33" s="372"/>
+      <c r="F33" s="372"/>
+      <c r="G33" s="372"/>
+      <c r="H33" s="372"/>
+      <c r="I33" s="372"/>
+      <c r="J33" s="372"/>
+      <c r="K33" s="372"/>
+      <c r="L33" s="372"/>
+      <c r="M33" s="372"/>
+      <c r="N33" s="372"/>
+      <c r="O33" s="372"/>
+      <c r="P33" s="373"/>
     </row>
   </sheetData>
   <mergeCells count="15">
-    <mergeCell ref="C10:D10"/>
-    <mergeCell ref="B11:B20"/>
-    <mergeCell ref="C11:C12"/>
-    <mergeCell ref="C13:C14"/>
-    <mergeCell ref="C15:C16"/>
-    <mergeCell ref="C17:C18"/>
-    <mergeCell ref="C19:C20"/>
     <mergeCell ref="B29:P29"/>
     <mergeCell ref="B30:P33"/>
     <mergeCell ref="B21:B22"/>
@@ -61083,6 +61063,13 @@
     <mergeCell ref="C23:C24"/>
     <mergeCell ref="B25:B27"/>
     <mergeCell ref="C25:C27"/>
+    <mergeCell ref="C10:D10"/>
+    <mergeCell ref="B11:B20"/>
+    <mergeCell ref="C11:C12"/>
+    <mergeCell ref="C13:C14"/>
+    <mergeCell ref="C15:C16"/>
+    <mergeCell ref="C17:C18"/>
+    <mergeCell ref="C19:C20"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup scale="67" orientation="landscape" r:id="rId1"/>
@@ -61314,6 +61301,15 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <lcf76f155ced4ddcb4097134ff3c332f xmlns="8bf418b7-79e0-4993-aa07-d31c53a64380">
@@ -61322,15 +61318,6 @@
     <TaxCatchAll xmlns="268ad1c4-fabf-4dd0-b894-8fd5403102c0" xsi:nil="true"/>
   </documentManagement>
 </p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -61353,6 +61340,14 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6AAFA3EB-B8AB-4135-B122-0B0233A6C07D}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{900DAED1-575B-462E-9521-61C8D8B6DAE7}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
@@ -61361,12 +61356,4 @@
     <ds:schemaRef ds:uri="268ad1c4-fabf-4dd0-b894-8fd5403102c0"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6AAFA3EB-B8AB-4135-B122-0B0233A6C07D}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Customer Rate Tariff Template_Week 29_2026.xlsx
+++ b/Customer Rate Tariff Template_Week 29_2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\stephanie.galera.RAMPSLOGISTICS\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C5A211DB-B627-4298-A23B-D3C7B90E8BCA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6CD7113F-445F-4157-B8CB-CC119DF18DB2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{493693A0-0616-4273-B364-7C8DEB21885C}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{493693A0-0616-4273-B364-7C8DEB21885C}"/>
   </bookViews>
   <sheets>
     <sheet name="TT" sheetId="28" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4478" uniqueCount="242">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4478" uniqueCount="243">
   <si>
     <t>USA / TRINIDAD SHIPPING TARIFF</t>
   </si>
@@ -772,6 +772,9 @@
   </si>
   <si>
     <t>Foshan/Gaoming</t>
+  </si>
+  <si>
+    <t>15-25</t>
   </si>
 </sst>
 </file>
@@ -2333,25 +2336,13 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2360,19 +2351,7 @@
     <xf numFmtId="0" fontId="5" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2393,6 +2372,30 @@
     <xf numFmtId="0" fontId="5" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2401,6 +2404,141 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="36" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="46" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="47" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="61" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="60" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="60" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="59" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="45" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="66" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="63" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2432,140 +2570,56 @@
     <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="36" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="60" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="59" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="45" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="66" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="63" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="60" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="60" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="61" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="46" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="47" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="36" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2603,63 +2657,67 @@
     <xf numFmtId="0" fontId="0" fillId="5" borderId="58" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="36" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="38" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="61" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="65" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="61" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="62" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="60" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="62" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="64" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="5" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="11" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2674,77 +2732,7 @@
     <xf numFmtId="0" fontId="6" fillId="3" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="61" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="62" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="64" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="61" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="62" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="38" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="65" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="26" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="27" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="29" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -2769,8 +2757,23 @@
     <xf numFmtId="0" fontId="0" fillId="5" borderId="35" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="26" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="29" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="5" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="27" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -4232,32 +4235,32 @@
       <c r="P7" s="18"/>
     </row>
     <row r="8" spans="2:20" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B8" s="232" t="s">
+      <c r="B8" s="228" t="s">
         <v>0</v>
       </c>
-      <c r="C8" s="232"/>
-      <c r="D8" s="232"/>
-      <c r="E8" s="232"/>
-      <c r="F8" s="232"/>
-      <c r="G8" s="232"/>
-      <c r="H8" s="232"/>
-      <c r="I8" s="232"/>
-      <c r="J8" s="232"/>
-      <c r="K8" s="232"/>
-      <c r="L8" s="232"/>
-      <c r="M8" s="232"/>
-      <c r="N8" s="232"/>
-      <c r="O8" s="232"/>
-      <c r="P8" s="232"/>
+      <c r="C8" s="228"/>
+      <c r="D8" s="228"/>
+      <c r="E8" s="228"/>
+      <c r="F8" s="228"/>
+      <c r="G8" s="228"/>
+      <c r="H8" s="228"/>
+      <c r="I8" s="228"/>
+      <c r="J8" s="228"/>
+      <c r="K8" s="228"/>
+      <c r="L8" s="228"/>
+      <c r="M8" s="228"/>
+      <c r="N8" s="228"/>
+      <c r="O8" s="228"/>
+      <c r="P8" s="228"/>
     </row>
     <row r="9" spans="2:20" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B9" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C9" s="230" t="s">
+      <c r="C9" s="229" t="s">
         <v>2</v>
       </c>
-      <c r="D9" s="230"/>
+      <c r="D9" s="229"/>
       <c r="E9" s="120" t="s">
         <v>3</v>
       </c>
@@ -4299,10 +4302,10 @@
       </c>
     </row>
     <row r="10" spans="2:20" x14ac:dyDescent="0.3">
-      <c r="B10" s="295" t="s">
+      <c r="B10" s="247" t="s">
         <v>16</v>
       </c>
-      <c r="C10" s="295" t="s">
+      <c r="C10" s="247" t="s">
         <v>17</v>
       </c>
       <c r="D10" s="20" t="s">
@@ -4351,8 +4354,8 @@
       </c>
     </row>
     <row r="11" spans="2:20" x14ac:dyDescent="0.3">
-      <c r="B11" s="296"/>
-      <c r="C11" s="296"/>
+      <c r="B11" s="248"/>
+      <c r="C11" s="248"/>
       <c r="D11" s="20" t="s">
         <v>24</v>
       </c>
@@ -4399,8 +4402,8 @@
       </c>
     </row>
     <row r="12" spans="2:20" x14ac:dyDescent="0.3">
-      <c r="B12" s="296"/>
-      <c r="C12" s="295" t="s">
+      <c r="B12" s="248"/>
+      <c r="C12" s="247" t="s">
         <v>17</v>
       </c>
       <c r="D12" s="111" t="s">
@@ -4450,8 +4453,8 @@
       </c>
     </row>
     <row r="13" spans="2:20" x14ac:dyDescent="0.3">
-      <c r="B13" s="296"/>
-      <c r="C13" s="296"/>
+      <c r="B13" s="248"/>
+      <c r="C13" s="248"/>
       <c r="D13" s="111" t="s">
         <v>24</v>
       </c>
@@ -4500,10 +4503,10 @@
       </c>
     </row>
     <row r="14" spans="2:20" x14ac:dyDescent="0.3">
-      <c r="B14" s="297" t="s">
+      <c r="B14" s="249" t="s">
         <v>26</v>
       </c>
-      <c r="C14" s="257" t="s">
+      <c r="C14" s="251" t="s">
         <v>17</v>
       </c>
       <c r="D14" s="20" t="s">
@@ -4553,8 +4556,8 @@
       </c>
     </row>
     <row r="15" spans="2:20" x14ac:dyDescent="0.3">
-      <c r="B15" s="298"/>
-      <c r="C15" s="257"/>
+      <c r="B15" s="250"/>
+      <c r="C15" s="251"/>
       <c r="D15" s="20" t="s">
         <v>24</v>
       </c>
@@ -4602,10 +4605,10 @@
       </c>
     </row>
     <row r="16" spans="2:20" x14ac:dyDescent="0.3">
-      <c r="B16" s="297" t="s">
+      <c r="B16" s="249" t="s">
         <v>28</v>
       </c>
-      <c r="C16" s="297" t="s">
+      <c r="C16" s="249" t="s">
         <v>17</v>
       </c>
       <c r="D16" s="20" t="s">
@@ -4655,8 +4658,8 @@
       </c>
     </row>
     <row r="17" spans="2:20" x14ac:dyDescent="0.3">
-      <c r="B17" s="298"/>
-      <c r="C17" s="298"/>
+      <c r="B17" s="250"/>
+      <c r="C17" s="250"/>
       <c r="D17" s="20" t="s">
         <v>24</v>
       </c>
@@ -4704,10 +4707,10 @@
       </c>
     </row>
     <row r="18" spans="2:20" x14ac:dyDescent="0.3">
-      <c r="B18" s="297" t="s">
+      <c r="B18" s="249" t="s">
         <v>30</v>
       </c>
-      <c r="C18" s="257" t="s">
+      <c r="C18" s="251" t="s">
         <v>31</v>
       </c>
       <c r="D18" s="20" t="s">
@@ -4758,8 +4761,8 @@
       </c>
     </row>
     <row r="19" spans="2:20" x14ac:dyDescent="0.3">
-      <c r="B19" s="301"/>
-      <c r="C19" s="257"/>
+      <c r="B19" s="259"/>
+      <c r="C19" s="251"/>
       <c r="D19" s="20" t="s">
         <v>24</v>
       </c>
@@ -4808,8 +4811,8 @@
       </c>
     </row>
     <row r="20" spans="2:20" x14ac:dyDescent="0.3">
-      <c r="B20" s="301"/>
-      <c r="C20" s="257" t="s">
+      <c r="B20" s="259"/>
+      <c r="C20" s="251" t="s">
         <v>17</v>
       </c>
       <c r="D20" s="20" t="s">
@@ -4859,8 +4862,8 @@
       </c>
     </row>
     <row r="21" spans="2:20" x14ac:dyDescent="0.3">
-      <c r="B21" s="298"/>
-      <c r="C21" s="257"/>
+      <c r="B21" s="250"/>
+      <c r="C21" s="251"/>
       <c r="D21" s="20" t="s">
         <v>24</v>
       </c>
@@ -4945,74 +4948,74 @@
       <c r="P23" s="192"/>
     </row>
     <row r="24" spans="2:20" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B24" s="292" t="s">
+      <c r="B24" s="261" t="s">
         <v>35</v>
       </c>
-      <c r="C24" s="292"/>
-      <c r="D24" s="292"/>
-      <c r="E24" s="292"/>
-      <c r="F24" s="292"/>
-      <c r="G24" s="292"/>
-      <c r="H24" s="292"/>
-      <c r="I24" s="292"/>
-      <c r="J24" s="292"/>
-      <c r="K24" s="292"/>
-      <c r="L24" s="292"/>
-      <c r="M24" s="292"/>
-      <c r="N24" s="292"/>
-      <c r="O24" s="292"/>
-      <c r="P24" s="292"/>
+      <c r="C24" s="261"/>
+      <c r="D24" s="261"/>
+      <c r="E24" s="261"/>
+      <c r="F24" s="261"/>
+      <c r="G24" s="261"/>
+      <c r="H24" s="261"/>
+      <c r="I24" s="261"/>
+      <c r="J24" s="261"/>
+      <c r="K24" s="261"/>
+      <c r="L24" s="261"/>
+      <c r="M24" s="261"/>
+      <c r="N24" s="261"/>
+      <c r="O24" s="261"/>
+      <c r="P24" s="261"/>
     </row>
     <row r="25" spans="2:20" x14ac:dyDescent="0.3">
-      <c r="B25" s="292"/>
-      <c r="C25" s="292"/>
-      <c r="D25" s="292"/>
-      <c r="E25" s="292"/>
-      <c r="F25" s="292"/>
-      <c r="G25" s="292"/>
-      <c r="H25" s="292"/>
-      <c r="I25" s="292"/>
-      <c r="J25" s="292"/>
-      <c r="K25" s="292"/>
-      <c r="L25" s="292"/>
-      <c r="M25" s="292"/>
-      <c r="N25" s="292"/>
-      <c r="O25" s="292"/>
-      <c r="P25" s="292"/>
+      <c r="B25" s="261"/>
+      <c r="C25" s="261"/>
+      <c r="D25" s="261"/>
+      <c r="E25" s="261"/>
+      <c r="F25" s="261"/>
+      <c r="G25" s="261"/>
+      <c r="H25" s="261"/>
+      <c r="I25" s="261"/>
+      <c r="J25" s="261"/>
+      <c r="K25" s="261"/>
+      <c r="L25" s="261"/>
+      <c r="M25" s="261"/>
+      <c r="N25" s="261"/>
+      <c r="O25" s="261"/>
+      <c r="P25" s="261"/>
     </row>
     <row r="26" spans="2:20" x14ac:dyDescent="0.3">
-      <c r="B26" s="292"/>
-      <c r="C26" s="292"/>
-      <c r="D26" s="292"/>
-      <c r="E26" s="292"/>
-      <c r="F26" s="292"/>
-      <c r="G26" s="292"/>
-      <c r="H26" s="292"/>
-      <c r="I26" s="292"/>
-      <c r="J26" s="292"/>
-      <c r="K26" s="292"/>
-      <c r="L26" s="292"/>
-      <c r="M26" s="292"/>
-      <c r="N26" s="292"/>
-      <c r="O26" s="292"/>
-      <c r="P26" s="292"/>
+      <c r="B26" s="261"/>
+      <c r="C26" s="261"/>
+      <c r="D26" s="261"/>
+      <c r="E26" s="261"/>
+      <c r="F26" s="261"/>
+      <c r="G26" s="261"/>
+      <c r="H26" s="261"/>
+      <c r="I26" s="261"/>
+      <c r="J26" s="261"/>
+      <c r="K26" s="261"/>
+      <c r="L26" s="261"/>
+      <c r="M26" s="261"/>
+      <c r="N26" s="261"/>
+      <c r="O26" s="261"/>
+      <c r="P26" s="261"/>
     </row>
     <row r="27" spans="2:20" x14ac:dyDescent="0.3">
-      <c r="B27" s="292"/>
-      <c r="C27" s="292"/>
-      <c r="D27" s="292"/>
-      <c r="E27" s="292"/>
-      <c r="F27" s="292"/>
-      <c r="G27" s="292"/>
-      <c r="H27" s="292"/>
-      <c r="I27" s="292"/>
-      <c r="J27" s="292"/>
-      <c r="K27" s="292"/>
-      <c r="L27" s="292"/>
-      <c r="M27" s="292"/>
-      <c r="N27" s="292"/>
-      <c r="O27" s="292"/>
-      <c r="P27" s="292"/>
+      <c r="B27" s="261"/>
+      <c r="C27" s="261"/>
+      <c r="D27" s="261"/>
+      <c r="E27" s="261"/>
+      <c r="F27" s="261"/>
+      <c r="G27" s="261"/>
+      <c r="H27" s="261"/>
+      <c r="I27" s="261"/>
+      <c r="J27" s="261"/>
+      <c r="K27" s="261"/>
+      <c r="L27" s="261"/>
+      <c r="M27" s="261"/>
+      <c r="N27" s="261"/>
+      <c r="O27" s="261"/>
+      <c r="P27" s="261"/>
     </row>
     <row r="28" spans="2:20" x14ac:dyDescent="0.3">
       <c r="B28" s="35"/>
@@ -5141,32 +5144,32 @@
       <c r="Q34" s="28"/>
     </row>
     <row r="35" spans="2:20" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B35" s="299" t="s">
+      <c r="B35" s="252" t="s">
         <v>36</v>
       </c>
-      <c r="C35" s="237"/>
-      <c r="D35" s="237"/>
-      <c r="E35" s="237"/>
-      <c r="F35" s="237"/>
-      <c r="G35" s="237"/>
-      <c r="H35" s="237"/>
-      <c r="I35" s="237"/>
-      <c r="J35" s="237"/>
-      <c r="K35" s="237"/>
-      <c r="L35" s="237"/>
-      <c r="M35" s="237"/>
-      <c r="N35" s="237"/>
-      <c r="O35" s="237"/>
-      <c r="P35" s="237"/>
+      <c r="C35" s="225"/>
+      <c r="D35" s="225"/>
+      <c r="E35" s="225"/>
+      <c r="F35" s="225"/>
+      <c r="G35" s="225"/>
+      <c r="H35" s="225"/>
+      <c r="I35" s="225"/>
+      <c r="J35" s="225"/>
+      <c r="K35" s="225"/>
+      <c r="L35" s="225"/>
+      <c r="M35" s="225"/>
+      <c r="N35" s="225"/>
+      <c r="O35" s="225"/>
+      <c r="P35" s="225"/>
     </row>
     <row r="36" spans="2:20" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B36" s="120" t="s">
         <v>1</v>
       </c>
-      <c r="C36" s="230" t="s">
+      <c r="C36" s="229" t="s">
         <v>2</v>
       </c>
-      <c r="D36" s="230"/>
+      <c r="D36" s="229"/>
       <c r="E36" s="120" t="s">
         <v>3</v>
       </c>
@@ -5197,16 +5200,16 @@
       <c r="N36" s="120" t="s">
         <v>14</v>
       </c>
-      <c r="O36" s="230" t="s">
+      <c r="O36" s="229" t="s">
         <v>38</v>
       </c>
-      <c r="P36" s="230"/>
+      <c r="P36" s="229"/>
       <c r="T36" s="193" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="37" spans="2:20" x14ac:dyDescent="0.3">
-      <c r="B37" s="300" t="s">
+      <c r="B37" s="253" t="s">
         <v>39</v>
       </c>
       <c r="C37" s="138" t="s">
@@ -5248,16 +5251,16 @@
       <c r="N37" s="94" t="s">
         <v>41</v>
       </c>
-      <c r="O37" s="281" t="s">
+      <c r="O37" s="254" t="s">
         <v>42</v>
       </c>
-      <c r="P37" s="282"/>
+      <c r="P37" s="255"/>
       <c r="T37" s="53" t="s">
         <v>43</v>
       </c>
     </row>
     <row r="38" spans="2:20" x14ac:dyDescent="0.3">
-      <c r="B38" s="300"/>
+      <c r="B38" s="253"/>
       <c r="C38" s="138" t="s">
         <v>17</v>
       </c>
@@ -5297,8 +5300,8 @@
       <c r="N38" s="94" t="s">
         <v>41</v>
       </c>
-      <c r="O38" s="283"/>
-      <c r="P38" s="284"/>
+      <c r="O38" s="256"/>
+      <c r="P38" s="257"/>
       <c r="T38" s="53" t="s">
         <v>43</v>
       </c>
@@ -5443,78 +5446,78 @@
       <c r="Q42" s="7"/>
     </row>
     <row r="43" spans="2:20" x14ac:dyDescent="0.3">
-      <c r="B43" s="224" t="s">
+      <c r="B43" s="236" t="s">
         <v>35</v>
       </c>
-      <c r="C43" s="225"/>
-      <c r="D43" s="225"/>
-      <c r="E43" s="225"/>
-      <c r="F43" s="225"/>
-      <c r="G43" s="225"/>
-      <c r="H43" s="225"/>
-      <c r="I43" s="225"/>
-      <c r="J43" s="225"/>
-      <c r="K43" s="225"/>
-      <c r="L43" s="225"/>
-      <c r="M43" s="225"/>
-      <c r="N43" s="225"/>
-      <c r="O43" s="225"/>
-      <c r="P43" s="225"/>
-      <c r="Q43" s="226"/>
+      <c r="C43" s="237"/>
+      <c r="D43" s="237"/>
+      <c r="E43" s="237"/>
+      <c r="F43" s="237"/>
+      <c r="G43" s="237"/>
+      <c r="H43" s="237"/>
+      <c r="I43" s="237"/>
+      <c r="J43" s="237"/>
+      <c r="K43" s="237"/>
+      <c r="L43" s="237"/>
+      <c r="M43" s="237"/>
+      <c r="N43" s="237"/>
+      <c r="O43" s="237"/>
+      <c r="P43" s="237"/>
+      <c r="Q43" s="238"/>
     </row>
     <row r="44" spans="2:20" x14ac:dyDescent="0.3">
-      <c r="B44" s="224"/>
-      <c r="C44" s="225"/>
-      <c r="D44" s="225"/>
-      <c r="E44" s="225"/>
-      <c r="F44" s="225"/>
-      <c r="G44" s="225"/>
-      <c r="H44" s="225"/>
-      <c r="I44" s="225"/>
-      <c r="J44" s="225"/>
-      <c r="K44" s="225"/>
-      <c r="L44" s="225"/>
-      <c r="M44" s="225"/>
-      <c r="N44" s="225"/>
-      <c r="O44" s="225"/>
-      <c r="P44" s="225"/>
-      <c r="Q44" s="226"/>
+      <c r="B44" s="236"/>
+      <c r="C44" s="237"/>
+      <c r="D44" s="237"/>
+      <c r="E44" s="237"/>
+      <c r="F44" s="237"/>
+      <c r="G44" s="237"/>
+      <c r="H44" s="237"/>
+      <c r="I44" s="237"/>
+      <c r="J44" s="237"/>
+      <c r="K44" s="237"/>
+      <c r="L44" s="237"/>
+      <c r="M44" s="237"/>
+      <c r="N44" s="237"/>
+      <c r="O44" s="237"/>
+      <c r="P44" s="237"/>
+      <c r="Q44" s="238"/>
     </row>
     <row r="45" spans="2:20" x14ac:dyDescent="0.3">
-      <c r="B45" s="224"/>
-      <c r="C45" s="225"/>
-      <c r="D45" s="225"/>
-      <c r="E45" s="225"/>
-      <c r="F45" s="225"/>
-      <c r="G45" s="225"/>
-      <c r="H45" s="225"/>
-      <c r="I45" s="225"/>
-      <c r="J45" s="225"/>
-      <c r="K45" s="225"/>
-      <c r="L45" s="225"/>
-      <c r="M45" s="225"/>
-      <c r="N45" s="225"/>
-      <c r="O45" s="225"/>
-      <c r="P45" s="225"/>
-      <c r="Q45" s="226"/>
+      <c r="B45" s="236"/>
+      <c r="C45" s="237"/>
+      <c r="D45" s="237"/>
+      <c r="E45" s="237"/>
+      <c r="F45" s="237"/>
+      <c r="G45" s="237"/>
+      <c r="H45" s="237"/>
+      <c r="I45" s="237"/>
+      <c r="J45" s="237"/>
+      <c r="K45" s="237"/>
+      <c r="L45" s="237"/>
+      <c r="M45" s="237"/>
+      <c r="N45" s="237"/>
+      <c r="O45" s="237"/>
+      <c r="P45" s="237"/>
+      <c r="Q45" s="238"/>
     </row>
     <row r="46" spans="2:20" x14ac:dyDescent="0.3">
-      <c r="B46" s="227"/>
-      <c r="C46" s="228"/>
-      <c r="D46" s="228"/>
-      <c r="E46" s="228"/>
-      <c r="F46" s="228"/>
-      <c r="G46" s="228"/>
-      <c r="H46" s="228"/>
-      <c r="I46" s="228"/>
-      <c r="J46" s="228"/>
-      <c r="K46" s="228"/>
-      <c r="L46" s="228"/>
-      <c r="M46" s="228"/>
-      <c r="N46" s="228"/>
-      <c r="O46" s="228"/>
-      <c r="P46" s="228"/>
-      <c r="Q46" s="229"/>
+      <c r="B46" s="239"/>
+      <c r="C46" s="240"/>
+      <c r="D46" s="240"/>
+      <c r="E46" s="240"/>
+      <c r="F46" s="240"/>
+      <c r="G46" s="240"/>
+      <c r="H46" s="240"/>
+      <c r="I46" s="240"/>
+      <c r="J46" s="240"/>
+      <c r="K46" s="240"/>
+      <c r="L46" s="240"/>
+      <c r="M46" s="240"/>
+      <c r="N46" s="240"/>
+      <c r="O46" s="240"/>
+      <c r="P46" s="240"/>
+      <c r="Q46" s="241"/>
     </row>
     <row r="47" spans="2:20" x14ac:dyDescent="0.3">
       <c r="B47" s="35"/>
@@ -5699,16 +5702,16 @@
       <c r="P56" s="245"/>
       <c r="Q56" s="245"/>
       <c r="R56" s="245"/>
-      <c r="S56" s="272"/>
+      <c r="S56" s="262"/>
     </row>
     <row r="57" spans="2:20" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B57" s="97" t="s">
         <v>1</v>
       </c>
-      <c r="C57" s="230" t="s">
+      <c r="C57" s="229" t="s">
         <v>2</v>
       </c>
-      <c r="D57" s="230"/>
+      <c r="D57" s="229"/>
       <c r="E57" s="120" t="s">
         <v>3</v>
       </c>
@@ -5748,19 +5751,19 @@
       <c r="Q57" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="R57" s="293" t="s">
+      <c r="R57" s="263" t="s">
         <v>38</v>
       </c>
-      <c r="S57" s="294"/>
+      <c r="S57" s="264"/>
       <c r="T57" s="129" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="58" spans="2:20" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B58" s="262" t="s">
+      <c r="B58" s="265" t="s">
         <v>55</v>
       </c>
-      <c r="C58" s="263" t="s">
+      <c r="C58" s="260" t="s">
         <v>56</v>
       </c>
       <c r="D58" s="139" t="s">
@@ -5808,17 +5811,17 @@
       <c r="Q58" s="142" t="s">
         <v>60</v>
       </c>
-      <c r="R58" s="264" t="s">
+      <c r="R58" s="266" t="s">
         <v>61</v>
       </c>
-      <c r="S58" s="265"/>
+      <c r="S58" s="267"/>
       <c r="T58" s="130" t="s">
         <v>62</v>
       </c>
     </row>
     <row r="59" spans="2:20" x14ac:dyDescent="0.3">
-      <c r="B59" s="262"/>
-      <c r="C59" s="263"/>
+      <c r="B59" s="265"/>
+      <c r="C59" s="260"/>
       <c r="D59" s="139" t="s">
         <v>24</v>
       </c>
@@ -5864,17 +5867,17 @@
       <c r="Q59" s="142" t="s">
         <v>60</v>
       </c>
-      <c r="R59" s="266"/>
-      <c r="S59" s="267"/>
+      <c r="R59" s="268"/>
+      <c r="S59" s="269"/>
       <c r="T59" s="130" t="s">
         <v>62</v>
       </c>
     </row>
     <row r="60" spans="2:20" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B60" s="262" t="s">
+      <c r="B60" s="265" t="s">
         <v>241</v>
       </c>
-      <c r="C60" s="263" t="s">
+      <c r="C60" s="260" t="s">
         <v>56</v>
       </c>
       <c r="D60" s="139" t="s">
@@ -5922,15 +5925,15 @@
       <c r="Q60" s="142" t="s">
         <v>60</v>
       </c>
-      <c r="R60" s="266"/>
-      <c r="S60" s="267"/>
+      <c r="R60" s="268"/>
+      <c r="S60" s="269"/>
       <c r="T60" s="130" t="s">
         <v>62</v>
       </c>
     </row>
     <row r="61" spans="2:20" x14ac:dyDescent="0.3">
-      <c r="B61" s="262"/>
-      <c r="C61" s="263"/>
+      <c r="B61" s="265"/>
+      <c r="C61" s="260"/>
       <c r="D61" s="139" t="s">
         <v>24</v>
       </c>
@@ -5976,17 +5979,17 @@
       <c r="Q61" s="142" t="s">
         <v>60</v>
       </c>
-      <c r="R61" s="288"/>
-      <c r="S61" s="289"/>
+      <c r="R61" s="270"/>
+      <c r="S61" s="271"/>
       <c r="T61" s="130" t="s">
         <v>62</v>
       </c>
     </row>
     <row r="62" spans="2:20" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B62" s="279" t="s">
+      <c r="B62" s="276" t="s">
         <v>63</v>
       </c>
-      <c r="C62" s="238" t="s">
+      <c r="C62" s="230" t="s">
         <v>31</v>
       </c>
       <c r="D62" s="117" t="s">
@@ -6034,17 +6037,17 @@
       <c r="Q62" s="94" t="s">
         <v>64</v>
       </c>
-      <c r="R62" s="281" t="s">
+      <c r="R62" s="254" t="s">
         <v>65</v>
       </c>
-      <c r="S62" s="282"/>
+      <c r="S62" s="255"/>
       <c r="T62" s="130" t="s">
         <v>66</v>
       </c>
     </row>
     <row r="63" spans="2:20" x14ac:dyDescent="0.3">
-      <c r="B63" s="280"/>
-      <c r="C63" s="239"/>
+      <c r="B63" s="277"/>
+      <c r="C63" s="231"/>
       <c r="D63" s="117" t="s">
         <v>24</v>
       </c>
@@ -6090,17 +6093,17 @@
       <c r="Q63" s="94" t="s">
         <v>64</v>
       </c>
-      <c r="R63" s="283"/>
-      <c r="S63" s="284"/>
+      <c r="R63" s="256"/>
+      <c r="S63" s="257"/>
       <c r="T63" s="130" t="s">
         <v>66</v>
       </c>
     </row>
     <row r="64" spans="2:20" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B64" s="262" t="s">
+      <c r="B64" s="265" t="s">
         <v>67</v>
       </c>
-      <c r="C64" s="263" t="s">
+      <c r="C64" s="260" t="s">
         <v>56</v>
       </c>
       <c r="D64" s="139" t="s">
@@ -6148,17 +6151,17 @@
       <c r="Q64" s="142" t="s">
         <v>60</v>
       </c>
-      <c r="R64" s="264" t="s">
+      <c r="R64" s="266" t="s">
         <v>61</v>
       </c>
-      <c r="S64" s="265"/>
+      <c r="S64" s="267"/>
       <c r="T64" s="130" t="s">
         <v>62</v>
       </c>
     </row>
     <row r="65" spans="2:20" x14ac:dyDescent="0.3">
-      <c r="B65" s="262"/>
-      <c r="C65" s="263"/>
+      <c r="B65" s="265"/>
+      <c r="C65" s="260"/>
       <c r="D65" s="139" t="s">
         <v>24</v>
       </c>
@@ -6204,17 +6207,17 @@
       <c r="Q65" s="142" t="s">
         <v>60</v>
       </c>
-      <c r="R65" s="266"/>
-      <c r="S65" s="267"/>
+      <c r="R65" s="268"/>
+      <c r="S65" s="269"/>
       <c r="T65" s="130" t="s">
         <v>62</v>
       </c>
     </row>
     <row r="66" spans="2:20" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B66" s="279" t="s">
+      <c r="B66" s="276" t="s">
         <v>68</v>
       </c>
-      <c r="C66" s="238" t="s">
+      <c r="C66" s="230" t="s">
         <v>31</v>
       </c>
       <c r="D66" s="117" t="s">
@@ -6262,17 +6265,17 @@
       <c r="Q66" s="94" t="s">
         <v>64</v>
       </c>
-      <c r="R66" s="281" t="s">
+      <c r="R66" s="254" t="s">
         <v>65</v>
       </c>
-      <c r="S66" s="282"/>
+      <c r="S66" s="255"/>
       <c r="T66" s="130" t="s">
         <v>66</v>
       </c>
     </row>
     <row r="67" spans="2:20" x14ac:dyDescent="0.3">
-      <c r="B67" s="280"/>
-      <c r="C67" s="239"/>
+      <c r="B67" s="277"/>
+      <c r="C67" s="231"/>
       <c r="D67" s="117" t="s">
         <v>24</v>
       </c>
@@ -6318,17 +6321,17 @@
       <c r="Q67" s="94" t="s">
         <v>64</v>
       </c>
-      <c r="R67" s="283"/>
-      <c r="S67" s="284"/>
+      <c r="R67" s="256"/>
+      <c r="S67" s="257"/>
       <c r="T67" s="130" t="s">
         <v>66</v>
       </c>
     </row>
     <row r="68" spans="2:20" x14ac:dyDescent="0.3">
-      <c r="B68" s="290" t="s">
+      <c r="B68" s="281" t="s">
         <v>69</v>
       </c>
-      <c r="C68" s="263" t="s">
+      <c r="C68" s="260" t="s">
         <v>56</v>
       </c>
       <c r="D68" s="139" t="s">
@@ -6376,17 +6379,17 @@
       <c r="Q68" s="142" t="s">
         <v>60</v>
       </c>
-      <c r="R68" s="264" t="s">
+      <c r="R68" s="266" t="s">
         <v>61</v>
       </c>
-      <c r="S68" s="265"/>
+      <c r="S68" s="267"/>
       <c r="T68" s="130" t="s">
         <v>62</v>
       </c>
     </row>
     <row r="69" spans="2:20" x14ac:dyDescent="0.3">
-      <c r="B69" s="291"/>
-      <c r="C69" s="263"/>
+      <c r="B69" s="282"/>
+      <c r="C69" s="260"/>
       <c r="D69" s="139" t="s">
         <v>24</v>
       </c>
@@ -6432,17 +6435,17 @@
       <c r="Q69" s="142" t="s">
         <v>60</v>
       </c>
-      <c r="R69" s="266"/>
-      <c r="S69" s="267"/>
+      <c r="R69" s="268"/>
+      <c r="S69" s="269"/>
       <c r="T69" s="130" t="s">
         <v>62</v>
       </c>
     </row>
     <row r="70" spans="2:20" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B70" s="262" t="s">
+      <c r="B70" s="265" t="s">
         <v>70</v>
       </c>
-      <c r="C70" s="263" t="s">
+      <c r="C70" s="260" t="s">
         <v>56</v>
       </c>
       <c r="D70" s="139" t="s">
@@ -6490,15 +6493,15 @@
       <c r="Q70" s="142" t="s">
         <v>60</v>
       </c>
-      <c r="R70" s="266"/>
-      <c r="S70" s="267"/>
+      <c r="R70" s="268"/>
+      <c r="S70" s="269"/>
       <c r="T70" s="130" t="s">
         <v>62</v>
       </c>
     </row>
     <row r="71" spans="2:20" x14ac:dyDescent="0.3">
-      <c r="B71" s="262"/>
-      <c r="C71" s="263"/>
+      <c r="B71" s="265"/>
+      <c r="C71" s="260"/>
       <c r="D71" s="139" t="s">
         <v>24</v>
       </c>
@@ -6544,17 +6547,17 @@
       <c r="Q71" s="142" t="s">
         <v>60</v>
       </c>
-      <c r="R71" s="288"/>
-      <c r="S71" s="289"/>
+      <c r="R71" s="270"/>
+      <c r="S71" s="271"/>
       <c r="T71" s="130" t="s">
         <v>62</v>
       </c>
     </row>
     <row r="72" spans="2:20" x14ac:dyDescent="0.3">
-      <c r="B72" s="285" t="s">
+      <c r="B72" s="278" t="s">
         <v>71</v>
       </c>
-      <c r="C72" s="286" t="s">
+      <c r="C72" s="279" t="s">
         <v>31</v>
       </c>
       <c r="D72" s="185" t="s">
@@ -6602,17 +6605,17 @@
       <c r="Q72" s="187" t="s">
         <v>72</v>
       </c>
-      <c r="R72" s="268" t="s">
+      <c r="R72" s="272" t="s">
         <v>73</v>
       </c>
-      <c r="S72" s="269"/>
+      <c r="S72" s="273"/>
       <c r="T72" s="130" t="s">
         <v>74</v>
       </c>
     </row>
     <row r="73" spans="2:20" x14ac:dyDescent="0.3">
-      <c r="B73" s="285"/>
-      <c r="C73" s="287"/>
+      <c r="B73" s="278"/>
+      <c r="C73" s="280"/>
       <c r="D73" s="185" t="s">
         <v>24</v>
       </c>
@@ -6658,17 +6661,17 @@
       <c r="Q73" s="187" t="s">
         <v>72</v>
       </c>
-      <c r="R73" s="270"/>
-      <c r="S73" s="271"/>
+      <c r="R73" s="274"/>
+      <c r="S73" s="275"/>
       <c r="T73" s="130" t="s">
         <v>74</v>
       </c>
     </row>
     <row r="74" spans="2:20" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B74" s="262" t="s">
-        <v>75</v>
-      </c>
-      <c r="C74" s="263" t="s">
+      <c r="B74" s="265" t="s">
+        <v>75</v>
+      </c>
+      <c r="C74" s="260" t="s">
         <v>56</v>
       </c>
       <c r="D74" s="139" t="s">
@@ -6716,17 +6719,17 @@
       <c r="Q74" s="142" t="s">
         <v>60</v>
       </c>
-      <c r="R74" s="264" t="s">
+      <c r="R74" s="266" t="s">
         <v>61</v>
       </c>
-      <c r="S74" s="265"/>
+      <c r="S74" s="267"/>
       <c r="T74" s="130" t="s">
         <v>62</v>
       </c>
     </row>
     <row r="75" spans="2:20" x14ac:dyDescent="0.3">
-      <c r="B75" s="262"/>
-      <c r="C75" s="263"/>
+      <c r="B75" s="265"/>
+      <c r="C75" s="260"/>
       <c r="D75" s="139" t="s">
         <v>24</v>
       </c>
@@ -6772,17 +6775,17 @@
       <c r="Q75" s="142" t="s">
         <v>60</v>
       </c>
-      <c r="R75" s="266"/>
-      <c r="S75" s="267"/>
+      <c r="R75" s="268"/>
+      <c r="S75" s="269"/>
       <c r="T75" s="130" t="s">
         <v>62</v>
       </c>
     </row>
     <row r="76" spans="2:20" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B76" s="262" t="s">
+      <c r="B76" s="265" t="s">
         <v>76</v>
       </c>
-      <c r="C76" s="263" t="s">
+      <c r="C76" s="260" t="s">
         <v>56</v>
       </c>
       <c r="D76" s="139" t="s">
@@ -6830,15 +6833,15 @@
       <c r="Q76" s="142" t="s">
         <v>60</v>
       </c>
-      <c r="R76" s="266"/>
-      <c r="S76" s="267"/>
+      <c r="R76" s="268"/>
+      <c r="S76" s="269"/>
       <c r="T76" s="130" t="s">
         <v>62</v>
       </c>
     </row>
     <row r="77" spans="2:20" x14ac:dyDescent="0.3">
-      <c r="B77" s="262"/>
-      <c r="C77" s="263"/>
+      <c r="B77" s="265"/>
+      <c r="C77" s="260"/>
       <c r="D77" s="139" t="s">
         <v>24</v>
       </c>
@@ -6884,17 +6887,17 @@
       <c r="Q77" s="142" t="s">
         <v>60</v>
       </c>
-      <c r="R77" s="266"/>
-      <c r="S77" s="267"/>
+      <c r="R77" s="268"/>
+      <c r="S77" s="269"/>
       <c r="T77" s="130" t="s">
         <v>62</v>
       </c>
     </row>
     <row r="78" spans="2:20" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B78" s="262" t="s">
+      <c r="B78" s="265" t="s">
         <v>77</v>
       </c>
-      <c r="C78" s="263" t="s">
+      <c r="C78" s="260" t="s">
         <v>56</v>
       </c>
       <c r="D78" s="139" t="s">
@@ -6942,15 +6945,15 @@
       <c r="Q78" s="142" t="s">
         <v>60</v>
       </c>
-      <c r="R78" s="266"/>
-      <c r="S78" s="267"/>
+      <c r="R78" s="268"/>
+      <c r="S78" s="269"/>
       <c r="T78" s="130" t="s">
         <v>62</v>
       </c>
     </row>
     <row r="79" spans="2:20" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B79" s="262"/>
-      <c r="C79" s="263"/>
+      <c r="B79" s="265"/>
+      <c r="C79" s="260"/>
       <c r="D79" s="139" t="s">
         <v>24</v>
       </c>
@@ -6996,8 +6999,8 @@
       <c r="Q79" s="142" t="s">
         <v>60</v>
       </c>
-      <c r="R79" s="288"/>
-      <c r="S79" s="289"/>
+      <c r="R79" s="270"/>
+      <c r="S79" s="271"/>
       <c r="T79" s="130" t="s">
         <v>62</v>
       </c>
@@ -7021,18 +7024,18 @@
       <c r="O80" s="245"/>
       <c r="P80" s="245"/>
       <c r="Q80" s="245"/>
-      <c r="R80" s="232"/>
-      <c r="S80" s="273"/>
+      <c r="R80" s="228"/>
+      <c r="S80" s="286"/>
       <c r="T80" s="130"/>
     </row>
     <row r="81" spans="2:20" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B81" s="97" t="s">
         <v>1</v>
       </c>
-      <c r="C81" s="259" t="s">
+      <c r="C81" s="283" t="s">
         <v>2</v>
       </c>
-      <c r="D81" s="260"/>
+      <c r="D81" s="284"/>
       <c r="E81" s="120" t="s">
         <v>3</v>
       </c>
@@ -7072,17 +7075,17 @@
       <c r="Q81" s="120" t="s">
         <v>14</v>
       </c>
-      <c r="R81" s="259" t="s">
+      <c r="R81" s="283" t="s">
         <v>38</v>
       </c>
-      <c r="S81" s="261"/>
+      <c r="S81" s="285"/>
       <c r="T81" s="130"/>
     </row>
     <row r="82" spans="2:20" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B82" s="274" t="s">
+      <c r="B82" s="287" t="s">
         <v>79</v>
       </c>
-      <c r="C82" s="276" t="s">
+      <c r="C82" s="289" t="s">
         <v>80</v>
       </c>
       <c r="D82" s="139" t="s">
@@ -7130,17 +7133,17 @@
       <c r="Q82" s="142" t="s">
         <v>60</v>
       </c>
-      <c r="R82" s="268" t="s">
+      <c r="R82" s="272" t="s">
         <v>81</v>
       </c>
-      <c r="S82" s="269"/>
+      <c r="S82" s="273"/>
       <c r="T82" s="130" t="s">
         <v>74</v>
       </c>
     </row>
     <row r="83" spans="2:20" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B83" s="275"/>
-      <c r="C83" s="277"/>
+      <c r="B83" s="288"/>
+      <c r="C83" s="290"/>
       <c r="D83" s="139" t="s">
         <v>24</v>
       </c>
@@ -7186,8 +7189,8 @@
       <c r="Q83" s="142" t="s">
         <v>60</v>
       </c>
-      <c r="R83" s="270"/>
-      <c r="S83" s="271"/>
+      <c r="R83" s="274"/>
+      <c r="S83" s="275"/>
       <c r="T83" s="130" t="s">
         <v>74</v>
       </c>
@@ -7212,17 +7215,17 @@
       <c r="P84" s="245"/>
       <c r="Q84" s="245"/>
       <c r="R84" s="245"/>
-      <c r="S84" s="272"/>
+      <c r="S84" s="262"/>
       <c r="T84" s="130"/>
     </row>
     <row r="85" spans="2:20" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B85" s="97" t="s">
         <v>1</v>
       </c>
-      <c r="C85" s="259" t="s">
+      <c r="C85" s="283" t="s">
         <v>2</v>
       </c>
-      <c r="D85" s="260"/>
+      <c r="D85" s="284"/>
       <c r="E85" s="120" t="s">
         <v>3</v>
       </c>
@@ -7262,17 +7265,17 @@
       <c r="Q85" s="120" t="s">
         <v>14</v>
       </c>
-      <c r="R85" s="259" t="s">
+      <c r="R85" s="283" t="s">
         <v>38</v>
       </c>
-      <c r="S85" s="261"/>
+      <c r="S85" s="285"/>
       <c r="T85" s="130"/>
     </row>
     <row r="86" spans="2:20" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B86" s="262" t="s">
+      <c r="B86" s="265" t="s">
         <v>83</v>
       </c>
-      <c r="C86" s="263" t="s">
+      <c r="C86" s="260" t="s">
         <v>80</v>
       </c>
       <c r="D86" s="139" t="s">
@@ -7320,17 +7323,17 @@
       <c r="Q86" s="142" t="s">
         <v>60</v>
       </c>
-      <c r="R86" s="268" t="s">
+      <c r="R86" s="272" t="s">
         <v>81</v>
       </c>
-      <c r="S86" s="269"/>
+      <c r="S86" s="273"/>
       <c r="T86" s="130" t="s">
         <v>62</v>
       </c>
     </row>
     <row r="87" spans="2:20" x14ac:dyDescent="0.3">
-      <c r="B87" s="262"/>
-      <c r="C87" s="263"/>
+      <c r="B87" s="265"/>
+      <c r="C87" s="260"/>
       <c r="D87" s="139" t="s">
         <v>24</v>
       </c>
@@ -7376,43 +7379,43 @@
       <c r="Q87" s="142" t="s">
         <v>60</v>
       </c>
-      <c r="R87" s="270"/>
-      <c r="S87" s="271"/>
+      <c r="R87" s="274"/>
+      <c r="S87" s="275"/>
       <c r="T87" s="130" t="s">
         <v>62</v>
       </c>
     </row>
     <row r="88" spans="2:20" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B88" s="236" t="s">
-        <v>85</v>
-      </c>
-      <c r="C88" s="237"/>
-      <c r="D88" s="237"/>
-      <c r="E88" s="237"/>
-      <c r="F88" s="237"/>
-      <c r="G88" s="237"/>
-      <c r="H88" s="237"/>
-      <c r="I88" s="237"/>
-      <c r="J88" s="237"/>
-      <c r="K88" s="237"/>
-      <c r="L88" s="237"/>
-      <c r="M88" s="237"/>
-      <c r="N88" s="237"/>
-      <c r="O88" s="237"/>
-      <c r="P88" s="237"/>
-      <c r="Q88" s="237"/>
-      <c r="R88" s="237"/>
-      <c r="S88" s="278"/>
+      <c r="B88" s="224" t="s">
+        <v>85</v>
+      </c>
+      <c r="C88" s="225"/>
+      <c r="D88" s="225"/>
+      <c r="E88" s="225"/>
+      <c r="F88" s="225"/>
+      <c r="G88" s="225"/>
+      <c r="H88" s="225"/>
+      <c r="I88" s="225"/>
+      <c r="J88" s="225"/>
+      <c r="K88" s="225"/>
+      <c r="L88" s="225"/>
+      <c r="M88" s="225"/>
+      <c r="N88" s="225"/>
+      <c r="O88" s="225"/>
+      <c r="P88" s="225"/>
+      <c r="Q88" s="225"/>
+      <c r="R88" s="225"/>
+      <c r="S88" s="291"/>
       <c r="T88" s="130"/>
     </row>
     <row r="89" spans="2:20" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B89" s="97" t="s">
         <v>1</v>
       </c>
-      <c r="C89" s="259" t="s">
+      <c r="C89" s="283" t="s">
         <v>2</v>
       </c>
-      <c r="D89" s="260"/>
+      <c r="D89" s="284"/>
       <c r="E89" s="120" t="s">
         <v>3</v>
       </c>
@@ -7452,17 +7455,17 @@
       <c r="Q89" s="120" t="s">
         <v>14</v>
       </c>
-      <c r="R89" s="259" t="s">
+      <c r="R89" s="283" t="s">
         <v>38</v>
       </c>
-      <c r="S89" s="261"/>
+      <c r="S89" s="285"/>
       <c r="T89" s="130"/>
     </row>
     <row r="90" spans="2:20" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B90" s="262" t="s">
+      <c r="B90" s="265" t="s">
         <v>86</v>
       </c>
-      <c r="C90" s="263" t="s">
+      <c r="C90" s="260" t="s">
         <v>80</v>
       </c>
       <c r="D90" s="139" t="s">
@@ -7510,17 +7513,17 @@
       <c r="Q90" s="142" t="s">
         <v>60</v>
       </c>
-      <c r="R90" s="268" t="s">
+      <c r="R90" s="272" t="s">
         <v>81</v>
       </c>
-      <c r="S90" s="269"/>
+      <c r="S90" s="273"/>
       <c r="T90" s="130" t="s">
         <v>62</v>
       </c>
     </row>
     <row r="91" spans="2:20" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B91" s="262"/>
-      <c r="C91" s="263"/>
+      <c r="B91" s="265"/>
+      <c r="C91" s="260"/>
       <c r="D91" s="139" t="s">
         <v>24</v>
       </c>
@@ -7566,43 +7569,43 @@
       <c r="Q91" s="142" t="s">
         <v>60</v>
       </c>
-      <c r="R91" s="270"/>
-      <c r="S91" s="271"/>
+      <c r="R91" s="274"/>
+      <c r="S91" s="275"/>
       <c r="T91" s="130" t="s">
         <v>62</v>
       </c>
     </row>
     <row r="92" spans="2:20" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B92" s="236" t="s">
+      <c r="B92" s="224" t="s">
         <v>87</v>
       </c>
-      <c r="C92" s="237"/>
-      <c r="D92" s="237"/>
-      <c r="E92" s="237"/>
-      <c r="F92" s="237"/>
-      <c r="G92" s="237"/>
-      <c r="H92" s="237"/>
-      <c r="I92" s="237"/>
-      <c r="J92" s="237"/>
-      <c r="K92" s="237"/>
-      <c r="L92" s="237"/>
-      <c r="M92" s="237"/>
-      <c r="N92" s="237"/>
-      <c r="O92" s="237"/>
-      <c r="P92" s="237"/>
-      <c r="Q92" s="237"/>
-      <c r="R92" s="237"/>
-      <c r="S92" s="278"/>
+      <c r="C92" s="225"/>
+      <c r="D92" s="225"/>
+      <c r="E92" s="225"/>
+      <c r="F92" s="225"/>
+      <c r="G92" s="225"/>
+      <c r="H92" s="225"/>
+      <c r="I92" s="225"/>
+      <c r="J92" s="225"/>
+      <c r="K92" s="225"/>
+      <c r="L92" s="225"/>
+      <c r="M92" s="225"/>
+      <c r="N92" s="225"/>
+      <c r="O92" s="225"/>
+      <c r="P92" s="225"/>
+      <c r="Q92" s="225"/>
+      <c r="R92" s="225"/>
+      <c r="S92" s="291"/>
       <c r="T92" s="130"/>
     </row>
     <row r="93" spans="2:20" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B93" s="97" t="s">
         <v>1</v>
       </c>
-      <c r="C93" s="259" t="s">
+      <c r="C93" s="283" t="s">
         <v>2</v>
       </c>
-      <c r="D93" s="260"/>
+      <c r="D93" s="284"/>
       <c r="E93" s="120" t="s">
         <v>3</v>
       </c>
@@ -7642,17 +7645,17 @@
       <c r="Q93" s="120" t="s">
         <v>14</v>
       </c>
-      <c r="R93" s="259" t="s">
+      <c r="R93" s="283" t="s">
         <v>38</v>
       </c>
-      <c r="S93" s="261"/>
+      <c r="S93" s="285"/>
       <c r="T93" s="130"/>
     </row>
     <row r="94" spans="2:20" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B94" s="262" t="s">
+      <c r="B94" s="265" t="s">
         <v>88</v>
       </c>
-      <c r="C94" s="263" t="s">
+      <c r="C94" s="260" t="s">
         <v>80</v>
       </c>
       <c r="D94" s="139" t="s">
@@ -7700,17 +7703,17 @@
       <c r="Q94" s="142" t="s">
         <v>60</v>
       </c>
-      <c r="R94" s="268" t="s">
+      <c r="R94" s="272" t="s">
         <v>81</v>
       </c>
-      <c r="S94" s="269"/>
+      <c r="S94" s="273"/>
       <c r="T94" s="130" t="s">
         <v>62</v>
       </c>
     </row>
     <row r="95" spans="2:20" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B95" s="262"/>
-      <c r="C95" s="263"/>
+      <c r="B95" s="265"/>
+      <c r="C95" s="260"/>
       <c r="D95" s="139" t="s">
         <v>24</v>
       </c>
@@ -7756,8 +7759,8 @@
       <c r="Q95" s="142" t="s">
         <v>60</v>
       </c>
-      <c r="R95" s="270"/>
-      <c r="S95" s="271"/>
+      <c r="R95" s="274"/>
+      <c r="S95" s="275"/>
       <c r="T95" s="130" t="s">
         <v>62</v>
       </c>
@@ -7781,17 +7784,17 @@
       <c r="O96" s="245"/>
       <c r="P96" s="245"/>
       <c r="Q96" s="245"/>
-      <c r="R96" s="232"/>
-      <c r="S96" s="232"/>
+      <c r="R96" s="228"/>
+      <c r="S96" s="228"/>
     </row>
     <row r="97" spans="2:21" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B97" s="97" t="s">
         <v>1</v>
       </c>
-      <c r="C97" s="259" t="s">
+      <c r="C97" s="283" t="s">
         <v>2</v>
       </c>
-      <c r="D97" s="260"/>
+      <c r="D97" s="284"/>
       <c r="E97" s="120" t="s">
         <v>3</v>
       </c>
@@ -7831,16 +7834,16 @@
       <c r="Q97" s="120" t="s">
         <v>14</v>
       </c>
-      <c r="R97" s="259" t="s">
+      <c r="R97" s="283" t="s">
         <v>38</v>
       </c>
-      <c r="S97" s="261"/>
+      <c r="S97" s="285"/>
     </row>
     <row r="98" spans="2:21" x14ac:dyDescent="0.3">
-      <c r="B98" s="262" t="s">
+      <c r="B98" s="265" t="s">
         <v>92</v>
       </c>
-      <c r="C98" s="263" t="s">
+      <c r="C98" s="260" t="s">
         <v>80</v>
       </c>
       <c r="D98" s="139" t="s">
@@ -7888,18 +7891,18 @@
       <c r="Q98" s="142" t="s">
         <v>60</v>
       </c>
-      <c r="R98" s="264" t="s">
+      <c r="R98" s="266" t="s">
         <v>93</v>
       </c>
-      <c r="S98" s="265"/>
+      <c r="S98" s="267"/>
       <c r="T98" s="130" t="s">
         <v>62</v>
       </c>
       <c r="U98"/>
     </row>
     <row r="99" spans="2:21" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B99" s="262"/>
-      <c r="C99" s="263"/>
+      <c r="B99" s="265"/>
+      <c r="C99" s="260"/>
       <c r="D99" s="139" t="s">
         <v>24</v>
       </c>
@@ -7945,8 +7948,8 @@
       <c r="Q99" s="142" t="s">
         <v>60</v>
       </c>
-      <c r="R99" s="266"/>
-      <c r="S99" s="267"/>
+      <c r="R99" s="268"/>
+      <c r="S99" s="269"/>
       <c r="T99" s="130" t="s">
         <v>62</v>
       </c>
@@ -7972,16 +7975,16 @@
       <c r="P100" s="245"/>
       <c r="Q100" s="245"/>
       <c r="R100" s="245"/>
-      <c r="S100" s="272"/>
+      <c r="S100" s="262"/>
     </row>
     <row r="101" spans="2:21" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B101" s="97" t="s">
         <v>1</v>
       </c>
-      <c r="C101" s="259" t="s">
+      <c r="C101" s="283" t="s">
         <v>2</v>
       </c>
-      <c r="D101" s="260"/>
+      <c r="D101" s="284"/>
       <c r="E101" s="120" t="s">
         <v>3</v>
       </c>
@@ -8021,16 +8024,16 @@
       <c r="Q101" s="120" t="s">
         <v>14</v>
       </c>
-      <c r="R101" s="259" t="s">
+      <c r="R101" s="283" t="s">
         <v>38</v>
       </c>
-      <c r="S101" s="261"/>
+      <c r="S101" s="285"/>
     </row>
     <row r="102" spans="2:21" x14ac:dyDescent="0.3">
-      <c r="B102" s="262" t="s">
+      <c r="B102" s="265" t="s">
         <v>95</v>
       </c>
-      <c r="C102" s="263" t="s">
+      <c r="C102" s="260" t="s">
         <v>31</v>
       </c>
       <c r="D102" s="139" t="s">
@@ -8078,18 +8081,18 @@
       <c r="Q102" s="142" t="s">
         <v>60</v>
       </c>
-      <c r="R102" s="264" t="s">
+      <c r="R102" s="266" t="s">
         <v>93</v>
       </c>
-      <c r="S102" s="265"/>
+      <c r="S102" s="267"/>
       <c r="T102" s="184" t="s">
         <v>96</v>
       </c>
       <c r="U102"/>
     </row>
     <row r="103" spans="2:21" x14ac:dyDescent="0.3">
-      <c r="B103" s="262"/>
-      <c r="C103" s="263"/>
+      <c r="B103" s="265"/>
+      <c r="C103" s="260"/>
       <c r="D103" s="139" t="s">
         <v>24</v>
       </c>
@@ -8135,8 +8138,8 @@
       <c r="Q103" s="142" t="s">
         <v>60</v>
       </c>
-      <c r="R103" s="266"/>
-      <c r="S103" s="267"/>
+      <c r="R103" s="268"/>
+      <c r="S103" s="269"/>
       <c r="T103" s="184" t="s">
         <v>96</v>
       </c>
@@ -8163,137 +8166,137 @@
       <c r="S104" s="136"/>
     </row>
     <row r="105" spans="2:21" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B105" s="247" t="s">
+      <c r="B105" s="292" t="s">
         <v>34</v>
       </c>
-      <c r="C105" s="248"/>
-      <c r="D105" s="248"/>
-      <c r="E105" s="248"/>
-      <c r="F105" s="248"/>
-      <c r="G105" s="248"/>
-      <c r="H105" s="248"/>
-      <c r="I105" s="248"/>
-      <c r="J105" s="248"/>
-      <c r="K105" s="248"/>
-      <c r="L105" s="248"/>
-      <c r="M105" s="248"/>
-      <c r="N105" s="248"/>
-      <c r="O105" s="248"/>
-      <c r="P105" s="248"/>
-      <c r="Q105" s="248"/>
-      <c r="R105" s="248"/>
-      <c r="S105" s="249"/>
+      <c r="C105" s="293"/>
+      <c r="D105" s="293"/>
+      <c r="E105" s="293"/>
+      <c r="F105" s="293"/>
+      <c r="G105" s="293"/>
+      <c r="H105" s="293"/>
+      <c r="I105" s="293"/>
+      <c r="J105" s="293"/>
+      <c r="K105" s="293"/>
+      <c r="L105" s="293"/>
+      <c r="M105" s="293"/>
+      <c r="N105" s="293"/>
+      <c r="O105" s="293"/>
+      <c r="P105" s="293"/>
+      <c r="Q105" s="293"/>
+      <c r="R105" s="293"/>
+      <c r="S105" s="294"/>
     </row>
     <row r="106" spans="2:21" x14ac:dyDescent="0.3">
-      <c r="B106" s="250" t="s">
+      <c r="B106" s="295" t="s">
         <v>35</v>
       </c>
-      <c r="C106" s="251"/>
-      <c r="D106" s="251"/>
-      <c r="E106" s="251"/>
-      <c r="F106" s="251"/>
-      <c r="G106" s="251"/>
-      <c r="H106" s="251"/>
-      <c r="I106" s="251"/>
-      <c r="J106" s="251"/>
-      <c r="K106" s="251"/>
-      <c r="L106" s="251"/>
-      <c r="M106" s="251"/>
-      <c r="N106" s="251"/>
-      <c r="O106" s="251"/>
-      <c r="P106" s="251"/>
-      <c r="Q106" s="251"/>
-      <c r="R106" s="251"/>
-      <c r="S106" s="252"/>
+      <c r="C106" s="296"/>
+      <c r="D106" s="296"/>
+      <c r="E106" s="296"/>
+      <c r="F106" s="296"/>
+      <c r="G106" s="296"/>
+      <c r="H106" s="296"/>
+      <c r="I106" s="296"/>
+      <c r="J106" s="296"/>
+      <c r="K106" s="296"/>
+      <c r="L106" s="296"/>
+      <c r="M106" s="296"/>
+      <c r="N106" s="296"/>
+      <c r="O106" s="296"/>
+      <c r="P106" s="296"/>
+      <c r="Q106" s="296"/>
+      <c r="R106" s="296"/>
+      <c r="S106" s="297"/>
     </row>
     <row r="107" spans="2:21" x14ac:dyDescent="0.3">
-      <c r="B107" s="250"/>
-      <c r="C107" s="251"/>
-      <c r="D107" s="251"/>
-      <c r="E107" s="251"/>
-      <c r="F107" s="251"/>
-      <c r="G107" s="251"/>
-      <c r="H107" s="251"/>
-      <c r="I107" s="251"/>
-      <c r="J107" s="251"/>
-      <c r="K107" s="251"/>
-      <c r="L107" s="251"/>
-      <c r="M107" s="251"/>
-      <c r="N107" s="251"/>
-      <c r="O107" s="251"/>
-      <c r="P107" s="251"/>
-      <c r="Q107" s="251"/>
-      <c r="R107" s="251"/>
-      <c r="S107" s="252"/>
+      <c r="B107" s="295"/>
+      <c r="C107" s="296"/>
+      <c r="D107" s="296"/>
+      <c r="E107" s="296"/>
+      <c r="F107" s="296"/>
+      <c r="G107" s="296"/>
+      <c r="H107" s="296"/>
+      <c r="I107" s="296"/>
+      <c r="J107" s="296"/>
+      <c r="K107" s="296"/>
+      <c r="L107" s="296"/>
+      <c r="M107" s="296"/>
+      <c r="N107" s="296"/>
+      <c r="O107" s="296"/>
+      <c r="P107" s="296"/>
+      <c r="Q107" s="296"/>
+      <c r="R107" s="296"/>
+      <c r="S107" s="297"/>
     </row>
     <row r="108" spans="2:21" x14ac:dyDescent="0.3">
-      <c r="B108" s="250"/>
-      <c r="C108" s="251"/>
-      <c r="D108" s="251"/>
-      <c r="E108" s="251"/>
-      <c r="F108" s="251"/>
-      <c r="G108" s="251"/>
-      <c r="H108" s="251"/>
-      <c r="I108" s="251"/>
-      <c r="J108" s="251"/>
-      <c r="K108" s="251"/>
-      <c r="L108" s="251"/>
-      <c r="M108" s="251"/>
-      <c r="N108" s="251"/>
-      <c r="O108" s="251"/>
-      <c r="P108" s="251"/>
-      <c r="Q108" s="251"/>
-      <c r="R108" s="251"/>
-      <c r="S108" s="252"/>
+      <c r="B108" s="295"/>
+      <c r="C108" s="296"/>
+      <c r="D108" s="296"/>
+      <c r="E108" s="296"/>
+      <c r="F108" s="296"/>
+      <c r="G108" s="296"/>
+      <c r="H108" s="296"/>
+      <c r="I108" s="296"/>
+      <c r="J108" s="296"/>
+      <c r="K108" s="296"/>
+      <c r="L108" s="296"/>
+      <c r="M108" s="296"/>
+      <c r="N108" s="296"/>
+      <c r="O108" s="296"/>
+      <c r="P108" s="296"/>
+      <c r="Q108" s="296"/>
+      <c r="R108" s="296"/>
+      <c r="S108" s="297"/>
     </row>
     <row r="109" spans="2:21" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B109" s="253"/>
-      <c r="C109" s="254"/>
-      <c r="D109" s="254"/>
-      <c r="E109" s="254"/>
-      <c r="F109" s="254"/>
-      <c r="G109" s="254"/>
-      <c r="H109" s="254"/>
-      <c r="I109" s="254"/>
-      <c r="J109" s="254"/>
-      <c r="K109" s="254"/>
-      <c r="L109" s="254"/>
-      <c r="M109" s="254"/>
-      <c r="N109" s="254"/>
-      <c r="O109" s="254"/>
-      <c r="P109" s="254"/>
-      <c r="Q109" s="254"/>
-      <c r="R109" s="254"/>
-      <c r="S109" s="255"/>
+      <c r="B109" s="298"/>
+      <c r="C109" s="299"/>
+      <c r="D109" s="299"/>
+      <c r="E109" s="299"/>
+      <c r="F109" s="299"/>
+      <c r="G109" s="299"/>
+      <c r="H109" s="299"/>
+      <c r="I109" s="299"/>
+      <c r="J109" s="299"/>
+      <c r="K109" s="299"/>
+      <c r="L109" s="299"/>
+      <c r="M109" s="299"/>
+      <c r="N109" s="299"/>
+      <c r="O109" s="299"/>
+      <c r="P109" s="299"/>
+      <c r="Q109" s="299"/>
+      <c r="R109" s="299"/>
+      <c r="S109" s="300"/>
     </row>
     <row r="118" spans="2:20" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B118" s="256" t="s">
+      <c r="B118" s="301" t="s">
         <v>97</v>
       </c>
-      <c r="C118" s="256"/>
-      <c r="D118" s="256"/>
-      <c r="E118" s="256"/>
-      <c r="F118" s="256"/>
-      <c r="G118" s="256"/>
-      <c r="H118" s="256"/>
-      <c r="I118" s="256"/>
-      <c r="J118" s="256"/>
-      <c r="K118" s="256"/>
-      <c r="L118" s="256"/>
-      <c r="M118" s="256"/>
-      <c r="N118" s="256"/>
-      <c r="O118" s="256"/>
-      <c r="P118" s="256"/>
+      <c r="C118" s="301"/>
+      <c r="D118" s="301"/>
+      <c r="E118" s="301"/>
+      <c r="F118" s="301"/>
+      <c r="G118" s="301"/>
+      <c r="H118" s="301"/>
+      <c r="I118" s="301"/>
+      <c r="J118" s="301"/>
+      <c r="K118" s="301"/>
+      <c r="L118" s="301"/>
+      <c r="M118" s="301"/>
+      <c r="N118" s="301"/>
+      <c r="O118" s="301"/>
+      <c r="P118" s="301"/>
       <c r="Q118" s="131"/>
     </row>
     <row r="119" spans="2:20" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B119" s="120" t="s">
         <v>1</v>
       </c>
-      <c r="C119" s="230" t="s">
+      <c r="C119" s="229" t="s">
         <v>2</v>
       </c>
-      <c r="D119" s="230"/>
+      <c r="D119" s="229"/>
       <c r="E119" s="120" t="s">
         <v>3</v>
       </c>
@@ -8324,20 +8327,20 @@
       <c r="N119" s="120" t="s">
         <v>14</v>
       </c>
-      <c r="O119" s="230" t="s">
+      <c r="O119" s="229" t="s">
         <v>38</v>
       </c>
-      <c r="P119" s="230"/>
-      <c r="Q119" s="230"/>
+      <c r="P119" s="229"/>
+      <c r="Q119" s="229"/>
       <c r="T119" s="129" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="120" spans="2:20" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B120" s="233" t="s">
+      <c r="B120" s="226" t="s">
         <v>99</v>
       </c>
-      <c r="C120" s="257" t="s">
+      <c r="C120" s="251" t="s">
         <v>17</v>
       </c>
       <c r="D120" s="20" t="s">
@@ -8385,8 +8388,8 @@
       </c>
     </row>
     <row r="121" spans="2:20" x14ac:dyDescent="0.3">
-      <c r="B121" s="233"/>
-      <c r="C121" s="257"/>
+      <c r="B121" s="226"/>
+      <c r="C121" s="251"/>
       <c r="D121" s="20" t="s">
         <v>24</v>
       </c>
@@ -8468,78 +8471,78 @@
       <c r="Q123" s="7"/>
     </row>
     <row r="124" spans="2:20" x14ac:dyDescent="0.3">
-      <c r="B124" s="224" t="s">
+      <c r="B124" s="236" t="s">
         <v>35</v>
       </c>
-      <c r="C124" s="225"/>
-      <c r="D124" s="225"/>
-      <c r="E124" s="225"/>
-      <c r="F124" s="225"/>
-      <c r="G124" s="225"/>
-      <c r="H124" s="225"/>
-      <c r="I124" s="225"/>
-      <c r="J124" s="225"/>
-      <c r="K124" s="225"/>
-      <c r="L124" s="225"/>
-      <c r="M124" s="225"/>
-      <c r="N124" s="225"/>
-      <c r="O124" s="225"/>
-      <c r="P124" s="225"/>
-      <c r="Q124" s="226"/>
+      <c r="C124" s="237"/>
+      <c r="D124" s="237"/>
+      <c r="E124" s="237"/>
+      <c r="F124" s="237"/>
+      <c r="G124" s="237"/>
+      <c r="H124" s="237"/>
+      <c r="I124" s="237"/>
+      <c r="J124" s="237"/>
+      <c r="K124" s="237"/>
+      <c r="L124" s="237"/>
+      <c r="M124" s="237"/>
+      <c r="N124" s="237"/>
+      <c r="O124" s="237"/>
+      <c r="P124" s="237"/>
+      <c r="Q124" s="238"/>
     </row>
     <row r="125" spans="2:20" x14ac:dyDescent="0.3">
-      <c r="B125" s="224"/>
-      <c r="C125" s="225"/>
-      <c r="D125" s="225"/>
-      <c r="E125" s="225"/>
-      <c r="F125" s="225"/>
-      <c r="G125" s="225"/>
-      <c r="H125" s="225"/>
-      <c r="I125" s="225"/>
-      <c r="J125" s="225"/>
-      <c r="K125" s="225"/>
-      <c r="L125" s="225"/>
-      <c r="M125" s="225"/>
-      <c r="N125" s="225"/>
-      <c r="O125" s="225"/>
-      <c r="P125" s="225"/>
-      <c r="Q125" s="226"/>
+      <c r="B125" s="236"/>
+      <c r="C125" s="237"/>
+      <c r="D125" s="237"/>
+      <c r="E125" s="237"/>
+      <c r="F125" s="237"/>
+      <c r="G125" s="237"/>
+      <c r="H125" s="237"/>
+      <c r="I125" s="237"/>
+      <c r="J125" s="237"/>
+      <c r="K125" s="237"/>
+      <c r="L125" s="237"/>
+      <c r="M125" s="237"/>
+      <c r="N125" s="237"/>
+      <c r="O125" s="237"/>
+      <c r="P125" s="237"/>
+      <c r="Q125" s="238"/>
     </row>
     <row r="126" spans="2:20" x14ac:dyDescent="0.3">
-      <c r="B126" s="224"/>
-      <c r="C126" s="225"/>
-      <c r="D126" s="225"/>
-      <c r="E126" s="225"/>
-      <c r="F126" s="225"/>
-      <c r="G126" s="225"/>
-      <c r="H126" s="225"/>
-      <c r="I126" s="225"/>
-      <c r="J126" s="225"/>
-      <c r="K126" s="225"/>
-      <c r="L126" s="225"/>
-      <c r="M126" s="225"/>
-      <c r="N126" s="225"/>
-      <c r="O126" s="225"/>
-      <c r="P126" s="225"/>
-      <c r="Q126" s="226"/>
+      <c r="B126" s="236"/>
+      <c r="C126" s="237"/>
+      <c r="D126" s="237"/>
+      <c r="E126" s="237"/>
+      <c r="F126" s="237"/>
+      <c r="G126" s="237"/>
+      <c r="H126" s="237"/>
+      <c r="I126" s="237"/>
+      <c r="J126" s="237"/>
+      <c r="K126" s="237"/>
+      <c r="L126" s="237"/>
+      <c r="M126" s="237"/>
+      <c r="N126" s="237"/>
+      <c r="O126" s="237"/>
+      <c r="P126" s="237"/>
+      <c r="Q126" s="238"/>
     </row>
     <row r="127" spans="2:20" x14ac:dyDescent="0.3">
-      <c r="B127" s="227"/>
-      <c r="C127" s="228"/>
-      <c r="D127" s="228"/>
-      <c r="E127" s="228"/>
-      <c r="F127" s="228"/>
-      <c r="G127" s="228"/>
-      <c r="H127" s="228"/>
-      <c r="I127" s="228"/>
-      <c r="J127" s="228"/>
-      <c r="K127" s="228"/>
-      <c r="L127" s="228"/>
-      <c r="M127" s="228"/>
-      <c r="N127" s="228"/>
-      <c r="O127" s="228"/>
-      <c r="P127" s="228"/>
-      <c r="Q127" s="229"/>
+      <c r="B127" s="239"/>
+      <c r="C127" s="240"/>
+      <c r="D127" s="240"/>
+      <c r="E127" s="240"/>
+      <c r="F127" s="240"/>
+      <c r="G127" s="240"/>
+      <c r="H127" s="240"/>
+      <c r="I127" s="240"/>
+      <c r="J127" s="240"/>
+      <c r="K127" s="240"/>
+      <c r="L127" s="240"/>
+      <c r="M127" s="240"/>
+      <c r="N127" s="240"/>
+      <c r="O127" s="240"/>
+      <c r="P127" s="240"/>
+      <c r="Q127" s="241"/>
     </row>
     <row r="128" spans="2:20" x14ac:dyDescent="0.3">
       <c r="B128" s="35"/>
@@ -8584,10 +8587,10 @@
       <c r="B135" s="97" t="s">
         <v>1</v>
       </c>
-      <c r="C135" s="230" t="s">
+      <c r="C135" s="229" t="s">
         <v>2</v>
       </c>
-      <c r="D135" s="230"/>
+      <c r="D135" s="229"/>
       <c r="E135" s="120" t="s">
         <v>3</v>
       </c>
@@ -8684,7 +8687,7 @@
       <c r="B137" s="246" t="s">
         <v>106</v>
       </c>
-      <c r="C137" s="233" t="s">
+      <c r="C137" s="226" t="s">
         <v>31</v>
       </c>
       <c r="D137" s="117" t="s">
@@ -8735,7 +8738,7 @@
     </row>
     <row r="138" spans="2:20" x14ac:dyDescent="0.3">
       <c r="B138" s="246"/>
-      <c r="C138" s="233"/>
+      <c r="C138" s="226"/>
       <c r="D138" s="117" t="s">
         <v>24</v>
       </c>
@@ -8806,10 +8809,10 @@
       <c r="B142" s="97" t="s">
         <v>1</v>
       </c>
-      <c r="C142" s="230" t="s">
+      <c r="C142" s="229" t="s">
         <v>2</v>
       </c>
-      <c r="D142" s="230"/>
+      <c r="D142" s="229"/>
       <c r="E142" s="120" t="s">
         <v>3</v>
       </c>
@@ -8848,10 +8851,10 @@
       </c>
     </row>
     <row r="143" spans="2:20" x14ac:dyDescent="0.3">
-      <c r="B143" s="233" t="s">
+      <c r="B143" s="226" t="s">
         <v>108</v>
       </c>
-      <c r="C143" s="233" t="s">
+      <c r="C143" s="226" t="s">
         <v>17</v>
       </c>
       <c r="D143" s="117" t="s">
@@ -8897,8 +8900,8 @@
       </c>
     </row>
     <row r="144" spans="2:20" x14ac:dyDescent="0.3">
-      <c r="B144" s="233"/>
-      <c r="C144" s="233"/>
+      <c r="B144" s="226"/>
+      <c r="C144" s="226"/>
       <c r="D144" s="117" t="s">
         <v>24</v>
       </c>
@@ -8942,10 +8945,10 @@
       </c>
     </row>
     <row r="145" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B145" s="233" t="s">
+      <c r="B145" s="226" t="s">
         <v>110</v>
       </c>
-      <c r="C145" s="233" t="s">
+      <c r="C145" s="226" t="s">
         <v>31</v>
       </c>
       <c r="D145" s="117" t="s">
@@ -8991,8 +8994,8 @@
       </c>
     </row>
     <row r="146" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B146" s="233"/>
-      <c r="C146" s="233"/>
+      <c r="B146" s="226"/>
+      <c r="C146" s="226"/>
       <c r="D146" s="117" t="s">
         <v>24</v>
       </c>
@@ -9062,78 +9065,78 @@
       <c r="Q148" s="7"/>
     </row>
     <row r="149" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B149" s="224" t="s">
+      <c r="B149" s="236" t="s">
         <v>35</v>
       </c>
-      <c r="C149" s="225"/>
-      <c r="D149" s="225"/>
-      <c r="E149" s="225"/>
-      <c r="F149" s="225"/>
-      <c r="G149" s="225"/>
-      <c r="H149" s="225"/>
-      <c r="I149" s="225"/>
-      <c r="J149" s="225"/>
-      <c r="K149" s="225"/>
-      <c r="L149" s="225"/>
-      <c r="M149" s="225"/>
-      <c r="N149" s="225"/>
-      <c r="O149" s="225"/>
-      <c r="P149" s="225"/>
-      <c r="Q149" s="226"/>
+      <c r="C149" s="237"/>
+      <c r="D149" s="237"/>
+      <c r="E149" s="237"/>
+      <c r="F149" s="237"/>
+      <c r="G149" s="237"/>
+      <c r="H149" s="237"/>
+      <c r="I149" s="237"/>
+      <c r="J149" s="237"/>
+      <c r="K149" s="237"/>
+      <c r="L149" s="237"/>
+      <c r="M149" s="237"/>
+      <c r="N149" s="237"/>
+      <c r="O149" s="237"/>
+      <c r="P149" s="237"/>
+      <c r="Q149" s="238"/>
     </row>
     <row r="150" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B150" s="224"/>
-      <c r="C150" s="225"/>
-      <c r="D150" s="225"/>
-      <c r="E150" s="225"/>
-      <c r="F150" s="225"/>
-      <c r="G150" s="225"/>
-      <c r="H150" s="225"/>
-      <c r="I150" s="225"/>
-      <c r="J150" s="225"/>
-      <c r="K150" s="225"/>
-      <c r="L150" s="225"/>
-      <c r="M150" s="225"/>
-      <c r="N150" s="225"/>
-      <c r="O150" s="225"/>
-      <c r="P150" s="225"/>
-      <c r="Q150" s="226"/>
+      <c r="B150" s="236"/>
+      <c r="C150" s="237"/>
+      <c r="D150" s="237"/>
+      <c r="E150" s="237"/>
+      <c r="F150" s="237"/>
+      <c r="G150" s="237"/>
+      <c r="H150" s="237"/>
+      <c r="I150" s="237"/>
+      <c r="J150" s="237"/>
+      <c r="K150" s="237"/>
+      <c r="L150" s="237"/>
+      <c r="M150" s="237"/>
+      <c r="N150" s="237"/>
+      <c r="O150" s="237"/>
+      <c r="P150" s="237"/>
+      <c r="Q150" s="238"/>
     </row>
     <row r="151" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B151" s="224"/>
-      <c r="C151" s="225"/>
-      <c r="D151" s="225"/>
-      <c r="E151" s="225"/>
-      <c r="F151" s="225"/>
-      <c r="G151" s="225"/>
-      <c r="H151" s="225"/>
-      <c r="I151" s="225"/>
-      <c r="J151" s="225"/>
-      <c r="K151" s="225"/>
-      <c r="L151" s="225"/>
-      <c r="M151" s="225"/>
-      <c r="N151" s="225"/>
-      <c r="O151" s="225"/>
-      <c r="P151" s="225"/>
-      <c r="Q151" s="226"/>
+      <c r="B151" s="236"/>
+      <c r="C151" s="237"/>
+      <c r="D151" s="237"/>
+      <c r="E151" s="237"/>
+      <c r="F151" s="237"/>
+      <c r="G151" s="237"/>
+      <c r="H151" s="237"/>
+      <c r="I151" s="237"/>
+      <c r="J151" s="237"/>
+      <c r="K151" s="237"/>
+      <c r="L151" s="237"/>
+      <c r="M151" s="237"/>
+      <c r="N151" s="237"/>
+      <c r="O151" s="237"/>
+      <c r="P151" s="237"/>
+      <c r="Q151" s="238"/>
     </row>
     <row r="152" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B152" s="227"/>
-      <c r="C152" s="228"/>
-      <c r="D152" s="228"/>
-      <c r="E152" s="228"/>
-      <c r="F152" s="228"/>
-      <c r="G152" s="228"/>
-      <c r="H152" s="228"/>
-      <c r="I152" s="228"/>
-      <c r="J152" s="228"/>
-      <c r="K152" s="228"/>
-      <c r="L152" s="228"/>
-      <c r="M152" s="228"/>
-      <c r="N152" s="228"/>
-      <c r="O152" s="228"/>
-      <c r="P152" s="228"/>
-      <c r="Q152" s="229"/>
+      <c r="B152" s="239"/>
+      <c r="C152" s="240"/>
+      <c r="D152" s="240"/>
+      <c r="E152" s="240"/>
+      <c r="F152" s="240"/>
+      <c r="G152" s="240"/>
+      <c r="H152" s="240"/>
+      <c r="I152" s="240"/>
+      <c r="J152" s="240"/>
+      <c r="K152" s="240"/>
+      <c r="L152" s="240"/>
+      <c r="M152" s="240"/>
+      <c r="N152" s="240"/>
+      <c r="O152" s="240"/>
+      <c r="P152" s="240"/>
+      <c r="Q152" s="241"/>
     </row>
     <row r="154" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B154" s="35"/>
@@ -9176,10 +9179,10 @@
       <c r="B161" s="97" t="s">
         <v>1</v>
       </c>
-      <c r="C161" s="230" t="s">
+      <c r="C161" s="229" t="s">
         <v>2</v>
       </c>
-      <c r="D161" s="230"/>
+      <c r="D161" s="229"/>
       <c r="E161" s="120" t="s">
         <v>3</v>
       </c>
@@ -9221,7 +9224,7 @@
       <c r="B162" s="246" t="s">
         <v>112</v>
       </c>
-      <c r="C162" s="233" t="s">
+      <c r="C162" s="226" t="s">
         <v>113</v>
       </c>
       <c r="D162" s="117" t="s">
@@ -9257,7 +9260,7 @@
         <v>2738</v>
       </c>
       <c r="N162" s="94" t="s">
-        <v>104</v>
+        <v>242</v>
       </c>
       <c r="O162" s="215" t="s">
         <v>21</v>
@@ -9268,7 +9271,7 @@
     </row>
     <row r="163" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B163" s="246"/>
-      <c r="C163" s="233"/>
+      <c r="C163" s="226"/>
       <c r="D163" s="117" t="s">
         <v>24</v>
       </c>
@@ -9302,7 +9305,7 @@
         <v>3038</v>
       </c>
       <c r="N163" s="94" t="s">
-        <v>104</v>
+        <v>242</v>
       </c>
       <c r="O163" s="215" t="s">
         <v>21</v>
@@ -9332,78 +9335,78 @@
       <c r="Q165" s="7"/>
     </row>
     <row r="166" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B166" s="224" t="s">
+      <c r="B166" s="236" t="s">
         <v>35</v>
       </c>
-      <c r="C166" s="225"/>
-      <c r="D166" s="225"/>
-      <c r="E166" s="225"/>
-      <c r="F166" s="225"/>
-      <c r="G166" s="225"/>
-      <c r="H166" s="225"/>
-      <c r="I166" s="225"/>
-      <c r="J166" s="225"/>
-      <c r="K166" s="225"/>
-      <c r="L166" s="225"/>
-      <c r="M166" s="225"/>
-      <c r="N166" s="225"/>
-      <c r="O166" s="225"/>
-      <c r="P166" s="225"/>
-      <c r="Q166" s="226"/>
+      <c r="C166" s="237"/>
+      <c r="D166" s="237"/>
+      <c r="E166" s="237"/>
+      <c r="F166" s="237"/>
+      <c r="G166" s="237"/>
+      <c r="H166" s="237"/>
+      <c r="I166" s="237"/>
+      <c r="J166" s="237"/>
+      <c r="K166" s="237"/>
+      <c r="L166" s="237"/>
+      <c r="M166" s="237"/>
+      <c r="N166" s="237"/>
+      <c r="O166" s="237"/>
+      <c r="P166" s="237"/>
+      <c r="Q166" s="238"/>
     </row>
     <row r="167" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B167" s="224"/>
-      <c r="C167" s="225"/>
-      <c r="D167" s="225"/>
-      <c r="E167" s="225"/>
-      <c r="F167" s="225"/>
-      <c r="G167" s="225"/>
-      <c r="H167" s="225"/>
-      <c r="I167" s="225"/>
-      <c r="J167" s="225"/>
-      <c r="K167" s="225"/>
-      <c r="L167" s="225"/>
-      <c r="M167" s="225"/>
-      <c r="N167" s="225"/>
-      <c r="O167" s="225"/>
-      <c r="P167" s="225"/>
-      <c r="Q167" s="226"/>
+      <c r="B167" s="236"/>
+      <c r="C167" s="237"/>
+      <c r="D167" s="237"/>
+      <c r="E167" s="237"/>
+      <c r="F167" s="237"/>
+      <c r="G167" s="237"/>
+      <c r="H167" s="237"/>
+      <c r="I167" s="237"/>
+      <c r="J167" s="237"/>
+      <c r="K167" s="237"/>
+      <c r="L167" s="237"/>
+      <c r="M167" s="237"/>
+      <c r="N167" s="237"/>
+      <c r="O167" s="237"/>
+      <c r="P167" s="237"/>
+      <c r="Q167" s="238"/>
     </row>
     <row r="168" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B168" s="224"/>
-      <c r="C168" s="225"/>
-      <c r="D168" s="225"/>
-      <c r="E168" s="225"/>
-      <c r="F168" s="225"/>
-      <c r="G168" s="225"/>
-      <c r="H168" s="225"/>
-      <c r="I168" s="225"/>
-      <c r="J168" s="225"/>
-      <c r="K168" s="225"/>
-      <c r="L168" s="225"/>
-      <c r="M168" s="225"/>
-      <c r="N168" s="225"/>
-      <c r="O168" s="225"/>
-      <c r="P168" s="225"/>
-      <c r="Q168" s="226"/>
+      <c r="B168" s="236"/>
+      <c r="C168" s="237"/>
+      <c r="D168" s="237"/>
+      <c r="E168" s="237"/>
+      <c r="F168" s="237"/>
+      <c r="G168" s="237"/>
+      <c r="H168" s="237"/>
+      <c r="I168" s="237"/>
+      <c r="J168" s="237"/>
+      <c r="K168" s="237"/>
+      <c r="L168" s="237"/>
+      <c r="M168" s="237"/>
+      <c r="N168" s="237"/>
+      <c r="O168" s="237"/>
+      <c r="P168" s="237"/>
+      <c r="Q168" s="238"/>
     </row>
     <row r="169" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B169" s="227"/>
-      <c r="C169" s="228"/>
-      <c r="D169" s="228"/>
-      <c r="E169" s="228"/>
-      <c r="F169" s="228"/>
-      <c r="G169" s="228"/>
-      <c r="H169" s="228"/>
-      <c r="I169" s="228"/>
-      <c r="J169" s="228"/>
-      <c r="K169" s="228"/>
-      <c r="L169" s="228"/>
-      <c r="M169" s="228"/>
-      <c r="N169" s="228"/>
-      <c r="O169" s="228"/>
-      <c r="P169" s="228"/>
-      <c r="Q169" s="229"/>
+      <c r="B169" s="239"/>
+      <c r="C169" s="240"/>
+      <c r="D169" s="240"/>
+      <c r="E169" s="240"/>
+      <c r="F169" s="240"/>
+      <c r="G169" s="240"/>
+      <c r="H169" s="240"/>
+      <c r="I169" s="240"/>
+      <c r="J169" s="240"/>
+      <c r="K169" s="240"/>
+      <c r="L169" s="240"/>
+      <c r="M169" s="240"/>
+      <c r="N169" s="240"/>
+      <c r="O169" s="240"/>
+      <c r="P169" s="240"/>
+      <c r="Q169" s="241"/>
     </row>
     <row r="170" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B170" s="35"/>
@@ -9442,33 +9445,33 @@
       <c r="Q171" s="35"/>
     </row>
     <row r="173" spans="2:17" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B173" s="231" t="s">
+      <c r="B173" s="227" t="s">
         <v>114</v>
       </c>
-      <c r="C173" s="232"/>
-      <c r="D173" s="232"/>
-      <c r="E173" s="232"/>
-      <c r="F173" s="232"/>
-      <c r="G173" s="232"/>
-      <c r="H173" s="232"/>
-      <c r="I173" s="232"/>
-      <c r="J173" s="232"/>
-      <c r="K173" s="232"/>
-      <c r="L173" s="232"/>
-      <c r="M173" s="232"/>
-      <c r="N173" s="232"/>
-      <c r="O173" s="232"/>
-      <c r="P173" s="232"/>
-      <c r="Q173" s="232"/>
+      <c r="C173" s="228"/>
+      <c r="D173" s="228"/>
+      <c r="E173" s="228"/>
+      <c r="F173" s="228"/>
+      <c r="G173" s="228"/>
+      <c r="H173" s="228"/>
+      <c r="I173" s="228"/>
+      <c r="J173" s="228"/>
+      <c r="K173" s="228"/>
+      <c r="L173" s="228"/>
+      <c r="M173" s="228"/>
+      <c r="N173" s="228"/>
+      <c r="O173" s="228"/>
+      <c r="P173" s="228"/>
+      <c r="Q173" s="228"/>
     </row>
     <row r="174" spans="2:17" ht="43.2" x14ac:dyDescent="0.3">
       <c r="B174" s="97" t="s">
         <v>1</v>
       </c>
-      <c r="C174" s="230" t="s">
+      <c r="C174" s="229" t="s">
         <v>2</v>
       </c>
-      <c r="D174" s="230"/>
+      <c r="D174" s="229"/>
       <c r="E174" s="120" t="s">
         <v>3</v>
       </c>
@@ -9510,10 +9513,10 @@
       </c>
     </row>
     <row r="175" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B175" s="238" t="s">
+      <c r="B175" s="230" t="s">
         <v>120</v>
       </c>
-      <c r="C175" s="233" t="s">
+      <c r="C175" s="226" t="s">
         <v>31</v>
       </c>
       <c r="D175" s="117" t="s">
@@ -9562,8 +9565,8 @@
       </c>
     </row>
     <row r="176" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B176" s="239"/>
-      <c r="C176" s="233"/>
+      <c r="B176" s="231"/>
+      <c r="C176" s="226"/>
       <c r="D176" s="117" t="s">
         <v>24</v>
       </c>
@@ -9650,10 +9653,10 @@
       <c r="B187" s="97" t="s">
         <v>1</v>
       </c>
-      <c r="C187" s="230" t="s">
+      <c r="C187" s="229" t="s">
         <v>2</v>
       </c>
-      <c r="D187" s="230"/>
+      <c r="D187" s="229"/>
       <c r="E187" s="120" t="s">
         <v>3</v>
       </c>
@@ -9695,7 +9698,7 @@
       <c r="B188" s="246" t="s">
         <v>124</v>
       </c>
-      <c r="C188" s="233" t="s">
+      <c r="C188" s="226" t="s">
         <v>89</v>
       </c>
       <c r="D188" s="117" t="s">
@@ -9742,7 +9745,7 @@
     </row>
     <row r="189" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B189" s="246"/>
-      <c r="C189" s="233"/>
+      <c r="C189" s="226"/>
       <c r="D189" s="117" t="s">
         <v>24</v>
       </c>
@@ -9790,6 +9793,104 @@
     </row>
   </sheetData>
   <mergeCells count="122">
+    <mergeCell ref="B160:P160"/>
+    <mergeCell ref="C161:D161"/>
+    <mergeCell ref="B162:B163"/>
+    <mergeCell ref="C162:C163"/>
+    <mergeCell ref="B166:Q169"/>
+    <mergeCell ref="C142:D142"/>
+    <mergeCell ref="B145:B146"/>
+    <mergeCell ref="C145:C146"/>
+    <mergeCell ref="B149:Q152"/>
+    <mergeCell ref="B124:Q127"/>
+    <mergeCell ref="B134:P134"/>
+    <mergeCell ref="C135:D135"/>
+    <mergeCell ref="B137:B138"/>
+    <mergeCell ref="C137:C138"/>
+    <mergeCell ref="B141:P141"/>
+    <mergeCell ref="B143:B144"/>
+    <mergeCell ref="C143:C144"/>
+    <mergeCell ref="B105:S105"/>
+    <mergeCell ref="B106:S109"/>
+    <mergeCell ref="B118:P118"/>
+    <mergeCell ref="C119:D119"/>
+    <mergeCell ref="O119:Q119"/>
+    <mergeCell ref="B120:B121"/>
+    <mergeCell ref="C120:C121"/>
+    <mergeCell ref="O120:Q121"/>
+    <mergeCell ref="C101:D101"/>
+    <mergeCell ref="R101:S101"/>
+    <mergeCell ref="B102:B103"/>
+    <mergeCell ref="C102:C103"/>
+    <mergeCell ref="R102:S103"/>
+    <mergeCell ref="B96:S96"/>
+    <mergeCell ref="C97:D97"/>
+    <mergeCell ref="R97:S97"/>
+    <mergeCell ref="B98:B99"/>
+    <mergeCell ref="C98:C99"/>
+    <mergeCell ref="R98:S99"/>
+    <mergeCell ref="B94:B95"/>
+    <mergeCell ref="C94:C95"/>
+    <mergeCell ref="R94:S95"/>
+    <mergeCell ref="C89:D89"/>
+    <mergeCell ref="R89:S89"/>
+    <mergeCell ref="B90:B91"/>
+    <mergeCell ref="C90:C91"/>
+    <mergeCell ref="R90:S91"/>
+    <mergeCell ref="B100:S100"/>
+    <mergeCell ref="R86:S87"/>
+    <mergeCell ref="B80:S80"/>
+    <mergeCell ref="C81:D81"/>
+    <mergeCell ref="R81:S81"/>
+    <mergeCell ref="B82:B83"/>
+    <mergeCell ref="C82:C83"/>
+    <mergeCell ref="R82:S83"/>
+    <mergeCell ref="B92:S92"/>
+    <mergeCell ref="C93:D93"/>
+    <mergeCell ref="R93:S93"/>
+    <mergeCell ref="B88:S88"/>
+    <mergeCell ref="B173:Q173"/>
+    <mergeCell ref="R72:S73"/>
+    <mergeCell ref="B62:B63"/>
+    <mergeCell ref="C62:C63"/>
+    <mergeCell ref="B64:B65"/>
+    <mergeCell ref="C64:C65"/>
+    <mergeCell ref="R64:S65"/>
+    <mergeCell ref="R62:S63"/>
+    <mergeCell ref="R66:S67"/>
+    <mergeCell ref="B70:B71"/>
+    <mergeCell ref="C70:C71"/>
+    <mergeCell ref="B72:B73"/>
+    <mergeCell ref="C72:C73"/>
+    <mergeCell ref="R68:S71"/>
+    <mergeCell ref="B66:B67"/>
+    <mergeCell ref="C66:C67"/>
+    <mergeCell ref="B68:B69"/>
+    <mergeCell ref="C68:C69"/>
+    <mergeCell ref="B84:S84"/>
+    <mergeCell ref="C85:D85"/>
+    <mergeCell ref="R85:S85"/>
+    <mergeCell ref="B86:B87"/>
+    <mergeCell ref="C86:C87"/>
+    <mergeCell ref="B78:B79"/>
+    <mergeCell ref="C78:C79"/>
+    <mergeCell ref="C20:C21"/>
+    <mergeCell ref="B24:P27"/>
+    <mergeCell ref="O40:P40"/>
+    <mergeCell ref="B43:Q46"/>
+    <mergeCell ref="B56:S56"/>
+    <mergeCell ref="C57:D57"/>
+    <mergeCell ref="R57:S57"/>
+    <mergeCell ref="B58:B59"/>
+    <mergeCell ref="C58:C59"/>
+    <mergeCell ref="R58:S61"/>
+    <mergeCell ref="B60:B61"/>
+    <mergeCell ref="C60:C61"/>
+    <mergeCell ref="R74:S79"/>
+    <mergeCell ref="B74:B75"/>
+    <mergeCell ref="C74:C75"/>
+    <mergeCell ref="B76:B77"/>
+    <mergeCell ref="C76:C77"/>
     <mergeCell ref="B186:P186"/>
     <mergeCell ref="C187:D187"/>
     <mergeCell ref="B188:B189"/>
@@ -9814,104 +9915,6 @@
     <mergeCell ref="C16:C17"/>
     <mergeCell ref="B18:B21"/>
     <mergeCell ref="C18:C19"/>
-    <mergeCell ref="C78:C79"/>
-    <mergeCell ref="C20:C21"/>
-    <mergeCell ref="B24:P27"/>
-    <mergeCell ref="O40:P40"/>
-    <mergeCell ref="B43:Q46"/>
-    <mergeCell ref="B56:S56"/>
-    <mergeCell ref="C57:D57"/>
-    <mergeCell ref="R57:S57"/>
-    <mergeCell ref="B58:B59"/>
-    <mergeCell ref="C58:C59"/>
-    <mergeCell ref="R58:S61"/>
-    <mergeCell ref="B60:B61"/>
-    <mergeCell ref="C60:C61"/>
-    <mergeCell ref="R74:S79"/>
-    <mergeCell ref="B74:B75"/>
-    <mergeCell ref="C74:C75"/>
-    <mergeCell ref="B76:B77"/>
-    <mergeCell ref="C76:C77"/>
-    <mergeCell ref="B173:Q173"/>
-    <mergeCell ref="R72:S73"/>
-    <mergeCell ref="B62:B63"/>
-    <mergeCell ref="C62:C63"/>
-    <mergeCell ref="B64:B65"/>
-    <mergeCell ref="C64:C65"/>
-    <mergeCell ref="R64:S65"/>
-    <mergeCell ref="R62:S63"/>
-    <mergeCell ref="R66:S67"/>
-    <mergeCell ref="B70:B71"/>
-    <mergeCell ref="C70:C71"/>
-    <mergeCell ref="B72:B73"/>
-    <mergeCell ref="C72:C73"/>
-    <mergeCell ref="R68:S71"/>
-    <mergeCell ref="B66:B67"/>
-    <mergeCell ref="C66:C67"/>
-    <mergeCell ref="B68:B69"/>
-    <mergeCell ref="C68:C69"/>
-    <mergeCell ref="B84:S84"/>
-    <mergeCell ref="C85:D85"/>
-    <mergeCell ref="R85:S85"/>
-    <mergeCell ref="B86:B87"/>
-    <mergeCell ref="C86:C87"/>
-    <mergeCell ref="B78:B79"/>
-    <mergeCell ref="R86:S87"/>
-    <mergeCell ref="B80:S80"/>
-    <mergeCell ref="C81:D81"/>
-    <mergeCell ref="R81:S81"/>
-    <mergeCell ref="B82:B83"/>
-    <mergeCell ref="C82:C83"/>
-    <mergeCell ref="R82:S83"/>
-    <mergeCell ref="B92:S92"/>
-    <mergeCell ref="C93:D93"/>
-    <mergeCell ref="R93:S93"/>
-    <mergeCell ref="B88:S88"/>
-    <mergeCell ref="B94:B95"/>
-    <mergeCell ref="C94:C95"/>
-    <mergeCell ref="R94:S95"/>
-    <mergeCell ref="C89:D89"/>
-    <mergeCell ref="R89:S89"/>
-    <mergeCell ref="B90:B91"/>
-    <mergeCell ref="C90:C91"/>
-    <mergeCell ref="R90:S91"/>
-    <mergeCell ref="B100:S100"/>
-    <mergeCell ref="C101:D101"/>
-    <mergeCell ref="R101:S101"/>
-    <mergeCell ref="B102:B103"/>
-    <mergeCell ref="C102:C103"/>
-    <mergeCell ref="R102:S103"/>
-    <mergeCell ref="B96:S96"/>
-    <mergeCell ref="C97:D97"/>
-    <mergeCell ref="R97:S97"/>
-    <mergeCell ref="B98:B99"/>
-    <mergeCell ref="C98:C99"/>
-    <mergeCell ref="R98:S99"/>
-    <mergeCell ref="B124:Q127"/>
-    <mergeCell ref="B134:P134"/>
-    <mergeCell ref="C135:D135"/>
-    <mergeCell ref="B137:B138"/>
-    <mergeCell ref="C137:C138"/>
-    <mergeCell ref="B141:P141"/>
-    <mergeCell ref="B143:B144"/>
-    <mergeCell ref="C143:C144"/>
-    <mergeCell ref="B105:S105"/>
-    <mergeCell ref="B106:S109"/>
-    <mergeCell ref="B118:P118"/>
-    <mergeCell ref="C119:D119"/>
-    <mergeCell ref="O119:Q119"/>
-    <mergeCell ref="B120:B121"/>
-    <mergeCell ref="C120:C121"/>
-    <mergeCell ref="O120:Q121"/>
-    <mergeCell ref="B160:P160"/>
-    <mergeCell ref="C161:D161"/>
-    <mergeCell ref="B162:B163"/>
-    <mergeCell ref="C162:C163"/>
-    <mergeCell ref="B166:Q169"/>
-    <mergeCell ref="C142:D142"/>
-    <mergeCell ref="B145:B146"/>
-    <mergeCell ref="C145:C146"/>
-    <mergeCell ref="B149:Q152"/>
   </mergeCells>
   <phoneticPr fontId="14" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -9950,33 +9953,33 @@
   <sheetData>
     <row r="6" spans="2:17" ht="12" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="9" spans="2:17" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B9" s="232" t="s">
+      <c r="B9" s="228" t="s">
         <v>126</v>
       </c>
-      <c r="C9" s="232"/>
-      <c r="D9" s="232"/>
-      <c r="E9" s="232"/>
-      <c r="F9" s="232"/>
-      <c r="G9" s="232"/>
-      <c r="H9" s="232"/>
-      <c r="I9" s="232"/>
-      <c r="J9" s="232"/>
-      <c r="K9" s="232"/>
-      <c r="L9" s="232"/>
-      <c r="M9" s="232"/>
-      <c r="N9" s="232"/>
-      <c r="O9" s="232"/>
-      <c r="P9" s="232"/>
-      <c r="Q9" s="232"/>
+      <c r="C9" s="228"/>
+      <c r="D9" s="228"/>
+      <c r="E9" s="228"/>
+      <c r="F9" s="228"/>
+      <c r="G9" s="228"/>
+      <c r="H9" s="228"/>
+      <c r="I9" s="228"/>
+      <c r="J9" s="228"/>
+      <c r="K9" s="228"/>
+      <c r="L9" s="228"/>
+      <c r="M9" s="228"/>
+      <c r="N9" s="228"/>
+      <c r="O9" s="228"/>
+      <c r="P9" s="228"/>
+      <c r="Q9" s="228"/>
     </row>
     <row r="10" spans="2:17" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B10" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C10" s="314" t="s">
+      <c r="C10" s="317" t="s">
         <v>2</v>
       </c>
-      <c r="D10" s="314"/>
+      <c r="D10" s="317"/>
       <c r="E10" s="8" t="s">
         <v>3</v>
       </c>
@@ -10018,10 +10021,10 @@
       </c>
     </row>
     <row r="11" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B11" s="257" t="s">
+      <c r="B11" s="251" t="s">
         <v>16</v>
       </c>
-      <c r="C11" s="257" t="s">
+      <c r="C11" s="251" t="s">
         <v>120</v>
       </c>
       <c r="D11" s="53" t="s">
@@ -10071,8 +10074,8 @@
       </c>
     </row>
     <row r="12" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B12" s="257"/>
-      <c r="C12" s="257"/>
+      <c r="B12" s="251"/>
+      <c r="C12" s="251"/>
       <c r="D12" s="53" t="s">
         <v>24</v>
       </c>
@@ -10120,10 +10123,10 @@
       </c>
     </row>
     <row r="13" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B13" s="257" t="s">
+      <c r="B13" s="251" t="s">
         <v>26</v>
       </c>
-      <c r="C13" s="257" t="s">
+      <c r="C13" s="251" t="s">
         <v>120</v>
       </c>
       <c r="D13" s="53" t="s">
@@ -10173,8 +10176,8 @@
       </c>
     </row>
     <row r="14" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B14" s="257"/>
-      <c r="C14" s="257"/>
+      <c r="B14" s="251"/>
+      <c r="C14" s="251"/>
       <c r="D14" s="53" t="s">
         <v>24</v>
       </c>
@@ -10222,10 +10225,10 @@
       </c>
     </row>
     <row r="15" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B15" s="297" t="s">
+      <c r="B15" s="249" t="s">
         <v>28</v>
       </c>
-      <c r="C15" s="257" t="s">
+      <c r="C15" s="251" t="s">
         <v>120</v>
       </c>
       <c r="D15" s="53" t="s">
@@ -10275,8 +10278,8 @@
       </c>
     </row>
     <row r="16" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B16" s="297"/>
-      <c r="C16" s="257"/>
+      <c r="B16" s="249"/>
+      <c r="C16" s="251"/>
       <c r="D16" s="53" t="s">
         <v>24</v>
       </c>
@@ -10324,10 +10327,10 @@
       </c>
     </row>
     <row r="17" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="B17" s="257" t="s">
+      <c r="B17" s="251" t="s">
         <v>132</v>
       </c>
-      <c r="C17" s="257" t="s">
+      <c r="C17" s="251" t="s">
         <v>120</v>
       </c>
       <c r="D17" s="53" t="s">
@@ -10377,8 +10380,8 @@
       </c>
     </row>
     <row r="18" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="B18" s="257"/>
-      <c r="C18" s="257"/>
+      <c r="B18" s="251"/>
+      <c r="C18" s="251"/>
       <c r="D18" s="53" t="s">
         <v>24</v>
       </c>
@@ -10443,103 +10446,103 @@
       <c r="Q19" s="34"/>
     </row>
     <row r="20" spans="2:18" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B20" s="303" t="s">
+      <c r="B20" s="320" t="s">
         <v>34</v>
       </c>
-      <c r="C20" s="304"/>
-      <c r="D20" s="304"/>
-      <c r="E20" s="304"/>
-      <c r="F20" s="304"/>
-      <c r="G20" s="304"/>
-      <c r="H20" s="304"/>
-      <c r="I20" s="304"/>
-      <c r="J20" s="304"/>
-      <c r="K20" s="304"/>
-      <c r="L20" s="304"/>
-      <c r="M20" s="304"/>
-      <c r="N20" s="304"/>
-      <c r="O20" s="304"/>
-      <c r="P20" s="304"/>
-      <c r="Q20" s="304"/>
-      <c r="R20" s="305"/>
+      <c r="C20" s="321"/>
+      <c r="D20" s="321"/>
+      <c r="E20" s="321"/>
+      <c r="F20" s="321"/>
+      <c r="G20" s="321"/>
+      <c r="H20" s="321"/>
+      <c r="I20" s="321"/>
+      <c r="J20" s="321"/>
+      <c r="K20" s="321"/>
+      <c r="L20" s="321"/>
+      <c r="M20" s="321"/>
+      <c r="N20" s="321"/>
+      <c r="O20" s="321"/>
+      <c r="P20" s="321"/>
+      <c r="Q20" s="321"/>
+      <c r="R20" s="322"/>
     </row>
     <row r="21" spans="2:18" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B21" s="306" t="s">
+      <c r="B21" s="323" t="s">
         <v>35</v>
       </c>
-      <c r="C21" s="307"/>
-      <c r="D21" s="307"/>
-      <c r="E21" s="307"/>
-      <c r="F21" s="307"/>
-      <c r="G21" s="307"/>
-      <c r="H21" s="307"/>
-      <c r="I21" s="307"/>
-      <c r="J21" s="307"/>
-      <c r="K21" s="307"/>
-      <c r="L21" s="307"/>
-      <c r="M21" s="307"/>
-      <c r="N21" s="307"/>
-      <c r="O21" s="307"/>
-      <c r="P21" s="307"/>
-      <c r="Q21" s="307"/>
-      <c r="R21" s="308"/>
+      <c r="C21" s="324"/>
+      <c r="D21" s="324"/>
+      <c r="E21" s="324"/>
+      <c r="F21" s="324"/>
+      <c r="G21" s="324"/>
+      <c r="H21" s="324"/>
+      <c r="I21" s="324"/>
+      <c r="J21" s="324"/>
+      <c r="K21" s="324"/>
+      <c r="L21" s="324"/>
+      <c r="M21" s="324"/>
+      <c r="N21" s="324"/>
+      <c r="O21" s="324"/>
+      <c r="P21" s="324"/>
+      <c r="Q21" s="324"/>
+      <c r="R21" s="325"/>
     </row>
     <row r="22" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="B22" s="309"/>
-      <c r="C22" s="251"/>
-      <c r="D22" s="251"/>
-      <c r="E22" s="251"/>
-      <c r="F22" s="251"/>
-      <c r="G22" s="251"/>
-      <c r="H22" s="251"/>
-      <c r="I22" s="251"/>
-      <c r="J22" s="251"/>
-      <c r="K22" s="251"/>
-      <c r="L22" s="251"/>
-      <c r="M22" s="251"/>
-      <c r="N22" s="251"/>
-      <c r="O22" s="251"/>
-      <c r="P22" s="251"/>
-      <c r="Q22" s="251"/>
-      <c r="R22" s="310"/>
+      <c r="B22" s="326"/>
+      <c r="C22" s="296"/>
+      <c r="D22" s="296"/>
+      <c r="E22" s="296"/>
+      <c r="F22" s="296"/>
+      <c r="G22" s="296"/>
+      <c r="H22" s="296"/>
+      <c r="I22" s="296"/>
+      <c r="J22" s="296"/>
+      <c r="K22" s="296"/>
+      <c r="L22" s="296"/>
+      <c r="M22" s="296"/>
+      <c r="N22" s="296"/>
+      <c r="O22" s="296"/>
+      <c r="P22" s="296"/>
+      <c r="Q22" s="296"/>
+      <c r="R22" s="327"/>
     </row>
     <row r="23" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="B23" s="309"/>
-      <c r="C23" s="251"/>
-      <c r="D23" s="251"/>
-      <c r="E23" s="251"/>
-      <c r="F23" s="251"/>
-      <c r="G23" s="251"/>
-      <c r="H23" s="251"/>
-      <c r="I23" s="251"/>
-      <c r="J23" s="251"/>
-      <c r="K23" s="251"/>
-      <c r="L23" s="251"/>
-      <c r="M23" s="251"/>
-      <c r="N23" s="251"/>
-      <c r="O23" s="251"/>
-      <c r="P23" s="251"/>
-      <c r="Q23" s="251"/>
-      <c r="R23" s="310"/>
+      <c r="B23" s="326"/>
+      <c r="C23" s="296"/>
+      <c r="D23" s="296"/>
+      <c r="E23" s="296"/>
+      <c r="F23" s="296"/>
+      <c r="G23" s="296"/>
+      <c r="H23" s="296"/>
+      <c r="I23" s="296"/>
+      <c r="J23" s="296"/>
+      <c r="K23" s="296"/>
+      <c r="L23" s="296"/>
+      <c r="M23" s="296"/>
+      <c r="N23" s="296"/>
+      <c r="O23" s="296"/>
+      <c r="P23" s="296"/>
+      <c r="Q23" s="296"/>
+      <c r="R23" s="327"/>
     </row>
     <row r="24" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="B24" s="311"/>
-      <c r="C24" s="312"/>
-      <c r="D24" s="312"/>
-      <c r="E24" s="312"/>
-      <c r="F24" s="312"/>
-      <c r="G24" s="312"/>
-      <c r="H24" s="312"/>
-      <c r="I24" s="312"/>
-      <c r="J24" s="312"/>
-      <c r="K24" s="312"/>
-      <c r="L24" s="312"/>
-      <c r="M24" s="312"/>
-      <c r="N24" s="312"/>
-      <c r="O24" s="312"/>
-      <c r="P24" s="312"/>
-      <c r="Q24" s="312"/>
-      <c r="R24" s="313"/>
+      <c r="B24" s="328"/>
+      <c r="C24" s="329"/>
+      <c r="D24" s="329"/>
+      <c r="E24" s="329"/>
+      <c r="F24" s="329"/>
+      <c r="G24" s="329"/>
+      <c r="H24" s="329"/>
+      <c r="I24" s="329"/>
+      <c r="J24" s="329"/>
+      <c r="K24" s="329"/>
+      <c r="L24" s="329"/>
+      <c r="M24" s="329"/>
+      <c r="N24" s="329"/>
+      <c r="O24" s="329"/>
+      <c r="P24" s="329"/>
+      <c r="Q24" s="329"/>
+      <c r="R24" s="330"/>
     </row>
     <row r="25" spans="2:18" x14ac:dyDescent="0.3">
       <c r="B25" s="27"/>
@@ -10695,34 +10698,34 @@
       <c r="Q33" s="34"/>
     </row>
     <row r="34" spans="2:21" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B34" s="299" t="s">
+      <c r="B34" s="252" t="s">
         <v>134</v>
       </c>
-      <c r="C34" s="299"/>
-      <c r="D34" s="299"/>
-      <c r="E34" s="299"/>
-      <c r="F34" s="299"/>
-      <c r="G34" s="299"/>
-      <c r="H34" s="299"/>
-      <c r="I34" s="299"/>
-      <c r="J34" s="299"/>
-      <c r="K34" s="299"/>
-      <c r="L34" s="299"/>
-      <c r="M34" s="299"/>
-      <c r="N34" s="299"/>
-      <c r="O34" s="299"/>
-      <c r="P34" s="299"/>
-      <c r="Q34" s="299"/>
-      <c r="R34" s="299"/>
+      <c r="C34" s="252"/>
+      <c r="D34" s="252"/>
+      <c r="E34" s="252"/>
+      <c r="F34" s="252"/>
+      <c r="G34" s="252"/>
+      <c r="H34" s="252"/>
+      <c r="I34" s="252"/>
+      <c r="J34" s="252"/>
+      <c r="K34" s="252"/>
+      <c r="L34" s="252"/>
+      <c r="M34" s="252"/>
+      <c r="N34" s="252"/>
+      <c r="O34" s="252"/>
+      <c r="P34" s="252"/>
+      <c r="Q34" s="252"/>
+      <c r="R34" s="252"/>
     </row>
     <row r="35" spans="2:21" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B35" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C35" s="314" t="s">
+      <c r="C35" s="317" t="s">
         <v>2</v>
       </c>
-      <c r="D35" s="314"/>
+      <c r="D35" s="317"/>
       <c r="E35" s="127" t="s">
         <v>135</v>
       </c>
@@ -10756,20 +10759,20 @@
       <c r="O35" s="124" t="s">
         <v>127</v>
       </c>
-      <c r="P35" s="230" t="s">
+      <c r="P35" s="229" t="s">
         <v>38</v>
       </c>
-      <c r="Q35" s="230"/>
-      <c r="R35" s="230"/>
+      <c r="Q35" s="229"/>
+      <c r="R35" s="229"/>
       <c r="U35" s="120" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="36" spans="2:21" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B36" s="300" t="s">
+      <c r="B36" s="253" t="s">
         <v>137</v>
       </c>
-      <c r="C36" s="257" t="s">
+      <c r="C36" s="251" t="s">
         <v>120</v>
       </c>
       <c r="D36" s="53" t="s">
@@ -10811,18 +10814,18 @@
       <c r="O36" s="53" t="s">
         <v>129</v>
       </c>
-      <c r="P36" s="281" t="s">
+      <c r="P36" s="254" t="s">
         <v>139</v>
       </c>
-      <c r="Q36" s="327"/>
-      <c r="R36" s="282"/>
+      <c r="Q36" s="312"/>
+      <c r="R36" s="255"/>
       <c r="U36" s="53" t="s">
         <v>140</v>
       </c>
     </row>
     <row r="37" spans="2:21" x14ac:dyDescent="0.3">
-      <c r="B37" s="300"/>
-      <c r="C37" s="257"/>
+      <c r="B37" s="253"/>
+      <c r="C37" s="251"/>
       <c r="D37" s="53" t="s">
         <v>24</v>
       </c>
@@ -10862,9 +10865,9 @@
       <c r="O37" s="53" t="s">
         <v>129</v>
       </c>
-      <c r="P37" s="328"/>
-      <c r="Q37" s="329"/>
-      <c r="R37" s="330"/>
+      <c r="P37" s="313"/>
+      <c r="Q37" s="314"/>
+      <c r="R37" s="315"/>
       <c r="U37" s="53" t="s">
         <v>140</v>
       </c>
@@ -10914,11 +10917,11 @@
       <c r="O38" s="53" t="s">
         <v>143</v>
       </c>
-      <c r="P38" s="320" t="s">
+      <c r="P38" s="309" t="s">
         <v>144</v>
       </c>
-      <c r="Q38" s="321"/>
-      <c r="R38" s="322"/>
+      <c r="Q38" s="310"/>
+      <c r="R38" s="311"/>
       <c r="U38" s="53" t="s">
         <v>145</v>
       </c>
@@ -10969,11 +10972,11 @@
       <c r="O39" s="53" t="s">
         <v>129</v>
       </c>
-      <c r="P39" s="320" t="s">
+      <c r="P39" s="309" t="s">
         <v>144</v>
       </c>
-      <c r="Q39" s="321"/>
-      <c r="R39" s="322"/>
+      <c r="Q39" s="310"/>
+      <c r="R39" s="311"/>
       <c r="U39" s="53" t="s">
         <v>140</v>
       </c>
@@ -11019,86 +11022,86 @@
       <c r="S41" s="7"/>
     </row>
     <row r="42" spans="2:21" x14ac:dyDescent="0.3">
-      <c r="B42" s="224" t="s">
+      <c r="B42" s="236" t="s">
         <v>35</v>
       </c>
-      <c r="C42" s="224"/>
-      <c r="D42" s="224"/>
-      <c r="E42" s="224"/>
-      <c r="F42" s="224"/>
-      <c r="G42" s="224"/>
-      <c r="H42" s="224"/>
-      <c r="I42" s="224"/>
-      <c r="J42" s="224"/>
-      <c r="K42" s="224"/>
-      <c r="L42" s="224"/>
-      <c r="M42" s="224"/>
-      <c r="N42" s="224"/>
-      <c r="O42" s="224"/>
-      <c r="P42" s="224"/>
-      <c r="Q42" s="224"/>
-      <c r="R42" s="224"/>
-      <c r="S42" s="224"/>
+      <c r="C42" s="236"/>
+      <c r="D42" s="236"/>
+      <c r="E42" s="236"/>
+      <c r="F42" s="236"/>
+      <c r="G42" s="236"/>
+      <c r="H42" s="236"/>
+      <c r="I42" s="236"/>
+      <c r="J42" s="236"/>
+      <c r="K42" s="236"/>
+      <c r="L42" s="236"/>
+      <c r="M42" s="236"/>
+      <c r="N42" s="236"/>
+      <c r="O42" s="236"/>
+      <c r="P42" s="236"/>
+      <c r="Q42" s="236"/>
+      <c r="R42" s="236"/>
+      <c r="S42" s="236"/>
     </row>
     <row r="43" spans="2:21" x14ac:dyDescent="0.3">
-      <c r="B43" s="224"/>
-      <c r="C43" s="224"/>
-      <c r="D43" s="224"/>
-      <c r="E43" s="224"/>
-      <c r="F43" s="224"/>
-      <c r="G43" s="224"/>
-      <c r="H43" s="224"/>
-      <c r="I43" s="224"/>
-      <c r="J43" s="224"/>
-      <c r="K43" s="224"/>
-      <c r="L43" s="224"/>
-      <c r="M43" s="224"/>
-      <c r="N43" s="224"/>
-      <c r="O43" s="224"/>
-      <c r="P43" s="224"/>
-      <c r="Q43" s="224"/>
-      <c r="R43" s="224"/>
-      <c r="S43" s="224"/>
+      <c r="B43" s="236"/>
+      <c r="C43" s="236"/>
+      <c r="D43" s="236"/>
+      <c r="E43" s="236"/>
+      <c r="F43" s="236"/>
+      <c r="G43" s="236"/>
+      <c r="H43" s="236"/>
+      <c r="I43" s="236"/>
+      <c r="J43" s="236"/>
+      <c r="K43" s="236"/>
+      <c r="L43" s="236"/>
+      <c r="M43" s="236"/>
+      <c r="N43" s="236"/>
+      <c r="O43" s="236"/>
+      <c r="P43" s="236"/>
+      <c r="Q43" s="236"/>
+      <c r="R43" s="236"/>
+      <c r="S43" s="236"/>
     </row>
     <row r="44" spans="2:21" x14ac:dyDescent="0.3">
-      <c r="B44" s="224"/>
-      <c r="C44" s="224"/>
-      <c r="D44" s="224"/>
-      <c r="E44" s="224"/>
-      <c r="F44" s="224"/>
-      <c r="G44" s="224"/>
-      <c r="H44" s="224"/>
-      <c r="I44" s="224"/>
-      <c r="J44" s="224"/>
-      <c r="K44" s="224"/>
-      <c r="L44" s="224"/>
-      <c r="M44" s="224"/>
-      <c r="N44" s="224"/>
-      <c r="O44" s="224"/>
-      <c r="P44" s="224"/>
-      <c r="Q44" s="224"/>
-      <c r="R44" s="224"/>
-      <c r="S44" s="224"/>
+      <c r="B44" s="236"/>
+      <c r="C44" s="236"/>
+      <c r="D44" s="236"/>
+      <c r="E44" s="236"/>
+      <c r="F44" s="236"/>
+      <c r="G44" s="236"/>
+      <c r="H44" s="236"/>
+      <c r="I44" s="236"/>
+      <c r="J44" s="236"/>
+      <c r="K44" s="236"/>
+      <c r="L44" s="236"/>
+      <c r="M44" s="236"/>
+      <c r="N44" s="236"/>
+      <c r="O44" s="236"/>
+      <c r="P44" s="236"/>
+      <c r="Q44" s="236"/>
+      <c r="R44" s="236"/>
+      <c r="S44" s="236"/>
     </row>
     <row r="45" spans="2:21" x14ac:dyDescent="0.3">
-      <c r="B45" s="227"/>
-      <c r="C45" s="227"/>
-      <c r="D45" s="227"/>
-      <c r="E45" s="227"/>
-      <c r="F45" s="227"/>
-      <c r="G45" s="227"/>
-      <c r="H45" s="227"/>
-      <c r="I45" s="227"/>
-      <c r="J45" s="227"/>
-      <c r="K45" s="227"/>
-      <c r="L45" s="227"/>
-      <c r="M45" s="227"/>
-      <c r="N45" s="227"/>
-      <c r="O45" s="227"/>
-      <c r="P45" s="227"/>
-      <c r="Q45" s="227"/>
-      <c r="R45" s="227"/>
-      <c r="S45" s="227"/>
+      <c r="B45" s="239"/>
+      <c r="C45" s="239"/>
+      <c r="D45" s="239"/>
+      <c r="E45" s="239"/>
+      <c r="F45" s="239"/>
+      <c r="G45" s="239"/>
+      <c r="H45" s="239"/>
+      <c r="I45" s="239"/>
+      <c r="J45" s="239"/>
+      <c r="K45" s="239"/>
+      <c r="L45" s="239"/>
+      <c r="M45" s="239"/>
+      <c r="N45" s="239"/>
+      <c r="O45" s="239"/>
+      <c r="P45" s="239"/>
+      <c r="Q45" s="239"/>
+      <c r="R45" s="239"/>
+      <c r="S45" s="239"/>
     </row>
     <row r="46" spans="2:21" x14ac:dyDescent="0.3">
       <c r="B46" s="42"/>
@@ -11279,10 +11282,10 @@
       <c r="B56" s="97" t="s">
         <v>1</v>
       </c>
-      <c r="C56" s="230" t="s">
+      <c r="C56" s="229" t="s">
         <v>2</v>
       </c>
-      <c r="D56" s="230"/>
+      <c r="D56" s="229"/>
       <c r="E56" s="120" t="s">
         <v>3</v>
       </c>
@@ -11327,7 +11330,7 @@
       </c>
     </row>
     <row r="57" spans="2:21" ht="22.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B57" s="315" t="s">
+      <c r="B57" s="308" t="s">
         <v>152</v>
       </c>
       <c r="C57" s="316" t="s">
@@ -11372,7 +11375,7 @@
       <c r="O57" s="208" t="s">
         <v>60</v>
       </c>
-      <c r="P57" s="318" t="s">
+      <c r="P57" s="302" t="s">
         <v>81</v>
       </c>
       <c r="Q57" s="143" t="s">
@@ -11383,7 +11386,7 @@
       </c>
     </row>
     <row r="58" spans="2:21" x14ac:dyDescent="0.3">
-      <c r="B58" s="315"/>
+      <c r="B58" s="308"/>
       <c r="C58" s="316"/>
       <c r="D58" s="143" t="s">
         <v>24</v>
@@ -11424,7 +11427,7 @@
       <c r="O58" s="208" t="s">
         <v>60</v>
       </c>
-      <c r="P58" s="319"/>
+      <c r="P58" s="303"/>
       <c r="Q58" s="143" t="s">
         <v>130</v>
       </c>
@@ -11433,7 +11436,7 @@
       </c>
     </row>
     <row r="59" spans="2:21" x14ac:dyDescent="0.3">
-      <c r="B59" s="315" t="s">
+      <c r="B59" s="308" t="s">
         <v>154</v>
       </c>
       <c r="C59" s="316" t="s">
@@ -11478,14 +11481,14 @@
       <c r="O59" s="208" t="s">
         <v>60</v>
       </c>
-      <c r="P59" s="319"/>
+      <c r="P59" s="303"/>
       <c r="Q59" s="143" t="s">
         <v>130</v>
       </c>
       <c r="U59" s="53"/>
     </row>
     <row r="60" spans="2:21" ht="28.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B60" s="315"/>
+      <c r="B60" s="308"/>
       <c r="C60" s="316"/>
       <c r="D60" s="143" t="s">
         <v>24</v>
@@ -11526,14 +11529,14 @@
       <c r="O60" s="208" t="s">
         <v>60</v>
       </c>
-      <c r="P60" s="323"/>
+      <c r="P60" s="304"/>
       <c r="Q60" s="143" t="s">
         <v>130</v>
       </c>
       <c r="U60" s="53"/>
     </row>
     <row r="61" spans="2:21" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B61" s="315" t="s">
+      <c r="B61" s="308" t="s">
         <v>155</v>
       </c>
       <c r="C61" s="316" t="s">
@@ -11578,7 +11581,7 @@
       <c r="O61" s="208" t="s">
         <v>64</v>
       </c>
-      <c r="P61" s="324" t="s">
+      <c r="P61" s="305" t="s">
         <v>65</v>
       </c>
       <c r="Q61" s="143" t="s">
@@ -11589,7 +11592,7 @@
       </c>
     </row>
     <row r="62" spans="2:21" x14ac:dyDescent="0.3">
-      <c r="B62" s="315"/>
+      <c r="B62" s="308"/>
       <c r="C62" s="316"/>
       <c r="D62" s="143" t="s">
         <v>24</v>
@@ -11630,7 +11633,7 @@
       <c r="O62" s="208" t="s">
         <v>64</v>
       </c>
-      <c r="P62" s="325"/>
+      <c r="P62" s="306"/>
       <c r="Q62" s="143" t="s">
         <v>156</v>
       </c>
@@ -11639,7 +11642,7 @@
       </c>
     </row>
     <row r="63" spans="2:21" x14ac:dyDescent="0.3">
-      <c r="B63" s="315" t="s">
+      <c r="B63" s="308" t="s">
         <v>158</v>
       </c>
       <c r="C63" s="316" t="s">
@@ -11684,7 +11687,7 @@
       <c r="O63" s="208" t="s">
         <v>64</v>
       </c>
-      <c r="P63" s="325"/>
+      <c r="P63" s="306"/>
       <c r="Q63" s="143" t="s">
         <v>156</v>
       </c>
@@ -11693,7 +11696,7 @@
       </c>
     </row>
     <row r="64" spans="2:21" x14ac:dyDescent="0.3">
-      <c r="B64" s="315"/>
+      <c r="B64" s="308"/>
       <c r="C64" s="316"/>
       <c r="D64" s="143" t="s">
         <v>24</v>
@@ -11734,7 +11737,7 @@
       <c r="O64" s="208" t="s">
         <v>64</v>
       </c>
-      <c r="P64" s="326"/>
+      <c r="P64" s="307"/>
       <c r="Q64" s="143" t="s">
         <v>156</v>
       </c>
@@ -11743,34 +11746,34 @@
       </c>
     </row>
     <row r="65" spans="2:63 3073:12199 12790:15083" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B65" s="236" t="s">
+      <c r="B65" s="224" t="s">
         <v>159</v>
       </c>
-      <c r="C65" s="236"/>
-      <c r="D65" s="231"/>
-      <c r="E65" s="231"/>
-      <c r="F65" s="236"/>
-      <c r="G65" s="231"/>
-      <c r="H65" s="231"/>
-      <c r="I65" s="236"/>
-      <c r="J65" s="231"/>
-      <c r="K65" s="231"/>
-      <c r="L65" s="231"/>
-      <c r="M65" s="236"/>
-      <c r="N65" s="231"/>
-      <c r="O65" s="231"/>
-      <c r="P65" s="231"/>
-      <c r="Q65" s="231"/>
+      <c r="C65" s="224"/>
+      <c r="D65" s="227"/>
+      <c r="E65" s="227"/>
+      <c r="F65" s="224"/>
+      <c r="G65" s="227"/>
+      <c r="H65" s="227"/>
+      <c r="I65" s="224"/>
+      <c r="J65" s="227"/>
+      <c r="K65" s="227"/>
+      <c r="L65" s="227"/>
+      <c r="M65" s="224"/>
+      <c r="N65" s="227"/>
+      <c r="O65" s="227"/>
+      <c r="P65" s="227"/>
+      <c r="Q65" s="227"/>
       <c r="U65" s="53"/>
     </row>
     <row r="66" spans="2:63 3073:12199 12790:15083" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B66" s="97" t="s">
         <v>1</v>
       </c>
-      <c r="C66" s="230" t="s">
+      <c r="C66" s="229" t="s">
         <v>2</v>
       </c>
-      <c r="D66" s="230"/>
+      <c r="D66" s="229"/>
       <c r="E66" s="8" t="s">
         <v>3</v>
       </c>
@@ -11813,7 +11816,7 @@
       <c r="U66" s="53"/>
     </row>
     <row r="67" spans="2:63 3073:12199 12790:15083" x14ac:dyDescent="0.3">
-      <c r="B67" s="274" t="s">
+      <c r="B67" s="287" t="s">
         <v>160</v>
       </c>
       <c r="C67" s="211" t="s">
@@ -11858,7 +11861,7 @@
       <c r="O67" s="208" t="s">
         <v>60</v>
       </c>
-      <c r="P67" s="318" t="s">
+      <c r="P67" s="302" t="s">
         <v>81</v>
       </c>
       <c r="Q67" s="149" t="s">
@@ -43317,7 +43320,7 @@
       </c>
     </row>
     <row r="68" spans="2:63 3073:12199 12790:15083" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B68" s="317"/>
+      <c r="B68" s="318"/>
       <c r="C68" s="211" t="s">
         <v>120</v>
       </c>
@@ -43360,7 +43363,7 @@
       <c r="O68" s="208" t="s">
         <v>60</v>
       </c>
-      <c r="P68" s="319"/>
+      <c r="P68" s="303"/>
       <c r="Q68" s="149" t="s">
         <v>130</v>
       </c>
@@ -54859,10 +54862,10 @@
       <c r="B70" s="97" t="s">
         <v>1</v>
       </c>
-      <c r="C70" s="230" t="s">
+      <c r="C70" s="229" t="s">
         <v>2</v>
       </c>
-      <c r="D70" s="230"/>
+      <c r="D70" s="229"/>
       <c r="E70" s="8" t="s">
         <v>3</v>
       </c>
@@ -54905,7 +54908,7 @@
       <c r="U70" s="53"/>
     </row>
     <row r="71" spans="2:63 3073:12199 12790:15083" x14ac:dyDescent="0.3">
-      <c r="B71" s="274" t="s">
+      <c r="B71" s="287" t="s">
         <v>162</v>
       </c>
       <c r="C71" s="211" t="s">
@@ -54950,7 +54953,7 @@
       <c r="O71" s="208" t="s">
         <v>60</v>
       </c>
-      <c r="P71" s="318" t="s">
+      <c r="P71" s="302" t="s">
         <v>81</v>
       </c>
       <c r="Q71" s="149" t="s">
@@ -54959,7 +54962,7 @@
       <c r="U71" s="53"/>
     </row>
     <row r="72" spans="2:63 3073:12199 12790:15083" x14ac:dyDescent="0.3">
-      <c r="B72" s="317"/>
+      <c r="B72" s="318"/>
       <c r="C72" s="211" t="s">
         <v>120</v>
       </c>
@@ -55002,7 +55005,7 @@
       <c r="O72" s="208" t="s">
         <v>60</v>
       </c>
-      <c r="P72" s="319"/>
+      <c r="P72" s="303"/>
       <c r="Q72" s="149" t="s">
         <v>130</v>
       </c>
@@ -55032,121 +55035,121 @@
       <c r="T74" s="6"/>
     </row>
     <row r="75" spans="2:63 3073:12199 12790:15083" x14ac:dyDescent="0.3">
-      <c r="B75" s="292" t="s">
+      <c r="B75" s="261" t="s">
         <v>35</v>
       </c>
-      <c r="C75" s="292"/>
-      <c r="D75" s="292"/>
-      <c r="E75" s="292"/>
-      <c r="F75" s="292"/>
-      <c r="G75" s="292"/>
-      <c r="H75" s="292"/>
-      <c r="I75" s="292"/>
-      <c r="J75" s="292"/>
-      <c r="K75" s="292"/>
-      <c r="L75" s="292"/>
-      <c r="M75" s="292"/>
-      <c r="N75" s="292"/>
-      <c r="O75" s="292"/>
-      <c r="P75" s="292"/>
-      <c r="Q75" s="292"/>
-      <c r="R75" s="292"/>
-      <c r="S75" s="292"/>
-      <c r="T75" s="292"/>
+      <c r="C75" s="261"/>
+      <c r="D75" s="261"/>
+      <c r="E75" s="261"/>
+      <c r="F75" s="261"/>
+      <c r="G75" s="261"/>
+      <c r="H75" s="261"/>
+      <c r="I75" s="261"/>
+      <c r="J75" s="261"/>
+      <c r="K75" s="261"/>
+      <c r="L75" s="261"/>
+      <c r="M75" s="261"/>
+      <c r="N75" s="261"/>
+      <c r="O75" s="261"/>
+      <c r="P75" s="261"/>
+      <c r="Q75" s="261"/>
+      <c r="R75" s="261"/>
+      <c r="S75" s="261"/>
+      <c r="T75" s="261"/>
     </row>
     <row r="76" spans="2:63 3073:12199 12790:15083" x14ac:dyDescent="0.3">
-      <c r="B76" s="292"/>
-      <c r="C76" s="292"/>
-      <c r="D76" s="292"/>
-      <c r="E76" s="292"/>
-      <c r="F76" s="292"/>
-      <c r="G76" s="292"/>
-      <c r="H76" s="292"/>
-      <c r="I76" s="292"/>
-      <c r="J76" s="292"/>
-      <c r="K76" s="292"/>
-      <c r="L76" s="292"/>
-      <c r="M76" s="292"/>
-      <c r="N76" s="292"/>
-      <c r="O76" s="292"/>
-      <c r="P76" s="292"/>
-      <c r="Q76" s="292"/>
-      <c r="R76" s="292"/>
-      <c r="S76" s="292"/>
-      <c r="T76" s="292"/>
+      <c r="B76" s="261"/>
+      <c r="C76" s="261"/>
+      <c r="D76" s="261"/>
+      <c r="E76" s="261"/>
+      <c r="F76" s="261"/>
+      <c r="G76" s="261"/>
+      <c r="H76" s="261"/>
+      <c r="I76" s="261"/>
+      <c r="J76" s="261"/>
+      <c r="K76" s="261"/>
+      <c r="L76" s="261"/>
+      <c r="M76" s="261"/>
+      <c r="N76" s="261"/>
+      <c r="O76" s="261"/>
+      <c r="P76" s="261"/>
+      <c r="Q76" s="261"/>
+      <c r="R76" s="261"/>
+      <c r="S76" s="261"/>
+      <c r="T76" s="261"/>
     </row>
     <row r="77" spans="2:63 3073:12199 12790:15083" x14ac:dyDescent="0.3">
-      <c r="B77" s="292"/>
-      <c r="C77" s="292"/>
-      <c r="D77" s="292"/>
-      <c r="E77" s="292"/>
-      <c r="F77" s="292"/>
-      <c r="G77" s="292"/>
-      <c r="H77" s="292"/>
-      <c r="I77" s="292"/>
-      <c r="J77" s="292"/>
-      <c r="K77" s="292"/>
-      <c r="L77" s="292"/>
-      <c r="M77" s="292"/>
-      <c r="N77" s="292"/>
-      <c r="O77" s="292"/>
-      <c r="P77" s="292"/>
-      <c r="Q77" s="292"/>
-      <c r="R77" s="292"/>
-      <c r="S77" s="292"/>
-      <c r="T77" s="292"/>
+      <c r="B77" s="261"/>
+      <c r="C77" s="261"/>
+      <c r="D77" s="261"/>
+      <c r="E77" s="261"/>
+      <c r="F77" s="261"/>
+      <c r="G77" s="261"/>
+      <c r="H77" s="261"/>
+      <c r="I77" s="261"/>
+      <c r="J77" s="261"/>
+      <c r="K77" s="261"/>
+      <c r="L77" s="261"/>
+      <c r="M77" s="261"/>
+      <c r="N77" s="261"/>
+      <c r="O77" s="261"/>
+      <c r="P77" s="261"/>
+      <c r="Q77" s="261"/>
+      <c r="R77" s="261"/>
+      <c r="S77" s="261"/>
+      <c r="T77" s="261"/>
     </row>
     <row r="78" spans="2:63 3073:12199 12790:15083" x14ac:dyDescent="0.3">
-      <c r="B78" s="292"/>
-      <c r="C78" s="292"/>
-      <c r="D78" s="292"/>
-      <c r="E78" s="292"/>
-      <c r="F78" s="292"/>
-      <c r="G78" s="292"/>
-      <c r="H78" s="292"/>
-      <c r="I78" s="292"/>
-      <c r="J78" s="292"/>
-      <c r="K78" s="292"/>
-      <c r="L78" s="292"/>
-      <c r="M78" s="292"/>
-      <c r="N78" s="292"/>
-      <c r="O78" s="292"/>
-      <c r="P78" s="292"/>
-      <c r="Q78" s="292"/>
-      <c r="R78" s="292"/>
-      <c r="S78" s="292"/>
-      <c r="T78" s="292"/>
+      <c r="B78" s="261"/>
+      <c r="C78" s="261"/>
+      <c r="D78" s="261"/>
+      <c r="E78" s="261"/>
+      <c r="F78" s="261"/>
+      <c r="G78" s="261"/>
+      <c r="H78" s="261"/>
+      <c r="I78" s="261"/>
+      <c r="J78" s="261"/>
+      <c r="K78" s="261"/>
+      <c r="L78" s="261"/>
+      <c r="M78" s="261"/>
+      <c r="N78" s="261"/>
+      <c r="O78" s="261"/>
+      <c r="P78" s="261"/>
+      <c r="Q78" s="261"/>
+      <c r="R78" s="261"/>
+      <c r="S78" s="261"/>
+      <c r="T78" s="261"/>
     </row>
     <row r="87" spans="2:20" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B87" s="232" t="s">
+      <c r="B87" s="228" t="s">
         <v>164</v>
       </c>
-      <c r="C87" s="232"/>
-      <c r="D87" s="232"/>
-      <c r="E87" s="232"/>
-      <c r="F87" s="232"/>
-      <c r="G87" s="232"/>
-      <c r="H87" s="232"/>
-      <c r="I87" s="232"/>
-      <c r="J87" s="232"/>
-      <c r="K87" s="232"/>
-      <c r="L87" s="232"/>
-      <c r="M87" s="232"/>
-      <c r="N87" s="232"/>
-      <c r="O87" s="232"/>
-      <c r="P87" s="232"/>
-      <c r="Q87" s="232"/>
-      <c r="R87" s="232"/>
-      <c r="S87" s="232"/>
+      <c r="C87" s="228"/>
+      <c r="D87" s="228"/>
+      <c r="E87" s="228"/>
+      <c r="F87" s="228"/>
+      <c r="G87" s="228"/>
+      <c r="H87" s="228"/>
+      <c r="I87" s="228"/>
+      <c r="J87" s="228"/>
+      <c r="K87" s="228"/>
+      <c r="L87" s="228"/>
+      <c r="M87" s="228"/>
+      <c r="N87" s="228"/>
+      <c r="O87" s="228"/>
+      <c r="P87" s="228"/>
+      <c r="Q87" s="228"/>
+      <c r="R87" s="228"/>
+      <c r="S87" s="228"/>
     </row>
     <row r="88" spans="2:20" ht="27" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B88" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C88" s="314" t="s">
+      <c r="C88" s="317" t="s">
         <v>2</v>
       </c>
-      <c r="D88" s="314"/>
+      <c r="D88" s="317"/>
       <c r="E88" s="127" t="s">
         <v>135</v>
       </c>
@@ -55183,17 +55186,17 @@
       <c r="P88" s="17" t="s">
         <v>127</v>
       </c>
-      <c r="Q88" s="230" t="s">
+      <c r="Q88" s="229" t="s">
         <v>38</v>
       </c>
-      <c r="R88" s="230"/>
-      <c r="S88" s="230"/>
+      <c r="R88" s="229"/>
+      <c r="S88" s="229"/>
     </row>
     <row r="89" spans="2:20" ht="28.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B89" s="238" t="s">
+      <c r="B89" s="230" t="s">
         <v>99</v>
       </c>
-      <c r="C89" s="257" t="s">
+      <c r="C89" s="251" t="s">
         <v>120</v>
       </c>
       <c r="D89" s="53" t="s">
@@ -55244,8 +55247,8 @@
       <c r="S89" s="258"/>
     </row>
     <row r="90" spans="2:20" x14ac:dyDescent="0.3">
-      <c r="B90" s="233"/>
-      <c r="C90" s="257"/>
+      <c r="B90" s="226"/>
+      <c r="C90" s="251"/>
       <c r="D90" s="53" t="s">
         <v>24</v>
       </c>
@@ -55315,90 +55318,90 @@
       <c r="T92" s="6"/>
     </row>
     <row r="93" spans="2:20" x14ac:dyDescent="0.3">
-      <c r="B93" s="292" t="s">
+      <c r="B93" s="261" t="s">
         <v>35</v>
       </c>
-      <c r="C93" s="292"/>
-      <c r="D93" s="292"/>
-      <c r="E93" s="292"/>
-      <c r="F93" s="292"/>
-      <c r="G93" s="292"/>
-      <c r="H93" s="292"/>
-      <c r="I93" s="292"/>
-      <c r="J93" s="292"/>
-      <c r="K93" s="292"/>
-      <c r="L93" s="292"/>
-      <c r="M93" s="292"/>
-      <c r="N93" s="292"/>
-      <c r="O93" s="292"/>
-      <c r="P93" s="292"/>
-      <c r="Q93" s="292"/>
-      <c r="R93" s="292"/>
-      <c r="S93" s="292"/>
-      <c r="T93" s="292"/>
+      <c r="C93" s="261"/>
+      <c r="D93" s="261"/>
+      <c r="E93" s="261"/>
+      <c r="F93" s="261"/>
+      <c r="G93" s="261"/>
+      <c r="H93" s="261"/>
+      <c r="I93" s="261"/>
+      <c r="J93" s="261"/>
+      <c r="K93" s="261"/>
+      <c r="L93" s="261"/>
+      <c r="M93" s="261"/>
+      <c r="N93" s="261"/>
+      <c r="O93" s="261"/>
+      <c r="P93" s="261"/>
+      <c r="Q93" s="261"/>
+      <c r="R93" s="261"/>
+      <c r="S93" s="261"/>
+      <c r="T93" s="261"/>
     </row>
     <row r="94" spans="2:20" x14ac:dyDescent="0.3">
-      <c r="B94" s="292"/>
-      <c r="C94" s="292"/>
-      <c r="D94" s="292"/>
-      <c r="E94" s="292"/>
-      <c r="F94" s="292"/>
-      <c r="G94" s="292"/>
-      <c r="H94" s="292"/>
-      <c r="I94" s="292"/>
-      <c r="J94" s="292"/>
-      <c r="K94" s="292"/>
-      <c r="L94" s="292"/>
-      <c r="M94" s="292"/>
-      <c r="N94" s="292"/>
-      <c r="O94" s="292"/>
-      <c r="P94" s="292"/>
-      <c r="Q94" s="292"/>
-      <c r="R94" s="292"/>
-      <c r="S94" s="292"/>
-      <c r="T94" s="292"/>
+      <c r="B94" s="261"/>
+      <c r="C94" s="261"/>
+      <c r="D94" s="261"/>
+      <c r="E94" s="261"/>
+      <c r="F94" s="261"/>
+      <c r="G94" s="261"/>
+      <c r="H94" s="261"/>
+      <c r="I94" s="261"/>
+      <c r="J94" s="261"/>
+      <c r="K94" s="261"/>
+      <c r="L94" s="261"/>
+      <c r="M94" s="261"/>
+      <c r="N94" s="261"/>
+      <c r="O94" s="261"/>
+      <c r="P94" s="261"/>
+      <c r="Q94" s="261"/>
+      <c r="R94" s="261"/>
+      <c r="S94" s="261"/>
+      <c r="T94" s="261"/>
     </row>
     <row r="95" spans="2:20" x14ac:dyDescent="0.3">
-      <c r="B95" s="292"/>
-      <c r="C95" s="292"/>
-      <c r="D95" s="292"/>
-      <c r="E95" s="292"/>
-      <c r="F95" s="292"/>
-      <c r="G95" s="292"/>
-      <c r="H95" s="292"/>
-      <c r="I95" s="292"/>
-      <c r="J95" s="292"/>
-      <c r="K95" s="292"/>
-      <c r="L95" s="292"/>
-      <c r="M95" s="292"/>
-      <c r="N95" s="292"/>
-      <c r="O95" s="292"/>
-      <c r="P95" s="292"/>
-      <c r="Q95" s="292"/>
-      <c r="R95" s="292"/>
-      <c r="S95" s="292"/>
-      <c r="T95" s="292"/>
+      <c r="B95" s="261"/>
+      <c r="C95" s="261"/>
+      <c r="D95" s="261"/>
+      <c r="E95" s="261"/>
+      <c r="F95" s="261"/>
+      <c r="G95" s="261"/>
+      <c r="H95" s="261"/>
+      <c r="I95" s="261"/>
+      <c r="J95" s="261"/>
+      <c r="K95" s="261"/>
+      <c r="L95" s="261"/>
+      <c r="M95" s="261"/>
+      <c r="N95" s="261"/>
+      <c r="O95" s="261"/>
+      <c r="P95" s="261"/>
+      <c r="Q95" s="261"/>
+      <c r="R95" s="261"/>
+      <c r="S95" s="261"/>
+      <c r="T95" s="261"/>
     </row>
     <row r="96" spans="2:20" x14ac:dyDescent="0.3">
-      <c r="B96" s="292"/>
-      <c r="C96" s="292"/>
-      <c r="D96" s="292"/>
-      <c r="E96" s="292"/>
-      <c r="F96" s="292"/>
-      <c r="G96" s="292"/>
-      <c r="H96" s="292"/>
-      <c r="I96" s="292"/>
-      <c r="J96" s="292"/>
-      <c r="K96" s="292"/>
-      <c r="L96" s="292"/>
-      <c r="M96" s="292"/>
-      <c r="N96" s="292"/>
-      <c r="O96" s="292"/>
-      <c r="P96" s="292"/>
-      <c r="Q96" s="292"/>
-      <c r="R96" s="292"/>
-      <c r="S96" s="292"/>
-      <c r="T96" s="292"/>
+      <c r="B96" s="261"/>
+      <c r="C96" s="261"/>
+      <c r="D96" s="261"/>
+      <c r="E96" s="261"/>
+      <c r="F96" s="261"/>
+      <c r="G96" s="261"/>
+      <c r="H96" s="261"/>
+      <c r="I96" s="261"/>
+      <c r="J96" s="261"/>
+      <c r="K96" s="261"/>
+      <c r="L96" s="261"/>
+      <c r="M96" s="261"/>
+      <c r="N96" s="261"/>
+      <c r="O96" s="261"/>
+      <c r="P96" s="261"/>
+      <c r="Q96" s="261"/>
+      <c r="R96" s="261"/>
+      <c r="S96" s="261"/>
+      <c r="T96" s="261"/>
     </row>
     <row r="106" spans="2:17" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="107" spans="2:17" ht="28.8" x14ac:dyDescent="0.3">
@@ -55425,10 +55428,10 @@
       <c r="B108" s="97" t="s">
         <v>1</v>
       </c>
-      <c r="C108" s="230" t="s">
+      <c r="C108" s="229" t="s">
         <v>2</v>
       </c>
-      <c r="D108" s="230"/>
+      <c r="D108" s="229"/>
       <c r="E108" s="8" t="s">
         <v>3</v>
       </c>
@@ -55470,10 +55473,10 @@
       </c>
     </row>
     <row r="109" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B109" s="302" t="s">
+      <c r="B109" s="319" t="s">
         <v>169</v>
       </c>
-      <c r="C109" s="257" t="s">
+      <c r="C109" s="251" t="s">
         <v>120</v>
       </c>
       <c r="D109" s="53" t="s">
@@ -55522,8 +55525,8 @@
       </c>
     </row>
     <row r="110" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B110" s="302"/>
-      <c r="C110" s="257"/>
+      <c r="B110" s="319"/>
+      <c r="C110" s="251"/>
       <c r="D110" s="53" t="s">
         <v>24</v>
       </c>
@@ -55594,10 +55597,10 @@
       <c r="B121" s="97" t="s">
         <v>1</v>
       </c>
-      <c r="C121" s="230" t="s">
+      <c r="C121" s="229" t="s">
         <v>2</v>
       </c>
-      <c r="D121" s="230"/>
+      <c r="D121" s="229"/>
       <c r="E121" s="8" t="s">
         <v>3</v>
       </c>
@@ -55639,10 +55642,10 @@
       </c>
     </row>
     <row r="122" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B122" s="302" t="s">
+      <c r="B122" s="319" t="s">
         <v>174</v>
       </c>
-      <c r="C122" s="257" t="s">
+      <c r="C122" s="251" t="s">
         <v>120</v>
       </c>
       <c r="D122" s="53" t="s">
@@ -55691,10 +55694,10 @@
       </c>
     </row>
     <row r="123" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B123" s="302" t="s">
+      <c r="B123" s="319" t="s">
         <v>174</v>
       </c>
-      <c r="C123" s="257" t="s">
+      <c r="C123" s="251" t="s">
         <v>120</v>
       </c>
       <c r="D123" s="53" t="s">
@@ -55743,10 +55746,10 @@
       </c>
     </row>
     <row r="124" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B124" s="302" t="s">
+      <c r="B124" s="319" t="s">
         <v>175</v>
       </c>
-      <c r="C124" s="257" t="s">
+      <c r="C124" s="251" t="s">
         <v>120</v>
       </c>
       <c r="D124" s="53" t="s">
@@ -55796,8 +55799,8 @@
       </c>
     </row>
     <row r="125" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B125" s="302"/>
-      <c r="C125" s="257"/>
+      <c r="B125" s="319"/>
+      <c r="C125" s="251"/>
       <c r="D125" s="53" t="s">
         <v>24</v>
       </c>
@@ -55846,19 +55849,36 @@
     </row>
   </sheetData>
   <mergeCells count="59">
-    <mergeCell ref="P57:P60"/>
-    <mergeCell ref="P61:P64"/>
-    <mergeCell ref="B11:B12"/>
-    <mergeCell ref="C11:C12"/>
-    <mergeCell ref="B61:B62"/>
-    <mergeCell ref="P39:R39"/>
-    <mergeCell ref="B15:B16"/>
-    <mergeCell ref="C15:C16"/>
-    <mergeCell ref="B17:B18"/>
-    <mergeCell ref="C17:C18"/>
-    <mergeCell ref="B36:B37"/>
-    <mergeCell ref="C36:C37"/>
-    <mergeCell ref="P36:R37"/>
+    <mergeCell ref="B124:B125"/>
+    <mergeCell ref="C124:C125"/>
+    <mergeCell ref="B122:B123"/>
+    <mergeCell ref="C122:C123"/>
+    <mergeCell ref="B20:R20"/>
+    <mergeCell ref="B21:R24"/>
+    <mergeCell ref="B109:B110"/>
+    <mergeCell ref="C109:C110"/>
+    <mergeCell ref="B89:B90"/>
+    <mergeCell ref="C89:C90"/>
+    <mergeCell ref="Q89:S90"/>
+    <mergeCell ref="B93:T96"/>
+    <mergeCell ref="B107:Q107"/>
+    <mergeCell ref="C108:D108"/>
+    <mergeCell ref="B120:Q120"/>
+    <mergeCell ref="C121:D121"/>
+    <mergeCell ref="Q88:S88"/>
+    <mergeCell ref="B87:S87"/>
+    <mergeCell ref="C88:D88"/>
+    <mergeCell ref="C66:D66"/>
+    <mergeCell ref="B63:B64"/>
+    <mergeCell ref="C63:C64"/>
+    <mergeCell ref="B65:Q65"/>
+    <mergeCell ref="C70:D70"/>
+    <mergeCell ref="B75:T78"/>
+    <mergeCell ref="B67:B68"/>
+    <mergeCell ref="B69:Q69"/>
+    <mergeCell ref="B71:B72"/>
+    <mergeCell ref="P67:P68"/>
+    <mergeCell ref="P71:P72"/>
     <mergeCell ref="B9:Q9"/>
     <mergeCell ref="C61:C62"/>
     <mergeCell ref="B13:B14"/>
@@ -55875,36 +55895,19 @@
     <mergeCell ref="B59:B60"/>
     <mergeCell ref="C59:C60"/>
     <mergeCell ref="C10:D10"/>
-    <mergeCell ref="Q88:S88"/>
-    <mergeCell ref="B87:S87"/>
-    <mergeCell ref="C88:D88"/>
-    <mergeCell ref="C66:D66"/>
-    <mergeCell ref="B63:B64"/>
-    <mergeCell ref="C63:C64"/>
-    <mergeCell ref="B65:Q65"/>
-    <mergeCell ref="C70:D70"/>
-    <mergeCell ref="B75:T78"/>
-    <mergeCell ref="B67:B68"/>
-    <mergeCell ref="B69:Q69"/>
-    <mergeCell ref="B71:B72"/>
-    <mergeCell ref="P67:P68"/>
-    <mergeCell ref="P71:P72"/>
-    <mergeCell ref="B124:B125"/>
-    <mergeCell ref="C124:C125"/>
-    <mergeCell ref="B122:B123"/>
-    <mergeCell ref="C122:C123"/>
-    <mergeCell ref="B20:R20"/>
-    <mergeCell ref="B21:R24"/>
-    <mergeCell ref="B109:B110"/>
-    <mergeCell ref="C109:C110"/>
-    <mergeCell ref="B89:B90"/>
-    <mergeCell ref="C89:C90"/>
-    <mergeCell ref="Q89:S90"/>
-    <mergeCell ref="B93:T96"/>
-    <mergeCell ref="B107:Q107"/>
-    <mergeCell ref="C108:D108"/>
-    <mergeCell ref="B120:Q120"/>
-    <mergeCell ref="C121:D121"/>
+    <mergeCell ref="P57:P60"/>
+    <mergeCell ref="P61:P64"/>
+    <mergeCell ref="B11:B12"/>
+    <mergeCell ref="C11:C12"/>
+    <mergeCell ref="B61:B62"/>
+    <mergeCell ref="P39:R39"/>
+    <mergeCell ref="B15:B16"/>
+    <mergeCell ref="C15:C16"/>
+    <mergeCell ref="B17:B18"/>
+    <mergeCell ref="C17:C18"/>
+    <mergeCell ref="B36:B37"/>
+    <mergeCell ref="C36:C37"/>
+    <mergeCell ref="P36:R37"/>
   </mergeCells>
   <phoneticPr fontId="14" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -55942,8 +55945,8 @@
     <row r="8" spans="2:18" x14ac:dyDescent="0.3">
       <c r="B8" s="126"/>
       <c r="C8" s="126"/>
-      <c r="D8" s="339"/>
-      <c r="E8" s="339"/>
+      <c r="D8" s="333"/>
+      <c r="E8" s="333"/>
       <c r="F8" s="126"/>
       <c r="G8" s="126"/>
       <c r="H8" s="126"/>
@@ -55959,32 +55962,32 @@
       <c r="R8" s="126"/>
     </row>
     <row r="9" spans="2:18" ht="28.8" x14ac:dyDescent="0.55000000000000004">
-      <c r="B9" s="342" t="s">
+      <c r="B9" s="336" t="s">
         <v>176</v>
       </c>
-      <c r="C9" s="342"/>
-      <c r="D9" s="342"/>
-      <c r="E9" s="342"/>
-      <c r="F9" s="342"/>
-      <c r="G9" s="342"/>
-      <c r="H9" s="342"/>
-      <c r="I9" s="342"/>
-      <c r="J9" s="342"/>
-      <c r="K9" s="342"/>
-      <c r="L9" s="342"/>
-      <c r="M9" s="342"/>
-      <c r="N9" s="342"/>
-      <c r="O9" s="342"/>
-      <c r="P9" s="342"/>
+      <c r="C9" s="336"/>
+      <c r="D9" s="336"/>
+      <c r="E9" s="336"/>
+      <c r="F9" s="336"/>
+      <c r="G9" s="336"/>
+      <c r="H9" s="336"/>
+      <c r="I9" s="336"/>
+      <c r="J9" s="336"/>
+      <c r="K9" s="336"/>
+      <c r="L9" s="336"/>
+      <c r="M9" s="336"/>
+      <c r="N9" s="336"/>
+      <c r="O9" s="336"/>
+      <c r="P9" s="336"/>
     </row>
     <row r="10" spans="2:18" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B10" s="127" t="s">
         <v>1</v>
       </c>
-      <c r="C10" s="340" t="s">
+      <c r="C10" s="351" t="s">
         <v>2</v>
       </c>
-      <c r="D10" s="341"/>
+      <c r="D10" s="352"/>
       <c r="E10" s="12" t="s">
         <v>3</v>
       </c>
@@ -56024,10 +56027,10 @@
       <c r="Q10" s="126"/>
     </row>
     <row r="11" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="B11" s="331" t="s">
+      <c r="B11" s="353" t="s">
         <v>179</v>
       </c>
-      <c r="C11" s="331" t="s">
+      <c r="C11" s="353" t="s">
         <v>180</v>
       </c>
       <c r="D11" s="41" t="s">
@@ -56075,8 +56078,8 @@
       <c r="Q11" s="126"/>
     </row>
     <row r="12" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="B12" s="332"/>
-      <c r="C12" s="332"/>
+      <c r="B12" s="354"/>
+      <c r="C12" s="354"/>
       <c r="D12" s="41" t="s">
         <v>24</v>
       </c>
@@ -56122,10 +56125,10 @@
       <c r="Q12" s="126"/>
     </row>
     <row r="13" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="B13" s="331" t="s">
+      <c r="B13" s="353" t="s">
         <v>182</v>
       </c>
-      <c r="C13" s="331" t="s">
+      <c r="C13" s="353" t="s">
         <v>180</v>
       </c>
       <c r="D13" s="41" t="s">
@@ -56173,8 +56176,8 @@
       <c r="Q13" s="126"/>
     </row>
     <row r="14" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="B14" s="332"/>
-      <c r="C14" s="332"/>
+      <c r="B14" s="354"/>
+      <c r="C14" s="354"/>
       <c r="D14" s="41" t="s">
         <v>24</v>
       </c>
@@ -56220,10 +56223,10 @@
       <c r="Q14" s="126"/>
     </row>
     <row r="15" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="B15" s="331" t="s">
+      <c r="B15" s="353" t="s">
         <v>132</v>
       </c>
-      <c r="C15" s="331" t="s">
+      <c r="C15" s="353" t="s">
         <v>180</v>
       </c>
       <c r="D15" s="41" t="s">
@@ -56271,8 +56274,8 @@
       <c r="Q15" s="126"/>
     </row>
     <row r="16" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="B16" s="332"/>
-      <c r="C16" s="332"/>
+      <c r="B16" s="354"/>
+      <c r="C16" s="354"/>
       <c r="D16" s="41" t="s">
         <v>24</v>
       </c>
@@ -56332,93 +56335,93 @@
       <c r="N17" s="34"/>
     </row>
     <row r="18" spans="2:17" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B18" s="336" t="s">
+      <c r="B18" s="357" t="s">
         <v>34</v>
       </c>
-      <c r="C18" s="337"/>
-      <c r="D18" s="337"/>
-      <c r="E18" s="337"/>
-      <c r="F18" s="337"/>
-      <c r="G18" s="337"/>
-      <c r="H18" s="337"/>
-      <c r="I18" s="337"/>
-      <c r="J18" s="337"/>
-      <c r="K18" s="337"/>
-      <c r="L18" s="337"/>
-      <c r="M18" s="337"/>
-      <c r="N18" s="337"/>
-      <c r="O18" s="337"/>
-      <c r="P18" s="338"/>
+      <c r="C18" s="358"/>
+      <c r="D18" s="358"/>
+      <c r="E18" s="358"/>
+      <c r="F18" s="358"/>
+      <c r="G18" s="358"/>
+      <c r="H18" s="358"/>
+      <c r="I18" s="358"/>
+      <c r="J18" s="358"/>
+      <c r="K18" s="358"/>
+      <c r="L18" s="358"/>
+      <c r="M18" s="358"/>
+      <c r="N18" s="358"/>
+      <c r="O18" s="358"/>
+      <c r="P18" s="359"/>
     </row>
     <row r="19" spans="2:17" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B19" s="306" t="s">
+      <c r="B19" s="323" t="s">
         <v>35</v>
       </c>
-      <c r="C19" s="307"/>
-      <c r="D19" s="307"/>
-      <c r="E19" s="307"/>
-      <c r="F19" s="307"/>
-      <c r="G19" s="307"/>
-      <c r="H19" s="307"/>
-      <c r="I19" s="307"/>
-      <c r="J19" s="307"/>
-      <c r="K19" s="307"/>
-      <c r="L19" s="307"/>
-      <c r="M19" s="307"/>
-      <c r="N19" s="307"/>
-      <c r="O19" s="307"/>
-      <c r="P19" s="308"/>
+      <c r="C19" s="324"/>
+      <c r="D19" s="324"/>
+      <c r="E19" s="324"/>
+      <c r="F19" s="324"/>
+      <c r="G19" s="324"/>
+      <c r="H19" s="324"/>
+      <c r="I19" s="324"/>
+      <c r="J19" s="324"/>
+      <c r="K19" s="324"/>
+      <c r="L19" s="324"/>
+      <c r="M19" s="324"/>
+      <c r="N19" s="324"/>
+      <c r="O19" s="324"/>
+      <c r="P19" s="325"/>
     </row>
     <row r="20" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B20" s="309"/>
-      <c r="C20" s="251"/>
-      <c r="D20" s="251"/>
-      <c r="E20" s="251"/>
-      <c r="F20" s="251"/>
-      <c r="G20" s="251"/>
-      <c r="H20" s="251"/>
-      <c r="I20" s="251"/>
-      <c r="J20" s="251"/>
-      <c r="K20" s="251"/>
-      <c r="L20" s="251"/>
-      <c r="M20" s="251"/>
-      <c r="N20" s="251"/>
-      <c r="O20" s="251"/>
-      <c r="P20" s="310"/>
+      <c r="B20" s="326"/>
+      <c r="C20" s="296"/>
+      <c r="D20" s="296"/>
+      <c r="E20" s="296"/>
+      <c r="F20" s="296"/>
+      <c r="G20" s="296"/>
+      <c r="H20" s="296"/>
+      <c r="I20" s="296"/>
+      <c r="J20" s="296"/>
+      <c r="K20" s="296"/>
+      <c r="L20" s="296"/>
+      <c r="M20" s="296"/>
+      <c r="N20" s="296"/>
+      <c r="O20" s="296"/>
+      <c r="P20" s="327"/>
     </row>
     <row r="21" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B21" s="309"/>
-      <c r="C21" s="251"/>
-      <c r="D21" s="251"/>
-      <c r="E21" s="251"/>
-      <c r="F21" s="251"/>
-      <c r="G21" s="251"/>
-      <c r="H21" s="251"/>
-      <c r="I21" s="251"/>
-      <c r="J21" s="251"/>
-      <c r="K21" s="251"/>
-      <c r="L21" s="251"/>
-      <c r="M21" s="251"/>
-      <c r="N21" s="251"/>
-      <c r="O21" s="251"/>
-      <c r="P21" s="310"/>
+      <c r="B21" s="326"/>
+      <c r="C21" s="296"/>
+      <c r="D21" s="296"/>
+      <c r="E21" s="296"/>
+      <c r="F21" s="296"/>
+      <c r="G21" s="296"/>
+      <c r="H21" s="296"/>
+      <c r="I21" s="296"/>
+      <c r="J21" s="296"/>
+      <c r="K21" s="296"/>
+      <c r="L21" s="296"/>
+      <c r="M21" s="296"/>
+      <c r="N21" s="296"/>
+      <c r="O21" s="296"/>
+      <c r="P21" s="327"/>
     </row>
     <row r="22" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B22" s="311"/>
-      <c r="C22" s="312"/>
-      <c r="D22" s="312"/>
-      <c r="E22" s="312"/>
-      <c r="F22" s="312"/>
-      <c r="G22" s="312"/>
-      <c r="H22" s="312"/>
-      <c r="I22" s="312"/>
-      <c r="J22" s="312"/>
-      <c r="K22" s="312"/>
-      <c r="L22" s="312"/>
-      <c r="M22" s="312"/>
-      <c r="N22" s="312"/>
-      <c r="O22" s="312"/>
-      <c r="P22" s="313"/>
+      <c r="B22" s="328"/>
+      <c r="C22" s="329"/>
+      <c r="D22" s="329"/>
+      <c r="E22" s="329"/>
+      <c r="F22" s="329"/>
+      <c r="G22" s="329"/>
+      <c r="H22" s="329"/>
+      <c r="I22" s="329"/>
+      <c r="J22" s="329"/>
+      <c r="K22" s="329"/>
+      <c r="L22" s="329"/>
+      <c r="M22" s="329"/>
+      <c r="N22" s="329"/>
+      <c r="O22" s="329"/>
+      <c r="P22" s="330"/>
     </row>
     <row r="23" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B23" s="27"/>
@@ -56548,33 +56551,33 @@
       <c r="N31" s="34"/>
     </row>
     <row r="32" spans="2:17" ht="28.8" x14ac:dyDescent="0.55000000000000004">
-      <c r="B32" s="333" t="s">
+      <c r="B32" s="355" t="s">
         <v>184</v>
       </c>
-      <c r="C32" s="334"/>
-      <c r="D32" s="334"/>
-      <c r="E32" s="334"/>
-      <c r="F32" s="334"/>
-      <c r="G32" s="334"/>
-      <c r="H32" s="334"/>
-      <c r="I32" s="334"/>
-      <c r="J32" s="334"/>
-      <c r="K32" s="334"/>
-      <c r="L32" s="334"/>
-      <c r="M32" s="334"/>
-      <c r="N32" s="334"/>
-      <c r="O32" s="334"/>
-      <c r="P32" s="334"/>
-      <c r="Q32" s="335"/>
+      <c r="C32" s="335"/>
+      <c r="D32" s="335"/>
+      <c r="E32" s="335"/>
+      <c r="F32" s="335"/>
+      <c r="G32" s="335"/>
+      <c r="H32" s="335"/>
+      <c r="I32" s="335"/>
+      <c r="J32" s="335"/>
+      <c r="K32" s="335"/>
+      <c r="L32" s="335"/>
+      <c r="M32" s="335"/>
+      <c r="N32" s="335"/>
+      <c r="O32" s="335"/>
+      <c r="P32" s="335"/>
+      <c r="Q32" s="356"/>
     </row>
     <row r="33" spans="2:19" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B33" s="127" t="s">
         <v>1</v>
       </c>
-      <c r="C33" s="343" t="s">
+      <c r="C33" s="360" t="s">
         <v>2</v>
       </c>
-      <c r="D33" s="343"/>
+      <c r="D33" s="360"/>
       <c r="E33" s="127" t="s">
         <v>135</v>
       </c>
@@ -56608,19 +56611,19 @@
       <c r="O33" s="127" t="s">
         <v>14</v>
       </c>
-      <c r="P33" s="259" t="s">
+      <c r="P33" s="283" t="s">
         <v>38</v>
       </c>
-      <c r="Q33" s="260"/>
+      <c r="Q33" s="284"/>
       <c r="S33" s="121" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="34" spans="2:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B34" s="348" t="s">
+      <c r="B34" s="344" t="s">
         <v>188</v>
       </c>
-      <c r="C34" s="349" t="s">
+      <c r="C34" s="345" t="s">
         <v>180</v>
       </c>
       <c r="D34" s="40" t="s">
@@ -56661,17 +56664,17 @@
       <c r="O34" s="40" t="s">
         <v>46</v>
       </c>
-      <c r="P34" s="281" t="s">
+      <c r="P34" s="254" t="s">
         <v>189</v>
       </c>
-      <c r="Q34" s="282"/>
+      <c r="Q34" s="255"/>
       <c r="S34" s="53" t="s">
         <v>190</v>
       </c>
     </row>
     <row r="35" spans="2:19" x14ac:dyDescent="0.3">
-      <c r="B35" s="348"/>
-      <c r="C35" s="349"/>
+      <c r="B35" s="344"/>
+      <c r="C35" s="345"/>
       <c r="D35" s="40" t="s">
         <v>24</v>
       </c>
@@ -56710,8 +56713,8 @@
       <c r="O35" s="40" t="s">
         <v>46</v>
       </c>
-      <c r="P35" s="328"/>
-      <c r="Q35" s="330"/>
+      <c r="P35" s="313"/>
+      <c r="Q35" s="315"/>
       <c r="S35" s="53" t="s">
         <v>190</v>
       </c>
@@ -56761,8 +56764,8 @@
       <c r="O36" s="40" t="s">
         <v>46</v>
       </c>
-      <c r="P36" s="283"/>
-      <c r="Q36" s="284"/>
+      <c r="P36" s="256"/>
+      <c r="Q36" s="257"/>
       <c r="S36" s="53" t="s">
         <v>145</v>
       </c>
@@ -56818,74 +56821,74 @@
       <c r="P39" s="7"/>
     </row>
     <row r="40" spans="2:19" x14ac:dyDescent="0.3">
-      <c r="B40" s="224" t="s">
+      <c r="B40" s="236" t="s">
         <v>35</v>
       </c>
-      <c r="C40" s="225"/>
-      <c r="D40" s="225"/>
-      <c r="E40" s="225"/>
-      <c r="F40" s="225"/>
-      <c r="G40" s="225"/>
-      <c r="H40" s="225"/>
-      <c r="I40" s="225"/>
-      <c r="J40" s="225"/>
-      <c r="K40" s="225"/>
-      <c r="L40" s="225"/>
-      <c r="M40" s="225"/>
-      <c r="N40" s="225"/>
-      <c r="O40" s="225"/>
-      <c r="P40" s="226"/>
+      <c r="C40" s="237"/>
+      <c r="D40" s="237"/>
+      <c r="E40" s="237"/>
+      <c r="F40" s="237"/>
+      <c r="G40" s="237"/>
+      <c r="H40" s="237"/>
+      <c r="I40" s="237"/>
+      <c r="J40" s="237"/>
+      <c r="K40" s="237"/>
+      <c r="L40" s="237"/>
+      <c r="M40" s="237"/>
+      <c r="N40" s="237"/>
+      <c r="O40" s="237"/>
+      <c r="P40" s="238"/>
     </row>
     <row r="41" spans="2:19" x14ac:dyDescent="0.3">
-      <c r="B41" s="224"/>
-      <c r="C41" s="225"/>
-      <c r="D41" s="225"/>
-      <c r="E41" s="225"/>
-      <c r="F41" s="225"/>
-      <c r="G41" s="225"/>
-      <c r="H41" s="225"/>
-      <c r="I41" s="225"/>
-      <c r="J41" s="225"/>
-      <c r="K41" s="225"/>
-      <c r="L41" s="225"/>
-      <c r="M41" s="225"/>
-      <c r="N41" s="225"/>
-      <c r="O41" s="225"/>
-      <c r="P41" s="226"/>
+      <c r="B41" s="236"/>
+      <c r="C41" s="237"/>
+      <c r="D41" s="237"/>
+      <c r="E41" s="237"/>
+      <c r="F41" s="237"/>
+      <c r="G41" s="237"/>
+      <c r="H41" s="237"/>
+      <c r="I41" s="237"/>
+      <c r="J41" s="237"/>
+      <c r="K41" s="237"/>
+      <c r="L41" s="237"/>
+      <c r="M41" s="237"/>
+      <c r="N41" s="237"/>
+      <c r="O41" s="237"/>
+      <c r="P41" s="238"/>
     </row>
     <row r="42" spans="2:19" x14ac:dyDescent="0.3">
-      <c r="B42" s="224"/>
-      <c r="C42" s="225"/>
-      <c r="D42" s="225"/>
-      <c r="E42" s="225"/>
-      <c r="F42" s="225"/>
-      <c r="G42" s="225"/>
-      <c r="H42" s="225"/>
-      <c r="I42" s="225"/>
-      <c r="J42" s="225"/>
-      <c r="K42" s="225"/>
-      <c r="L42" s="225"/>
-      <c r="M42" s="225"/>
-      <c r="N42" s="225"/>
-      <c r="O42" s="225"/>
-      <c r="P42" s="226"/>
+      <c r="B42" s="236"/>
+      <c r="C42" s="237"/>
+      <c r="D42" s="237"/>
+      <c r="E42" s="237"/>
+      <c r="F42" s="237"/>
+      <c r="G42" s="237"/>
+      <c r="H42" s="237"/>
+      <c r="I42" s="237"/>
+      <c r="J42" s="237"/>
+      <c r="K42" s="237"/>
+      <c r="L42" s="237"/>
+      <c r="M42" s="237"/>
+      <c r="N42" s="237"/>
+      <c r="O42" s="237"/>
+      <c r="P42" s="238"/>
     </row>
     <row r="43" spans="2:19" x14ac:dyDescent="0.3">
-      <c r="B43" s="227"/>
-      <c r="C43" s="228"/>
-      <c r="D43" s="228"/>
-      <c r="E43" s="228"/>
-      <c r="F43" s="228"/>
-      <c r="G43" s="228"/>
-      <c r="H43" s="228"/>
-      <c r="I43" s="228"/>
-      <c r="J43" s="228"/>
-      <c r="K43" s="228"/>
-      <c r="L43" s="228"/>
-      <c r="M43" s="228"/>
-      <c r="N43" s="228"/>
-      <c r="O43" s="228"/>
-      <c r="P43" s="229"/>
+      <c r="B43" s="239"/>
+      <c r="C43" s="240"/>
+      <c r="D43" s="240"/>
+      <c r="E43" s="240"/>
+      <c r="F43" s="240"/>
+      <c r="G43" s="240"/>
+      <c r="H43" s="240"/>
+      <c r="I43" s="240"/>
+      <c r="J43" s="240"/>
+      <c r="K43" s="240"/>
+      <c r="L43" s="240"/>
+      <c r="M43" s="240"/>
+      <c r="N43" s="240"/>
+      <c r="O43" s="240"/>
+      <c r="P43" s="241"/>
     </row>
     <row r="44" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B44" s="42"/>
@@ -57000,33 +57003,33 @@
       <c r="O51" s="126"/>
     </row>
     <row r="52" spans="2:19" ht="28.8" x14ac:dyDescent="0.55000000000000004">
-      <c r="B52" s="345" t="s">
+      <c r="B52" s="346" t="s">
         <v>195</v>
       </c>
-      <c r="C52" s="346"/>
-      <c r="D52" s="346"/>
-      <c r="E52" s="346"/>
-      <c r="F52" s="346"/>
-      <c r="G52" s="346"/>
-      <c r="H52" s="346"/>
-      <c r="I52" s="346"/>
-      <c r="J52" s="346"/>
-      <c r="K52" s="346"/>
-      <c r="L52" s="346"/>
-      <c r="M52" s="346"/>
-      <c r="N52" s="346"/>
-      <c r="O52" s="346"/>
-      <c r="P52" s="346"/>
-      <c r="Q52" s="347"/>
+      <c r="C52" s="347"/>
+      <c r="D52" s="347"/>
+      <c r="E52" s="347"/>
+      <c r="F52" s="347"/>
+      <c r="G52" s="347"/>
+      <c r="H52" s="347"/>
+      <c r="I52" s="347"/>
+      <c r="J52" s="347"/>
+      <c r="K52" s="347"/>
+      <c r="L52" s="347"/>
+      <c r="M52" s="347"/>
+      <c r="N52" s="347"/>
+      <c r="O52" s="347"/>
+      <c r="P52" s="347"/>
+      <c r="Q52" s="348"/>
     </row>
     <row r="53" spans="2:19" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B53" s="97" t="s">
         <v>1</v>
       </c>
-      <c r="C53" s="230" t="s">
+      <c r="C53" s="229" t="s">
         <v>2</v>
       </c>
-      <c r="D53" s="230"/>
+      <c r="D53" s="229"/>
       <c r="E53" s="120" t="s">
         <v>3</v>
       </c>
@@ -57074,7 +57077,7 @@
       <c r="B54" s="246" t="s">
         <v>196</v>
       </c>
-      <c r="C54" s="344" t="s">
+      <c r="C54" s="331" t="s">
         <v>180</v>
       </c>
       <c r="D54" s="53" t="s">
@@ -57128,7 +57131,7 @@
     </row>
     <row r="55" spans="2:19" ht="42" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B55" s="246"/>
-      <c r="C55" s="344"/>
+      <c r="C55" s="331"/>
       <c r="D55" s="53" t="s">
         <v>24</v>
       </c>
@@ -57179,34 +57182,34 @@
       </c>
     </row>
     <row r="56" spans="2:19" ht="28.8" x14ac:dyDescent="0.55000000000000004">
-      <c r="B56" s="345" t="s">
+      <c r="B56" s="346" t="s">
         <v>198</v>
       </c>
-      <c r="C56" s="346"/>
-      <c r="D56" s="346"/>
-      <c r="E56" s="346"/>
-      <c r="F56" s="346"/>
-      <c r="G56" s="346"/>
-      <c r="H56" s="346"/>
-      <c r="I56" s="346"/>
-      <c r="J56" s="346"/>
-      <c r="K56" s="346"/>
-      <c r="L56" s="346"/>
-      <c r="M56" s="346"/>
-      <c r="N56" s="346"/>
-      <c r="O56" s="346"/>
-      <c r="P56" s="346"/>
-      <c r="Q56" s="347"/>
+      <c r="C56" s="347"/>
+      <c r="D56" s="347"/>
+      <c r="E56" s="347"/>
+      <c r="F56" s="347"/>
+      <c r="G56" s="347"/>
+      <c r="H56" s="347"/>
+      <c r="I56" s="347"/>
+      <c r="J56" s="347"/>
+      <c r="K56" s="347"/>
+      <c r="L56" s="347"/>
+      <c r="M56" s="347"/>
+      <c r="N56" s="347"/>
+      <c r="O56" s="347"/>
+      <c r="P56" s="347"/>
+      <c r="Q56" s="348"/>
       <c r="S56" s="53"/>
     </row>
     <row r="57" spans="2:19" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B57" s="97" t="s">
         <v>1</v>
       </c>
-      <c r="C57" s="230" t="s">
+      <c r="C57" s="229" t="s">
         <v>2</v>
       </c>
-      <c r="D57" s="230"/>
+      <c r="D57" s="229"/>
       <c r="E57" s="120" t="s">
         <v>3</v>
       </c>
@@ -57252,7 +57255,7 @@
       <c r="B58" s="246" t="s">
         <v>79</v>
       </c>
-      <c r="C58" s="344" t="s">
+      <c r="C58" s="331" t="s">
         <v>180</v>
       </c>
       <c r="D58" s="53" t="s">
@@ -57297,7 +57300,7 @@
       <c r="P58" s="53" t="s">
         <v>64</v>
       </c>
-      <c r="Q58" s="356" t="s">
+      <c r="Q58" s="341" t="s">
         <v>199</v>
       </c>
       <c r="S58" s="53" t="s">
@@ -57306,7 +57309,7 @@
     </row>
     <row r="59" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B59" s="246"/>
-      <c r="C59" s="344"/>
+      <c r="C59" s="331"/>
       <c r="D59" s="53" t="s">
         <v>24</v>
       </c>
@@ -57349,40 +57352,40 @@
       <c r="P59" s="53" t="s">
         <v>64</v>
       </c>
-      <c r="Q59" s="357"/>
+      <c r="Q59" s="342"/>
       <c r="S59" s="53" t="s">
         <v>200</v>
       </c>
     </row>
     <row r="60" spans="2:19" ht="28.8" x14ac:dyDescent="0.55000000000000004">
-      <c r="B60" s="350" t="s">
+      <c r="B60" s="334" t="s">
         <v>201</v>
       </c>
-      <c r="C60" s="334"/>
-      <c r="D60" s="334"/>
-      <c r="E60" s="334"/>
-      <c r="F60" s="334"/>
-      <c r="G60" s="334"/>
-      <c r="H60" s="334"/>
-      <c r="I60" s="334"/>
-      <c r="J60" s="334"/>
-      <c r="K60" s="334"/>
-      <c r="L60" s="334"/>
-      <c r="M60" s="334"/>
-      <c r="N60" s="334"/>
-      <c r="O60" s="334"/>
-      <c r="P60" s="334"/>
-      <c r="Q60" s="351"/>
+      <c r="C60" s="335"/>
+      <c r="D60" s="335"/>
+      <c r="E60" s="335"/>
+      <c r="F60" s="335"/>
+      <c r="G60" s="335"/>
+      <c r="H60" s="335"/>
+      <c r="I60" s="335"/>
+      <c r="J60" s="335"/>
+      <c r="K60" s="335"/>
+      <c r="L60" s="335"/>
+      <c r="M60" s="335"/>
+      <c r="N60" s="335"/>
+      <c r="O60" s="335"/>
+      <c r="P60" s="335"/>
+      <c r="Q60" s="337"/>
       <c r="S60" s="53"/>
     </row>
     <row r="61" spans="2:19" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B61" s="109" t="s">
         <v>1</v>
       </c>
-      <c r="C61" s="314" t="s">
+      <c r="C61" s="317" t="s">
         <v>2</v>
       </c>
-      <c r="D61" s="314"/>
+      <c r="D61" s="317"/>
       <c r="E61" s="8" t="s">
         <v>3</v>
       </c>
@@ -57425,10 +57428,10 @@
       <c r="S61" s="53"/>
     </row>
     <row r="62" spans="2:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B62" s="352" t="s">
+      <c r="B62" s="343" t="s">
         <v>202</v>
       </c>
-      <c r="C62" s="344" t="s">
+      <c r="C62" s="331" t="s">
         <v>180</v>
       </c>
       <c r="D62" s="53" t="s">
@@ -57473,7 +57476,7 @@
       <c r="P62" s="53" t="s">
         <v>64</v>
       </c>
-      <c r="Q62" s="356" t="s">
+      <c r="Q62" s="341" t="s">
         <v>199</v>
       </c>
       <c r="S62" s="53" t="s">
@@ -57481,8 +57484,8 @@
       </c>
     </row>
     <row r="63" spans="2:19" x14ac:dyDescent="0.3">
-      <c r="B63" s="352"/>
-      <c r="C63" s="344"/>
+      <c r="B63" s="343"/>
+      <c r="C63" s="331"/>
       <c r="D63" s="53" t="s">
         <v>24</v>
       </c>
@@ -57525,40 +57528,40 @@
       <c r="P63" s="53" t="s">
         <v>64</v>
       </c>
-      <c r="Q63" s="357"/>
+      <c r="Q63" s="342"/>
       <c r="S63" s="53" t="s">
         <v>200</v>
       </c>
     </row>
     <row r="64" spans="2:19" ht="28.8" x14ac:dyDescent="0.55000000000000004">
-      <c r="B64" s="350" t="s">
+      <c r="B64" s="334" t="s">
         <v>203</v>
       </c>
-      <c r="C64" s="334"/>
-      <c r="D64" s="334"/>
-      <c r="E64" s="334"/>
-      <c r="F64" s="334"/>
-      <c r="G64" s="334"/>
-      <c r="H64" s="334"/>
-      <c r="I64" s="334"/>
-      <c r="J64" s="334"/>
-      <c r="K64" s="334"/>
-      <c r="L64" s="334"/>
-      <c r="M64" s="334"/>
-      <c r="N64" s="334"/>
-      <c r="O64" s="334"/>
-      <c r="P64" s="334"/>
-      <c r="Q64" s="351"/>
+      <c r="C64" s="335"/>
+      <c r="D64" s="335"/>
+      <c r="E64" s="335"/>
+      <c r="F64" s="335"/>
+      <c r="G64" s="335"/>
+      <c r="H64" s="335"/>
+      <c r="I64" s="335"/>
+      <c r="J64" s="335"/>
+      <c r="K64" s="335"/>
+      <c r="L64" s="335"/>
+      <c r="M64" s="335"/>
+      <c r="N64" s="335"/>
+      <c r="O64" s="335"/>
+      <c r="P64" s="335"/>
+      <c r="Q64" s="337"/>
       <c r="S64" s="53"/>
     </row>
     <row r="65" spans="2:19" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B65" s="109" t="s">
         <v>1</v>
       </c>
-      <c r="C65" s="314" t="s">
+      <c r="C65" s="317" t="s">
         <v>2</v>
       </c>
-      <c r="D65" s="314"/>
+      <c r="D65" s="317"/>
       <c r="E65" s="8" t="s">
         <v>3</v>
       </c>
@@ -57601,10 +57604,10 @@
       <c r="S65" s="53"/>
     </row>
     <row r="66" spans="2:19" x14ac:dyDescent="0.3">
-      <c r="B66" s="352" t="s">
+      <c r="B66" s="343" t="s">
         <v>204</v>
       </c>
-      <c r="C66" s="344" t="s">
+      <c r="C66" s="331" t="s">
         <v>180</v>
       </c>
       <c r="D66" s="53" t="s">
@@ -57649,7 +57652,7 @@
       <c r="P66" s="53" t="s">
         <v>64</v>
       </c>
-      <c r="Q66" s="353" t="s">
+      <c r="Q66" s="339" t="s">
         <v>205</v>
       </c>
       <c r="S66" s="53" t="s">
@@ -57657,8 +57660,8 @@
       </c>
     </row>
     <row r="67" spans="2:19" x14ac:dyDescent="0.3">
-      <c r="B67" s="352"/>
-      <c r="C67" s="344"/>
+      <c r="B67" s="343"/>
+      <c r="C67" s="331"/>
       <c r="D67" s="53" t="s">
         <v>24</v>
       </c>
@@ -57701,40 +57704,40 @@
       <c r="P67" s="53" t="s">
         <v>64</v>
       </c>
-      <c r="Q67" s="354"/>
+      <c r="Q67" s="349"/>
       <c r="S67" s="53" t="s">
         <v>200</v>
       </c>
     </row>
     <row r="68" spans="2:19" ht="28.8" x14ac:dyDescent="0.55000000000000004">
-      <c r="B68" s="350" t="s">
+      <c r="B68" s="334" t="s">
         <v>206</v>
       </c>
-      <c r="C68" s="334"/>
-      <c r="D68" s="334"/>
-      <c r="E68" s="334"/>
-      <c r="F68" s="334"/>
-      <c r="G68" s="334"/>
-      <c r="H68" s="334"/>
-      <c r="I68" s="334"/>
-      <c r="J68" s="334"/>
-      <c r="K68" s="334"/>
-      <c r="L68" s="334"/>
-      <c r="M68" s="334"/>
-      <c r="N68" s="334"/>
-      <c r="O68" s="334"/>
-      <c r="P68" s="334"/>
-      <c r="Q68" s="351"/>
+      <c r="C68" s="335"/>
+      <c r="D68" s="335"/>
+      <c r="E68" s="335"/>
+      <c r="F68" s="335"/>
+      <c r="G68" s="335"/>
+      <c r="H68" s="335"/>
+      <c r="I68" s="335"/>
+      <c r="J68" s="335"/>
+      <c r="K68" s="335"/>
+      <c r="L68" s="335"/>
+      <c r="M68" s="335"/>
+      <c r="N68" s="335"/>
+      <c r="O68" s="335"/>
+      <c r="P68" s="335"/>
+      <c r="Q68" s="337"/>
       <c r="S68" s="53"/>
     </row>
     <row r="69" spans="2:19" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B69" s="109" t="s">
         <v>1</v>
       </c>
-      <c r="C69" s="314" t="s">
+      <c r="C69" s="317" t="s">
         <v>2</v>
       </c>
-      <c r="D69" s="314"/>
+      <c r="D69" s="317"/>
       <c r="E69" s="8" t="s">
         <v>3</v>
       </c>
@@ -57780,7 +57783,7 @@
       <c r="B70" s="246" t="s">
         <v>207</v>
       </c>
-      <c r="C70" s="344" t="s">
+      <c r="C70" s="331" t="s">
         <v>180</v>
       </c>
       <c r="D70" s="53" t="s">
@@ -57825,7 +57828,7 @@
       <c r="P70" s="53" t="s">
         <v>60</v>
       </c>
-      <c r="Q70" s="353" t="s">
+      <c r="Q70" s="339" t="s">
         <v>205</v>
       </c>
       <c r="S70" s="53" t="s">
@@ -57834,7 +57837,7 @@
     </row>
     <row r="71" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B71" s="246"/>
-      <c r="C71" s="344"/>
+      <c r="C71" s="331"/>
       <c r="D71" s="53" t="s">
         <v>24</v>
       </c>
@@ -57877,39 +57880,39 @@
       <c r="P71" s="53" t="s">
         <v>60</v>
       </c>
-      <c r="Q71" s="355"/>
+      <c r="Q71" s="350"/>
       <c r="S71" s="53" t="s">
         <v>200</v>
       </c>
     </row>
     <row r="72" spans="2:19" ht="28.8" x14ac:dyDescent="0.55000000000000004">
-      <c r="B72" s="350" t="s">
+      <c r="B72" s="334" t="s">
         <v>208</v>
       </c>
-      <c r="C72" s="334"/>
-      <c r="D72" s="334"/>
-      <c r="E72" s="334"/>
-      <c r="F72" s="334"/>
-      <c r="G72" s="334"/>
-      <c r="H72" s="334"/>
-      <c r="I72" s="334"/>
-      <c r="J72" s="334"/>
-      <c r="K72" s="334"/>
-      <c r="L72" s="334"/>
-      <c r="M72" s="334"/>
-      <c r="N72" s="342"/>
-      <c r="O72" s="334"/>
-      <c r="P72" s="334"/>
-      <c r="Q72" s="351"/>
+      <c r="C72" s="335"/>
+      <c r="D72" s="335"/>
+      <c r="E72" s="335"/>
+      <c r="F72" s="335"/>
+      <c r="G72" s="335"/>
+      <c r="H72" s="335"/>
+      <c r="I72" s="335"/>
+      <c r="J72" s="335"/>
+      <c r="K72" s="335"/>
+      <c r="L72" s="335"/>
+      <c r="M72" s="335"/>
+      <c r="N72" s="336"/>
+      <c r="O72" s="335"/>
+      <c r="P72" s="335"/>
+      <c r="Q72" s="337"/>
     </row>
     <row r="73" spans="2:19" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B73" s="109" t="s">
         <v>1</v>
       </c>
-      <c r="C73" s="314" t="s">
+      <c r="C73" s="317" t="s">
         <v>2</v>
       </c>
-      <c r="D73" s="314"/>
+      <c r="D73" s="317"/>
       <c r="E73" s="8" t="s">
         <v>3</v>
       </c>
@@ -57954,7 +57957,7 @@
       <c r="B74" s="246" t="s">
         <v>209</v>
       </c>
-      <c r="C74" s="344" t="s">
+      <c r="C74" s="331" t="s">
         <v>180</v>
       </c>
       <c r="D74" s="53" t="s">
@@ -57999,7 +58002,7 @@
       <c r="P74" s="53" t="s">
         <v>64</v>
       </c>
-      <c r="Q74" s="353" t="s">
+      <c r="Q74" s="339" t="s">
         <v>205</v>
       </c>
       <c r="S74" s="53" t="s">
@@ -58007,8 +58010,8 @@
       </c>
     </row>
     <row r="75" spans="2:19" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B75" s="358"/>
-      <c r="C75" s="360"/>
+      <c r="B75" s="338"/>
+      <c r="C75" s="332"/>
       <c r="D75" s="90" t="s">
         <v>24</v>
       </c>
@@ -58051,7 +58054,7 @@
       <c r="P75" s="90" t="s">
         <v>64</v>
       </c>
-      <c r="Q75" s="359"/>
+      <c r="Q75" s="340"/>
       <c r="S75" s="53" t="s">
         <v>200</v>
       </c>
@@ -58059,10 +58062,10 @@
     <row r="76" spans="2:19" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B76" s="126"/>
       <c r="C76" s="126"/>
-      <c r="D76" s="339" t="s">
+      <c r="D76" s="333" t="s">
         <v>210</v>
       </c>
-      <c r="E76" s="339"/>
+      <c r="E76" s="333"/>
       <c r="F76" s="126"/>
       <c r="G76" s="126"/>
       <c r="H76" s="126"/>
@@ -58078,133 +58081,133 @@
       <c r="R76" s="126"/>
     </row>
     <row r="77" spans="2:19" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B77" s="247" t="s">
+      <c r="B77" s="292" t="s">
         <v>34</v>
       </c>
-      <c r="C77" s="248"/>
-      <c r="D77" s="248"/>
-      <c r="E77" s="248"/>
-      <c r="F77" s="248"/>
-      <c r="G77" s="248"/>
-      <c r="H77" s="248"/>
-      <c r="I77" s="248"/>
-      <c r="J77" s="248"/>
-      <c r="K77" s="248"/>
-      <c r="L77" s="248"/>
-      <c r="M77" s="248"/>
-      <c r="N77" s="248"/>
-      <c r="O77" s="248"/>
-      <c r="P77" s="248"/>
-      <c r="Q77" s="248"/>
-      <c r="R77" s="249"/>
+      <c r="C77" s="293"/>
+      <c r="D77" s="293"/>
+      <c r="E77" s="293"/>
+      <c r="F77" s="293"/>
+      <c r="G77" s="293"/>
+      <c r="H77" s="293"/>
+      <c r="I77" s="293"/>
+      <c r="J77" s="293"/>
+      <c r="K77" s="293"/>
+      <c r="L77" s="293"/>
+      <c r="M77" s="293"/>
+      <c r="N77" s="293"/>
+      <c r="O77" s="293"/>
+      <c r="P77" s="293"/>
+      <c r="Q77" s="293"/>
+      <c r="R77" s="294"/>
     </row>
     <row r="78" spans="2:19" x14ac:dyDescent="0.3">
-      <c r="B78" s="250" t="s">
+      <c r="B78" s="295" t="s">
         <v>35</v>
       </c>
-      <c r="C78" s="251"/>
-      <c r="D78" s="251"/>
-      <c r="E78" s="251"/>
-      <c r="F78" s="251"/>
-      <c r="G78" s="251"/>
-      <c r="H78" s="251"/>
-      <c r="I78" s="251"/>
-      <c r="J78" s="251"/>
-      <c r="K78" s="251"/>
-      <c r="L78" s="251"/>
-      <c r="M78" s="251"/>
-      <c r="N78" s="251"/>
-      <c r="O78" s="251"/>
-      <c r="P78" s="251"/>
-      <c r="Q78" s="251"/>
-      <c r="R78" s="252"/>
+      <c r="C78" s="296"/>
+      <c r="D78" s="296"/>
+      <c r="E78" s="296"/>
+      <c r="F78" s="296"/>
+      <c r="G78" s="296"/>
+      <c r="H78" s="296"/>
+      <c r="I78" s="296"/>
+      <c r="J78" s="296"/>
+      <c r="K78" s="296"/>
+      <c r="L78" s="296"/>
+      <c r="M78" s="296"/>
+      <c r="N78" s="296"/>
+      <c r="O78" s="296"/>
+      <c r="P78" s="296"/>
+      <c r="Q78" s="296"/>
+      <c r="R78" s="297"/>
     </row>
     <row r="79" spans="2:19" x14ac:dyDescent="0.3">
-      <c r="B79" s="250"/>
-      <c r="C79" s="251"/>
-      <c r="D79" s="251"/>
-      <c r="E79" s="251"/>
-      <c r="F79" s="251"/>
-      <c r="G79" s="251"/>
-      <c r="H79" s="251"/>
-      <c r="I79" s="251"/>
-      <c r="J79" s="251"/>
-      <c r="K79" s="251"/>
-      <c r="L79" s="251"/>
-      <c r="M79" s="251"/>
-      <c r="N79" s="251"/>
-      <c r="O79" s="251"/>
-      <c r="P79" s="251"/>
-      <c r="Q79" s="251"/>
-      <c r="R79" s="252"/>
+      <c r="B79" s="295"/>
+      <c r="C79" s="296"/>
+      <c r="D79" s="296"/>
+      <c r="E79" s="296"/>
+      <c r="F79" s="296"/>
+      <c r="G79" s="296"/>
+      <c r="H79" s="296"/>
+      <c r="I79" s="296"/>
+      <c r="J79" s="296"/>
+      <c r="K79" s="296"/>
+      <c r="L79" s="296"/>
+      <c r="M79" s="296"/>
+      <c r="N79" s="296"/>
+      <c r="O79" s="296"/>
+      <c r="P79" s="296"/>
+      <c r="Q79" s="296"/>
+      <c r="R79" s="297"/>
     </row>
     <row r="80" spans="2:19" x14ac:dyDescent="0.3">
-      <c r="B80" s="250"/>
-      <c r="C80" s="251"/>
-      <c r="D80" s="251"/>
-      <c r="E80" s="251"/>
-      <c r="F80" s="251"/>
-      <c r="G80" s="251"/>
-      <c r="H80" s="251"/>
-      <c r="I80" s="251"/>
-      <c r="J80" s="251"/>
-      <c r="K80" s="251"/>
-      <c r="L80" s="251"/>
-      <c r="M80" s="251"/>
-      <c r="N80" s="251"/>
-      <c r="O80" s="251"/>
-      <c r="P80" s="251"/>
-      <c r="Q80" s="251"/>
-      <c r="R80" s="252"/>
+      <c r="B80" s="295"/>
+      <c r="C80" s="296"/>
+      <c r="D80" s="296"/>
+      <c r="E80" s="296"/>
+      <c r="F80" s="296"/>
+      <c r="G80" s="296"/>
+      <c r="H80" s="296"/>
+      <c r="I80" s="296"/>
+      <c r="J80" s="296"/>
+      <c r="K80" s="296"/>
+      <c r="L80" s="296"/>
+      <c r="M80" s="296"/>
+      <c r="N80" s="296"/>
+      <c r="O80" s="296"/>
+      <c r="P80" s="296"/>
+      <c r="Q80" s="296"/>
+      <c r="R80" s="297"/>
     </row>
     <row r="81" spans="2:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B81" s="253"/>
-      <c r="C81" s="254"/>
-      <c r="D81" s="254"/>
-      <c r="E81" s="254"/>
-      <c r="F81" s="254"/>
-      <c r="G81" s="254"/>
-      <c r="H81" s="254"/>
-      <c r="I81" s="254"/>
-      <c r="J81" s="254"/>
-      <c r="K81" s="254"/>
-      <c r="L81" s="254"/>
-      <c r="M81" s="254"/>
-      <c r="N81" s="254"/>
-      <c r="O81" s="254"/>
-      <c r="P81" s="254"/>
-      <c r="Q81" s="254"/>
-      <c r="R81" s="255"/>
+      <c r="B81" s="298"/>
+      <c r="C81" s="299"/>
+      <c r="D81" s="299"/>
+      <c r="E81" s="299"/>
+      <c r="F81" s="299"/>
+      <c r="G81" s="299"/>
+      <c r="H81" s="299"/>
+      <c r="I81" s="299"/>
+      <c r="J81" s="299"/>
+      <c r="K81" s="299"/>
+      <c r="L81" s="299"/>
+      <c r="M81" s="299"/>
+      <c r="N81" s="299"/>
+      <c r="O81" s="299"/>
+      <c r="P81" s="299"/>
+      <c r="Q81" s="299"/>
+      <c r="R81" s="300"/>
     </row>
     <row r="89" spans="2:18" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B89" s="256" t="s">
+      <c r="B89" s="301" t="s">
         <v>211</v>
       </c>
-      <c r="C89" s="256"/>
-      <c r="D89" s="256"/>
-      <c r="E89" s="256"/>
-      <c r="F89" s="256"/>
-      <c r="G89" s="256"/>
-      <c r="H89" s="256"/>
-      <c r="I89" s="256"/>
-      <c r="J89" s="256"/>
-      <c r="K89" s="256"/>
-      <c r="L89" s="256"/>
-      <c r="M89" s="256"/>
-      <c r="N89" s="256"/>
-      <c r="O89" s="256"/>
-      <c r="P89" s="256"/>
-      <c r="Q89" s="256"/>
-      <c r="R89" s="256"/>
+      <c r="C89" s="301"/>
+      <c r="D89" s="301"/>
+      <c r="E89" s="301"/>
+      <c r="F89" s="301"/>
+      <c r="G89" s="301"/>
+      <c r="H89" s="301"/>
+      <c r="I89" s="301"/>
+      <c r="J89" s="301"/>
+      <c r="K89" s="301"/>
+      <c r="L89" s="301"/>
+      <c r="M89" s="301"/>
+      <c r="N89" s="301"/>
+      <c r="O89" s="301"/>
+      <c r="P89" s="301"/>
+      <c r="Q89" s="301"/>
+      <c r="R89" s="301"/>
     </row>
     <row r="90" spans="2:18" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B90" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C90" s="314" t="s">
+      <c r="C90" s="317" t="s">
         <v>2</v>
       </c>
-      <c r="D90" s="314"/>
+      <c r="D90" s="317"/>
       <c r="E90" s="127" t="s">
         <v>135</v>
       </c>
@@ -58241,16 +58244,16 @@
       <c r="P90" s="124" t="s">
         <v>127</v>
       </c>
-      <c r="Q90" s="230" t="s">
+      <c r="Q90" s="229" t="s">
         <v>38</v>
       </c>
-      <c r="R90" s="230"/>
+      <c r="R90" s="229"/>
     </row>
     <row r="91" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="B91" s="233" t="s">
+      <c r="B91" s="226" t="s">
         <v>99</v>
       </c>
-      <c r="C91" s="257" t="s">
+      <c r="C91" s="251" t="s">
         <v>180</v>
       </c>
       <c r="D91" s="53" t="s">
@@ -58300,8 +58303,8 @@
       <c r="R91" s="258"/>
     </row>
     <row r="92" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="B92" s="233"/>
-      <c r="C92" s="257"/>
+      <c r="B92" s="226"/>
+      <c r="C92" s="251"/>
       <c r="D92" s="53" t="s">
         <v>24</v>
       </c>
@@ -58368,82 +58371,82 @@
       <c r="R94" s="6"/>
     </row>
     <row r="95" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="B95" s="292" t="s">
+      <c r="B95" s="261" t="s">
         <v>35</v>
       </c>
-      <c r="C95" s="292"/>
-      <c r="D95" s="292"/>
-      <c r="E95" s="292"/>
-      <c r="F95" s="292"/>
-      <c r="G95" s="292"/>
-      <c r="H95" s="292"/>
-      <c r="I95" s="292"/>
-      <c r="J95" s="292"/>
-      <c r="K95" s="292"/>
-      <c r="L95" s="292"/>
-      <c r="M95" s="292"/>
-      <c r="N95" s="292"/>
-      <c r="O95" s="292"/>
-      <c r="P95" s="292"/>
-      <c r="Q95" s="292"/>
-      <c r="R95" s="292"/>
+      <c r="C95" s="261"/>
+      <c r="D95" s="261"/>
+      <c r="E95" s="261"/>
+      <c r="F95" s="261"/>
+      <c r="G95" s="261"/>
+      <c r="H95" s="261"/>
+      <c r="I95" s="261"/>
+      <c r="J95" s="261"/>
+      <c r="K95" s="261"/>
+      <c r="L95" s="261"/>
+      <c r="M95" s="261"/>
+      <c r="N95" s="261"/>
+      <c r="O95" s="261"/>
+      <c r="P95" s="261"/>
+      <c r="Q95" s="261"/>
+      <c r="R95" s="261"/>
     </row>
     <row r="96" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="B96" s="292"/>
-      <c r="C96" s="292"/>
-      <c r="D96" s="292"/>
-      <c r="E96" s="292"/>
-      <c r="F96" s="292"/>
-      <c r="G96" s="292"/>
-      <c r="H96" s="292"/>
-      <c r="I96" s="292"/>
-      <c r="J96" s="292"/>
-      <c r="K96" s="292"/>
-      <c r="L96" s="292"/>
-      <c r="M96" s="292"/>
-      <c r="N96" s="292"/>
-      <c r="O96" s="292"/>
-      <c r="P96" s="292"/>
-      <c r="Q96" s="292"/>
-      <c r="R96" s="292"/>
+      <c r="B96" s="261"/>
+      <c r="C96" s="261"/>
+      <c r="D96" s="261"/>
+      <c r="E96" s="261"/>
+      <c r="F96" s="261"/>
+      <c r="G96" s="261"/>
+      <c r="H96" s="261"/>
+      <c r="I96" s="261"/>
+      <c r="J96" s="261"/>
+      <c r="K96" s="261"/>
+      <c r="L96" s="261"/>
+      <c r="M96" s="261"/>
+      <c r="N96" s="261"/>
+      <c r="O96" s="261"/>
+      <c r="P96" s="261"/>
+      <c r="Q96" s="261"/>
+      <c r="R96" s="261"/>
     </row>
     <row r="97" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="B97" s="292"/>
-      <c r="C97" s="292"/>
-      <c r="D97" s="292"/>
-      <c r="E97" s="292"/>
-      <c r="F97" s="292"/>
-      <c r="G97" s="292"/>
-      <c r="H97" s="292"/>
-      <c r="I97" s="292"/>
-      <c r="J97" s="292"/>
-      <c r="K97" s="292"/>
-      <c r="L97" s="292"/>
-      <c r="M97" s="292"/>
-      <c r="N97" s="292"/>
-      <c r="O97" s="292"/>
-      <c r="P97" s="292"/>
-      <c r="Q97" s="292"/>
-      <c r="R97" s="292"/>
+      <c r="B97" s="261"/>
+      <c r="C97" s="261"/>
+      <c r="D97" s="261"/>
+      <c r="E97" s="261"/>
+      <c r="F97" s="261"/>
+      <c r="G97" s="261"/>
+      <c r="H97" s="261"/>
+      <c r="I97" s="261"/>
+      <c r="J97" s="261"/>
+      <c r="K97" s="261"/>
+      <c r="L97" s="261"/>
+      <c r="M97" s="261"/>
+      <c r="N97" s="261"/>
+      <c r="O97" s="261"/>
+      <c r="P97" s="261"/>
+      <c r="Q97" s="261"/>
+      <c r="R97" s="261"/>
     </row>
     <row r="98" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="B98" s="292"/>
-      <c r="C98" s="292"/>
-      <c r="D98" s="292"/>
-      <c r="E98" s="292"/>
-      <c r="F98" s="292"/>
-      <c r="G98" s="292"/>
-      <c r="H98" s="292"/>
-      <c r="I98" s="292"/>
-      <c r="J98" s="292"/>
-      <c r="K98" s="292"/>
-      <c r="L98" s="292"/>
-      <c r="M98" s="292"/>
-      <c r="N98" s="292"/>
-      <c r="O98" s="292"/>
-      <c r="P98" s="292"/>
-      <c r="Q98" s="292"/>
-      <c r="R98" s="292"/>
+      <c r="B98" s="261"/>
+      <c r="C98" s="261"/>
+      <c r="D98" s="261"/>
+      <c r="E98" s="261"/>
+      <c r="F98" s="261"/>
+      <c r="G98" s="261"/>
+      <c r="H98" s="261"/>
+      <c r="I98" s="261"/>
+      <c r="J98" s="261"/>
+      <c r="K98" s="261"/>
+      <c r="L98" s="261"/>
+      <c r="M98" s="261"/>
+      <c r="N98" s="261"/>
+      <c r="O98" s="261"/>
+      <c r="P98" s="261"/>
+      <c r="Q98" s="261"/>
+      <c r="R98" s="261"/>
     </row>
     <row r="99" spans="2:18" x14ac:dyDescent="0.3">
       <c r="B99" s="122"/>
@@ -58465,34 +58468,34 @@
       <c r="R99" s="122"/>
     </row>
     <row r="100" spans="2:18" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B100" s="231" t="s">
+      <c r="B100" s="227" t="s">
         <v>214</v>
       </c>
-      <c r="C100" s="232"/>
-      <c r="D100" s="232"/>
-      <c r="E100" s="232"/>
-      <c r="F100" s="232"/>
-      <c r="G100" s="232"/>
-      <c r="H100" s="232"/>
-      <c r="I100" s="232"/>
-      <c r="J100" s="232"/>
-      <c r="K100" s="232"/>
-      <c r="L100" s="232"/>
-      <c r="M100" s="232"/>
-      <c r="N100" s="232"/>
-      <c r="O100" s="232"/>
-      <c r="P100" s="232"/>
-      <c r="Q100" s="232"/>
-      <c r="R100" s="232"/>
+      <c r="C100" s="228"/>
+      <c r="D100" s="228"/>
+      <c r="E100" s="228"/>
+      <c r="F100" s="228"/>
+      <c r="G100" s="228"/>
+      <c r="H100" s="228"/>
+      <c r="I100" s="228"/>
+      <c r="J100" s="228"/>
+      <c r="K100" s="228"/>
+      <c r="L100" s="228"/>
+      <c r="M100" s="228"/>
+      <c r="N100" s="228"/>
+      <c r="O100" s="228"/>
+      <c r="P100" s="228"/>
+      <c r="Q100" s="228"/>
+      <c r="R100" s="228"/>
     </row>
     <row r="101" spans="2:18" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B101" s="97" t="s">
         <v>1</v>
       </c>
-      <c r="C101" s="230" t="s">
+      <c r="C101" s="229" t="s">
         <v>2</v>
       </c>
-      <c r="D101" s="230"/>
+      <c r="D101" s="229"/>
       <c r="E101" s="8" t="s">
         <v>3</v>
       </c>
@@ -58537,10 +58540,10 @@
       </c>
     </row>
     <row r="102" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="B102" s="302" t="s">
+      <c r="B102" s="319" t="s">
         <v>108</v>
       </c>
-      <c r="C102" s="257" t="s">
+      <c r="C102" s="251" t="s">
         <v>180</v>
       </c>
       <c r="D102" s="53" t="s">
@@ -58592,8 +58595,8 @@
       </c>
     </row>
     <row r="103" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="B103" s="302"/>
-      <c r="C103" s="257"/>
+      <c r="B103" s="319"/>
+      <c r="C103" s="251"/>
       <c r="D103" s="53" t="s">
         <v>24</v>
       </c>
@@ -58643,10 +58646,10 @@
       </c>
     </row>
     <row r="104" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="B104" s="302" t="s">
+      <c r="B104" s="319" t="s">
         <v>175</v>
       </c>
-      <c r="C104" s="257" t="s">
+      <c r="C104" s="251" t="s">
         <v>180</v>
       </c>
       <c r="D104" s="53" t="s">
@@ -58699,8 +58702,8 @@
       </c>
     </row>
     <row r="105" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="B105" s="302"/>
-      <c r="C105" s="257"/>
+      <c r="B105" s="319"/>
+      <c r="C105" s="251"/>
       <c r="D105" s="53" t="s">
         <v>24</v>
       </c>
@@ -58752,39 +58755,20 @@
     </row>
   </sheetData>
   <mergeCells count="63">
-    <mergeCell ref="C101:D101"/>
-    <mergeCell ref="B104:B105"/>
-    <mergeCell ref="C104:C105"/>
-    <mergeCell ref="C74:C75"/>
-    <mergeCell ref="B89:R89"/>
-    <mergeCell ref="D76:E76"/>
-    <mergeCell ref="B77:R77"/>
-    <mergeCell ref="B78:R81"/>
-    <mergeCell ref="B91:B92"/>
-    <mergeCell ref="C91:C92"/>
-    <mergeCell ref="Q91:R92"/>
-    <mergeCell ref="B95:R98"/>
-    <mergeCell ref="B72:Q72"/>
-    <mergeCell ref="C73:D73"/>
-    <mergeCell ref="B74:B75"/>
-    <mergeCell ref="C90:D90"/>
-    <mergeCell ref="Q90:R90"/>
-    <mergeCell ref="Q74:Q75"/>
-    <mergeCell ref="B64:Q64"/>
-    <mergeCell ref="C65:D65"/>
-    <mergeCell ref="Q58:Q59"/>
-    <mergeCell ref="C58:C59"/>
-    <mergeCell ref="B60:Q60"/>
-    <mergeCell ref="C61:D61"/>
-    <mergeCell ref="B62:B63"/>
-    <mergeCell ref="C62:C63"/>
-    <mergeCell ref="Q62:Q63"/>
-    <mergeCell ref="B34:B35"/>
-    <mergeCell ref="C34:C35"/>
-    <mergeCell ref="B40:P43"/>
-    <mergeCell ref="B52:Q52"/>
-    <mergeCell ref="C53:D53"/>
-    <mergeCell ref="P34:Q36"/>
+    <mergeCell ref="B15:B16"/>
+    <mergeCell ref="C15:C16"/>
+    <mergeCell ref="P33:Q33"/>
+    <mergeCell ref="B32:Q32"/>
+    <mergeCell ref="B18:P18"/>
+    <mergeCell ref="B19:P22"/>
+    <mergeCell ref="C33:D33"/>
+    <mergeCell ref="D8:E8"/>
+    <mergeCell ref="C10:D10"/>
+    <mergeCell ref="B11:B12"/>
+    <mergeCell ref="C11:C12"/>
+    <mergeCell ref="B13:B14"/>
+    <mergeCell ref="C13:C14"/>
+    <mergeCell ref="B9:P9"/>
     <mergeCell ref="B54:B55"/>
     <mergeCell ref="C54:C55"/>
     <mergeCell ref="B102:B103"/>
@@ -58801,20 +58785,39 @@
     <mergeCell ref="B58:B59"/>
     <mergeCell ref="Q66:Q67"/>
     <mergeCell ref="Q70:Q71"/>
-    <mergeCell ref="D8:E8"/>
-    <mergeCell ref="C10:D10"/>
-    <mergeCell ref="B11:B12"/>
-    <mergeCell ref="C11:C12"/>
-    <mergeCell ref="B13:B14"/>
-    <mergeCell ref="C13:C14"/>
-    <mergeCell ref="B9:P9"/>
-    <mergeCell ref="B15:B16"/>
-    <mergeCell ref="C15:C16"/>
-    <mergeCell ref="P33:Q33"/>
-    <mergeCell ref="B32:Q32"/>
-    <mergeCell ref="B18:P18"/>
-    <mergeCell ref="B19:P22"/>
-    <mergeCell ref="C33:D33"/>
+    <mergeCell ref="B34:B35"/>
+    <mergeCell ref="C34:C35"/>
+    <mergeCell ref="B40:P43"/>
+    <mergeCell ref="B52:Q52"/>
+    <mergeCell ref="C53:D53"/>
+    <mergeCell ref="P34:Q36"/>
+    <mergeCell ref="B64:Q64"/>
+    <mergeCell ref="C65:D65"/>
+    <mergeCell ref="Q58:Q59"/>
+    <mergeCell ref="C58:C59"/>
+    <mergeCell ref="B60:Q60"/>
+    <mergeCell ref="C61:D61"/>
+    <mergeCell ref="B62:B63"/>
+    <mergeCell ref="C62:C63"/>
+    <mergeCell ref="Q62:Q63"/>
+    <mergeCell ref="B72:Q72"/>
+    <mergeCell ref="C73:D73"/>
+    <mergeCell ref="B74:B75"/>
+    <mergeCell ref="C90:D90"/>
+    <mergeCell ref="Q90:R90"/>
+    <mergeCell ref="Q74:Q75"/>
+    <mergeCell ref="C101:D101"/>
+    <mergeCell ref="B104:B105"/>
+    <mergeCell ref="C104:C105"/>
+    <mergeCell ref="C74:C75"/>
+    <mergeCell ref="B89:R89"/>
+    <mergeCell ref="D76:E76"/>
+    <mergeCell ref="B77:R77"/>
+    <mergeCell ref="B78:R81"/>
+    <mergeCell ref="B91:B92"/>
+    <mergeCell ref="C91:C92"/>
+    <mergeCell ref="Q91:R92"/>
+    <mergeCell ref="B95:R98"/>
   </mergeCells>
   <phoneticPr fontId="12" alignment="center"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -58857,33 +58860,33 @@
   </cols>
   <sheetData>
     <row r="8" spans="2:19" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B8" s="231" t="s">
-        <v>215</v>
-      </c>
-      <c r="C8" s="232"/>
-      <c r="D8" s="232"/>
-      <c r="E8" s="232"/>
-      <c r="F8" s="232"/>
-      <c r="G8" s="232"/>
-      <c r="H8" s="232"/>
-      <c r="I8" s="232"/>
-      <c r="J8" s="232"/>
-      <c r="K8" s="232"/>
-      <c r="L8" s="232"/>
-      <c r="M8" s="232"/>
-      <c r="N8" s="232"/>
-      <c r="O8" s="232"/>
-      <c r="P8" s="232"/>
-      <c r="Q8" s="232"/>
+      <c r="B8" s="227" t="s">
+        <v>215</v>
+      </c>
+      <c r="C8" s="228"/>
+      <c r="D8" s="228"/>
+      <c r="E8" s="228"/>
+      <c r="F8" s="228"/>
+      <c r="G8" s="228"/>
+      <c r="H8" s="228"/>
+      <c r="I8" s="228"/>
+      <c r="J8" s="228"/>
+      <c r="K8" s="228"/>
+      <c r="L8" s="228"/>
+      <c r="M8" s="228"/>
+      <c r="N8" s="228"/>
+      <c r="O8" s="228"/>
+      <c r="P8" s="228"/>
+      <c r="Q8" s="228"/>
     </row>
     <row r="9" spans="2:19" ht="57.6" x14ac:dyDescent="0.3">
       <c r="B9" s="97" t="s">
         <v>1</v>
       </c>
-      <c r="C9" s="230" t="s">
+      <c r="C9" s="229" t="s">
         <v>2</v>
       </c>
-      <c r="D9" s="230"/>
+      <c r="D9" s="229"/>
       <c r="E9" s="120" t="s">
         <v>3</v>
       </c>
@@ -58925,10 +58928,10 @@
       </c>
     </row>
     <row r="10" spans="2:19" x14ac:dyDescent="0.3">
-      <c r="B10" s="238" t="s">
+      <c r="B10" s="230" t="s">
         <v>31</v>
       </c>
-      <c r="C10" s="233" t="s">
+      <c r="C10" s="226" t="s">
         <v>120</v>
       </c>
       <c r="D10" s="117" t="s">
@@ -58977,8 +58980,8 @@
       </c>
     </row>
     <row r="11" spans="2:19" x14ac:dyDescent="0.3">
-      <c r="B11" s="239"/>
-      <c r="C11" s="233"/>
+      <c r="B11" s="231"/>
+      <c r="C11" s="226"/>
       <c r="D11" s="117" t="s">
         <v>24</v>
       </c>
@@ -59025,34 +59028,34 @@
       </c>
     </row>
     <row r="12" spans="2:19" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B12" s="231" t="s">
+      <c r="B12" s="227" t="s">
         <v>217</v>
       </c>
-      <c r="C12" s="232"/>
-      <c r="D12" s="232"/>
-      <c r="E12" s="232"/>
-      <c r="F12" s="232"/>
-      <c r="G12" s="232"/>
-      <c r="H12" s="232"/>
-      <c r="I12" s="232"/>
-      <c r="J12" s="232"/>
-      <c r="K12" s="232"/>
-      <c r="L12" s="232"/>
-      <c r="M12" s="232"/>
-      <c r="N12" s="232"/>
-      <c r="O12" s="232"/>
-      <c r="P12" s="232"/>
-      <c r="Q12" s="232"/>
-      <c r="R12" s="232"/>
+      <c r="C12" s="228"/>
+      <c r="D12" s="228"/>
+      <c r="E12" s="228"/>
+      <c r="F12" s="228"/>
+      <c r="G12" s="228"/>
+      <c r="H12" s="228"/>
+      <c r="I12" s="228"/>
+      <c r="J12" s="228"/>
+      <c r="K12" s="228"/>
+      <c r="L12" s="228"/>
+      <c r="M12" s="228"/>
+      <c r="N12" s="228"/>
+      <c r="O12" s="228"/>
+      <c r="P12" s="228"/>
+      <c r="Q12" s="228"/>
+      <c r="R12" s="228"/>
     </row>
     <row r="13" spans="2:19" ht="57.6" x14ac:dyDescent="0.3">
       <c r="B13" s="97" t="s">
         <v>1</v>
       </c>
-      <c r="C13" s="230" t="s">
+      <c r="C13" s="229" t="s">
         <v>2</v>
       </c>
-      <c r="D13" s="230"/>
+      <c r="D13" s="229"/>
       <c r="E13" s="120" t="s">
         <v>3</v>
       </c>
@@ -59100,10 +59103,10 @@
       </c>
     </row>
     <row r="14" spans="2:19" x14ac:dyDescent="0.3">
-      <c r="B14" s="233" t="s">
+      <c r="B14" s="226" t="s">
         <v>31</v>
       </c>
-      <c r="C14" s="233" t="s">
+      <c r="C14" s="226" t="s">
         <v>180</v>
       </c>
       <c r="D14" s="117" t="s">
@@ -59158,8 +59161,8 @@
       </c>
     </row>
     <row r="15" spans="2:19" x14ac:dyDescent="0.3">
-      <c r="B15" s="233"/>
-      <c r="C15" s="233"/>
+      <c r="B15" s="226"/>
+      <c r="C15" s="226"/>
       <c r="D15" s="117" t="s">
         <v>24</v>
       </c>
@@ -59212,33 +59215,33 @@
       </c>
     </row>
     <row r="16" spans="2:19" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B16" s="242" t="s">
+      <c r="B16" s="234" t="s">
         <v>221</v>
       </c>
-      <c r="C16" s="243"/>
-      <c r="D16" s="243"/>
-      <c r="E16" s="243"/>
-      <c r="F16" s="243"/>
-      <c r="G16" s="243"/>
-      <c r="H16" s="243"/>
-      <c r="I16" s="243"/>
-      <c r="J16" s="243"/>
-      <c r="K16" s="243"/>
-      <c r="L16" s="243"/>
-      <c r="M16" s="243"/>
-      <c r="N16" s="243"/>
-      <c r="O16" s="243"/>
-      <c r="P16" s="243"/>
-      <c r="Q16" s="243"/>
+      <c r="C16" s="235"/>
+      <c r="D16" s="235"/>
+      <c r="E16" s="235"/>
+      <c r="F16" s="235"/>
+      <c r="G16" s="235"/>
+      <c r="H16" s="235"/>
+      <c r="I16" s="235"/>
+      <c r="J16" s="235"/>
+      <c r="K16" s="235"/>
+      <c r="L16" s="235"/>
+      <c r="M16" s="235"/>
+      <c r="N16" s="235"/>
+      <c r="O16" s="235"/>
+      <c r="P16" s="235"/>
+      <c r="Q16" s="235"/>
     </row>
     <row r="17" spans="2:17" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B17" s="97" t="s">
         <v>1</v>
       </c>
-      <c r="C17" s="230" t="s">
+      <c r="C17" s="229" t="s">
         <v>2</v>
       </c>
-      <c r="D17" s="230"/>
+      <c r="D17" s="229"/>
       <c r="E17" s="120" t="s">
         <v>3</v>
       </c>
@@ -59272,16 +59275,16 @@
       <c r="O17" s="120" t="s">
         <v>14</v>
       </c>
-      <c r="P17" s="240" t="s">
-        <v>150</v>
-      </c>
-      <c r="Q17" s="241"/>
+      <c r="P17" s="232" t="s">
+        <v>150</v>
+      </c>
+      <c r="Q17" s="233"/>
     </row>
     <row r="18" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B18" s="233" t="s">
+      <c r="B18" s="226" t="s">
         <v>31</v>
       </c>
-      <c r="C18" s="233" t="s">
+      <c r="C18" s="226" t="s">
         <v>222</v>
       </c>
       <c r="D18" s="117" t="s">
@@ -59328,8 +59331,8 @@
       <c r="Q18" s="53"/>
     </row>
     <row r="19" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B19" s="233"/>
-      <c r="C19" s="233"/>
+      <c r="B19" s="226"/>
+      <c r="C19" s="226"/>
       <c r="D19" s="117" t="s">
         <v>24</v>
       </c>
@@ -59374,32 +59377,32 @@
       <c r="Q19" s="53"/>
     </row>
     <row r="20" spans="2:17" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B20" s="236" t="s">
+      <c r="B20" s="224" t="s">
         <v>224</v>
       </c>
-      <c r="C20" s="237"/>
-      <c r="D20" s="237"/>
-      <c r="E20" s="237"/>
-      <c r="F20" s="237"/>
-      <c r="G20" s="237"/>
-      <c r="H20" s="237"/>
-      <c r="I20" s="237"/>
-      <c r="J20" s="237"/>
-      <c r="K20" s="237"/>
-      <c r="L20" s="237"/>
-      <c r="M20" s="237"/>
-      <c r="N20" s="237"/>
-      <c r="O20" s="237"/>
+      <c r="C20" s="225"/>
+      <c r="D20" s="225"/>
+      <c r="E20" s="225"/>
+      <c r="F20" s="225"/>
+      <c r="G20" s="225"/>
+      <c r="H20" s="225"/>
+      <c r="I20" s="225"/>
+      <c r="J20" s="225"/>
+      <c r="K20" s="225"/>
+      <c r="L20" s="225"/>
+      <c r="M20" s="225"/>
+      <c r="N20" s="225"/>
+      <c r="O20" s="225"/>
       <c r="P20" s="222"/>
     </row>
     <row r="21" spans="2:17" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B21" s="97" t="s">
         <v>1</v>
       </c>
-      <c r="C21" s="230" t="s">
+      <c r="C21" s="229" t="s">
         <v>2</v>
       </c>
-      <c r="D21" s="230"/>
+      <c r="D21" s="229"/>
       <c r="E21" s="120" t="s">
         <v>3</v>
       </c>
@@ -59433,14 +59436,14 @@
       <c r="O21" s="120" t="s">
         <v>150</v>
       </c>
-      <c r="P21" s="234"/>
-      <c r="Q21" s="235"/>
+      <c r="P21" s="242"/>
+      <c r="Q21" s="243"/>
     </row>
     <row r="22" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B22" s="238" t="s">
+      <c r="B22" s="230" t="s">
         <v>17</v>
       </c>
-      <c r="C22" s="238" t="s">
+      <c r="C22" s="230" t="s">
         <v>225</v>
       </c>
       <c r="D22" s="117" t="s">
@@ -59486,8 +59489,8 @@
       <c r="Q22" s="174"/>
     </row>
     <row r="23" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B23" s="239"/>
-      <c r="C23" s="239"/>
+      <c r="B23" s="231"/>
+      <c r="C23" s="231"/>
       <c r="D23" s="117" t="s">
         <v>24</v>
       </c>
@@ -59530,32 +59533,32 @@
       <c r="Q23" s="220"/>
     </row>
     <row r="24" spans="2:17" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B24" s="231" t="s">
+      <c r="B24" s="227" t="s">
         <v>227</v>
       </c>
-      <c r="C24" s="232"/>
-      <c r="D24" s="232"/>
-      <c r="E24" s="232"/>
-      <c r="F24" s="232"/>
-      <c r="G24" s="232"/>
-      <c r="H24" s="232"/>
-      <c r="I24" s="232"/>
-      <c r="J24" s="232"/>
-      <c r="K24" s="232"/>
-      <c r="L24" s="232"/>
-      <c r="M24" s="232"/>
-      <c r="N24" s="232"/>
-      <c r="O24" s="232"/>
+      <c r="C24" s="228"/>
+      <c r="D24" s="228"/>
+      <c r="E24" s="228"/>
+      <c r="F24" s="228"/>
+      <c r="G24" s="228"/>
+      <c r="H24" s="228"/>
+      <c r="I24" s="228"/>
+      <c r="J24" s="228"/>
+      <c r="K24" s="228"/>
+      <c r="L24" s="228"/>
+      <c r="M24" s="228"/>
+      <c r="N24" s="228"/>
+      <c r="O24" s="228"/>
       <c r="P24" s="61"/>
     </row>
     <row r="25" spans="2:17" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B25" s="97" t="s">
         <v>1</v>
       </c>
-      <c r="C25" s="230" t="s">
+      <c r="C25" s="229" t="s">
         <v>2</v>
       </c>
-      <c r="D25" s="230"/>
+      <c r="D25" s="229"/>
       <c r="E25" s="120" t="s">
         <v>3</v>
       </c>
@@ -59593,10 +59596,10 @@
       <c r="Q25" s="223"/>
     </row>
     <row r="26" spans="2:17" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B26" s="233" t="s">
+      <c r="B26" s="226" t="s">
         <v>17</v>
       </c>
-      <c r="C26" s="233" t="s">
+      <c r="C26" s="226" t="s">
         <v>124</v>
       </c>
       <c r="D26" s="117" t="s">
@@ -59642,8 +59645,8 @@
       <c r="P26" s="61"/>
     </row>
     <row r="27" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B27" s="233"/>
-      <c r="C27" s="233"/>
+      <c r="B27" s="226"/>
+      <c r="C27" s="226"/>
       <c r="D27" s="117" t="s">
         <v>24</v>
       </c>
@@ -59707,78 +59710,78 @@
       <c r="Q29" s="7"/>
     </row>
     <row r="30" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B30" s="224" t="s">
+      <c r="B30" s="236" t="s">
         <v>35</v>
       </c>
-      <c r="C30" s="225"/>
-      <c r="D30" s="225"/>
-      <c r="E30" s="225"/>
-      <c r="F30" s="225"/>
-      <c r="G30" s="225"/>
-      <c r="H30" s="225"/>
-      <c r="I30" s="225"/>
-      <c r="J30" s="225"/>
-      <c r="K30" s="225"/>
-      <c r="L30" s="225"/>
-      <c r="M30" s="225"/>
-      <c r="N30" s="225"/>
-      <c r="O30" s="225"/>
-      <c r="P30" s="225"/>
-      <c r="Q30" s="226"/>
+      <c r="C30" s="237"/>
+      <c r="D30" s="237"/>
+      <c r="E30" s="237"/>
+      <c r="F30" s="237"/>
+      <c r="G30" s="237"/>
+      <c r="H30" s="237"/>
+      <c r="I30" s="237"/>
+      <c r="J30" s="237"/>
+      <c r="K30" s="237"/>
+      <c r="L30" s="237"/>
+      <c r="M30" s="237"/>
+      <c r="N30" s="237"/>
+      <c r="O30" s="237"/>
+      <c r="P30" s="237"/>
+      <c r="Q30" s="238"/>
     </row>
     <row r="31" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B31" s="224"/>
-      <c r="C31" s="225"/>
-      <c r="D31" s="225"/>
-      <c r="E31" s="225"/>
-      <c r="F31" s="225"/>
-      <c r="G31" s="225"/>
-      <c r="H31" s="225"/>
-      <c r="I31" s="225"/>
-      <c r="J31" s="225"/>
-      <c r="K31" s="225"/>
-      <c r="L31" s="225"/>
-      <c r="M31" s="225"/>
-      <c r="N31" s="225"/>
-      <c r="O31" s="225"/>
-      <c r="P31" s="225"/>
-      <c r="Q31" s="226"/>
+      <c r="B31" s="236"/>
+      <c r="C31" s="237"/>
+      <c r="D31" s="237"/>
+      <c r="E31" s="237"/>
+      <c r="F31" s="237"/>
+      <c r="G31" s="237"/>
+      <c r="H31" s="237"/>
+      <c r="I31" s="237"/>
+      <c r="J31" s="237"/>
+      <c r="K31" s="237"/>
+      <c r="L31" s="237"/>
+      <c r="M31" s="237"/>
+      <c r="N31" s="237"/>
+      <c r="O31" s="237"/>
+      <c r="P31" s="237"/>
+      <c r="Q31" s="238"/>
     </row>
     <row r="32" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B32" s="224"/>
-      <c r="C32" s="225"/>
-      <c r="D32" s="225"/>
-      <c r="E32" s="225"/>
-      <c r="F32" s="225"/>
-      <c r="G32" s="225"/>
-      <c r="H32" s="225"/>
-      <c r="I32" s="225"/>
-      <c r="J32" s="225"/>
-      <c r="K32" s="225"/>
-      <c r="L32" s="225"/>
-      <c r="M32" s="225"/>
-      <c r="N32" s="225"/>
-      <c r="O32" s="225"/>
-      <c r="P32" s="225"/>
-      <c r="Q32" s="226"/>
+      <c r="B32" s="236"/>
+      <c r="C32" s="237"/>
+      <c r="D32" s="237"/>
+      <c r="E32" s="237"/>
+      <c r="F32" s="237"/>
+      <c r="G32" s="237"/>
+      <c r="H32" s="237"/>
+      <c r="I32" s="237"/>
+      <c r="J32" s="237"/>
+      <c r="K32" s="237"/>
+      <c r="L32" s="237"/>
+      <c r="M32" s="237"/>
+      <c r="N32" s="237"/>
+      <c r="O32" s="237"/>
+      <c r="P32" s="237"/>
+      <c r="Q32" s="238"/>
     </row>
     <row r="33" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B33" s="227"/>
-      <c r="C33" s="228"/>
-      <c r="D33" s="228"/>
-      <c r="E33" s="228"/>
-      <c r="F33" s="228"/>
-      <c r="G33" s="228"/>
-      <c r="H33" s="228"/>
-      <c r="I33" s="228"/>
-      <c r="J33" s="228"/>
-      <c r="K33" s="228"/>
-      <c r="L33" s="228"/>
-      <c r="M33" s="228"/>
-      <c r="N33" s="228"/>
-      <c r="O33" s="228"/>
-      <c r="P33" s="228"/>
-      <c r="Q33" s="229"/>
+      <c r="B33" s="239"/>
+      <c r="C33" s="240"/>
+      <c r="D33" s="240"/>
+      <c r="E33" s="240"/>
+      <c r="F33" s="240"/>
+      <c r="G33" s="240"/>
+      <c r="H33" s="240"/>
+      <c r="I33" s="240"/>
+      <c r="J33" s="240"/>
+      <c r="K33" s="240"/>
+      <c r="L33" s="240"/>
+      <c r="M33" s="240"/>
+      <c r="N33" s="240"/>
+      <c r="O33" s="240"/>
+      <c r="P33" s="240"/>
+      <c r="Q33" s="241"/>
     </row>
     <row r="34" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B34" s="35"/>
@@ -59908,6 +59911,15 @@
     </row>
   </sheetData>
   <mergeCells count="23">
+    <mergeCell ref="B30:Q33"/>
+    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="B24:O24"/>
+    <mergeCell ref="C25:D25"/>
+    <mergeCell ref="B26:B27"/>
+    <mergeCell ref="C26:C27"/>
+    <mergeCell ref="P21:Q21"/>
+    <mergeCell ref="B22:B23"/>
+    <mergeCell ref="C22:C23"/>
     <mergeCell ref="B20:O20"/>
     <mergeCell ref="C18:C19"/>
     <mergeCell ref="B14:B15"/>
@@ -59922,15 +59934,6 @@
     <mergeCell ref="B18:B19"/>
     <mergeCell ref="P17:Q17"/>
     <mergeCell ref="B16:Q16"/>
-    <mergeCell ref="B30:Q33"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="B24:O24"/>
-    <mergeCell ref="C25:D25"/>
-    <mergeCell ref="B26:B27"/>
-    <mergeCell ref="C26:C27"/>
-    <mergeCell ref="P21:Q21"/>
-    <mergeCell ref="B22:B23"/>
-    <mergeCell ref="C22:C23"/>
   </mergeCells>
   <phoneticPr fontId="14" type="noConversion"/>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
@@ -60118,10 +60121,10 @@
       <c r="B10" s="77" t="s">
         <v>1</v>
       </c>
-      <c r="C10" s="361" t="s">
+      <c r="C10" s="373" t="s">
         <v>2</v>
       </c>
-      <c r="D10" s="361"/>
+      <c r="D10" s="373"/>
       <c r="E10" s="15" t="s">
         <v>3</v>
       </c>
@@ -60160,10 +60163,10 @@
       </c>
     </row>
     <row r="11" spans="2:16" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B11" s="362" t="s">
+      <c r="B11" s="369" t="s">
         <v>229</v>
       </c>
-      <c r="C11" s="365" t="s">
+      <c r="C11" s="371" t="s">
         <v>31</v>
       </c>
       <c r="D11" s="45" t="s">
@@ -60209,8 +60212,8 @@
       </c>
     </row>
     <row r="12" spans="2:16" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B12" s="363"/>
-      <c r="C12" s="365"/>
+      <c r="B12" s="374"/>
+      <c r="C12" s="371"/>
       <c r="D12" s="45" t="s">
         <v>24</v>
       </c>
@@ -60254,8 +60257,8 @@
       </c>
     </row>
     <row r="13" spans="2:16" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B13" s="363"/>
-      <c r="C13" s="365" t="s">
+      <c r="B13" s="374"/>
+      <c r="C13" s="371" t="s">
         <v>17</v>
       </c>
       <c r="D13" s="45" t="s">
@@ -60301,8 +60304,8 @@
       </c>
     </row>
     <row r="14" spans="2:16" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B14" s="363"/>
-      <c r="C14" s="365"/>
+      <c r="B14" s="374"/>
+      <c r="C14" s="371"/>
       <c r="D14" s="45" t="s">
         <v>24</v>
       </c>
@@ -60346,8 +60349,8 @@
       </c>
     </row>
     <row r="15" spans="2:16" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B15" s="363"/>
-      <c r="C15" s="365" t="s">
+      <c r="B15" s="374"/>
+      <c r="C15" s="371" t="s">
         <v>31</v>
       </c>
       <c r="D15" s="45" t="s">
@@ -60393,8 +60396,8 @@
       </c>
     </row>
     <row r="16" spans="2:16" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B16" s="363"/>
-      <c r="C16" s="365"/>
+      <c r="B16" s="374"/>
+      <c r="C16" s="371"/>
       <c r="D16" s="45" t="s">
         <v>24</v>
       </c>
@@ -60438,8 +60441,8 @@
       </c>
     </row>
     <row r="17" spans="2:16" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B17" s="363"/>
-      <c r="C17" s="365" t="s">
+      <c r="B17" s="374"/>
+      <c r="C17" s="371" t="s">
         <v>31</v>
       </c>
       <c r="D17" s="45" t="s">
@@ -60485,8 +60488,8 @@
       </c>
     </row>
     <row r="18" spans="2:16" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B18" s="363"/>
-      <c r="C18" s="365"/>
+      <c r="B18" s="374"/>
+      <c r="C18" s="371"/>
       <c r="D18" s="45" t="s">
         <v>24</v>
       </c>
@@ -60530,8 +60533,8 @@
       </c>
     </row>
     <row r="19" spans="2:16" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="B19" s="363"/>
-      <c r="C19" s="365" t="s">
+      <c r="B19" s="374"/>
+      <c r="C19" s="371" t="s">
         <v>31</v>
       </c>
       <c r="D19" s="45" t="s">
@@ -60577,8 +60580,8 @@
       </c>
     </row>
     <row r="20" spans="2:16" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="B20" s="364"/>
-      <c r="C20" s="365"/>
+      <c r="B20" s="370"/>
+      <c r="C20" s="371"/>
       <c r="D20" s="45" t="s">
         <v>24</v>
       </c>
@@ -60622,10 +60625,10 @@
       </c>
     </row>
     <row r="21" spans="2:16" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B21" s="362" t="s">
+      <c r="B21" s="369" t="s">
         <v>234</v>
       </c>
-      <c r="C21" s="365" t="s">
+      <c r="C21" s="371" t="s">
         <v>31</v>
       </c>
       <c r="D21" s="45" t="s">
@@ -60671,8 +60674,8 @@
       </c>
     </row>
     <row r="22" spans="2:16" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B22" s="364"/>
-      <c r="C22" s="365"/>
+      <c r="B22" s="370"/>
+      <c r="C22" s="371"/>
       <c r="D22" s="45" t="s">
         <v>24</v>
       </c>
@@ -60716,10 +60719,10 @@
       </c>
     </row>
     <row r="23" spans="2:16" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B23" s="362" t="s">
+      <c r="B23" s="369" t="s">
         <v>235</v>
       </c>
-      <c r="C23" s="365" t="s">
+      <c r="C23" s="371" t="s">
         <v>31</v>
       </c>
       <c r="D23" s="45" t="s">
@@ -60765,8 +60768,8 @@
       </c>
     </row>
     <row r="24" spans="2:16" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B24" s="364"/>
-      <c r="C24" s="365"/>
+      <c r="B24" s="370"/>
+      <c r="C24" s="371"/>
       <c r="D24" s="45" t="s">
         <v>24</v>
       </c>
@@ -60813,7 +60816,7 @@
       <c r="B25" s="246" t="s">
         <v>237</v>
       </c>
-      <c r="C25" s="233" t="s">
+      <c r="C25" s="226" t="s">
         <v>31</v>
       </c>
       <c r="D25" s="40" t="s">
@@ -60860,7 +60863,7 @@
     </row>
     <row r="26" spans="2:16" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="B26" s="246"/>
-      <c r="C26" s="233"/>
+      <c r="C26" s="226"/>
       <c r="D26" s="40" t="s">
         <v>24</v>
       </c>
@@ -60904,8 +60907,8 @@
       </c>
     </row>
     <row r="27" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B27" s="358"/>
-      <c r="C27" s="374"/>
+      <c r="B27" s="338"/>
+      <c r="C27" s="372"/>
       <c r="D27" s="84" t="s">
         <v>18</v>
       </c>
@@ -60965,96 +60968,103 @@
       <c r="O28" s="28"/>
     </row>
     <row r="29" spans="2:16" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B29" s="366" t="s">
+      <c r="B29" s="361" t="s">
         <v>34</v>
       </c>
-      <c r="C29" s="367"/>
-      <c r="D29" s="367"/>
-      <c r="E29" s="367"/>
-      <c r="F29" s="367"/>
-      <c r="G29" s="367"/>
-      <c r="H29" s="367"/>
-      <c r="I29" s="367"/>
-      <c r="J29" s="367"/>
-      <c r="K29" s="367"/>
-      <c r="L29" s="367"/>
-      <c r="M29" s="367"/>
-      <c r="N29" s="367"/>
-      <c r="O29" s="367"/>
-      <c r="P29" s="368"/>
+      <c r="C29" s="362"/>
+      <c r="D29" s="362"/>
+      <c r="E29" s="362"/>
+      <c r="F29" s="362"/>
+      <c r="G29" s="362"/>
+      <c r="H29" s="362"/>
+      <c r="I29" s="362"/>
+      <c r="J29" s="362"/>
+      <c r="K29" s="362"/>
+      <c r="L29" s="362"/>
+      <c r="M29" s="362"/>
+      <c r="N29" s="362"/>
+      <c r="O29" s="362"/>
+      <c r="P29" s="363"/>
     </row>
     <row r="30" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="B30" s="369" t="s">
+      <c r="B30" s="364" t="s">
         <v>35</v>
       </c>
-      <c r="C30" s="225"/>
-      <c r="D30" s="225"/>
-      <c r="E30" s="225"/>
-      <c r="F30" s="225"/>
-      <c r="G30" s="225"/>
-      <c r="H30" s="225"/>
-      <c r="I30" s="225"/>
-      <c r="J30" s="225"/>
-      <c r="K30" s="225"/>
-      <c r="L30" s="225"/>
-      <c r="M30" s="225"/>
-      <c r="N30" s="225"/>
-      <c r="O30" s="225"/>
-      <c r="P30" s="370"/>
+      <c r="C30" s="237"/>
+      <c r="D30" s="237"/>
+      <c r="E30" s="237"/>
+      <c r="F30" s="237"/>
+      <c r="G30" s="237"/>
+      <c r="H30" s="237"/>
+      <c r="I30" s="237"/>
+      <c r="J30" s="237"/>
+      <c r="K30" s="237"/>
+      <c r="L30" s="237"/>
+      <c r="M30" s="237"/>
+      <c r="N30" s="237"/>
+      <c r="O30" s="237"/>
+      <c r="P30" s="365"/>
     </row>
     <row r="31" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="B31" s="369"/>
-      <c r="C31" s="225"/>
-      <c r="D31" s="225"/>
-      <c r="E31" s="225"/>
-      <c r="F31" s="225"/>
-      <c r="G31" s="225"/>
-      <c r="H31" s="225"/>
-      <c r="I31" s="225"/>
-      <c r="J31" s="225"/>
-      <c r="K31" s="225"/>
-      <c r="L31" s="225"/>
-      <c r="M31" s="225"/>
-      <c r="N31" s="225"/>
-      <c r="O31" s="225"/>
-      <c r="P31" s="370"/>
+      <c r="B31" s="364"/>
+      <c r="C31" s="237"/>
+      <c r="D31" s="237"/>
+      <c r="E31" s="237"/>
+      <c r="F31" s="237"/>
+      <c r="G31" s="237"/>
+      <c r="H31" s="237"/>
+      <c r="I31" s="237"/>
+      <c r="J31" s="237"/>
+      <c r="K31" s="237"/>
+      <c r="L31" s="237"/>
+      <c r="M31" s="237"/>
+      <c r="N31" s="237"/>
+      <c r="O31" s="237"/>
+      <c r="P31" s="365"/>
     </row>
     <row r="32" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="B32" s="369"/>
-      <c r="C32" s="225"/>
-      <c r="D32" s="225"/>
-      <c r="E32" s="225"/>
-      <c r="F32" s="225"/>
-      <c r="G32" s="225"/>
-      <c r="H32" s="225"/>
-      <c r="I32" s="225"/>
-      <c r="J32" s="225"/>
-      <c r="K32" s="225"/>
-      <c r="L32" s="225"/>
-      <c r="M32" s="225"/>
-      <c r="N32" s="225"/>
-      <c r="O32" s="225"/>
-      <c r="P32" s="370"/>
+      <c r="B32" s="364"/>
+      <c r="C32" s="237"/>
+      <c r="D32" s="237"/>
+      <c r="E32" s="237"/>
+      <c r="F32" s="237"/>
+      <c r="G32" s="237"/>
+      <c r="H32" s="237"/>
+      <c r="I32" s="237"/>
+      <c r="J32" s="237"/>
+      <c r="K32" s="237"/>
+      <c r="L32" s="237"/>
+      <c r="M32" s="237"/>
+      <c r="N32" s="237"/>
+      <c r="O32" s="237"/>
+      <c r="P32" s="365"/>
     </row>
     <row r="33" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B33" s="371"/>
-      <c r="C33" s="372"/>
-      <c r="D33" s="372"/>
-      <c r="E33" s="372"/>
-      <c r="F33" s="372"/>
-      <c r="G33" s="372"/>
-      <c r="H33" s="372"/>
-      <c r="I33" s="372"/>
-      <c r="J33" s="372"/>
-      <c r="K33" s="372"/>
-      <c r="L33" s="372"/>
-      <c r="M33" s="372"/>
-      <c r="N33" s="372"/>
-      <c r="O33" s="372"/>
-      <c r="P33" s="373"/>
+      <c r="B33" s="366"/>
+      <c r="C33" s="367"/>
+      <c r="D33" s="367"/>
+      <c r="E33" s="367"/>
+      <c r="F33" s="367"/>
+      <c r="G33" s="367"/>
+      <c r="H33" s="367"/>
+      <c r="I33" s="367"/>
+      <c r="J33" s="367"/>
+      <c r="K33" s="367"/>
+      <c r="L33" s="367"/>
+      <c r="M33" s="367"/>
+      <c r="N33" s="367"/>
+      <c r="O33" s="367"/>
+      <c r="P33" s="368"/>
     </row>
   </sheetData>
   <mergeCells count="15">
+    <mergeCell ref="C10:D10"/>
+    <mergeCell ref="B11:B20"/>
+    <mergeCell ref="C11:C12"/>
+    <mergeCell ref="C13:C14"/>
+    <mergeCell ref="C15:C16"/>
+    <mergeCell ref="C17:C18"/>
+    <mergeCell ref="C19:C20"/>
     <mergeCell ref="B29:P29"/>
     <mergeCell ref="B30:P33"/>
     <mergeCell ref="B21:B22"/>
@@ -61063,13 +61073,6 @@
     <mergeCell ref="C23:C24"/>
     <mergeCell ref="B25:B27"/>
     <mergeCell ref="C25:C27"/>
-    <mergeCell ref="C10:D10"/>
-    <mergeCell ref="B11:B20"/>
-    <mergeCell ref="C11:C12"/>
-    <mergeCell ref="C13:C14"/>
-    <mergeCell ref="C15:C16"/>
-    <mergeCell ref="C17:C18"/>
-    <mergeCell ref="C19:C20"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup scale="67" orientation="landscape" r:id="rId1"/>
@@ -61078,6 +61081,26 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="8bf418b7-79e0-4993-aa07-d31c53a64380">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="268ad1c4-fabf-4dd0-b894-8fd5403102c0" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100BF631F92D611394D900040A4BC36CE07" ma:contentTypeVersion="13" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="711a2ec75ffd0c152903cfa2dedf38be">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="8bf418b7-79e0-4993-aa07-d31c53a64380" xmlns:ns3="268ad1c4-fabf-4dd0-b894-8fd5403102c0" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="0628c710989f2757c815e19c03677863" ns2:_="" ns3:_="">
     <xsd:import namespace="8bf418b7-79e0-4993-aa07-d31c53a64380"/>
@@ -61300,27 +61323,26 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{900DAED1-575B-462E-9521-61C8D8B6DAE7}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="8bf418b7-79e0-4993-aa07-d31c53a64380"/>
+    <ds:schemaRef ds:uri="268ad1c4-fabf-4dd0-b894-8fd5403102c0"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="8bf418b7-79e0-4993-aa07-d31c53a64380">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="268ad1c4-fabf-4dd0-b894-8fd5403102c0" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6AAFA3EB-B8AB-4135-B122-0B0233A6C07D}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1A722593-7143-4ACD-9A00-2A0E70214590}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -61337,23 +61359,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6AAFA3EB-B8AB-4135-B122-0B0233A6C07D}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{900DAED1-575B-462E-9521-61C8D8B6DAE7}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="8bf418b7-79e0-4993-aa07-d31c53a64380"/>
-    <ds:schemaRef ds:uri="268ad1c4-fabf-4dd0-b894-8fd5403102c0"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>